--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -228,7 +228,7 @@
     <t>Thursday</t>
   </si>
   <si>
-    <t>Queens of the S. Age</t>
+    <t>Queens of the Stone Age</t>
   </si>
   <si>
     <t>Memorial Auditorium</t>
@@ -684,7 +684,7 @@
     <t>March of the Peaceful Army Tour</t>
   </si>
   <si>
-    <t>S. Temple Pilots</t>
+    <t>Stone Temple Pilots</t>
   </si>
   <si>
     <t>Richmond</t>
@@ -1116,7 +1116,7 @@
     <t>Boys Noize</t>
   </si>
   <si>
-    <t>Adam S.</t>
+    <t>Adam Sandler</t>
   </si>
   <si>
     <t>You're My Best Friend Tour</t>

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="388">
   <si>
     <t>Date</t>
   </si>
@@ -210,7 +210,7 @@
     <t>Sasquatch</t>
   </si>
   <si>
-    <t>NIN</t>
+    <t>Nine Inch Nails</t>
   </si>
   <si>
     <t>PNC Arena</t>
@@ -1141,9 +1141,6 @@
   </si>
   <si>
     <t>Teri Gender Bender</t>
-  </si>
-  <si>
-    <t>Nine Inch Nails</t>
   </si>
   <si>
     <t>Candlebox</t>
@@ -1925,7 +1922,7 @@
       <c r="B10" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="10" t="s">
         <v>65</v>
       </c>
       <c r="D10" s="8" t="s">
@@ -2035,7 +2032,7 @@
       <c r="B13" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="10" t="s">
         <v>65</v>
       </c>
       <c r="D13" s="8" t="s">
@@ -4012,7 +4009,7 @@
       <c r="B69" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="10" t="s">
         <v>65</v>
       </c>
       <c r="D69" s="8" t="s">
@@ -5265,7 +5262,7 @@
       <c r="B104" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C104" s="8" t="s">
+      <c r="C104" s="10" t="s">
         <v>65</v>
       </c>
       <c r="D104" s="8" t="s">
@@ -5412,7 +5409,7 @@
         <v>21</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>376</v>
+        <v>65</v>
       </c>
       <c r="D108" s="8" t="s">
         <v>100</v>
@@ -5448,7 +5445,7 @@
         <v>121</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>307</v>
@@ -5457,7 +5454,7 @@
         <v>147</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G109" s="10" t="s">
         <v>125</v>
@@ -5469,10 +5466,10 @@
         <v>19</v>
       </c>
       <c r="J109" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="K109" s="7" t="s">
         <v>379</v>
-      </c>
-      <c r="K109" s="7" t="s">
-        <v>380</v>
       </c>
       <c r="L109" s="7"/>
     </row>
@@ -5484,7 +5481,7 @@
         <v>46</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>40</v>
@@ -5505,10 +5502,10 @@
         <v>19</v>
       </c>
       <c r="J110" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="K110" s="18" t="s">
         <v>382</v>
-      </c>
-      <c r="K110" s="18" t="s">
-        <v>383</v>
       </c>
       <c r="L110" s="7"/>
     </row>
@@ -5541,10 +5538,10 @@
         <v>19</v>
       </c>
       <c r="J111" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="K111" s="14" t="s">
         <v>384</v>
-      </c>
-      <c r="K111" s="14" t="s">
-        <v>385</v>
       </c>
       <c r="L111" s="7"/>
     </row>
@@ -5556,7 +5553,7 @@
         <v>29</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>123</v>
@@ -5565,7 +5562,7 @@
         <v>41</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G112" s="14" t="s">
         <v>125</v>
@@ -5577,7 +5574,7 @@
         <v>19</v>
       </c>
       <c r="J112" s="14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="391">
   <si>
     <t>Date</t>
   </si>
@@ -771,7 +771,7 @@
     <t>We're F'n' Back! Tour / 2021 Stadium Tour</t>
   </si>
   <si>
-    <t>Welcome To Rockville Festival</t>
+    <t>Welcome To Rockville Festival - Day 1</t>
   </si>
   <si>
     <t>Daytona</t>
@@ -786,10 +786,19 @@
     <t>Slipknot, Cypress Hill, Grandson, Dead Sara, Spiritbox, Dana Dentata, A Day to Remember, Gojira, Dorothy, Teenage Wrist, Siiickbrain, Brass Against, NASCAR Aloe, Jeris Johnson, Blame My Youth, Contracult Collective, Them Evils, Revision, Revised, The Alpha Complex, A War Within, Scarlett O'hara, Dead Reckoning, Shadow the Earth, As You Were</t>
   </si>
   <si>
+    <t>Welcome To Rockville Festival - Day 2</t>
+  </si>
+  <si>
     <t>Metallica, Social Distortion, Pennywise, Ice Nine Kills, Ayron Jones, Austin Meade, Rob Zombie, Chevelle, Beartooth, Starset, Zero 9:36, Whit3 Collr, Wage War, Butcher Babies, Amigo the Devil, Bad Omens, Tallah, Eva Under Fire, Zero 9:36, Whit3 Collr, Divided Truth, ReBirth, Tragic, VENTRUSS, The Coursing, As You Were</t>
   </si>
   <si>
+    <t>Welcome To Rockville Festival- Day 3</t>
+  </si>
+  <si>
     <t>Disturbed, Staind, The Offspring, Badflower, Fever 333, Dead Poet Society, Brkn Love, Lamb of God, Asking Alexandria, Atreyu, Sick Puppies, Fame on Fire, Gwar, Crown the Empire, 3Teeth, All Good Things, Joyous Wolf, Reach NYC, Magnolia Bayou, Actus Reus, Widow7, Timmy Taylor, NoSelf, Troy, Higher Ground, As You Were</t>
+  </si>
+  <si>
+    <t>Welcome To Rockville Festival - Day 4</t>
   </si>
   <si>
     <t>Metallica, Mudvayne, Falling in Reverse, Sleeping with Sirens, Alien Weaponry, Goodbye June, Lynyrd Skynyrd, Mastodon, Anthrax, Dance Gavin Dance, Fire from the Gods, Survive the Sun, Code Orange, Jelly Roll, The Warning, Avoid, Hero the Band, As You Were, Lone Wolf, The Dev, Imperial Tide, Lines of Loyalty</t>
@@ -1622,7 +1631,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" ht="15.75" hidden="1" customHeight="1">
       <c r="A2" s="6">
         <v>36471.0</v>
       </c>
@@ -1656,7 +1665,7 @@
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" ht="15.75" hidden="1" customHeight="1">
       <c r="A3" s="6">
         <v>36571.0</v>
       </c>
@@ -1692,7 +1701,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" ht="15.75" hidden="1" customHeight="1">
       <c r="A4" s="6">
         <v>36578.0</v>
       </c>
@@ -1726,7 +1735,7 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" ht="15.75" hidden="1" customHeight="1">
       <c r="A5" s="6">
         <v>38107.0</v>
       </c>
@@ -1767,7 +1776,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" ht="15.75" hidden="1" customHeight="1">
       <c r="A6" s="6">
         <v>39658.0</v>
       </c>
@@ -1805,7 +1814,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" ht="15.75" hidden="1" customHeight="1">
       <c r="A7" s="6">
         <v>40364.0</v>
       </c>
@@ -1843,7 +1852,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="15.75" hidden="1" customHeight="1">
       <c r="A8" s="6">
         <v>41091.0</v>
       </c>
@@ -1879,7 +1888,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" ht="15.75" hidden="1" customHeight="1">
       <c r="A9" s="6">
         <v>41336.0</v>
       </c>
@@ -1915,7 +1924,7 @@
       </c>
       <c r="L9" s="7"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" ht="15.75" hidden="1" customHeight="1">
       <c r="A10" s="6">
         <v>41568.0</v>
       </c>
@@ -1951,7 +1960,7 @@
       </c>
       <c r="L10" s="7"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" ht="15.75" hidden="1" customHeight="1">
       <c r="A11" s="6">
         <v>41669.0</v>
       </c>
@@ -1989,7 +1998,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" ht="15.75" hidden="1" customHeight="1">
       <c r="A12" s="6">
         <v>41834.0</v>
       </c>
@@ -2025,7 +2034,7 @@
       </c>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" ht="15.75" hidden="1" customHeight="1">
       <c r="A13" s="6">
         <v>41862.0</v>
       </c>
@@ -2063,7 +2072,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" ht="15.75" hidden="1" customHeight="1">
       <c r="A14" s="6">
         <v>41899.0</v>
       </c>
@@ -2099,7 +2108,7 @@
       </c>
       <c r="L14" s="7"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" ht="15.75" hidden="1" customHeight="1">
       <c r="A15" s="6">
         <v>42135.0</v>
       </c>
@@ -2135,7 +2144,7 @@
       </c>
       <c r="L15" s="7"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" ht="15.75" hidden="1" customHeight="1">
       <c r="A16" s="6">
         <v>42204.0</v>
       </c>
@@ -2171,7 +2180,7 @@
       </c>
       <c r="L16" s="7"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" ht="15.75" hidden="1" customHeight="1">
       <c r="A17" s="6">
         <v>42216.0</v>
       </c>
@@ -2207,7 +2216,7 @@
       </c>
       <c r="L17" s="7"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" ht="15.75" hidden="1" customHeight="1">
       <c r="A18" s="6">
         <v>42318.0</v>
       </c>
@@ -2241,7 +2250,7 @@
       </c>
       <c r="L18" s="7"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" ht="15.75" hidden="1" customHeight="1">
       <c r="A19" s="6">
         <v>42395.0</v>
       </c>
@@ -2277,7 +2286,7 @@
       </c>
       <c r="L19" s="7"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" ht="15.75" hidden="1" customHeight="1">
       <c r="A20" s="6">
         <v>42467.0</v>
       </c>
@@ -2313,7 +2322,7 @@
       </c>
       <c r="L20" s="7"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" ht="15.75" hidden="1" customHeight="1">
       <c r="A21" s="6">
         <v>42479.0</v>
       </c>
@@ -2347,7 +2356,7 @@
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" ht="15.75" hidden="1" customHeight="1">
       <c r="A22" s="6">
         <v>42569.0</v>
       </c>
@@ -2381,7 +2390,7 @@
       </c>
       <c r="L22" s="7"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" ht="15.75" hidden="1" customHeight="1">
       <c r="A23" s="6">
         <v>42609.0</v>
       </c>
@@ -2417,7 +2426,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" ht="15.75" hidden="1" customHeight="1">
       <c r="A24" s="6">
         <v>42620.0</v>
       </c>
@@ -2451,7 +2460,7 @@
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" ht="15.75" hidden="1" customHeight="1">
       <c r="A25" s="6">
         <v>42633.0</v>
       </c>
@@ -2483,7 +2492,7 @@
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" ht="15.75" hidden="1" customHeight="1">
       <c r="A26" s="6">
         <v>42647.0</v>
       </c>
@@ -2519,7 +2528,7 @@
       </c>
       <c r="L26" s="7"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" ht="15.75" hidden="1" customHeight="1">
       <c r="A27" s="6">
         <v>42840.0</v>
       </c>
@@ -2555,7 +2564,7 @@
       </c>
       <c r="L27" s="7"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" ht="15.75" hidden="1" customHeight="1">
       <c r="A28" s="6">
         <v>42874.0</v>
       </c>
@@ -2591,7 +2600,7 @@
       </c>
       <c r="L28" s="7"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" ht="15.75" hidden="1" customHeight="1">
       <c r="A29" s="6">
         <v>42879.0</v>
       </c>
@@ -2627,7 +2636,7 @@
       </c>
       <c r="L29" s="7"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" ht="15.75" hidden="1" customHeight="1">
       <c r="A30" s="6">
         <v>42932.0</v>
       </c>
@@ -2663,7 +2672,7 @@
       </c>
       <c r="L30" s="7"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" ht="15.75" hidden="1" customHeight="1">
       <c r="A31" s="6">
         <v>42934.0</v>
       </c>
@@ -2699,7 +2708,7 @@
       </c>
       <c r="L31" s="7"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" ht="15.75" hidden="1" customHeight="1">
       <c r="A32" s="6">
         <v>42958.0</v>
       </c>
@@ -2737,7 +2746,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" ht="15.75" hidden="1" customHeight="1">
       <c r="A33" s="6">
         <v>43005.0</v>
       </c>
@@ -2771,7 +2780,7 @@
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" ht="15.75" hidden="1" customHeight="1">
       <c r="A34" s="6">
         <v>43018.0</v>
       </c>
@@ -2809,7 +2818,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" ht="15.75" hidden="1" customHeight="1">
       <c r="A35" s="6">
         <v>43214.0</v>
       </c>
@@ -2957,7 +2966,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" ht="15.75" hidden="1" customHeight="1">
       <c r="A39" s="6">
         <v>43256.0</v>
       </c>
@@ -2995,7 +3004,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" ht="15.75" hidden="1" customHeight="1">
       <c r="A40" s="6">
         <v>43280.0</v>
       </c>
@@ -3028,7 +3037,7 @@
       </c>
       <c r="L40" s="7"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" ht="15.75" hidden="1" customHeight="1">
       <c r="A41" s="6">
         <v>43347.0</v>
       </c>
@@ -3061,7 +3070,7 @@
       </c>
       <c r="L41" s="7"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" ht="15.75" hidden="1" customHeight="1">
       <c r="A42" s="6">
         <v>43405.0</v>
       </c>
@@ -3097,7 +3106,7 @@
       </c>
       <c r="L42" s="7"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" ht="15.75" hidden="1" customHeight="1">
       <c r="A43" s="6">
         <v>43471.0</v>
       </c>
@@ -3130,7 +3139,7 @@
       </c>
       <c r="L43" s="7"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" ht="15.75" hidden="1" customHeight="1">
       <c r="A44" s="6">
         <v>43493.0</v>
       </c>
@@ -3163,7 +3172,7 @@
       </c>
       <c r="L44" s="7"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" ht="15.75" hidden="1" customHeight="1">
       <c r="A45" s="6">
         <v>43536.0</v>
       </c>
@@ -3196,7 +3205,7 @@
       </c>
       <c r="L45" s="7"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" ht="15.75" hidden="1" customHeight="1">
       <c r="A46" s="6">
         <v>43561.0</v>
       </c>
@@ -3339,7 +3348,7 @@
       </c>
       <c r="L49" s="7"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" ht="15.75" hidden="1" customHeight="1">
       <c r="A50" s="6">
         <v>43601.0</v>
       </c>
@@ -3372,7 +3381,7 @@
       </c>
       <c r="L50" s="7"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" ht="15.75" hidden="1" customHeight="1">
       <c r="A51" s="6">
         <v>43613.0</v>
       </c>
@@ -3405,7 +3414,7 @@
       </c>
       <c r="L51" s="7"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" ht="15.75" hidden="1" customHeight="1">
       <c r="A52" s="6">
         <v>43695.0</v>
       </c>
@@ -3441,7 +3450,7 @@
       </c>
       <c r="L52" s="7"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" ht="15.75" hidden="1" customHeight="1">
       <c r="A53" s="6">
         <v>43727.0</v>
       </c>
@@ -3474,7 +3483,7 @@
       </c>
       <c r="L53" s="7"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" ht="15.75" hidden="1" customHeight="1">
       <c r="A54" s="6">
         <v>43733.0</v>
       </c>
@@ -3507,7 +3516,7 @@
       </c>
       <c r="L54" s="7"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" ht="15.75" hidden="1" customHeight="1">
       <c r="A55" s="6">
         <v>43788.0</v>
       </c>
@@ -3543,7 +3552,7 @@
       </c>
       <c r="L55" s="7"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" ht="15.75" hidden="1" customHeight="1">
       <c r="A56" s="6">
         <v>43793.0</v>
       </c>
@@ -3579,7 +3588,7 @@
       </c>
       <c r="L56" s="7"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" ht="15.75" hidden="1" customHeight="1">
       <c r="A57" s="6">
         <v>43847.0</v>
       </c>
@@ -3615,7 +3624,7 @@
       </c>
       <c r="L57" s="7"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" ht="15.75" hidden="1" customHeight="1">
       <c r="A58" s="6">
         <v>43869.0</v>
       </c>
@@ -3651,7 +3660,7 @@
       </c>
       <c r="L58" s="7"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" ht="15.75" hidden="1" customHeight="1">
       <c r="A59" s="6">
         <v>44450.0</v>
       </c>
@@ -3684,7 +3693,7 @@
       </c>
       <c r="L59" s="7"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" ht="15.75" hidden="1" customHeight="1">
       <c r="A60" s="6">
         <v>44468.0</v>
       </c>
@@ -3724,7 +3733,7 @@
       <c r="B61" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="10" t="s">
         <v>252</v>
       </c>
       <c r="D61" s="8" t="s">
@@ -3760,8 +3769,8 @@
       <c r="B62" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C62" s="8" t="s">
-        <v>252</v>
+      <c r="C62" s="10" t="s">
+        <v>257</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>253</v>
@@ -3785,7 +3794,7 @@
         <v>255</v>
       </c>
       <c r="K62" s="25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L62" s="14"/>
     </row>
@@ -3796,8 +3805,8 @@
       <c r="B63" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>252</v>
+      <c r="C63" s="10" t="s">
+        <v>259</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>253</v>
@@ -3821,7 +3830,7 @@
         <v>255</v>
       </c>
       <c r="K63" s="25" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L63" s="14"/>
     </row>
@@ -3832,8 +3841,8 @@
       <c r="B64" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C64" s="8" t="s">
-        <v>252</v>
+      <c r="C64" s="10" t="s">
+        <v>261</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>253</v>
@@ -3857,11 +3866,11 @@
         <v>255</v>
       </c>
       <c r="K64" s="25" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L64" s="14"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" ht="15.75" hidden="1" customHeight="1">
       <c r="A65" s="6">
         <v>44519.0</v>
       </c>
@@ -3869,7 +3878,7 @@
         <v>29</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>40</v>
@@ -3881,7 +3890,7 @@
         <v>66</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H65" s="8" t="s">
         <v>52</v>
@@ -3890,11 +3899,11 @@
         <v>19</v>
       </c>
       <c r="J65" s="18" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L65" s="7"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" ht="15.75" hidden="1" customHeight="1">
       <c r="A66" s="6">
         <v>44614.0</v>
       </c>
@@ -3905,13 +3914,13 @@
         <v>104</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>200</v>
@@ -3926,11 +3935,11 @@
         <v>241</v>
       </c>
       <c r="K66" s="25" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L66" s="7"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" ht="15.75" hidden="1" customHeight="1">
       <c r="A67" s="6">
         <v>44631.0</v>
       </c>
@@ -3938,7 +3947,7 @@
         <v>29</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>123</v>
@@ -3959,14 +3968,14 @@
         <v>19</v>
       </c>
       <c r="J67" s="18" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K67" s="25" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="L67" s="7"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" ht="15.75" hidden="1" customHeight="1">
       <c r="A68" s="6">
         <v>44640.0</v>
       </c>
@@ -3977,13 +3986,13 @@
         <v>104</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E68" s="16" t="s">
         <v>180</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G68" s="10" t="s">
         <v>200</v>
@@ -3998,11 +4007,11 @@
         <v>241</v>
       </c>
       <c r="K68" s="25" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L68" s="7"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" ht="15.75" hidden="1" customHeight="1">
       <c r="A69" s="6">
         <v>44679.0</v>
       </c>
@@ -4031,14 +4040,14 @@
         <v>19</v>
       </c>
       <c r="J69" s="18" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K69" s="25" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="L69" s="7"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" ht="15.75" hidden="1" customHeight="1">
       <c r="A70" s="6">
         <v>44701.0</v>
       </c>
@@ -4046,19 +4055,19 @@
         <v>29</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E70" s="16" t="s">
         <v>147</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H70" s="8" t="s">
         <v>18</v>
@@ -4067,14 +4076,14 @@
         <v>19</v>
       </c>
       <c r="J70" s="10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K70" s="19" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L70" s="7"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" ht="15.75" hidden="1" customHeight="1">
       <c r="A71" s="6">
         <v>44734.0</v>
       </c>
@@ -4103,14 +4112,14 @@
         <v>19</v>
       </c>
       <c r="J71" s="18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K71" s="25" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L71" s="7"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" ht="15.75" hidden="1" customHeight="1">
       <c r="A72" s="6">
         <v>44773.0</v>
       </c>
@@ -4118,7 +4127,7 @@
         <v>12</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>40</v>
@@ -4130,7 +4139,7 @@
         <v>66</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H72" s="8" t="s">
         <v>52</v>
@@ -4139,14 +4148,14 @@
         <v>19</v>
       </c>
       <c r="J72" s="18" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K72" s="25" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="L72" s="7"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" ht="15.75" hidden="1" customHeight="1">
       <c r="A73" s="6">
         <v>44791.0</v>
       </c>
@@ -4166,7 +4175,7 @@
         <v>66</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H73" s="8" t="s">
         <v>18</v>
@@ -4175,11 +4184,11 @@
         <v>19</v>
       </c>
       <c r="J73" s="18" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L73" s="7"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" ht="15.75" hidden="1" customHeight="1">
       <c r="A74" s="6">
         <v>44804.0</v>
       </c>
@@ -4187,16 +4196,16 @@
         <v>12</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G74" s="10" t="s">
         <v>200</v>
@@ -4208,14 +4217,14 @@
         <v>19</v>
       </c>
       <c r="J74" s="18" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K74" s="25" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L74" s="7"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" ht="15.75" hidden="1" customHeight="1">
       <c r="A75" s="6">
         <v>44831.0</v>
       </c>
@@ -4223,7 +4232,7 @@
         <v>21</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>40</v>
@@ -4244,16 +4253,16 @@
         <v>19</v>
       </c>
       <c r="J75" s="18" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="K75" s="25" t="s">
         <v>228</v>
       </c>
       <c r="L75" s="20" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" hidden="1" customHeight="1">
       <c r="A76" s="6">
         <v>44866.0</v>
       </c>
@@ -4282,10 +4291,10 @@
         <v>19</v>
       </c>
       <c r="J76" s="18" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K76" s="25" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L76" s="7"/>
     </row>
@@ -4296,8 +4305,8 @@
       <c r="B77" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C77" s="8" t="s">
-        <v>252</v>
+      <c r="C77" s="10" t="s">
+        <v>261</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>253</v>
@@ -4318,14 +4327,14 @@
         <v>19</v>
       </c>
       <c r="J77" s="19" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="K77" s="25" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L77" s="14"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" ht="15.75" hidden="1" customHeight="1">
       <c r="A78" s="6">
         <v>45142.0</v>
       </c>
@@ -4336,13 +4345,13 @@
         <v>142</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>200</v>
@@ -4354,10 +4363,10 @@
         <v>19</v>
       </c>
       <c r="J78" s="18" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="K78" s="25" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L78" s="7"/>
     </row>
@@ -4369,16 +4378,16 @@
         <v>70</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E79" s="16" t="s">
         <v>147</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G79" s="10" t="s">
         <v>125</v>
@@ -4390,16 +4399,16 @@
         <v>19</v>
       </c>
       <c r="J79" s="19" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="K79" s="25" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L79" s="14" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" hidden="1" customHeight="1">
       <c r="A80" s="6">
         <v>45213.0</v>
       </c>
@@ -4407,7 +4416,7 @@
         <v>121</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>244</v>
@@ -4416,7 +4425,7 @@
         <v>245</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G80" s="10" t="s">
         <v>198</v>
@@ -4428,11 +4437,11 @@
         <v>19</v>
       </c>
       <c r="J80" s="18" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L80" s="7"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" ht="15.75" hidden="1" customHeight="1">
       <c r="A81" s="6">
         <v>45228.0</v>
       </c>
@@ -4440,7 +4449,7 @@
         <v>12</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>40</v>
@@ -4461,14 +4470,14 @@
         <v>19</v>
       </c>
       <c r="J81" s="18" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="L81" s="7"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" ht="15.75" hidden="1" customHeight="1">
       <c r="A82" s="6">
         <v>45239.0</v>
       </c>
@@ -4476,7 +4485,7 @@
         <v>70</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>40</v>
@@ -4497,14 +4506,14 @@
         <v>19</v>
       </c>
       <c r="J82" s="18" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K82" s="25" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L82" s="7"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" ht="15.75" hidden="1" customHeight="1">
       <c r="A83" s="6">
         <v>45247.0</v>
       </c>
@@ -4512,7 +4521,7 @@
         <v>29</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>129</v>
@@ -4533,14 +4542,14 @@
         <v>19</v>
       </c>
       <c r="J83" s="18" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K83" s="25" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L83" s="7"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" ht="15.75" hidden="1" customHeight="1">
       <c r="A84" s="6">
         <v>45312.0</v>
       </c>
@@ -4569,14 +4578,14 @@
         <v>19</v>
       </c>
       <c r="J84" s="18" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="K84" s="25" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L84" s="7"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" ht="15.75" hidden="1" customHeight="1">
       <c r="A85" s="6">
         <v>45340.0</v>
       </c>
@@ -4605,14 +4614,14 @@
         <v>19</v>
       </c>
       <c r="J85" s="18" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="K85" s="25" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L85" s="7"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" ht="15.75" hidden="1" customHeight="1">
       <c r="A86" s="6">
         <v>45380.0</v>
       </c>
@@ -4620,7 +4629,7 @@
         <v>29</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>40</v>
@@ -4629,7 +4638,7 @@
         <v>41</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G86" s="10" t="s">
         <v>125</v>
@@ -4641,14 +4650,14 @@
         <v>19</v>
       </c>
       <c r="J86" s="18" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K86" s="25" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L86" s="7"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" ht="15.75" hidden="1" customHeight="1">
       <c r="A87" s="6">
         <v>45389.0</v>
       </c>
@@ -4656,7 +4665,7 @@
         <v>12</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>40</v>
@@ -4677,7 +4686,7 @@
         <v>19</v>
       </c>
       <c r="J87" s="18" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L87" s="18"/>
     </row>
@@ -4689,7 +4698,7 @@
         <v>70</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>179</v>
@@ -4698,7 +4707,7 @@
         <v>180</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G88" s="10" t="s">
         <v>125</v>
@@ -4710,10 +4719,10 @@
         <v>19</v>
       </c>
       <c r="J88" s="27" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K88" s="25" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L88" s="28"/>
     </row>
@@ -4725,7 +4734,7 @@
         <v>29</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>179</v>
@@ -4734,7 +4743,7 @@
         <v>180</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G89" s="10" t="s">
         <v>125</v>
@@ -4746,10 +4755,10 @@
         <v>19</v>
       </c>
       <c r="J89" s="27" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K89" s="25" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L89" s="28"/>
     </row>
@@ -4761,7 +4770,7 @@
         <v>121</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>179</v>
@@ -4770,7 +4779,7 @@
         <v>180</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G90" s="10" t="s">
         <v>125</v>
@@ -4782,10 +4791,10 @@
         <v>19</v>
       </c>
       <c r="J90" s="27" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K90" s="25" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="L90" s="28"/>
     </row>
@@ -4797,7 +4806,7 @@
         <v>12</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>179</v>
@@ -4806,7 +4815,7 @@
         <v>180</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G91" s="10" t="s">
         <v>125</v>
@@ -4818,14 +4827,14 @@
         <v>19</v>
       </c>
       <c r="J91" s="27" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K91" s="25" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L91" s="28"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" ht="15.75" hidden="1" customHeight="1">
       <c r="A92" s="6">
         <v>45469.0</v>
       </c>
@@ -4854,14 +4863,14 @@
         <v>19</v>
       </c>
       <c r="J92" s="18" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K92" s="18" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L92" s="7"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" ht="15.75" hidden="1" customHeight="1">
       <c r="A93" s="6">
         <v>45531.0</v>
       </c>
@@ -4869,7 +4878,7 @@
         <v>21</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>40</v>
@@ -4890,14 +4899,14 @@
         <v>19</v>
       </c>
       <c r="J93" s="18" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K93" s="18" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="L93" s="7"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" ht="15.75" hidden="1" customHeight="1">
       <c r="A94" s="6">
         <v>45537.0</v>
       </c>
@@ -4926,16 +4935,16 @@
         <v>19</v>
       </c>
       <c r="J94" s="18" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K94" s="19" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L94" s="20" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" hidden="1" customHeight="1">
       <c r="A95" s="6">
         <v>45553.0</v>
       </c>
@@ -4943,7 +4952,7 @@
         <v>86</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>40</v>
@@ -4964,14 +4973,14 @@
         <v>19</v>
       </c>
       <c r="J95" s="18" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K95" s="18" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L95" s="7"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" ht="15.75" hidden="1" customHeight="1">
       <c r="A96" s="6">
         <v>45740.0</v>
       </c>
@@ -4979,7 +4988,7 @@
         <v>46</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D96" s="7" t="s">
         <v>100</v>
@@ -5000,14 +5009,14 @@
         <v>19</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K96" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L96" s="7"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" ht="15.75" hidden="1" customHeight="1">
       <c r="A97" s="6">
         <v>45783.0</v>
       </c>
@@ -5015,7 +5024,7 @@
         <v>21</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>40</v>
@@ -5024,7 +5033,7 @@
         <v>41</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G97" s="10" t="s">
         <v>243</v>
@@ -5036,14 +5045,14 @@
         <v>19</v>
       </c>
       <c r="J97" s="18" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K97" s="18" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L97" s="7"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" ht="15.75" hidden="1" customHeight="1">
       <c r="A98" s="6">
         <v>45790.0</v>
       </c>
@@ -5060,7 +5069,7 @@
         <v>41</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G98" s="10" t="s">
         <v>125</v>
@@ -5072,14 +5081,14 @@
         <v>19</v>
       </c>
       <c r="J98" s="18" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K98" s="19" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L98" s="7"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" ht="15.75" hidden="1" customHeight="1">
       <c r="A99" s="6">
         <v>45808.0</v>
       </c>
@@ -5096,7 +5105,7 @@
         <v>41</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G99" s="10" t="s">
         <v>243</v>
@@ -5108,14 +5117,14 @@
         <v>19</v>
       </c>
       <c r="J99" s="18" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="K99" s="18" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L99" s="7"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" ht="15.75" hidden="1" customHeight="1">
       <c r="A100" s="6">
         <v>45853.0</v>
       </c>
@@ -5132,7 +5141,7 @@
         <v>41</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G100" s="10" t="s">
         <v>247</v>
@@ -5144,12 +5153,12 @@
         <v>19</v>
       </c>
       <c r="J100" s="18" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" ht="15.75" hidden="1" customHeight="1">
       <c r="A101" s="6">
         <v>45867.0</v>
       </c>
@@ -5157,7 +5166,7 @@
         <v>21</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>129</v>
@@ -5178,12 +5187,12 @@
         <v>19</v>
       </c>
       <c r="J101" s="18" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" ht="15.75" hidden="1" customHeight="1">
       <c r="A102" s="6">
         <v>45890.0</v>
       </c>
@@ -5191,7 +5200,7 @@
         <v>70</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>40</v>
@@ -5200,7 +5209,7 @@
         <v>41</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G102" s="10" t="s">
         <v>247</v>
@@ -5212,14 +5221,14 @@
         <v>19</v>
       </c>
       <c r="J102" s="18" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K102" s="18" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L102" s="7"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" ht="15.75" hidden="1" customHeight="1">
       <c r="A103" s="6">
         <v>45896.0</v>
       </c>
@@ -5230,13 +5239,13 @@
         <v>22</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E103" s="16" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G103" s="10" t="s">
         <v>200</v>
@@ -5248,14 +5257,14 @@
         <v>19</v>
       </c>
       <c r="J103" s="18" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K103" s="18" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L103" s="7"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" ht="15.75" hidden="1" customHeight="1">
       <c r="A104" s="6">
         <v>45905.0</v>
       </c>
@@ -5272,7 +5281,7 @@
         <v>41</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G104" s="10" t="s">
         <v>243</v>
@@ -5284,14 +5293,14 @@
         <v>19</v>
       </c>
       <c r="J104" s="18" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="K104" s="18" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="L104" s="7"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" ht="15.75" hidden="1" customHeight="1">
       <c r="A105" s="6">
         <v>45911.0</v>
       </c>
@@ -5299,7 +5308,7 @@
         <v>70</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>40</v>
@@ -5308,7 +5317,7 @@
         <v>41</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G105" s="10" t="s">
         <v>34</v>
@@ -5320,14 +5329,14 @@
         <v>19</v>
       </c>
       <c r="J105" s="18" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K105" s="19" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L105" s="7"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" ht="15.75" hidden="1" customHeight="1">
       <c r="A106" s="6">
         <v>45955.0</v>
       </c>
@@ -5335,7 +5344,7 @@
         <v>121</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>40</v>
@@ -5356,16 +5365,16 @@
         <v>19</v>
       </c>
       <c r="J106" s="18" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K106" s="19" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L106" s="20" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="107" ht="15.75" customHeight="1">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" hidden="1" customHeight="1">
       <c r="A107" s="6">
         <v>45965.0</v>
       </c>
@@ -5394,14 +5403,14 @@
         <v>19</v>
       </c>
       <c r="J107" s="18" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="K107" s="18" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L107" s="7"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" ht="15.75" hidden="1" customHeight="1">
       <c r="A108" s="6">
         <v>46063.0</v>
       </c>
@@ -5430,14 +5439,14 @@
         <v>19</v>
       </c>
       <c r="J108" s="18" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="L108" s="7"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" ht="15.75" hidden="1" customHeight="1">
       <c r="A109" s="6">
         <v>46088.0</v>
       </c>
@@ -5445,16 +5454,16 @@
         <v>121</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E109" s="16" t="s">
         <v>147</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G109" s="10" t="s">
         <v>125</v>
@@ -5466,14 +5475,14 @@
         <v>19</v>
       </c>
       <c r="J109" s="18" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L109" s="7"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" ht="15.75" hidden="1" customHeight="1">
       <c r="A110" s="6">
         <v>46097.0</v>
       </c>
@@ -5481,7 +5490,7 @@
         <v>46</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>40</v>
@@ -5490,7 +5499,7 @@
         <v>41</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G110" s="10" t="s">
         <v>200</v>
@@ -5502,14 +5511,14 @@
         <v>19</v>
       </c>
       <c r="J110" s="18" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K110" s="18" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L110" s="7"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" ht="15.75" hidden="1" customHeight="1">
       <c r="A111" s="6">
         <v>46113.0</v>
       </c>
@@ -5538,14 +5547,14 @@
         <v>19</v>
       </c>
       <c r="J111" s="18" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="K111" s="14" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L111" s="7"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" ht="15.75" hidden="1" customHeight="1">
       <c r="A112" s="6">
         <v>46129.0</v>
       </c>
@@ -5553,7 +5562,7 @@
         <v>29</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>123</v>
@@ -5562,7 +5571,7 @@
         <v>41</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="G112" s="14" t="s">
         <v>125</v>
@@ -5574,7 +5583,7 @@
         <v>19</v>
       </c>
       <c r="J112" s="14" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -18125,6 +18134,22 @@
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$M$112">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Rock on the Range Festival - Day 2"/>
+        <filter val="Rock on the Range Festival - Day 1"/>
+        <filter val="Rock on the Range Festival - Day 3"/>
+        <filter val="Welcome To Rockville Festival - Day 4"/>
+        <filter val="Welcome To Rockville Festival - Day 1"/>
+        <filter val="Welcome To Rockville Festival - Day 2"/>
+        <filter val="Epicenter Festival - Day 1"/>
+        <filter val="Sonic Temple Festival"/>
+        <filter val="Epicenter Festival - Day 2"/>
+        <filter val="Epicenter Festival - Day 3"/>
+        <filter val="Blue Ridge Rock Festival"/>
+        <filter val="Welcome To Rockville Festival- Day 3"/>
+      </filters>
+    </filterColumn>
     <sortState ref="A1:M112">
       <sortCondition ref="A1:A112"/>
     </sortState>

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -252,7 +252,7 @@
     <t>Billsburg Waterfront</t>
   </si>
   <si>
-    <t>Justin L., Jason C.</t>
+    <t>Justin L., Jason C., Alex F.</t>
   </si>
   <si>
     <t>Yes</t>

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Attended Show List" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Attended Show List'!$A$1:$M$120</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Attended Show List'!$A$1:$M$121</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="427">
   <si>
     <t>Date</t>
   </si>
@@ -144,13 +144,28 @@
     <t>Imani</t>
   </si>
   <si>
+    <t>Distrubed</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>WWF New York</t>
+  </si>
+  <si>
+    <t>The Sickness</t>
+  </si>
+  <si>
+    <t>Glassjaw, Nonpoint, From Zero, 6 Gig</t>
+  </si>
+  <si>
+    <t>CMJ Fest</t>
+  </si>
+  <si>
     <t>Tenacious D</t>
-  </si>
-  <si>
-    <t>New York</t>
-  </si>
-  <si>
-    <t>NY</t>
   </si>
   <si>
     <t>Irving Plaza</t>
@@ -1910,10 +1925,10 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="6">
-        <v>36819.0</v>
+        <v>36818.0</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>43</v>
@@ -1937,33 +1952,33 @@
       <c r="J7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K7" s="9"/>
+      <c r="K7" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="L7" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="6">
-        <v>37592.0</v>
+        <v>36819.0</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>50</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>54</v>
-      </c>
+      <c r="G8" s="9"/>
       <c r="H8" s="7" t="s">
         <v>18</v>
       </c>
@@ -1971,33 +1986,35 @@
         <v>27</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" s="9"/>
+        <v>52</v>
+      </c>
+      <c r="K8" s="9"/>
+      <c r="L8" s="7" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="6">
-        <v>37632.0</v>
+        <v>37592.0</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="9"/>
+      <c r="G9" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="H9" s="7" t="s">
         <v>18</v>
       </c>
@@ -2005,75 +2022,68 @@
         <v>27</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="7" t="s">
         <v>60</v>
       </c>
+      <c r="K9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="9"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="10">
-        <v>38107.0</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="11" t="s">
+      <c r="A10" s="6">
+        <v>37632.0</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="11" t="s">
+      <c r="C10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="D10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="21" t="s">
+      <c r="K10" s="9"/>
+      <c r="L10" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="K10" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="10">
-        <v>39658.0</v>
+        <v>38107.0</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>64</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>18</v>
@@ -2082,210 +2092,215 @@
         <v>27</v>
       </c>
       <c r="J11" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="K11" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="L11" s="23" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="10">
+        <v>39658.0</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="L12" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="10">
         <v>40364.0</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="B13" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="6">
+        <v>40947.0</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="K12" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="6">
-        <v>40947.0</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" s="7" t="s">
+      <c r="F14" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="10">
-        <v>41091.0</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I14" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" s="21" t="s">
+      <c r="I14" s="7"/>
+      <c r="J14" s="7" t="s">
         <v>93</v>
       </c>
       <c r="K14" s="9"/>
-      <c r="L14" s="9" t="s">
+      <c r="L14" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="10">
-        <v>41336.0</v>
-      </c>
-      <c r="B15" s="9" t="s">
+        <v>41091.0</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="14" t="s">
+      <c r="C15" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="L15" s="9"/>
+      <c r="J15" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="10">
-        <v>41568.0</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I16" s="24" t="s">
+        <v>41336.0</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="J16" s="21" t="s">
+      <c r="J16" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="K16" s="21" t="s">
+      <c r="K16" s="7" t="s">
         <v>101</v>
       </c>
       <c r="L16" s="9"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="10">
-        <v>41669.0</v>
+        <v>41568.0</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>102</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>103</v>
@@ -2294,310 +2309,312 @@
         <v>104</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I17" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J17" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="K17" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="L17" s="9" t="s">
-        <v>107</v>
-      </c>
+      <c r="L17" s="9"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="10">
-        <v>41834.0</v>
+        <v>41669.0</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>108</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I18" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="L18" s="9"/>
+        <v>111</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="10">
-        <v>41862.0</v>
+        <v>41834.0</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I19" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J19" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="K19" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="K19" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="L19" s="23" t="s">
-        <v>116</v>
-      </c>
+      <c r="L19" s="9"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="10">
-        <v>41899.0</v>
+        <v>41862.0</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>91</v>
-      </c>
       <c r="G20" s="13" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I20" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J20" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="K20" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="L20" s="9"/>
+      <c r="K20" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="L20" s="23" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="10">
-        <v>42135.0</v>
+        <v>41899.0</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>35</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I21" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="L21" s="9"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6">
+      <c r="A22" s="10">
+        <v>42135.0</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="L22" s="9"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="6">
         <v>42154.0</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="H22" s="7" t="s">
+      <c r="B23" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I22" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="10">
-        <v>42204.0</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I23" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J23" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>131</v>
-      </c>
+      <c r="I23" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="K23" s="9"/>
       <c r="L23" s="9"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="10">
-        <v>42216.0</v>
+        <v>42204.0</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I24" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J24" s="21" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L24" s="9"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="10">
-        <v>42318.0</v>
+        <v>42216.0</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="G25" s="9"/>
+        <v>137</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>59</v>
+      </c>
       <c r="H25" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I25" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J25" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="K25" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="K25" s="9" t="s">
         <v>138</v>
       </c>
       <c r="L25" s="9"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="10">
-        <v>42395.0</v>
+        <v>42318.0</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>29</v>
@@ -2606,21 +2623,19 @@
         <v>139</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G26" s="13" t="s">
         <v>141</v>
       </c>
+      <c r="G26" s="9"/>
       <c r="H26" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I26" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I26" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J26" s="21" t="s">
@@ -2633,19 +2648,19 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="10">
-        <v>42467.0</v>
+        <v>42395.0</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>144</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>145</v>
@@ -2654,246 +2669,246 @@
         <v>146</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I27" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I27" s="14" t="s">
         <v>27</v>
       </c>
       <c r="J27" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="K27" s="9" t="s">
+      <c r="K27" s="21" t="s">
         <v>148</v>
       </c>
       <c r="L27" s="9"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="10">
-        <v>42479.0</v>
+        <v>42467.0</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I28" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J28" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="K28" s="9"/>
+        <v>152</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>153</v>
+      </c>
       <c r="L28" s="9"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="10">
-        <v>42569.0</v>
-      </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" s="14" t="s">
+        <v>42479.0</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I29" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J29" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>155</v>
-      </c>
+      <c r="J29" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="K29" s="9"/>
       <c r="L29" s="9"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="10">
-        <v>42609.0</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="11" t="s">
+        <v>42569.0</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="E30" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="F30" s="11" t="s">
+      <c r="E30" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I30" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J30" s="21" t="s">
+      <c r="K30" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9" t="s">
-        <v>161</v>
-      </c>
+      <c r="L30" s="9"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="10">
-        <v>42620.0</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="9" t="s">
+        <v>42609.0</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="E31" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="H31" s="11" t="s">
         <v>18</v>
       </c>
       <c r="I31" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J31" s="9" t="s">
-        <v>163</v>
+      <c r="J31" s="21" t="s">
+        <v>165</v>
       </c>
       <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
+      <c r="L31" s="9" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="10">
-        <v>42633.0</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>157</v>
+        <v>42620.0</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H32" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I32" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J32" s="21" t="s">
-        <v>166</v>
+      <c r="J32" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="10">
-        <v>42647.0</v>
+        <v>42633.0</v>
       </c>
       <c r="B33" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>70</v>
+        <v>162</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>168</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="G33" s="9"/>
       <c r="H33" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I33" s="24" t="s">
+      <c r="I33" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J33" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="K33" s="21" t="s">
-        <v>170</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="K33" s="9"/>
       <c r="L33" s="9"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="10">
-        <v>42840.0</v>
+        <v>42647.0</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>99</v>
+        <v>137</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>173</v>
       </c>
       <c r="H34" s="11" t="s">
         <v>18</v>
@@ -2902,142 +2917,142 @@
         <v>27</v>
       </c>
       <c r="J34" s="21" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K34" s="21" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L34" s="9"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="10">
-        <v>42874.0</v>
+        <v>42840.0</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>175</v>
+        <v>103</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I35" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J35" s="21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K35" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L35" s="9"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="10">
-        <v>42879.0</v>
+        <v>42874.0</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>179</v>
+        <v>57</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>180</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I36" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J36" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="K36" s="21" t="s">
         <v>182</v>
-      </c>
-      <c r="K36" s="21" t="s">
-        <v>183</v>
       </c>
       <c r="L36" s="9"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="10">
-        <v>42932.0</v>
+        <v>42879.0</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="C37" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E37" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="D37" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E37" s="19" t="s">
-        <v>71</v>
-      </c>
       <c r="F37" s="11" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>146</v>
+        <v>186</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I37" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J37" s="21" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K37" s="21" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L37" s="9"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="10">
-        <v>42934.0</v>
+        <v>42932.0</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>143</v>
+        <v>189</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="G38" s="11" t="s">
-        <v>187</v>
+        <v>150</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>151</v>
       </c>
       <c r="H38" s="11" t="s">
         <v>18</v>
@@ -3046,66 +3061,64 @@
         <v>27</v>
       </c>
       <c r="J38" s="21" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K38" s="21" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L38" s="9"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="10">
-        <v>42958.0</v>
+        <v>42934.0</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="G39" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="G39" s="11" t="s">
         <v>192</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I39" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J39" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="K39" s="22" t="s">
+      <c r="K39" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="L39" s="9" t="s">
-        <v>195</v>
-      </c>
+      <c r="L39" s="9"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="10">
-        <v>43005.0</v>
+        <v>42958.0</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>51</v>
+        <v>195</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>196</v>
@@ -3114,639 +3127,644 @@
         <v>197</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I40" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I40" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J40" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
+      <c r="K40" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="10">
-        <v>43018.0</v>
+        <v>43005.0</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>102</v>
+        <v>89</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>199</v>
+        <v>56</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>200</v>
+        <v>57</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>201</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>17</v>
+        <v>202</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I41" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="I41" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J41" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="K41" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="L41" s="9" t="s">
-        <v>204</v>
-      </c>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="10">
-        <v>43214.0</v>
+        <v>43018.0</v>
       </c>
       <c r="B42" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C42" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E42" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="D42" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>71</v>
-      </c>
       <c r="F42" s="11" t="s">
-        <v>98</v>
+        <v>206</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I42" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I42" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J42" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
+      <c r="K42" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="25">
-        <v>43238.0</v>
-      </c>
-      <c r="B43" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>208</v>
+      <c r="A43" s="10">
+        <v>43214.0</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>210</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="F43" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G43" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="G43" s="13" t="s">
+      <c r="H43" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J43" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="H43" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I43" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="J43" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="K43" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="L43" s="7" t="s">
-        <v>215</v>
-      </c>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="25">
-        <v>43239.0</v>
+        <v>43238.0</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C44" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="F44" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="D44" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>211</v>
-      </c>
       <c r="G44" s="13" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I44" s="27" t="s">
         <v>27</v>
       </c>
       <c r="J44" s="22" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K44" s="28" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="25">
-        <v>43240.0</v>
+        <v>43239.0</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I45" s="27" t="s">
         <v>27</v>
       </c>
       <c r="J45" s="22" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K45" s="28" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L45" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="25">
+        <v>43240.0</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E46" s="19" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="10">
-        <v>43256.0</v>
-      </c>
-      <c r="B46" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C46" s="11" t="s">
+      <c r="F46" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I46" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J46" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="K46" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="L46" s="7" t="s">
         <v>220</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G46" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I46" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="J46" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="K46" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="L46" s="23" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="10">
-        <v>43280.0</v>
+        <v>43256.0</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>225</v>
+        <v>103</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H47" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I47" s="20" t="s">
+      <c r="I47" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J47" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="L47" s="9"/>
+      <c r="K47" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="L47" s="23" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="10">
-        <v>43347.0</v>
+        <v>43280.0</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="E48" s="19" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>91</v>
+        <v>230</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>228</v>
+        <v>164</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I48" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J48" s="21" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L48" s="9"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="10">
-        <v>43405.0</v>
+        <v>43347.0</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>61</v>
+        <v>232</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>135</v>
+        <v>56</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I49" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="I49" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J49" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="K49" s="28" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L49" s="9"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="10">
-        <v>43471.0</v>
+        <v>43405.0</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>233</v>
+        <v>66</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>64</v>
+        <v>235</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I50" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I50" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J50" s="21" t="s">
-        <v>234</v>
+        <v>236</v>
+      </c>
+      <c r="K50" s="28" t="s">
+        <v>237</v>
       </c>
       <c r="L50" s="9"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="10">
-        <v>43493.0</v>
+        <v>43471.0</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I51" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J51" s="21" t="s">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="L51" s="9"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="10">
-        <v>43536.0</v>
+        <v>43493.0</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>235</v>
+        <v>179</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>236</v>
+        <v>164</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I52" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J52" s="21" t="s">
-        <v>237</v>
+        <v>181</v>
       </c>
       <c r="L52" s="9"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="10">
-        <v>43561.0</v>
+        <v>43536.0</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>159</v>
+        <v>241</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I53" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I53" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J53" s="21" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="L53" s="9"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="10">
+        <v>43561.0</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G54" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I54" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J54" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="L54" s="9"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="10">
         <v>43595.0</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="B55" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I54" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="J54" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="K54" s="28" t="s">
+      <c r="C55" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="L54" s="9"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="6">
-        <v>43596.0</v>
-      </c>
-      <c r="B55" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C55" s="13" t="s">
+      <c r="D55" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="D55" s="11" t="s">
-        <v>241</v>
-      </c>
       <c r="E55" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>80</v>
+        <v>248</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>85</v>
       </c>
       <c r="I55" s="27" t="s">
         <v>27</v>
       </c>
       <c r="J55" s="22" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K55" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="L55" s="7" t="s">
-        <v>248</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="L55" s="9"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="6">
-        <v>43597.0</v>
+        <v>43596.0</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I56" s="27" t="s">
         <v>27</v>
       </c>
       <c r="J56" s="22" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K56" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="L56" s="9"/>
+        <v>252</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="10">
-        <v>43601.0</v>
-      </c>
-      <c r="B57" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>251</v>
+      <c r="A57" s="6">
+        <v>43597.0</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>254</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>70</v>
+        <v>246</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>132</v>
+        <v>247</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I57" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I57" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J57" s="21" t="s">
-        <v>252</v>
+      <c r="J57" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="K57" s="28" t="s">
+        <v>255</v>
       </c>
       <c r="L57" s="9"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="10">
-        <v>43613.0</v>
+        <v>43601.0</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>253</v>
+        <v>37</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>256</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>254</v>
+        <v>75</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>255</v>
+        <v>137</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="H58" s="11" t="s">
         <v>18</v>
@@ -3761,25 +3779,25 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="10">
-        <v>43695.0</v>
+        <v>43613.0</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C59" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C59" s="13" t="s">
         <v>258</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>70</v>
+        <v>259</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="H59" s="11" t="s">
         <v>18</v>
@@ -3788,775 +3806,775 @@
         <v>27</v>
       </c>
       <c r="J59" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="K59" s="28" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L59" s="9"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="10">
-        <v>43727.0</v>
+        <v>43695.0</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="E60" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F60" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="F60" s="11" t="s">
-        <v>265</v>
-      </c>
       <c r="G60" s="13" t="s">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="H60" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I60" s="24" t="s">
+      <c r="I60" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J60" s="21" t="s">
-        <v>267</v>
+        <v>265</v>
+      </c>
+      <c r="K60" s="28" t="s">
+        <v>266</v>
       </c>
       <c r="L60" s="9"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="10">
-        <v>43733.0</v>
+        <v>43727.0</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>50</v>
+        <v>267</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>135</v>
+        <v>268</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>71</v>
+        <v>269</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>159</v>
+        <v>271</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I61" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="I61" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J61" s="21" t="s">
-        <v>193</v>
+        <v>272</v>
       </c>
       <c r="L61" s="9"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="10">
-        <v>43788.0</v>
+        <v>43733.0</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I62" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J62" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="K62" s="28" t="s">
-        <v>272</v>
+        <v>198</v>
       </c>
       <c r="L62" s="9"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="10">
-        <v>43793.0</v>
+        <v>43788.0</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>98</v>
+        <v>274</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I63" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="I63" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J63" s="21" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="K63" s="28" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="L63" s="9"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="10">
-        <v>43847.0</v>
+        <v>43793.0</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>274</v>
+        <v>75</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>275</v>
+        <v>76</v>
       </c>
       <c r="F64" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G64" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I64" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J64" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="G64" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="H64" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I64" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J64" s="21" t="s">
-        <v>271</v>
-      </c>
       <c r="K64" s="28" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="L64" s="9"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="10">
-        <v>43869.0</v>
+        <v>43847.0</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>238</v>
+        <v>144</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>157</v>
+        <v>279</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>71</v>
+        <v>280</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>158</v>
+        <v>281</v>
       </c>
       <c r="G65" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I65" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J65" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="K65" s="28" t="s">
         <v>277</v>
-      </c>
-      <c r="H65" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I65" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="J65" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="K65" s="28" t="s">
-        <v>278</v>
       </c>
       <c r="L65" s="9"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="10">
-        <v>44450.0</v>
+        <v>43869.0</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>70</v>
+        <v>162</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>259</v>
+        <v>163</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>99</v>
+        <v>282</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I66" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I66" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J66" s="21" t="s">
-        <v>280</v>
+        <v>244</v>
+      </c>
+      <c r="K66" s="28" t="s">
+        <v>283</v>
       </c>
       <c r="L66" s="9"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="10">
-        <v>44468.0</v>
+        <v>44450.0</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>50</v>
+        <v>284</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>98</v>
+        <v>264</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I67" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J67" s="21" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="L67" s="9"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="25">
-        <v>44511.0</v>
-      </c>
-      <c r="B68" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>282</v>
+      <c r="A68" s="10">
+        <v>44468.0</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>283</v>
+        <v>75</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>284</v>
+        <v>103</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I68" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="I68" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J68" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="K68" s="28" t="s">
+      <c r="J68" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="L68" s="7"/>
+      <c r="L68" s="9"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="25">
-        <v>44512.0</v>
+        <v>44511.0</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C69" s="13" t="s">
         <v>287</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I69" s="27" t="s">
         <v>27</v>
       </c>
       <c r="J69" s="22" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K69" s="28" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L69" s="7"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="25">
-        <v>44513.0</v>
+        <v>44512.0</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C70" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F70" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="D70" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="E70" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="F70" s="11" t="s">
-        <v>284</v>
-      </c>
       <c r="G70" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I70" s="27" t="s">
         <v>27</v>
       </c>
       <c r="J70" s="22" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K70" s="28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L70" s="7"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="25">
-        <v>44514.0</v>
+        <v>44513.0</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I71" s="27" t="s">
         <v>27</v>
       </c>
       <c r="J71" s="22" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K71" s="28" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L71" s="7"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="10">
-        <v>44519.0</v>
-      </c>
-      <c r="B72" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>293</v>
+      <c r="A72" s="25">
+        <v>44514.0</v>
+      </c>
+      <c r="B72" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>296</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>70</v>
+        <v>288</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>98</v>
+        <v>289</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>294</v>
+        <v>164</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I72" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="I72" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J72" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="L72" s="9"/>
+      <c r="J72" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="K72" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="L72" s="7"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="10">
-        <v>44614.0</v>
+        <v>44519.0</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>139</v>
+        <v>298</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>296</v>
+        <v>75</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>297</v>
+        <v>76</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>298</v>
+        <v>103</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>230</v>
+        <v>299</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I73" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I73" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J73" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="K73" s="28" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L73" s="9"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="10">
-        <v>44631.0</v>
+        <v>44614.0</v>
       </c>
       <c r="B74" s="18" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>300</v>
+        <v>144</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>157</v>
+        <v>301</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>71</v>
+        <v>302</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>158</v>
+        <v>303</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I74" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J74" s="21" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="K74" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L74" s="9"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="10">
-        <v>44640.0</v>
+        <v>44631.0</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>139</v>
+        <v>305</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>303</v>
+        <v>162</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>304</v>
+        <v>163</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>230</v>
+        <v>278</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I75" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J75" s="21" t="s">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="K75" s="28" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="L75" s="9"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="10">
-        <v>44679.0</v>
+        <v>44640.0</v>
       </c>
       <c r="B76" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C76" s="13" t="s">
-        <v>97</v>
+        <v>21</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>144</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>70</v>
+        <v>308</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>71</v>
+        <v>215</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>132</v>
+        <v>309</v>
       </c>
       <c r="G76" s="13" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I76" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I76" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J76" s="21" t="s">
-        <v>305</v>
+        <v>276</v>
       </c>
       <c r="K76" s="28" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="L76" s="9"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="10">
-        <v>44701.0</v>
+        <v>44679.0</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>307</v>
+        <v>37</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>308</v>
+        <v>75</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="G77" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I77" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J77" s="21" t="s">
         <v>310</v>
       </c>
-      <c r="H77" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I77" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="J77" s="13" t="s">
+      <c r="K77" s="28" t="s">
         <v>311</v>
-      </c>
-      <c r="K77" s="22" t="s">
-        <v>312</v>
       </c>
       <c r="L77" s="9"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="10">
-        <v>44734.0</v>
+        <v>44701.0</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>134</v>
+        <v>312</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>124</v>
+        <v>313</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="G78" s="13" t="s">
-        <v>230</v>
+        <v>314</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>315</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I78" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I78" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J78" s="21" t="s">
-        <v>313</v>
-      </c>
-      <c r="K78" s="28" t="s">
-        <v>314</v>
+      <c r="J78" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="K78" s="22" t="s">
+        <v>317</v>
       </c>
       <c r="L78" s="9"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="10">
-        <v>44773.0</v>
+        <v>44734.0</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>315</v>
+        <v>139</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>316</v>
+        <v>235</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I79" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I79" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J79" s="21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K79" s="28" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L79" s="9"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="10">
-        <v>44791.0</v>
+        <v>44773.0</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I80" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J80" s="21" t="s">
-        <v>320</v>
+        <v>322</v>
+      </c>
+      <c r="K80" s="28" t="s">
+        <v>323</v>
       </c>
       <c r="L80" s="9"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="10">
-        <v>44804.0</v>
+        <v>44791.0</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>321</v>
+        <v>95</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>322</v>
+        <v>75</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>323</v>
+        <v>76</v>
       </c>
       <c r="F81" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G81" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="G81" s="13" t="s">
-        <v>230</v>
-      </c>
       <c r="H81" s="11" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I81" s="20" t="s">
         <v>27</v>
@@ -4564,1218 +4582,1215 @@
       <c r="J81" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="K81" s="28" t="s">
-        <v>326</v>
-      </c>
       <c r="L81" s="9"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="10">
-        <v>44831.0</v>
+        <v>44804.0</v>
       </c>
       <c r="B82" s="18" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C82" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="D82" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="D82" s="11" t="s">
-        <v>70</v>
-      </c>
       <c r="E82" s="19" t="s">
-        <v>71</v>
+        <v>328</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="G82" s="13" t="s">
-        <v>159</v>
+        <v>235</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I82" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="I82" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J82" s="21" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K82" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="L82" s="23" t="s">
-        <v>329</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="L82" s="9"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="10">
-        <v>44866.0</v>
+        <v>44831.0</v>
       </c>
       <c r="B83" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>134</v>
+        <v>332</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>136</v>
+        <v>264</v>
       </c>
       <c r="G83" s="13" t="s">
-        <v>230</v>
+        <v>164</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I83" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="I83" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J83" s="21" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K83" s="28" t="s">
-        <v>331</v>
-      </c>
-      <c r="L83" s="9"/>
+        <v>263</v>
+      </c>
+      <c r="L83" s="23" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="25">
+      <c r="A84" s="10">
+        <v>44866.0</v>
+      </c>
+      <c r="B84" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E84" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="G84" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="H84" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I84" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J84" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="K84" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="L84" s="9"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="25">
         <v>45067.0</v>
       </c>
-      <c r="B84" s="26" t="s">
+      <c r="B85" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C84" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="D84" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="E84" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="F84" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="G84" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="H84" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I84" s="27" t="s">
+      <c r="C85" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="E85" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="G85" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="H85" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I85" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J84" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="K84" s="28" t="s">
-        <v>333</v>
-      </c>
-      <c r="L84" s="7"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="10">
-        <v>45142.0</v>
-      </c>
-      <c r="B85" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="D85" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="E85" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="F85" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="G85" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="H85" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I85" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="J85" s="21" t="s">
+      <c r="J85" s="22" t="s">
         <v>337</v>
       </c>
       <c r="K85" s="28" t="s">
         <v>338</v>
       </c>
-      <c r="L85" s="9"/>
+      <c r="L85" s="7"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="25">
-        <v>45176.0</v>
-      </c>
-      <c r="B86" s="26" t="s">
-        <v>37</v>
+      <c r="A86" s="10">
+        <v>45142.0</v>
+      </c>
+      <c r="B86" s="18" t="s">
+        <v>12</v>
       </c>
       <c r="C86" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D86" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="D86" s="11" t="s">
+      <c r="E86" s="19" t="s">
         <v>340</v>
-      </c>
-      <c r="E86" s="19" t="s">
-        <v>179</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>341</v>
       </c>
       <c r="G86" s="13" t="s">
-        <v>159</v>
+        <v>235</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I86" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="I86" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="J86" s="22" t="s">
+      <c r="J86" s="21" t="s">
         <v>342</v>
       </c>
       <c r="K86" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="L86" s="7" t="s">
+      <c r="L86" s="9"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="25">
+        <v>45176.0</v>
+      </c>
+      <c r="B87" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C87" s="11" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="10">
-        <v>45213.0</v>
-      </c>
-      <c r="B87" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C87" s="11" t="s">
+      <c r="D87" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="D87" s="11" t="s">
-        <v>274</v>
-      </c>
       <c r="E87" s="19" t="s">
-        <v>275</v>
+        <v>184</v>
       </c>
       <c r="F87" s="11" t="s">
         <v>346</v>
       </c>
       <c r="G87" s="13" t="s">
-        <v>228</v>
+        <v>164</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I87" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="I87" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J87" s="21" t="s">
+      <c r="J87" s="22" t="s">
         <v>347</v>
       </c>
-      <c r="L87" s="9"/>
+      <c r="K87" s="28" t="s">
+        <v>348</v>
+      </c>
+      <c r="L87" s="7" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="10">
-        <v>45228.0</v>
+        <v>45213.0</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>70</v>
+        <v>279</v>
       </c>
       <c r="E88" s="19" t="s">
-        <v>71</v>
+        <v>280</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>145</v>
+        <v>351</v>
       </c>
       <c r="G88" s="13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I88" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="I88" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J88" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="K88" s="9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L88" s="9"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="10">
-        <v>45239.0</v>
+        <v>45228.0</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>159</v>
+        <v>235</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I89" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J89" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="K89" s="28" t="s">
-        <v>353</v>
+        <v>354</v>
+      </c>
+      <c r="K89" s="9" t="s">
+        <v>355</v>
       </c>
       <c r="L89" s="9"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="10">
-        <v>45247.0</v>
-      </c>
-      <c r="B90" s="26" t="s">
-        <v>12</v>
+        <v>45239.0</v>
+      </c>
+      <c r="B90" s="18" t="s">
+        <v>37</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>277</v>
+        <v>164</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I90" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J90" s="21" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K90" s="28" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L90" s="9"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="10">
-        <v>45312.0</v>
-      </c>
-      <c r="B91" s="18" t="s">
-        <v>21</v>
+        <v>45247.0</v>
+      </c>
+      <c r="B91" s="26" t="s">
+        <v>12</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>139</v>
+        <v>359</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>268</v>
+        <v>130</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I91" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="I91" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J91" s="21" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="K91" s="28" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L91" s="9"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="10">
-        <v>45340.0</v>
+        <v>45312.0</v>
       </c>
       <c r="B92" s="18" t="s">
         <v>21</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>274</v>
+        <v>140</v>
       </c>
       <c r="E92" s="19" t="s">
-        <v>275</v>
+        <v>76</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>64</v>
+        <v>278</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I92" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J92" s="21" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="K92" s="28" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="L92" s="9"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="10">
-        <v>45380.0</v>
+        <v>45340.0</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>359</v>
+        <v>144</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>70</v>
+        <v>279</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>71</v>
+        <v>280</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>360</v>
+        <v>281</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I93" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J93" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K93" s="28" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L93" s="9"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="10">
-        <v>45389.0</v>
+        <v>45380.0</v>
       </c>
       <c r="B94" s="18" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E94" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>259</v>
+        <v>365</v>
       </c>
       <c r="G94" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I94" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J94" s="21" t="s">
-        <v>363</v>
-      </c>
-      <c r="L94" s="21"/>
+        <v>366</v>
+      </c>
+      <c r="K94" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="L94" s="9"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="25">
-        <v>45428.0</v>
+      <c r="A95" s="10">
+        <v>45389.0</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="E95" s="19" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>365</v>
+        <v>264</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I95" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="I95" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J95" s="29" t="s">
-        <v>366</v>
-      </c>
-      <c r="K95" s="28" t="s">
-        <v>367</v>
-      </c>
-      <c r="L95" s="30"/>
+      <c r="J95" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="L95" s="21"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="25">
-        <v>45429.0</v>
-      </c>
-      <c r="B96" s="26" t="s">
-        <v>12</v>
+        <v>45428.0</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>37</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E96" s="19" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G96" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I96" s="27" t="s">
         <v>27</v>
       </c>
       <c r="J96" s="29" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K96" s="28" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L96" s="30"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="25">
-        <v>45430.0</v>
+        <v>45429.0</v>
       </c>
       <c r="B97" s="26" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I97" s="27" t="s">
         <v>27</v>
       </c>
       <c r="J97" s="29" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K97" s="28" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="L97" s="30"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="25">
-        <v>45431.0</v>
+        <v>45430.0</v>
       </c>
       <c r="B98" s="26" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E98" s="19" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G98" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I98" s="27" t="s">
         <v>27</v>
       </c>
       <c r="J98" s="29" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K98" s="28" t="s">
+        <v>374</v>
+      </c>
+      <c r="L98" s="30"/>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="25">
+        <v>45431.0</v>
+      </c>
+      <c r="B99" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="F99" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="L98" s="30"/>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="10">
-        <v>45469.0</v>
-      </c>
-      <c r="B99" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C99" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D99" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E99" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="F99" s="11" t="s">
-        <v>259</v>
-      </c>
       <c r="G99" s="13" t="s">
-        <v>273</v>
+        <v>164</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I99" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I99" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J99" s="21" t="s">
+      <c r="J99" s="29" t="s">
         <v>371</v>
       </c>
-      <c r="K99" s="21" t="s">
-        <v>372</v>
-      </c>
-      <c r="L99" s="9"/>
+      <c r="K99" s="28" t="s">
+        <v>375</v>
+      </c>
+      <c r="L99" s="30"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="10">
-        <v>45531.0</v>
+        <v>45469.0</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>354</v>
+        <v>176</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E100" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>132</v>
+        <v>264</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>159</v>
+        <v>278</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I100" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="I100" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J100" s="21" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K100" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="L100" s="9"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="10">
-        <v>45537.0</v>
+        <v>45531.0</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C101" s="13" t="s">
-        <v>253</v>
+        <v>29</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>359</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G101" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H101" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I101" s="20" t="s">
+      <c r="I101" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J101" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="K101" s="22" t="s">
-        <v>376</v>
-      </c>
-      <c r="L101" s="23" t="s">
-        <v>377</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="K101" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="L101" s="9"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="10">
-        <v>45553.0</v>
+        <v>45537.0</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>378</v>
+        <v>54</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>258</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E102" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>259</v>
+        <v>137</v>
       </c>
       <c r="G102" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H102" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I102" s="24" t="s">
+      <c r="I102" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J102" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="K102" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="L102" s="9"/>
+      <c r="K102" s="22" t="s">
+        <v>381</v>
+      </c>
+      <c r="L102" s="23" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="10">
-        <v>45740.0</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C103" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>135</v>
+        <v>45553.0</v>
+      </c>
+      <c r="B103" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="E103" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="F103" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="G103" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="H103" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F103" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="G103" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="H103" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I103" s="14" t="s">
+      <c r="I103" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="J103" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="K103" s="9" t="s">
-        <v>66</v>
+      <c r="J103" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="K103" s="21" t="s">
+        <v>385</v>
       </c>
       <c r="L103" s="9"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="10">
-        <v>45783.0</v>
-      </c>
-      <c r="B104" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>383</v>
-      </c>
-      <c r="D104" s="11" t="s">
-        <v>70</v>
+        <v>45740.0</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>140</v>
       </c>
       <c r="E104" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="H104" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I104" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J104" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="K104" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="F104" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="G104" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="H104" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I104" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J104" s="21" t="s">
-        <v>384</v>
-      </c>
-      <c r="K104" s="21" t="s">
-        <v>385</v>
       </c>
       <c r="L104" s="9"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="10">
-        <v>45790.0</v>
+        <v>45783.0</v>
       </c>
       <c r="B105" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>227</v>
+        <v>388</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="G105" s="13" t="s">
-        <v>159</v>
+        <v>278</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I105" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J105" s="21" t="s">
-        <v>386</v>
-      </c>
-      <c r="K105" s="22" t="s">
-        <v>387</v>
+        <v>389</v>
+      </c>
+      <c r="K105" s="21" t="s">
+        <v>390</v>
       </c>
       <c r="L105" s="9"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="10">
-        <v>45808.0</v>
+        <v>45790.0</v>
       </c>
       <c r="B106" s="18" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>174</v>
+        <v>232</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="E106" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="G106" s="13" t="s">
-        <v>273</v>
+        <v>164</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I106" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="I106" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J106" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="K106" s="21" t="s">
-        <v>389</v>
+        <v>391</v>
+      </c>
+      <c r="K106" s="22" t="s">
+        <v>392</v>
       </c>
       <c r="L106" s="9"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="10">
-        <v>45853.0</v>
+        <v>45808.0</v>
       </c>
       <c r="B107" s="18" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>262</v>
+        <v>179</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="G107" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I107" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J107" s="21" t="s">
-        <v>390</v>
-      </c>
-      <c r="K107" s="9"/>
+        <v>342</v>
+      </c>
+      <c r="K107" s="21" t="s">
+        <v>394</v>
+      </c>
       <c r="L107" s="9"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="10">
-        <v>45867.0</v>
+        <v>45853.0</v>
       </c>
       <c r="B108" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>391</v>
+        <v>267</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>125</v>
+        <v>365</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>159</v>
+        <v>282</v>
       </c>
       <c r="H108" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I108" s="20" t="s">
+      <c r="I108" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J108" s="21" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K108" s="9"/>
       <c r="L108" s="9"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="10">
-        <v>45890.0</v>
+        <v>45867.0</v>
       </c>
       <c r="B109" s="18" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>360</v>
+        <v>130</v>
       </c>
       <c r="G109" s="13" t="s">
-        <v>277</v>
+        <v>164</v>
       </c>
       <c r="H109" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I109" s="24" t="s">
+      <c r="I109" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J109" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="K109" s="21" t="s">
-        <v>395</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="K109" s="9"/>
       <c r="L109" s="9"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="10">
-        <v>45896.0</v>
+        <v>45890.0</v>
       </c>
       <c r="B110" s="18" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>30</v>
+        <v>398</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>334</v>
+        <v>75</v>
       </c>
       <c r="E110" s="19" t="s">
-        <v>335</v>
+        <v>76</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="G110" s="13" t="s">
-        <v>230</v>
+        <v>282</v>
       </c>
       <c r="H110" s="11" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I110" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J110" s="21" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K110" s="21" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="L110" s="9"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="10">
-        <v>45905.0</v>
+        <v>45896.0</v>
       </c>
       <c r="B111" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C111" s="13" t="s">
-        <v>97</v>
+        <v>89</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>70</v>
+        <v>339</v>
       </c>
       <c r="E111" s="19" t="s">
-        <v>71</v>
+        <v>340</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="G111" s="13" t="s">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="H111" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I111" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J111" s="21" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K111" s="21" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L111" s="9"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="10">
-        <v>45911.0</v>
+        <v>45905.0</v>
       </c>
       <c r="B112" s="18" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C112" s="13" t="s">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E112" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="G112" s="13" t="s">
-        <v>64</v>
+        <v>278</v>
       </c>
       <c r="H112" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I112" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I112" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J112" s="21" t="s">
-        <v>401</v>
-      </c>
-      <c r="K112" s="22" t="s">
-        <v>402</v>
+        <v>403</v>
+      </c>
+      <c r="K112" s="21" t="s">
+        <v>404</v>
       </c>
       <c r="L112" s="9"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="10">
-        <v>45955.0</v>
+        <v>45911.0</v>
       </c>
       <c r="B113" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>403</v>
+        <v>37</v>
+      </c>
+      <c r="C113" s="13" t="s">
+        <v>405</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E113" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>259</v>
+        <v>365</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>230</v>
+        <v>69</v>
       </c>
       <c r="H113" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I113" s="24" t="s">
+      <c r="I113" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J113" s="21" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K113" s="22" t="s">
-        <v>405</v>
-      </c>
-      <c r="L113" s="23" t="s">
-        <v>406</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="L113" s="9"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="10">
-        <v>45965.0</v>
+        <v>45955.0</v>
       </c>
       <c r="B114" s="18" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>66</v>
+        <v>408</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>145</v>
+        <v>264</v>
       </c>
       <c r="G114" s="13" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H114" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I114" s="20" t="s">
+      <c r="I114" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J114" s="21" t="s">
-        <v>407</v>
-      </c>
-      <c r="K114" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="L114" s="9"/>
+        <v>409</v>
+      </c>
+      <c r="K114" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="L114" s="23" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="10">
-        <v>46063.0</v>
+        <v>45965.0</v>
       </c>
       <c r="B115" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="E115" s="19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>268</v>
+        <v>150</v>
       </c>
       <c r="G115" s="13" t="s">
-        <v>159</v>
+        <v>235</v>
       </c>
       <c r="H115" s="11" t="s">
         <v>18</v>
@@ -5784,200 +5799,222 @@
         <v>27</v>
       </c>
       <c r="J115" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="K115" s="9" t="s">
-        <v>399</v>
+        <v>412</v>
+      </c>
+      <c r="K115" s="21" t="s">
+        <v>413</v>
       </c>
       <c r="L115" s="9"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="10">
-        <v>46088.0</v>
+        <v>46063.0</v>
       </c>
       <c r="B116" s="18" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>409</v>
+        <v>102</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>340</v>
+        <v>140</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>410</v>
+        <v>273</v>
       </c>
       <c r="G116" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H116" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I116" s="24" t="s">
+      <c r="I116" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J116" s="21" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="K116" s="9" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="L116" s="9"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="10">
-        <v>46097.0</v>
+        <v>46088.0</v>
       </c>
       <c r="B117" s="18" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>70</v>
+        <v>345</v>
       </c>
       <c r="E117" s="19" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="G117" s="13" t="s">
-        <v>230</v>
+        <v>164</v>
       </c>
       <c r="H117" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I117" s="20" t="s">
+      <c r="I117" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J117" s="21" t="s">
-        <v>414</v>
-      </c>
-      <c r="K117" s="21" t="s">
-        <v>415</v>
+        <v>416</v>
+      </c>
+      <c r="K117" s="9" t="s">
+        <v>417</v>
       </c>
       <c r="L117" s="9"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="6">
+      <c r="A118" s="10">
+        <v>46097.0</v>
+      </c>
+      <c r="B118" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E118" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F118" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="G118" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="H118" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I118" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J118" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="K118" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="L118" s="9"/>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="6">
         <v>46107.0</v>
       </c>
-      <c r="B118" s="7" t="s">
+      <c r="B119" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C118" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G118" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H118" s="7" t="s">
+      <c r="C119" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H119" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I118" s="17" t="s">
+      <c r="I119" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J118" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="K118" s="9"/>
-      <c r="L118" s="9"/>
-    </row>
-    <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="10">
-        <v>46113.0</v>
-      </c>
-      <c r="B119" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E119" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="F119" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="G119" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="H119" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I119" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="J119" s="21" t="s">
-        <v>417</v>
-      </c>
-      <c r="K119" s="7" t="s">
-        <v>418</v>
-      </c>
+      <c r="J119" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="K119" s="9"/>
       <c r="L119" s="9"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="10">
+        <v>46113.0</v>
+      </c>
+      <c r="B120" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E120" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F120" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G120" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="H120" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I120" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J120" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="K120" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="L120" s="9"/>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="10">
         <v>46129.0</v>
       </c>
-      <c r="B120" s="9" t="s">
+      <c r="B121" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C120" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="D120" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="E120" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="F120" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="G120" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H120" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I120" s="14" t="s">
+      <c r="C121" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E121" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="G121" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I121" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="J120" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="K120" s="9"/>
-      <c r="L120" s="9"/>
-    </row>
-    <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="10"/>
-      <c r="B121" s="9"/>
-      <c r="C121" s="9"/>
-      <c r="D121" s="9"/>
-      <c r="E121" s="16"/>
-      <c r="F121" s="9"/>
-      <c r="G121" s="9"/>
-      <c r="H121" s="9"/>
-      <c r="I121" s="9"/>
-      <c r="J121" s="9"/>
+      <c r="J121" s="7" t="s">
+        <v>426</v>
+      </c>
       <c r="K121" s="9"/>
       <c r="L121" s="9"/>
     </row>
@@ -8488,7 +8525,7 @@
       <c r="L300" s="9"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="A301" s="31"/>
+      <c r="A301" s="10"/>
       <c r="B301" s="9"/>
       <c r="C301" s="9"/>
       <c r="D301" s="9"/>
@@ -18399,10 +18436,24 @@
       <c r="K1008" s="9"/>
       <c r="L1008" s="9"/>
     </row>
+    <row r="1009" ht="15.75" customHeight="1">
+      <c r="A1009" s="31"/>
+      <c r="B1009" s="9"/>
+      <c r="C1009" s="9"/>
+      <c r="D1009" s="9"/>
+      <c r="E1009" s="16"/>
+      <c r="F1009" s="9"/>
+      <c r="G1009" s="9"/>
+      <c r="H1009" s="9"/>
+      <c r="I1009" s="9"/>
+      <c r="J1009" s="9"/>
+      <c r="K1009" s="9"/>
+      <c r="L1009" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$M$120">
-    <sortState ref="A1:M120">
-      <sortCondition ref="A1:A120"/>
+  <autoFilter ref="$A$1:$M$121">
+    <sortState ref="A1:M121">
+      <sortCondition ref="A1:A121"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
@@ -18417,16 +18468,16 @@
     <hyperlink r:id="rId9" ref="I9"/>
     <hyperlink r:id="rId10" ref="I10"/>
     <hyperlink r:id="rId11" ref="I11"/>
-    <hyperlink r:id="rId12" ref="L11"/>
-    <hyperlink r:id="rId13" ref="I12"/>
-    <hyperlink r:id="rId14" ref="I14"/>
+    <hyperlink r:id="rId12" ref="I12"/>
+    <hyperlink r:id="rId13" ref="L12"/>
+    <hyperlink r:id="rId14" ref="I13"/>
     <hyperlink r:id="rId15" ref="I15"/>
     <hyperlink r:id="rId16" ref="I16"/>
     <hyperlink r:id="rId17" ref="I17"/>
     <hyperlink r:id="rId18" ref="I18"/>
     <hyperlink r:id="rId19" ref="I19"/>
-    <hyperlink r:id="rId20" ref="L19"/>
-    <hyperlink r:id="rId21" ref="I20"/>
+    <hyperlink r:id="rId20" ref="I20"/>
+    <hyperlink r:id="rId21" ref="L20"/>
     <hyperlink r:id="rId22" ref="I21"/>
     <hyperlink r:id="rId23" ref="I22"/>
     <hyperlink r:id="rId24" ref="I23"/>
@@ -18453,8 +18504,8 @@
     <hyperlink r:id="rId45" ref="I44"/>
     <hyperlink r:id="rId46" ref="I45"/>
     <hyperlink r:id="rId47" ref="I46"/>
-    <hyperlink r:id="rId48" ref="L46"/>
-    <hyperlink r:id="rId49" ref="I47"/>
+    <hyperlink r:id="rId48" ref="I47"/>
+    <hyperlink r:id="rId49" ref="L47"/>
     <hyperlink r:id="rId50" ref="I48"/>
     <hyperlink r:id="rId51" ref="I49"/>
     <hyperlink r:id="rId52" ref="I50"/>
@@ -18490,8 +18541,8 @@
     <hyperlink r:id="rId82" ref="I80"/>
     <hyperlink r:id="rId83" ref="I81"/>
     <hyperlink r:id="rId84" ref="I82"/>
-    <hyperlink r:id="rId85" ref="L82"/>
-    <hyperlink r:id="rId86" ref="I83"/>
+    <hyperlink r:id="rId85" ref="I83"/>
+    <hyperlink r:id="rId86" ref="L83"/>
     <hyperlink r:id="rId87" ref="I84"/>
     <hyperlink r:id="rId88" ref="I85"/>
     <hyperlink r:id="rId89" ref="I86"/>
@@ -18510,8 +18561,8 @@
     <hyperlink r:id="rId102" ref="I99"/>
     <hyperlink r:id="rId103" ref="I100"/>
     <hyperlink r:id="rId104" ref="I101"/>
-    <hyperlink r:id="rId105" ref="L101"/>
-    <hyperlink r:id="rId106" ref="I102"/>
+    <hyperlink r:id="rId105" ref="I102"/>
+    <hyperlink r:id="rId106" ref="L102"/>
     <hyperlink r:id="rId107" ref="I103"/>
     <hyperlink r:id="rId108" ref="I104"/>
     <hyperlink r:id="rId109" ref="I105"/>
@@ -18523,18 +18574,19 @@
     <hyperlink r:id="rId115" ref="I111"/>
     <hyperlink r:id="rId116" ref="I112"/>
     <hyperlink r:id="rId117" ref="I113"/>
-    <hyperlink r:id="rId118" ref="L113"/>
-    <hyperlink r:id="rId119" ref="I114"/>
+    <hyperlink r:id="rId118" ref="I114"/>
+    <hyperlink r:id="rId119" ref="L114"/>
     <hyperlink r:id="rId120" ref="I115"/>
     <hyperlink r:id="rId121" ref="I116"/>
     <hyperlink r:id="rId122" ref="I117"/>
     <hyperlink r:id="rId123" ref="I118"/>
     <hyperlink r:id="rId124" ref="I119"/>
     <hyperlink r:id="rId125" ref="I120"/>
+    <hyperlink r:id="rId126" ref="I121"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId126"/>
+  <drawing r:id="rId127"/>
 </worksheet>
 </file>
--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="426">
   <si>
     <t>Date</t>
   </si>
@@ -144,7 +144,7 @@
     <t>Imani</t>
   </si>
   <si>
-    <t>Distrubed</t>
+    <t>Disturbed</t>
   </si>
   <si>
     <t>New York</t>
@@ -399,7 +399,7 @@
     <t>Le Butcherettes</t>
   </si>
   <si>
-    <t>Britt Floyd</t>
+    <t>Brit Floyd</t>
   </si>
   <si>
     <t>Durham</t>
@@ -529,9 +529,6 @@
   </si>
   <si>
     <t>We're All in This Together Tour</t>
-  </si>
-  <si>
-    <t>Disturbed</t>
   </si>
   <si>
     <t>Jeff Stark</t>
@@ -2896,7 +2893,7 @@
         <v>29</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>172</v>
+        <v>43</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>75</v>
@@ -2908,7 +2905,7 @@
         <v>137</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H34" s="11" t="s">
         <v>18</v>
@@ -2917,10 +2914,10 @@
         <v>27</v>
       </c>
       <c r="J34" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K34" s="21" t="s">
         <v>174</v>
-      </c>
-      <c r="K34" s="21" t="s">
-        <v>175</v>
       </c>
       <c r="L34" s="9"/>
     </row>
@@ -2932,7 +2929,7 @@
         <v>62</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>75</v>
@@ -2953,10 +2950,10 @@
         <v>27</v>
       </c>
       <c r="J35" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="K35" s="21" t="s">
         <v>177</v>
-      </c>
-      <c r="K35" s="21" t="s">
-        <v>178</v>
       </c>
       <c r="L35" s="9"/>
     </row>
@@ -2968,7 +2965,7 @@
         <v>12</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>56</v>
@@ -2977,7 +2974,7 @@
         <v>57</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>59</v>
@@ -2989,10 +2986,10 @@
         <v>27</v>
       </c>
       <c r="J36" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="K36" s="21" t="s">
         <v>181</v>
-      </c>
-      <c r="K36" s="21" t="s">
-        <v>182</v>
       </c>
       <c r="L36" s="9"/>
     </row>
@@ -3007,16 +3004,16 @@
         <v>144</v>
       </c>
       <c r="D37" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E37" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="F37" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="G37" s="13" t="s">
         <v>185</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>186</v>
       </c>
       <c r="H37" s="11" t="s">
         <v>85</v>
@@ -3025,10 +3022,10 @@
         <v>27</v>
       </c>
       <c r="J37" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="K37" s="21" t="s">
         <v>187</v>
-      </c>
-      <c r="K37" s="21" t="s">
-        <v>188</v>
       </c>
       <c r="L37" s="9"/>
     </row>
@@ -3040,7 +3037,7 @@
         <v>21</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>75</v>
@@ -3061,10 +3058,10 @@
         <v>27</v>
       </c>
       <c r="J38" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="K38" s="21" t="s">
         <v>190</v>
-      </c>
-      <c r="K38" s="21" t="s">
-        <v>191</v>
       </c>
       <c r="L38" s="9"/>
     </row>
@@ -3088,7 +3085,7 @@
         <v>137</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>18</v>
@@ -3097,10 +3094,10 @@
         <v>27</v>
       </c>
       <c r="J39" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="K39" s="21" t="s">
         <v>193</v>
-      </c>
-      <c r="K39" s="21" t="s">
-        <v>194</v>
       </c>
       <c r="L39" s="9"/>
     </row>
@@ -3115,16 +3112,16 @@
         <v>55</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F40" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="G40" s="13" t="s">
         <v>196</v>
-      </c>
-      <c r="G40" s="13" t="s">
-        <v>197</v>
       </c>
       <c r="H40" s="11" t="s">
         <v>85</v>
@@ -3133,13 +3130,13 @@
         <v>27</v>
       </c>
       <c r="J40" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="K40" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="K40" s="22" t="s">
+      <c r="L40" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="L40" s="9" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -3159,10 +3156,10 @@
         <v>57</v>
       </c>
       <c r="F41" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="G41" s="13" t="s">
         <v>201</v>
-      </c>
-      <c r="G41" s="13" t="s">
-        <v>202</v>
       </c>
       <c r="H41" s="11" t="s">
         <v>85</v>
@@ -3171,7 +3168,7 @@
         <v>27</v>
       </c>
       <c r="J41" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K41" s="9"/>
       <c r="L41" s="9"/>
@@ -3187,13 +3184,13 @@
         <v>107</v>
       </c>
       <c r="D42" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E42" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="F42" s="11" t="s">
         <v>205</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>206</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>17</v>
@@ -3205,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J42" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="K42" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="K42" s="21" t="s">
+      <c r="L42" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="L42" s="9" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -3222,7 +3219,7 @@
         <v>29</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>75</v>
@@ -3234,7 +3231,7 @@
         <v>103</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H43" s="11" t="s">
         <v>18</v>
@@ -3243,7 +3240,7 @@
         <v>27</v>
       </c>
       <c r="J43" s="21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
@@ -3256,19 +3253,19 @@
         <v>12</v>
       </c>
       <c r="C44" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D44" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="E44" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="E44" s="19" t="s">
+      <c r="F44" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="G44" s="13" t="s">
         <v>216</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>217</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>85</v>
@@ -3277,13 +3274,13 @@
         <v>27</v>
       </c>
       <c r="J44" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="K44" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="K44" s="28" t="s">
+      <c r="L44" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="L44" s="7" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
@@ -3294,19 +3291,19 @@
         <v>62</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D45" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E45" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="E45" s="19" t="s">
+      <c r="F45" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="G45" s="13" t="s">
         <v>216</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>217</v>
       </c>
       <c r="H45" s="11" t="s">
         <v>85</v>
@@ -3315,13 +3312,13 @@
         <v>27</v>
       </c>
       <c r="J45" s="22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K45" s="28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
@@ -3332,19 +3329,19 @@
         <v>21</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D46" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E46" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="F46" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="G46" s="13" t="s">
         <v>216</v>
-      </c>
-      <c r="G46" s="13" t="s">
-        <v>217</v>
       </c>
       <c r="H46" s="11" t="s">
         <v>85</v>
@@ -3353,13 +3350,13 @@
         <v>27</v>
       </c>
       <c r="J46" s="22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K46" s="28" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -3370,7 +3367,7 @@
         <v>29</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>75</v>
@@ -3391,13 +3388,13 @@
         <v>27</v>
       </c>
       <c r="J47" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="K47" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="K47" s="28" t="s">
+      <c r="L47" s="23" t="s">
         <v>227</v>
-      </c>
-      <c r="L47" s="23" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
@@ -3408,7 +3405,7 @@
         <v>12</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>75</v>
@@ -3417,7 +3414,7 @@
         <v>76</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G48" s="13" t="s">
         <v>164</v>
@@ -3429,7 +3426,7 @@
         <v>27</v>
       </c>
       <c r="J48" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L48" s="9"/>
     </row>
@@ -3441,7 +3438,7 @@
         <v>29</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>56</v>
@@ -3453,7 +3450,7 @@
         <v>96</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H49" s="11" t="s">
         <v>85</v>
@@ -3462,7 +3459,7 @@
         <v>27</v>
       </c>
       <c r="J49" s="21" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L49" s="9"/>
     </row>
@@ -3486,7 +3483,7 @@
         <v>145</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H50" s="11" t="s">
         <v>85</v>
@@ -3495,10 +3492,10 @@
         <v>27</v>
       </c>
       <c r="J50" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="K50" s="28" t="s">
         <v>236</v>
-      </c>
-      <c r="K50" s="28" t="s">
-        <v>237</v>
       </c>
       <c r="L50" s="9"/>
     </row>
@@ -3510,7 +3507,7 @@
         <v>21</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>75</v>
@@ -3531,7 +3528,7 @@
         <v>27</v>
       </c>
       <c r="J51" s="21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L51" s="9"/>
     </row>
@@ -3543,7 +3540,7 @@
         <v>54</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>75</v>
@@ -3564,7 +3561,7 @@
         <v>27</v>
       </c>
       <c r="J52" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L52" s="9"/>
     </row>
@@ -3576,7 +3573,7 @@
         <v>29</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>75</v>
@@ -3588,7 +3585,7 @@
         <v>103</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H53" s="11" t="s">
         <v>18</v>
@@ -3597,7 +3594,7 @@
         <v>27</v>
       </c>
       <c r="J53" s="21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L53" s="9"/>
     </row>
@@ -3609,7 +3606,7 @@
         <v>62</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D54" s="11" t="s">
         <v>75</v>
@@ -3630,7 +3627,7 @@
         <v>27</v>
       </c>
       <c r="J54" s="21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L54" s="9"/>
     </row>
@@ -3642,19 +3639,19 @@
         <v>12</v>
       </c>
       <c r="C55" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="D55" s="11" t="s">
         <v>245</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>246</v>
       </c>
       <c r="E55" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F55" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="G55" s="13" t="s">
         <v>247</v>
-      </c>
-      <c r="G55" s="13" t="s">
-        <v>248</v>
       </c>
       <c r="H55" s="11" t="s">
         <v>85</v>
@@ -3663,10 +3660,10 @@
         <v>27</v>
       </c>
       <c r="J55" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="K55" s="28" t="s">
         <v>249</v>
-      </c>
-      <c r="K55" s="28" t="s">
-        <v>250</v>
       </c>
       <c r="L55" s="9"/>
     </row>
@@ -3678,19 +3675,19 @@
         <v>62</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E56" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F56" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="G56" s="13" t="s">
         <v>247</v>
-      </c>
-      <c r="G56" s="13" t="s">
-        <v>248</v>
       </c>
       <c r="H56" s="13" t="s">
         <v>85</v>
@@ -3699,13 +3696,13 @@
         <v>27</v>
       </c>
       <c r="J56" s="22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K56" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="L56" s="7" t="s">
         <v>252</v>
-      </c>
-      <c r="L56" s="7" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
@@ -3716,19 +3713,19 @@
         <v>21</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E57" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F57" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="G57" s="13" t="s">
         <v>247</v>
-      </c>
-      <c r="G57" s="13" t="s">
-        <v>248</v>
       </c>
       <c r="H57" s="13" t="s">
         <v>85</v>
@@ -3737,10 +3734,10 @@
         <v>27</v>
       </c>
       <c r="J57" s="22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K57" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L57" s="9"/>
     </row>
@@ -3752,7 +3749,7 @@
         <v>37</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>75</v>
@@ -3773,7 +3770,7 @@
         <v>27</v>
       </c>
       <c r="J58" s="21" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L58" s="9"/>
     </row>
@@ -3785,19 +3782,19 @@
         <v>29</v>
       </c>
       <c r="C59" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="D59" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="E59" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="F59" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="E59" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="F59" s="11" t="s">
+      <c r="G59" s="13" t="s">
         <v>260</v>
-      </c>
-      <c r="G59" s="13" t="s">
-        <v>261</v>
       </c>
       <c r="H59" s="11" t="s">
         <v>18</v>
@@ -3806,7 +3803,7 @@
         <v>27</v>
       </c>
       <c r="J59" s="21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L59" s="9"/>
     </row>
@@ -3818,7 +3815,7 @@
         <v>21</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>75</v>
@@ -3827,10 +3824,10 @@
         <v>76</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H60" s="11" t="s">
         <v>18</v>
@@ -3839,10 +3836,10 @@
         <v>27</v>
       </c>
       <c r="J60" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="K60" s="28" t="s">
         <v>265</v>
-      </c>
-      <c r="K60" s="28" t="s">
-        <v>266</v>
       </c>
       <c r="L60" s="9"/>
     </row>
@@ -3854,19 +3851,19 @@
         <v>37</v>
       </c>
       <c r="C61" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="D61" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="E61" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="E61" s="19" t="s">
+      <c r="F61" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="G61" s="13" t="s">
         <v>270</v>
-      </c>
-      <c r="G61" s="13" t="s">
-        <v>271</v>
       </c>
       <c r="H61" s="11" t="s">
         <v>18</v>
@@ -3875,7 +3872,7 @@
         <v>27</v>
       </c>
       <c r="J61" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L61" s="9"/>
     </row>
@@ -3896,7 +3893,7 @@
         <v>76</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G62" s="13" t="s">
         <v>164</v>
@@ -3908,7 +3905,7 @@
         <v>27</v>
       </c>
       <c r="J62" s="21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L62" s="9"/>
     </row>
@@ -3929,10 +3926,10 @@
         <v>45</v>
       </c>
       <c r="F63" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="G63" s="13" t="s">
         <v>274</v>
-      </c>
-      <c r="G63" s="13" t="s">
-        <v>275</v>
       </c>
       <c r="H63" s="11" t="s">
         <v>85</v>
@@ -3941,10 +3938,10 @@
         <v>27</v>
       </c>
       <c r="J63" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="K63" s="28" t="s">
         <v>276</v>
-      </c>
-      <c r="K63" s="28" t="s">
-        <v>277</v>
       </c>
       <c r="L63" s="9"/>
     </row>
@@ -3968,7 +3965,7 @@
         <v>103</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H64" s="11" t="s">
         <v>85</v>
@@ -3977,10 +3974,10 @@
         <v>27</v>
       </c>
       <c r="J64" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="K64" s="28" t="s">
         <v>276</v>
-      </c>
-      <c r="K64" s="28" t="s">
-        <v>277</v>
       </c>
       <c r="L64" s="9"/>
     </row>
@@ -3995,13 +3992,13 @@
         <v>144</v>
       </c>
       <c r="D65" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="E65" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="E65" s="19" t="s">
+      <c r="F65" s="11" t="s">
         <v>280</v>
-      </c>
-      <c r="F65" s="11" t="s">
-        <v>281</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>164</v>
@@ -4013,10 +4010,10 @@
         <v>27</v>
       </c>
       <c r="J65" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="K65" s="28" t="s">
         <v>276</v>
-      </c>
-      <c r="K65" s="28" t="s">
-        <v>277</v>
       </c>
       <c r="L65" s="9"/>
     </row>
@@ -4028,7 +4025,7 @@
         <v>62</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D66" s="11" t="s">
         <v>162</v>
@@ -4040,7 +4037,7 @@
         <v>163</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H66" s="11" t="s">
         <v>85</v>
@@ -4049,10 +4046,10 @@
         <v>27</v>
       </c>
       <c r="J66" s="21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K66" s="28" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L66" s="9"/>
     </row>
@@ -4064,7 +4061,7 @@
         <v>62</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>75</v>
@@ -4073,7 +4070,7 @@
         <v>76</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>104</v>
@@ -4085,7 +4082,7 @@
         <v>27</v>
       </c>
       <c r="J67" s="21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L67" s="9"/>
     </row>
@@ -4118,7 +4115,7 @@
         <v>27</v>
       </c>
       <c r="J68" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L68" s="9"/>
     </row>
@@ -4130,16 +4127,16 @@
         <v>37</v>
       </c>
       <c r="C69" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="D69" s="11" t="s">
         <v>287</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>288</v>
       </c>
       <c r="E69" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>164</v>
@@ -4151,10 +4148,10 @@
         <v>27</v>
       </c>
       <c r="J69" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="K69" s="28" t="s">
         <v>290</v>
-      </c>
-      <c r="K69" s="28" t="s">
-        <v>291</v>
       </c>
       <c r="L69" s="7"/>
     </row>
@@ -4166,16 +4163,16 @@
         <v>12</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E70" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>164</v>
@@ -4187,10 +4184,10 @@
         <v>27</v>
       </c>
       <c r="J70" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K70" s="28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L70" s="7"/>
     </row>
@@ -4202,16 +4199,16 @@
         <v>62</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E71" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>164</v>
@@ -4223,10 +4220,10 @@
         <v>27</v>
       </c>
       <c r="J71" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K71" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L71" s="7"/>
     </row>
@@ -4238,16 +4235,16 @@
         <v>21</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E72" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>164</v>
@@ -4259,10 +4256,10 @@
         <v>27</v>
       </c>
       <c r="J72" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K72" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L72" s="7"/>
     </row>
@@ -4274,7 +4271,7 @@
         <v>12</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>75</v>
@@ -4286,7 +4283,7 @@
         <v>103</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H73" s="11" t="s">
         <v>85</v>
@@ -4295,7 +4292,7 @@
         <v>27</v>
       </c>
       <c r="J73" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L73" s="9"/>
     </row>
@@ -4310,16 +4307,16 @@
         <v>144</v>
       </c>
       <c r="D74" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E74" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="E74" s="19" t="s">
+      <c r="F74" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="F74" s="11" t="s">
-        <v>303</v>
-      </c>
       <c r="G74" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H74" s="11" t="s">
         <v>85</v>
@@ -4328,10 +4325,10 @@
         <v>27</v>
       </c>
       <c r="J74" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K74" s="28" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L74" s="9"/>
     </row>
@@ -4343,7 +4340,7 @@
         <v>12</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D75" s="11" t="s">
         <v>162</v>
@@ -4355,7 +4352,7 @@
         <v>163</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H75" s="11" t="s">
         <v>18</v>
@@ -4364,10 +4361,10 @@
         <v>27</v>
       </c>
       <c r="J75" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="K75" s="28" t="s">
         <v>306</v>
-      </c>
-      <c r="K75" s="28" t="s">
-        <v>307</v>
       </c>
       <c r="L75" s="9"/>
     </row>
@@ -4382,16 +4379,16 @@
         <v>144</v>
       </c>
       <c r="D76" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="F76" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="E76" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="F76" s="11" t="s">
-        <v>309</v>
-      </c>
       <c r="G76" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H76" s="11" t="s">
         <v>85</v>
@@ -4400,10 +4397,10 @@
         <v>27</v>
       </c>
       <c r="J76" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K76" s="28" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L76" s="9"/>
     </row>
@@ -4427,7 +4424,7 @@
         <v>137</v>
       </c>
       <c r="G77" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H77" s="11" t="s">
         <v>85</v>
@@ -4436,10 +4433,10 @@
         <v>27</v>
       </c>
       <c r="J77" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="K77" s="28" t="s">
         <v>310</v>
-      </c>
-      <c r="K77" s="28" t="s">
-        <v>311</v>
       </c>
       <c r="L77" s="9"/>
     </row>
@@ -4451,19 +4448,19 @@
         <v>12</v>
       </c>
       <c r="C78" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="D78" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="D78" s="11" t="s">
+      <c r="E78" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="F78" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="E78" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="F78" s="11" t="s">
+      <c r="G78" s="11" t="s">
         <v>314</v>
-      </c>
-      <c r="G78" s="11" t="s">
-        <v>315</v>
       </c>
       <c r="H78" s="11" t="s">
         <v>18</v>
@@ -4472,10 +4469,10 @@
         <v>27</v>
       </c>
       <c r="J78" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="K78" s="22" t="s">
         <v>316</v>
-      </c>
-      <c r="K78" s="22" t="s">
-        <v>317</v>
       </c>
       <c r="L78" s="9"/>
     </row>
@@ -4499,7 +4496,7 @@
         <v>130</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H79" s="11" t="s">
         <v>85</v>
@@ -4508,10 +4505,10 @@
         <v>27</v>
       </c>
       <c r="J79" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="K79" s="28" t="s">
         <v>318</v>
-      </c>
-      <c r="K79" s="28" t="s">
-        <v>319</v>
       </c>
       <c r="L79" s="9"/>
     </row>
@@ -4523,7 +4520,7 @@
         <v>21</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D80" s="11" t="s">
         <v>75</v>
@@ -4535,7 +4532,7 @@
         <v>103</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H80" s="11" t="s">
         <v>85</v>
@@ -4544,10 +4541,10 @@
         <v>27</v>
       </c>
       <c r="J80" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="K80" s="28" t="s">
         <v>322</v>
-      </c>
-      <c r="K80" s="28" t="s">
-        <v>323</v>
       </c>
       <c r="L80" s="9"/>
     </row>
@@ -4571,7 +4568,7 @@
         <v>103</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H81" s="11" t="s">
         <v>18</v>
@@ -4580,7 +4577,7 @@
         <v>27</v>
       </c>
       <c r="J81" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L81" s="9"/>
     </row>
@@ -4592,19 +4589,19 @@
         <v>21</v>
       </c>
       <c r="C82" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="D82" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="D82" s="11" t="s">
+      <c r="E82" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="E82" s="19" t="s">
+      <c r="F82" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="F82" s="11" t="s">
-        <v>329</v>
-      </c>
       <c r="G82" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H82" s="11" t="s">
         <v>85</v>
@@ -4613,10 +4610,10 @@
         <v>27</v>
       </c>
       <c r="J82" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="K82" s="28" t="s">
         <v>330</v>
-      </c>
-      <c r="K82" s="28" t="s">
-        <v>331</v>
       </c>
       <c r="L82" s="9"/>
     </row>
@@ -4628,7 +4625,7 @@
         <v>29</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D83" s="11" t="s">
         <v>75</v>
@@ -4637,7 +4634,7 @@
         <v>76</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G83" s="13" t="s">
         <v>164</v>
@@ -4649,13 +4646,13 @@
         <v>27</v>
       </c>
       <c r="J83" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="K83" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="L83" s="23" t="s">
         <v>333</v>
-      </c>
-      <c r="K83" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="L83" s="23" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
@@ -4678,7 +4675,7 @@
         <v>141</v>
       </c>
       <c r="G84" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H84" s="11" t="s">
         <v>85</v>
@@ -4687,10 +4684,10 @@
         <v>27</v>
       </c>
       <c r="J84" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="K84" s="28" t="s">
         <v>335</v>
-      </c>
-      <c r="K84" s="28" t="s">
-        <v>336</v>
       </c>
       <c r="L84" s="9"/>
     </row>
@@ -4702,16 +4699,16 @@
         <v>21</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E85" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G85" s="13" t="s">
         <v>164</v>
@@ -4723,10 +4720,10 @@
         <v>27</v>
       </c>
       <c r="J85" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="K85" s="28" t="s">
         <v>337</v>
-      </c>
-      <c r="K85" s="28" t="s">
-        <v>338</v>
       </c>
       <c r="L85" s="7"/>
     </row>
@@ -4738,19 +4735,19 @@
         <v>12</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D86" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="E86" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="E86" s="19" t="s">
+      <c r="F86" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="F86" s="11" t="s">
-        <v>341</v>
-      </c>
       <c r="G86" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H86" s="11" t="s">
         <v>85</v>
@@ -4759,10 +4756,10 @@
         <v>27</v>
       </c>
       <c r="J86" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="K86" s="28" t="s">
         <v>342</v>
-      </c>
-      <c r="K86" s="28" t="s">
-        <v>343</v>
       </c>
       <c r="L86" s="9"/>
     </row>
@@ -4774,16 +4771,16 @@
         <v>37</v>
       </c>
       <c r="C87" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="D87" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="D87" s="11" t="s">
+      <c r="E87" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="F87" s="11" t="s">
         <v>345</v>
-      </c>
-      <c r="E87" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="F87" s="11" t="s">
-        <v>346</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>164</v>
@@ -4795,13 +4792,13 @@
         <v>27</v>
       </c>
       <c r="J87" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="K87" s="28" t="s">
         <v>347</v>
       </c>
-      <c r="K87" s="28" t="s">
+      <c r="L87" s="7" t="s">
         <v>348</v>
-      </c>
-      <c r="L87" s="7" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
@@ -4812,19 +4809,19 @@
         <v>62</v>
       </c>
       <c r="C88" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="F88" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="D88" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="E88" s="19" t="s">
-        <v>280</v>
-      </c>
-      <c r="F88" s="11" t="s">
-        <v>351</v>
-      </c>
       <c r="G88" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H88" s="11" t="s">
         <v>85</v>
@@ -4833,7 +4830,7 @@
         <v>27</v>
       </c>
       <c r="J88" s="21" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L88" s="9"/>
     </row>
@@ -4845,7 +4842,7 @@
         <v>21</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D89" s="11" t="s">
         <v>75</v>
@@ -4857,7 +4854,7 @@
         <v>150</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H89" s="11" t="s">
         <v>85</v>
@@ -4866,10 +4863,10 @@
         <v>27</v>
       </c>
       <c r="J89" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="K89" s="9" t="s">
         <v>354</v>
-      </c>
-      <c r="K89" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="L89" s="9"/>
     </row>
@@ -4881,7 +4878,7 @@
         <v>37</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>75</v>
@@ -4902,10 +4899,10 @@
         <v>27</v>
       </c>
       <c r="J90" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="K90" s="28" t="s">
         <v>357</v>
-      </c>
-      <c r="K90" s="28" t="s">
-        <v>358</v>
       </c>
       <c r="L90" s="9"/>
     </row>
@@ -4917,7 +4914,7 @@
         <v>12</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D91" s="11" t="s">
         <v>129</v>
@@ -4929,7 +4926,7 @@
         <v>130</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H91" s="11" t="s">
         <v>18</v>
@@ -4938,10 +4935,10 @@
         <v>27</v>
       </c>
       <c r="J91" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="K91" s="28" t="s">
         <v>360</v>
-      </c>
-      <c r="K91" s="28" t="s">
-        <v>361</v>
       </c>
       <c r="L91" s="9"/>
     </row>
@@ -4962,10 +4959,10 @@
         <v>76</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H92" s="11" t="s">
         <v>85</v>
@@ -4974,10 +4971,10 @@
         <v>27</v>
       </c>
       <c r="J92" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="K92" s="28" t="s">
         <v>362</v>
-      </c>
-      <c r="K92" s="28" t="s">
-        <v>363</v>
       </c>
       <c r="L92" s="9"/>
     </row>
@@ -4992,13 +4989,13 @@
         <v>144</v>
       </c>
       <c r="D93" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="E93" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="E93" s="19" t="s">
+      <c r="F93" s="11" t="s">
         <v>280</v>
-      </c>
-      <c r="F93" s="11" t="s">
-        <v>281</v>
       </c>
       <c r="G93" s="13" t="s">
         <v>69</v>
@@ -5010,10 +5007,10 @@
         <v>27</v>
       </c>
       <c r="J93" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="K93" s="28" t="s">
         <v>362</v>
-      </c>
-      <c r="K93" s="28" t="s">
-        <v>363</v>
       </c>
       <c r="L93" s="9"/>
     </row>
@@ -5025,7 +5022,7 @@
         <v>12</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D94" s="11" t="s">
         <v>75</v>
@@ -5034,7 +5031,7 @@
         <v>76</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G94" s="13" t="s">
         <v>164</v>
@@ -5046,10 +5043,10 @@
         <v>27</v>
       </c>
       <c r="J94" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="K94" s="28" t="s">
         <v>366</v>
-      </c>
-      <c r="K94" s="28" t="s">
-        <v>367</v>
       </c>
       <c r="L94" s="9"/>
     </row>
@@ -5061,7 +5058,7 @@
         <v>21</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D95" s="11" t="s">
         <v>75</v>
@@ -5070,7 +5067,7 @@
         <v>76</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G95" s="13" t="s">
         <v>164</v>
@@ -5082,7 +5079,7 @@
         <v>27</v>
       </c>
       <c r="J95" s="21" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L95" s="21"/>
     </row>
@@ -5094,16 +5091,16 @@
         <v>37</v>
       </c>
       <c r="C96" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E96" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="F96" s="11" t="s">
         <v>369</v>
-      </c>
-      <c r="D96" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="E96" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="F96" s="11" t="s">
-        <v>370</v>
       </c>
       <c r="G96" s="13" t="s">
         <v>164</v>
@@ -5115,10 +5112,10 @@
         <v>27</v>
       </c>
       <c r="J96" s="29" t="s">
+        <v>370</v>
+      </c>
+      <c r="K96" s="28" t="s">
         <v>371</v>
-      </c>
-      <c r="K96" s="28" t="s">
-        <v>372</v>
       </c>
       <c r="L96" s="30"/>
     </row>
@@ -5130,16 +5127,16 @@
         <v>12</v>
       </c>
       <c r="C97" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E97" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="F97" s="11" t="s">
         <v>369</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="E97" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="F97" s="11" t="s">
-        <v>370</v>
       </c>
       <c r="G97" s="13" t="s">
         <v>164</v>
@@ -5151,10 +5148,10 @@
         <v>27</v>
       </c>
       <c r="J97" s="29" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K97" s="28" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L97" s="30"/>
     </row>
@@ -5166,16 +5163,16 @@
         <v>62</v>
       </c>
       <c r="C98" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E98" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="F98" s="11" t="s">
         <v>369</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="E98" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="F98" s="11" t="s">
-        <v>370</v>
       </c>
       <c r="G98" s="13" t="s">
         <v>164</v>
@@ -5187,10 +5184,10 @@
         <v>27</v>
       </c>
       <c r="J98" s="29" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K98" s="28" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L98" s="30"/>
     </row>
@@ -5202,16 +5199,16 @@
         <v>21</v>
       </c>
       <c r="C99" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="F99" s="11" t="s">
         <v>369</v>
-      </c>
-      <c r="D99" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="E99" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="F99" s="11" t="s">
-        <v>370</v>
       </c>
       <c r="G99" s="13" t="s">
         <v>164</v>
@@ -5223,10 +5220,10 @@
         <v>27</v>
       </c>
       <c r="J99" s="29" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K99" s="28" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L99" s="30"/>
     </row>
@@ -5238,7 +5235,7 @@
         <v>89</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D100" s="11" t="s">
         <v>75</v>
@@ -5247,10 +5244,10 @@
         <v>76</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H100" s="11" t="s">
         <v>85</v>
@@ -5259,10 +5256,10 @@
         <v>27</v>
       </c>
       <c r="J100" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="K100" s="21" t="s">
         <v>376</v>
-      </c>
-      <c r="K100" s="21" t="s">
-        <v>377</v>
       </c>
       <c r="L100" s="9"/>
     </row>
@@ -5274,7 +5271,7 @@
         <v>29</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D101" s="11" t="s">
         <v>75</v>
@@ -5295,10 +5292,10 @@
         <v>27</v>
       </c>
       <c r="J101" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="K101" s="21" t="s">
         <v>378</v>
-      </c>
-      <c r="K101" s="21" t="s">
-        <v>379</v>
       </c>
       <c r="L101" s="9"/>
     </row>
@@ -5310,7 +5307,7 @@
         <v>54</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D102" s="11" t="s">
         <v>75</v>
@@ -5331,13 +5328,13 @@
         <v>27</v>
       </c>
       <c r="J102" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="K102" s="22" t="s">
         <v>380</v>
       </c>
-      <c r="K102" s="22" t="s">
+      <c r="L102" s="23" t="s">
         <v>381</v>
-      </c>
-      <c r="L102" s="23" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
@@ -5348,7 +5345,7 @@
         <v>89</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D103" s="11" t="s">
         <v>75</v>
@@ -5357,7 +5354,7 @@
         <v>76</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G103" s="13" t="s">
         <v>164</v>
@@ -5369,10 +5366,10 @@
         <v>27</v>
       </c>
       <c r="J103" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="K103" s="21" t="s">
         <v>384</v>
-      </c>
-      <c r="K103" s="21" t="s">
-        <v>385</v>
       </c>
       <c r="L103" s="9"/>
     </row>
@@ -5384,7 +5381,7 @@
         <v>54</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>140</v>
@@ -5393,10 +5390,10 @@
         <v>76</v>
       </c>
       <c r="F104" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H104" s="9" t="s">
         <v>18</v>
@@ -5405,7 +5402,7 @@
         <v>27</v>
       </c>
       <c r="J104" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K104" s="9" t="s">
         <v>71</v>
@@ -5420,7 +5417,7 @@
         <v>29</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D105" s="11" t="s">
         <v>75</v>
@@ -5429,10 +5426,10 @@
         <v>76</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G105" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H105" s="11" t="s">
         <v>85</v>
@@ -5441,10 +5438,10 @@
         <v>27</v>
       </c>
       <c r="J105" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="K105" s="21" t="s">
         <v>389</v>
-      </c>
-      <c r="K105" s="21" t="s">
-        <v>390</v>
       </c>
       <c r="L105" s="9"/>
     </row>
@@ -5456,7 +5453,7 @@
         <v>29</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D106" s="11" t="s">
         <v>75</v>
@@ -5465,7 +5462,7 @@
         <v>76</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G106" s="13" t="s">
         <v>164</v>
@@ -5477,10 +5474,10 @@
         <v>27</v>
       </c>
       <c r="J106" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="K106" s="22" t="s">
         <v>391</v>
-      </c>
-      <c r="K106" s="22" t="s">
-        <v>392</v>
       </c>
       <c r="L106" s="9"/>
     </row>
@@ -5492,7 +5489,7 @@
         <v>62</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D107" s="11" t="s">
         <v>140</v>
@@ -5501,10 +5498,10 @@
         <v>76</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G107" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H107" s="11" t="s">
         <v>85</v>
@@ -5513,10 +5510,10 @@
         <v>27</v>
       </c>
       <c r="J107" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K107" s="21" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L107" s="9"/>
     </row>
@@ -5528,7 +5525,7 @@
         <v>29</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D108" s="11" t="s">
         <v>75</v>
@@ -5537,10 +5534,10 @@
         <v>76</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H108" s="11" t="s">
         <v>18</v>
@@ -5549,7 +5546,7 @@
         <v>27</v>
       </c>
       <c r="J108" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K108" s="9"/>
       <c r="L108" s="9"/>
@@ -5562,7 +5559,7 @@
         <v>29</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D109" s="11" t="s">
         <v>129</v>
@@ -5583,7 +5580,7 @@
         <v>27</v>
       </c>
       <c r="J109" s="21" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K109" s="9"/>
       <c r="L109" s="9"/>
@@ -5596,7 +5593,7 @@
         <v>37</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D110" s="11" t="s">
         <v>75</v>
@@ -5605,10 +5602,10 @@
         <v>76</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G110" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H110" s="11" t="s">
         <v>18</v>
@@ -5617,10 +5614,10 @@
         <v>27</v>
       </c>
       <c r="J110" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="K110" s="21" t="s">
         <v>399</v>
-      </c>
-      <c r="K110" s="21" t="s">
-        <v>400</v>
       </c>
       <c r="L110" s="9"/>
     </row>
@@ -5635,16 +5632,16 @@
         <v>30</v>
       </c>
       <c r="D111" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="E111" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="E111" s="19" t="s">
+      <c r="F111" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="F111" s="11" t="s">
-        <v>341</v>
-      </c>
       <c r="G111" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H111" s="11" t="s">
         <v>85</v>
@@ -5653,10 +5650,10 @@
         <v>27</v>
       </c>
       <c r="J111" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="K111" s="21" t="s">
         <v>401</v>
-      </c>
-      <c r="K111" s="21" t="s">
-        <v>402</v>
       </c>
       <c r="L111" s="9"/>
     </row>
@@ -5677,10 +5674,10 @@
         <v>76</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G112" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H112" s="11" t="s">
         <v>85</v>
@@ -5689,10 +5686,10 @@
         <v>27</v>
       </c>
       <c r="J112" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="K112" s="21" t="s">
         <v>403</v>
-      </c>
-      <c r="K112" s="21" t="s">
-        <v>404</v>
       </c>
       <c r="L112" s="9"/>
     </row>
@@ -5704,7 +5701,7 @@
         <v>37</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>75</v>
@@ -5713,7 +5710,7 @@
         <v>76</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G113" s="13" t="s">
         <v>69</v>
@@ -5725,10 +5722,10 @@
         <v>27</v>
       </c>
       <c r="J113" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="K113" s="22" t="s">
         <v>406</v>
-      </c>
-      <c r="K113" s="22" t="s">
-        <v>407</v>
       </c>
       <c r="L113" s="9"/>
     </row>
@@ -5740,7 +5737,7 @@
         <v>62</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D114" s="11" t="s">
         <v>75</v>
@@ -5749,10 +5746,10 @@
         <v>76</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G114" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H114" s="11" t="s">
         <v>18</v>
@@ -5761,13 +5758,13 @@
         <v>27</v>
       </c>
       <c r="J114" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="K114" s="22" t="s">
         <v>409</v>
       </c>
-      <c r="K114" s="22" t="s">
+      <c r="L114" s="23" t="s">
         <v>410</v>
-      </c>
-      <c r="L114" s="23" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
@@ -5790,7 +5787,7 @@
         <v>150</v>
       </c>
       <c r="G115" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H115" s="11" t="s">
         <v>18</v>
@@ -5799,10 +5796,10 @@
         <v>27</v>
       </c>
       <c r="J115" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="K115" s="21" t="s">
         <v>412</v>
-      </c>
-      <c r="K115" s="21" t="s">
-        <v>413</v>
       </c>
       <c r="L115" s="9"/>
     </row>
@@ -5823,7 +5820,7 @@
         <v>76</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G116" s="13" t="s">
         <v>164</v>
@@ -5835,10 +5832,10 @@
         <v>27</v>
       </c>
       <c r="J116" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="K116" s="9" t="s">
         <v>403</v>
-      </c>
-      <c r="K116" s="9" t="s">
-        <v>404</v>
       </c>
       <c r="L116" s="9"/>
     </row>
@@ -5850,16 +5847,16 @@
         <v>62</v>
       </c>
       <c r="C117" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="E117" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="F117" s="11" t="s">
         <v>414</v>
-      </c>
-      <c r="D117" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="E117" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="F117" s="11" t="s">
-        <v>415</v>
       </c>
       <c r="G117" s="13" t="s">
         <v>164</v>
@@ -5871,10 +5868,10 @@
         <v>27</v>
       </c>
       <c r="J117" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="K117" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="K117" s="9" t="s">
-        <v>417</v>
       </c>
       <c r="L117" s="9"/>
     </row>
@@ -5886,7 +5883,7 @@
         <v>54</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D118" s="11" t="s">
         <v>75</v>
@@ -5895,10 +5892,10 @@
         <v>76</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G118" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H118" s="11" t="s">
         <v>18</v>
@@ -5907,10 +5904,10 @@
         <v>27</v>
       </c>
       <c r="J118" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="K118" s="21" t="s">
         <v>419</v>
-      </c>
-      <c r="K118" s="21" t="s">
-        <v>420</v>
       </c>
       <c r="L118" s="9"/>
     </row>
@@ -5943,7 +5940,7 @@
         <v>27</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="K119" s="9"/>
       <c r="L119" s="9"/>
@@ -5968,7 +5965,7 @@
         <v>130</v>
       </c>
       <c r="G120" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H120" s="11" t="s">
         <v>85</v>
@@ -5977,10 +5974,10 @@
         <v>27</v>
       </c>
       <c r="J120" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="K120" s="7" t="s">
         <v>422</v>
-      </c>
-      <c r="K120" s="7" t="s">
-        <v>423</v>
       </c>
       <c r="L120" s="9"/>
     </row>
@@ -5992,7 +5989,7 @@
         <v>12</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D121" s="9" t="s">
         <v>162</v>
@@ -6001,7 +5998,7 @@
         <v>76</v>
       </c>
       <c r="F121" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G121" s="7" t="s">
         <v>164</v>
@@ -6013,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="K121" s="9"/>
       <c r="L121" s="9"/>

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="425">
   <si>
     <t>Date</t>
   </si>
@@ -582,10 +582,7 @@
     <t>In This Moment</t>
   </si>
   <si>
-    <t>Half God, Half Devil Tour</t>
-  </si>
-  <si>
-    <t>Motionless In White, Avatar, Gemini Syndrome</t>
+    <t xml:space="preserve">The Hellpop Tour 2016 </t>
   </si>
   <si>
     <t>Ed Brown</t>
@@ -3030,8 +3027,8 @@
       <c r="L37" s="9"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="10">
-        <v>42932.0</v>
+      <c r="A38" s="6">
+        <v>42557.0</v>
       </c>
       <c r="B38" s="18" t="s">
         <v>21</v>
@@ -3057,11 +3054,11 @@
       <c r="I38" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J38" s="21" t="s">
+      <c r="J38" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="K38" s="21" t="s">
-        <v>190</v>
+      <c r="K38" s="22" t="s">
+        <v>169</v>
       </c>
       <c r="L38" s="9"/>
     </row>
@@ -3085,7 +3082,7 @@
         <v>137</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>18</v>
@@ -3094,10 +3091,10 @@
         <v>27</v>
       </c>
       <c r="J39" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="K39" s="21" t="s">
         <v>192</v>
-      </c>
-      <c r="K39" s="21" t="s">
-        <v>193</v>
       </c>
       <c r="L39" s="9"/>
     </row>
@@ -3112,16 +3109,16 @@
         <v>55</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F40" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="G40" s="13" t="s">
         <v>195</v>
-      </c>
-      <c r="G40" s="13" t="s">
-        <v>196</v>
       </c>
       <c r="H40" s="11" t="s">
         <v>85</v>
@@ -3130,13 +3127,13 @@
         <v>27</v>
       </c>
       <c r="J40" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="K40" s="22" t="s">
         <v>197</v>
       </c>
-      <c r="K40" s="22" t="s">
+      <c r="L40" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="L40" s="9" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -3156,10 +3153,10 @@
         <v>57</v>
       </c>
       <c r="F41" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G41" s="13" t="s">
         <v>200</v>
-      </c>
-      <c r="G41" s="13" t="s">
-        <v>201</v>
       </c>
       <c r="H41" s="11" t="s">
         <v>85</v>
@@ -3168,7 +3165,7 @@
         <v>27</v>
       </c>
       <c r="J41" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K41" s="9"/>
       <c r="L41" s="9"/>
@@ -3184,13 +3181,13 @@
         <v>107</v>
       </c>
       <c r="D42" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E42" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="F42" s="11" t="s">
         <v>204</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>205</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>17</v>
@@ -3202,13 +3199,13 @@
         <v>27</v>
       </c>
       <c r="J42" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="K42" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="K42" s="21" t="s">
+      <c r="L42" s="9" t="s">
         <v>207</v>
-      </c>
-      <c r="L42" s="9" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -3219,7 +3216,7 @@
         <v>29</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>75</v>
@@ -3231,7 +3228,7 @@
         <v>103</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H43" s="11" t="s">
         <v>18</v>
@@ -3240,7 +3237,7 @@
         <v>27</v>
       </c>
       <c r="J43" s="21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
@@ -3253,19 +3250,19 @@
         <v>12</v>
       </c>
       <c r="C44" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="D44" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="E44" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="E44" s="19" t="s">
+      <c r="F44" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="G44" s="13" t="s">
         <v>215</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>216</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>85</v>
@@ -3274,13 +3271,13 @@
         <v>27</v>
       </c>
       <c r="J44" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="K44" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="K44" s="28" t="s">
+      <c r="L44" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="L44" s="7" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
@@ -3291,19 +3288,19 @@
         <v>62</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D45" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E45" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="E45" s="19" t="s">
+      <c r="F45" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="G45" s="13" t="s">
         <v>215</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>216</v>
       </c>
       <c r="H45" s="11" t="s">
         <v>85</v>
@@ -3312,13 +3309,13 @@
         <v>27</v>
       </c>
       <c r="J45" s="22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K45" s="28" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
@@ -3329,19 +3326,19 @@
         <v>21</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D46" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E46" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="F46" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="G46" s="13" t="s">
         <v>215</v>
-      </c>
-      <c r="G46" s="13" t="s">
-        <v>216</v>
       </c>
       <c r="H46" s="11" t="s">
         <v>85</v>
@@ -3350,13 +3347,13 @@
         <v>27</v>
       </c>
       <c r="J46" s="22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K46" s="28" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -3367,7 +3364,7 @@
         <v>29</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>75</v>
@@ -3388,13 +3385,13 @@
         <v>27</v>
       </c>
       <c r="J47" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="K47" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="K47" s="28" t="s">
+      <c r="L47" s="23" t="s">
         <v>226</v>
-      </c>
-      <c r="L47" s="23" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
@@ -3405,7 +3402,7 @@
         <v>12</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>75</v>
@@ -3414,7 +3411,7 @@
         <v>76</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G48" s="13" t="s">
         <v>164</v>
@@ -3426,7 +3423,7 @@
         <v>27</v>
       </c>
       <c r="J48" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L48" s="9"/>
     </row>
@@ -3438,7 +3435,7 @@
         <v>29</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>56</v>
@@ -3450,7 +3447,7 @@
         <v>96</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H49" s="11" t="s">
         <v>85</v>
@@ -3459,7 +3456,7 @@
         <v>27</v>
       </c>
       <c r="J49" s="21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L49" s="9"/>
     </row>
@@ -3483,7 +3480,7 @@
         <v>145</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H50" s="11" t="s">
         <v>85</v>
@@ -3492,10 +3489,10 @@
         <v>27</v>
       </c>
       <c r="J50" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="K50" s="28" t="s">
         <v>235</v>
-      </c>
-      <c r="K50" s="28" t="s">
-        <v>236</v>
       </c>
       <c r="L50" s="9"/>
     </row>
@@ -3507,7 +3504,7 @@
         <v>21</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>75</v>
@@ -3528,7 +3525,7 @@
         <v>27</v>
       </c>
       <c r="J51" s="21" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L51" s="9"/>
     </row>
@@ -3573,7 +3570,7 @@
         <v>29</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>75</v>
@@ -3585,7 +3582,7 @@
         <v>103</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H53" s="11" t="s">
         <v>18</v>
@@ -3594,7 +3591,7 @@
         <v>27</v>
       </c>
       <c r="J53" s="21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L53" s="9"/>
     </row>
@@ -3606,7 +3603,7 @@
         <v>62</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D54" s="11" t="s">
         <v>75</v>
@@ -3627,7 +3624,7 @@
         <v>27</v>
       </c>
       <c r="J54" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L54" s="9"/>
     </row>
@@ -3639,19 +3636,19 @@
         <v>12</v>
       </c>
       <c r="C55" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="D55" s="11" t="s">
         <v>244</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>245</v>
       </c>
       <c r="E55" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F55" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="G55" s="13" t="s">
         <v>246</v>
-      </c>
-      <c r="G55" s="13" t="s">
-        <v>247</v>
       </c>
       <c r="H55" s="11" t="s">
         <v>85</v>
@@ -3660,10 +3657,10 @@
         <v>27</v>
       </c>
       <c r="J55" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="K55" s="28" t="s">
         <v>248</v>
-      </c>
-      <c r="K55" s="28" t="s">
-        <v>249</v>
       </c>
       <c r="L55" s="9"/>
     </row>
@@ -3675,19 +3672,19 @@
         <v>62</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E56" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F56" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="G56" s="13" t="s">
         <v>246</v>
-      </c>
-      <c r="G56" s="13" t="s">
-        <v>247</v>
       </c>
       <c r="H56" s="13" t="s">
         <v>85</v>
@@ -3696,13 +3693,13 @@
         <v>27</v>
       </c>
       <c r="J56" s="22" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K56" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="L56" s="7" t="s">
         <v>251</v>
-      </c>
-      <c r="L56" s="7" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
@@ -3713,19 +3710,19 @@
         <v>21</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E57" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F57" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="G57" s="13" t="s">
         <v>246</v>
-      </c>
-      <c r="G57" s="13" t="s">
-        <v>247</v>
       </c>
       <c r="H57" s="13" t="s">
         <v>85</v>
@@ -3734,10 +3731,10 @@
         <v>27</v>
       </c>
       <c r="J57" s="22" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K57" s="28" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L57" s="9"/>
     </row>
@@ -3749,7 +3746,7 @@
         <v>37</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>75</v>
@@ -3770,7 +3767,7 @@
         <v>27</v>
       </c>
       <c r="J58" s="21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L58" s="9"/>
     </row>
@@ -3782,19 +3779,19 @@
         <v>29</v>
       </c>
       <c r="C59" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="D59" s="11" t="s">
         <v>257</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>258</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>183</v>
       </c>
       <c r="F59" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="G59" s="13" t="s">
         <v>259</v>
-      </c>
-      <c r="G59" s="13" t="s">
-        <v>260</v>
       </c>
       <c r="H59" s="11" t="s">
         <v>18</v>
@@ -3803,7 +3800,7 @@
         <v>27</v>
       </c>
       <c r="J59" s="21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L59" s="9"/>
     </row>
@@ -3815,7 +3812,7 @@
         <v>21</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>75</v>
@@ -3824,10 +3821,10 @@
         <v>76</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H60" s="11" t="s">
         <v>18</v>
@@ -3836,10 +3833,10 @@
         <v>27</v>
       </c>
       <c r="J60" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="K60" s="28" t="s">
         <v>264</v>
-      </c>
-      <c r="K60" s="28" t="s">
-        <v>265</v>
       </c>
       <c r="L60" s="9"/>
     </row>
@@ -3851,19 +3848,19 @@
         <v>37</v>
       </c>
       <c r="C61" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="D61" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="E61" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="E61" s="19" t="s">
+      <c r="F61" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="G61" s="13" t="s">
         <v>269</v>
-      </c>
-      <c r="G61" s="13" t="s">
-        <v>270</v>
       </c>
       <c r="H61" s="11" t="s">
         <v>18</v>
@@ -3872,7 +3869,7 @@
         <v>27</v>
       </c>
       <c r="J61" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L61" s="9"/>
     </row>
@@ -3893,7 +3890,7 @@
         <v>76</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G62" s="13" t="s">
         <v>164</v>
@@ -3905,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="J62" s="21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L62" s="9"/>
     </row>
@@ -3926,10 +3923,10 @@
         <v>45</v>
       </c>
       <c r="F63" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="G63" s="13" t="s">
         <v>273</v>
-      </c>
-      <c r="G63" s="13" t="s">
-        <v>274</v>
       </c>
       <c r="H63" s="11" t="s">
         <v>85</v>
@@ -3938,10 +3935,10 @@
         <v>27</v>
       </c>
       <c r="J63" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="K63" s="28" t="s">
         <v>275</v>
-      </c>
-      <c r="K63" s="28" t="s">
-        <v>276</v>
       </c>
       <c r="L63" s="9"/>
     </row>
@@ -3965,7 +3962,7 @@
         <v>103</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H64" s="11" t="s">
         <v>85</v>
@@ -3974,10 +3971,10 @@
         <v>27</v>
       </c>
       <c r="J64" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="K64" s="28" t="s">
         <v>275</v>
-      </c>
-      <c r="K64" s="28" t="s">
-        <v>276</v>
       </c>
       <c r="L64" s="9"/>
     </row>
@@ -3992,13 +3989,13 @@
         <v>144</v>
       </c>
       <c r="D65" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="E65" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="E65" s="19" t="s">
+      <c r="F65" s="11" t="s">
         <v>279</v>
-      </c>
-      <c r="F65" s="11" t="s">
-        <v>280</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>164</v>
@@ -4010,10 +4007,10 @@
         <v>27</v>
       </c>
       <c r="J65" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="K65" s="28" t="s">
         <v>275</v>
-      </c>
-      <c r="K65" s="28" t="s">
-        <v>276</v>
       </c>
       <c r="L65" s="9"/>
     </row>
@@ -4025,7 +4022,7 @@
         <v>62</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D66" s="11" t="s">
         <v>162</v>
@@ -4037,7 +4034,7 @@
         <v>163</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H66" s="11" t="s">
         <v>85</v>
@@ -4046,10 +4043,10 @@
         <v>27</v>
       </c>
       <c r="J66" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K66" s="28" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L66" s="9"/>
     </row>
@@ -4061,7 +4058,7 @@
         <v>62</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>75</v>
@@ -4070,7 +4067,7 @@
         <v>76</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>104</v>
@@ -4082,7 +4079,7 @@
         <v>27</v>
       </c>
       <c r="J67" s="21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L67" s="9"/>
     </row>
@@ -4115,7 +4112,7 @@
         <v>27</v>
       </c>
       <c r="J68" s="21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L68" s="9"/>
     </row>
@@ -4127,16 +4124,16 @@
         <v>37</v>
       </c>
       <c r="C69" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="D69" s="11" t="s">
         <v>286</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>287</v>
       </c>
       <c r="E69" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>164</v>
@@ -4148,10 +4145,10 @@
         <v>27</v>
       </c>
       <c r="J69" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="K69" s="28" t="s">
         <v>289</v>
-      </c>
-      <c r="K69" s="28" t="s">
-        <v>290</v>
       </c>
       <c r="L69" s="7"/>
     </row>
@@ -4163,16 +4160,16 @@
         <v>12</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E70" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>164</v>
@@ -4184,10 +4181,10 @@
         <v>27</v>
       </c>
       <c r="J70" s="22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K70" s="28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L70" s="7"/>
     </row>
@@ -4199,16 +4196,16 @@
         <v>62</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E71" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>164</v>
@@ -4220,10 +4217,10 @@
         <v>27</v>
       </c>
       <c r="J71" s="22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K71" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L71" s="7"/>
     </row>
@@ -4235,16 +4232,16 @@
         <v>21</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E72" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>164</v>
@@ -4256,10 +4253,10 @@
         <v>27</v>
       </c>
       <c r="J72" s="22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K72" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L72" s="7"/>
     </row>
@@ -4271,7 +4268,7 @@
         <v>12</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>75</v>
@@ -4283,7 +4280,7 @@
         <v>103</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H73" s="11" t="s">
         <v>85</v>
@@ -4292,7 +4289,7 @@
         <v>27</v>
       </c>
       <c r="J73" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L73" s="9"/>
     </row>
@@ -4307,16 +4304,16 @@
         <v>144</v>
       </c>
       <c r="D74" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="E74" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="E74" s="19" t="s">
+      <c r="F74" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="F74" s="11" t="s">
-        <v>302</v>
-      </c>
       <c r="G74" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H74" s="11" t="s">
         <v>85</v>
@@ -4325,10 +4322,10 @@
         <v>27</v>
       </c>
       <c r="J74" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K74" s="28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L74" s="9"/>
     </row>
@@ -4340,7 +4337,7 @@
         <v>12</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D75" s="11" t="s">
         <v>162</v>
@@ -4352,7 +4349,7 @@
         <v>163</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H75" s="11" t="s">
         <v>18</v>
@@ -4361,10 +4358,10 @@
         <v>27</v>
       </c>
       <c r="J75" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="K75" s="28" t="s">
         <v>305</v>
-      </c>
-      <c r="K75" s="28" t="s">
-        <v>306</v>
       </c>
       <c r="L75" s="9"/>
     </row>
@@ -4379,16 +4376,16 @@
         <v>144</v>
       </c>
       <c r="D76" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="F76" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="E76" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="F76" s="11" t="s">
-        <v>308</v>
-      </c>
       <c r="G76" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H76" s="11" t="s">
         <v>85</v>
@@ -4397,10 +4394,10 @@
         <v>27</v>
       </c>
       <c r="J76" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K76" s="28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L76" s="9"/>
     </row>
@@ -4424,7 +4421,7 @@
         <v>137</v>
       </c>
       <c r="G77" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H77" s="11" t="s">
         <v>85</v>
@@ -4433,10 +4430,10 @@
         <v>27</v>
       </c>
       <c r="J77" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="K77" s="28" t="s">
         <v>309</v>
-      </c>
-      <c r="K77" s="28" t="s">
-        <v>310</v>
       </c>
       <c r="L77" s="9"/>
     </row>
@@ -4448,19 +4445,19 @@
         <v>12</v>
       </c>
       <c r="C78" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="D78" s="11" t="s">
         <v>311</v>
-      </c>
-      <c r="D78" s="11" t="s">
-        <v>312</v>
       </c>
       <c r="E78" s="19" t="s">
         <v>183</v>
       </c>
       <c r="F78" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="G78" s="11" t="s">
         <v>313</v>
-      </c>
-      <c r="G78" s="11" t="s">
-        <v>314</v>
       </c>
       <c r="H78" s="11" t="s">
         <v>18</v>
@@ -4469,10 +4466,10 @@
         <v>27</v>
       </c>
       <c r="J78" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="K78" s="22" t="s">
         <v>315</v>
-      </c>
-      <c r="K78" s="22" t="s">
-        <v>316</v>
       </c>
       <c r="L78" s="9"/>
     </row>
@@ -4496,7 +4493,7 @@
         <v>130</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H79" s="11" t="s">
         <v>85</v>
@@ -4505,10 +4502,10 @@
         <v>27</v>
       </c>
       <c r="J79" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="K79" s="28" t="s">
         <v>317</v>
-      </c>
-      <c r="K79" s="28" t="s">
-        <v>318</v>
       </c>
       <c r="L79" s="9"/>
     </row>
@@ -4520,7 +4517,7 @@
         <v>21</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D80" s="11" t="s">
         <v>75</v>
@@ -4532,7 +4529,7 @@
         <v>103</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H80" s="11" t="s">
         <v>85</v>
@@ -4541,10 +4538,10 @@
         <v>27</v>
       </c>
       <c r="J80" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="K80" s="28" t="s">
         <v>321</v>
-      </c>
-      <c r="K80" s="28" t="s">
-        <v>322</v>
       </c>
       <c r="L80" s="9"/>
     </row>
@@ -4568,7 +4565,7 @@
         <v>103</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H81" s="11" t="s">
         <v>18</v>
@@ -4577,7 +4574,7 @@
         <v>27</v>
       </c>
       <c r="J81" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L81" s="9"/>
     </row>
@@ -4589,19 +4586,19 @@
         <v>21</v>
       </c>
       <c r="C82" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="D82" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="D82" s="11" t="s">
+      <c r="E82" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="E82" s="19" t="s">
+      <c r="F82" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="F82" s="11" t="s">
-        <v>328</v>
-      </c>
       <c r="G82" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H82" s="11" t="s">
         <v>85</v>
@@ -4610,10 +4607,10 @@
         <v>27</v>
       </c>
       <c r="J82" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="K82" s="28" t="s">
         <v>329</v>
-      </c>
-      <c r="K82" s="28" t="s">
-        <v>330</v>
       </c>
       <c r="L82" s="9"/>
     </row>
@@ -4625,7 +4622,7 @@
         <v>29</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D83" s="11" t="s">
         <v>75</v>
@@ -4634,7 +4631,7 @@
         <v>76</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G83" s="13" t="s">
         <v>164</v>
@@ -4646,13 +4643,13 @@
         <v>27</v>
       </c>
       <c r="J83" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="K83" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="L83" s="23" t="s">
         <v>332</v>
-      </c>
-      <c r="K83" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="L83" s="23" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
@@ -4675,7 +4672,7 @@
         <v>141</v>
       </c>
       <c r="G84" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H84" s="11" t="s">
         <v>85</v>
@@ -4684,10 +4681,10 @@
         <v>27</v>
       </c>
       <c r="J84" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="K84" s="28" t="s">
         <v>334</v>
-      </c>
-      <c r="K84" s="28" t="s">
-        <v>335</v>
       </c>
       <c r="L84" s="9"/>
     </row>
@@ -4699,16 +4696,16 @@
         <v>21</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E85" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G85" s="13" t="s">
         <v>164</v>
@@ -4720,10 +4717,10 @@
         <v>27</v>
       </c>
       <c r="J85" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="K85" s="28" t="s">
         <v>336</v>
-      </c>
-      <c r="K85" s="28" t="s">
-        <v>337</v>
       </c>
       <c r="L85" s="7"/>
     </row>
@@ -4738,16 +4735,16 @@
         <v>178</v>
       </c>
       <c r="D86" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="E86" s="19" t="s">
         <v>338</v>
       </c>
-      <c r="E86" s="19" t="s">
+      <c r="F86" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="F86" s="11" t="s">
-        <v>340</v>
-      </c>
       <c r="G86" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H86" s="11" t="s">
         <v>85</v>
@@ -4756,10 +4753,10 @@
         <v>27</v>
       </c>
       <c r="J86" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="K86" s="28" t="s">
         <v>341</v>
-      </c>
-      <c r="K86" s="28" t="s">
-        <v>342</v>
       </c>
       <c r="L86" s="9"/>
     </row>
@@ -4771,16 +4768,16 @@
         <v>37</v>
       </c>
       <c r="C87" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="D87" s="11" t="s">
         <v>343</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>344</v>
       </c>
       <c r="E87" s="19" t="s">
         <v>183</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>164</v>
@@ -4792,13 +4789,13 @@
         <v>27</v>
       </c>
       <c r="J87" s="22" t="s">
+        <v>345</v>
+      </c>
+      <c r="K87" s="28" t="s">
         <v>346</v>
       </c>
-      <c r="K87" s="28" t="s">
+      <c r="L87" s="7" t="s">
         <v>347</v>
-      </c>
-      <c r="L87" s="7" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
@@ -4809,19 +4806,19 @@
         <v>62</v>
       </c>
       <c r="C88" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="F88" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="D88" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="E88" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="F88" s="11" t="s">
-        <v>350</v>
-      </c>
       <c r="G88" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H88" s="11" t="s">
         <v>85</v>
@@ -4830,7 +4827,7 @@
         <v>27</v>
       </c>
       <c r="J88" s="21" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L88" s="9"/>
     </row>
@@ -4842,7 +4839,7 @@
         <v>21</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D89" s="11" t="s">
         <v>75</v>
@@ -4854,7 +4851,7 @@
         <v>150</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H89" s="11" t="s">
         <v>85</v>
@@ -4863,10 +4860,10 @@
         <v>27</v>
       </c>
       <c r="J89" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="K89" s="9" t="s">
         <v>353</v>
-      </c>
-      <c r="K89" s="9" t="s">
-        <v>354</v>
       </c>
       <c r="L89" s="9"/>
     </row>
@@ -4878,7 +4875,7 @@
         <v>37</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>75</v>
@@ -4899,10 +4896,10 @@
         <v>27</v>
       </c>
       <c r="J90" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="K90" s="28" t="s">
         <v>356</v>
-      </c>
-      <c r="K90" s="28" t="s">
-        <v>357</v>
       </c>
       <c r="L90" s="9"/>
     </row>
@@ -4914,7 +4911,7 @@
         <v>12</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D91" s="11" t="s">
         <v>129</v>
@@ -4926,7 +4923,7 @@
         <v>130</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H91" s="11" t="s">
         <v>18</v>
@@ -4935,10 +4932,10 @@
         <v>27</v>
       </c>
       <c r="J91" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="K91" s="28" t="s">
         <v>359</v>
-      </c>
-      <c r="K91" s="28" t="s">
-        <v>360</v>
       </c>
       <c r="L91" s="9"/>
     </row>
@@ -4959,10 +4956,10 @@
         <v>76</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H92" s="11" t="s">
         <v>85</v>
@@ -4971,10 +4968,10 @@
         <v>27</v>
       </c>
       <c r="J92" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="K92" s="28" t="s">
         <v>361</v>
-      </c>
-      <c r="K92" s="28" t="s">
-        <v>362</v>
       </c>
       <c r="L92" s="9"/>
     </row>
@@ -4989,13 +4986,13 @@
         <v>144</v>
       </c>
       <c r="D93" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="E93" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="E93" s="19" t="s">
+      <c r="F93" s="11" t="s">
         <v>279</v>
-      </c>
-      <c r="F93" s="11" t="s">
-        <v>280</v>
       </c>
       <c r="G93" s="13" t="s">
         <v>69</v>
@@ -5007,10 +5004,10 @@
         <v>27</v>
       </c>
       <c r="J93" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="K93" s="28" t="s">
         <v>361</v>
-      </c>
-      <c r="K93" s="28" t="s">
-        <v>362</v>
       </c>
       <c r="L93" s="9"/>
     </row>
@@ -5022,7 +5019,7 @@
         <v>12</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D94" s="11" t="s">
         <v>75</v>
@@ -5031,7 +5028,7 @@
         <v>76</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G94" s="13" t="s">
         <v>164</v>
@@ -5043,10 +5040,10 @@
         <v>27</v>
       </c>
       <c r="J94" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="K94" s="28" t="s">
         <v>365</v>
-      </c>
-      <c r="K94" s="28" t="s">
-        <v>366</v>
       </c>
       <c r="L94" s="9"/>
     </row>
@@ -5058,7 +5055,7 @@
         <v>21</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D95" s="11" t="s">
         <v>75</v>
@@ -5067,7 +5064,7 @@
         <v>76</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G95" s="13" t="s">
         <v>164</v>
@@ -5079,7 +5076,7 @@
         <v>27</v>
       </c>
       <c r="J95" s="21" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="L95" s="21"/>
     </row>
@@ -5091,16 +5088,16 @@
         <v>37</v>
       </c>
       <c r="C96" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E96" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="F96" s="11" t="s">
         <v>368</v>
-      </c>
-      <c r="D96" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="E96" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="F96" s="11" t="s">
-        <v>369</v>
       </c>
       <c r="G96" s="13" t="s">
         <v>164</v>
@@ -5112,10 +5109,10 @@
         <v>27</v>
       </c>
       <c r="J96" s="29" t="s">
+        <v>369</v>
+      </c>
+      <c r="K96" s="28" t="s">
         <v>370</v>
-      </c>
-      <c r="K96" s="28" t="s">
-        <v>371</v>
       </c>
       <c r="L96" s="30"/>
     </row>
@@ -5127,16 +5124,16 @@
         <v>12</v>
       </c>
       <c r="C97" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E97" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="F97" s="11" t="s">
         <v>368</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="E97" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="F97" s="11" t="s">
-        <v>369</v>
       </c>
       <c r="G97" s="13" t="s">
         <v>164</v>
@@ -5148,10 +5145,10 @@
         <v>27</v>
       </c>
       <c r="J97" s="29" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K97" s="28" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L97" s="30"/>
     </row>
@@ -5163,16 +5160,16 @@
         <v>62</v>
       </c>
       <c r="C98" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E98" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="F98" s="11" t="s">
         <v>368</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="E98" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="F98" s="11" t="s">
-        <v>369</v>
       </c>
       <c r="G98" s="13" t="s">
         <v>164</v>
@@ -5184,10 +5181,10 @@
         <v>27</v>
       </c>
       <c r="J98" s="29" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K98" s="28" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L98" s="30"/>
     </row>
@@ -5199,16 +5196,16 @@
         <v>21</v>
       </c>
       <c r="C99" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="F99" s="11" t="s">
         <v>368</v>
-      </c>
-      <c r="D99" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="E99" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="F99" s="11" t="s">
-        <v>369</v>
       </c>
       <c r="G99" s="13" t="s">
         <v>164</v>
@@ -5220,10 +5217,10 @@
         <v>27</v>
       </c>
       <c r="J99" s="29" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K99" s="28" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L99" s="30"/>
     </row>
@@ -5244,10 +5241,10 @@
         <v>76</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H100" s="11" t="s">
         <v>85</v>
@@ -5256,10 +5253,10 @@
         <v>27</v>
       </c>
       <c r="J100" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="K100" s="21" t="s">
         <v>375</v>
-      </c>
-      <c r="K100" s="21" t="s">
-        <v>376</v>
       </c>
       <c r="L100" s="9"/>
     </row>
@@ -5271,7 +5268,7 @@
         <v>29</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D101" s="11" t="s">
         <v>75</v>
@@ -5292,10 +5289,10 @@
         <v>27</v>
       </c>
       <c r="J101" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="K101" s="21" t="s">
         <v>377</v>
-      </c>
-      <c r="K101" s="21" t="s">
-        <v>378</v>
       </c>
       <c r="L101" s="9"/>
     </row>
@@ -5307,7 +5304,7 @@
         <v>54</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D102" s="11" t="s">
         <v>75</v>
@@ -5328,13 +5325,13 @@
         <v>27</v>
       </c>
       <c r="J102" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="K102" s="22" t="s">
         <v>379</v>
       </c>
-      <c r="K102" s="22" t="s">
+      <c r="L102" s="23" t="s">
         <v>380</v>
-      </c>
-      <c r="L102" s="23" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
@@ -5345,7 +5342,7 @@
         <v>89</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D103" s="11" t="s">
         <v>75</v>
@@ -5354,7 +5351,7 @@
         <v>76</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G103" s="13" t="s">
         <v>164</v>
@@ -5366,10 +5363,10 @@
         <v>27</v>
       </c>
       <c r="J103" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="K103" s="21" t="s">
         <v>383</v>
-      </c>
-      <c r="K103" s="21" t="s">
-        <v>384</v>
       </c>
       <c r="L103" s="9"/>
     </row>
@@ -5381,7 +5378,7 @@
         <v>54</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>140</v>
@@ -5390,10 +5387,10 @@
         <v>76</v>
       </c>
       <c r="F104" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H104" s="9" t="s">
         <v>18</v>
@@ -5402,7 +5399,7 @@
         <v>27</v>
       </c>
       <c r="J104" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K104" s="9" t="s">
         <v>71</v>
@@ -5417,7 +5414,7 @@
         <v>29</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D105" s="11" t="s">
         <v>75</v>
@@ -5426,10 +5423,10 @@
         <v>76</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G105" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H105" s="11" t="s">
         <v>85</v>
@@ -5438,10 +5435,10 @@
         <v>27</v>
       </c>
       <c r="J105" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="K105" s="21" t="s">
         <v>388</v>
-      </c>
-      <c r="K105" s="21" t="s">
-        <v>389</v>
       </c>
       <c r="L105" s="9"/>
     </row>
@@ -5453,7 +5450,7 @@
         <v>29</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D106" s="11" t="s">
         <v>75</v>
@@ -5462,7 +5459,7 @@
         <v>76</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G106" s="13" t="s">
         <v>164</v>
@@ -5474,10 +5471,10 @@
         <v>27</v>
       </c>
       <c r="J106" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="K106" s="22" t="s">
         <v>390</v>
-      </c>
-      <c r="K106" s="22" t="s">
-        <v>391</v>
       </c>
       <c r="L106" s="9"/>
     </row>
@@ -5498,10 +5495,10 @@
         <v>76</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G107" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H107" s="11" t="s">
         <v>85</v>
@@ -5510,10 +5507,10 @@
         <v>27</v>
       </c>
       <c r="J107" s="21" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K107" s="21" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L107" s="9"/>
     </row>
@@ -5525,7 +5522,7 @@
         <v>29</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D108" s="11" t="s">
         <v>75</v>
@@ -5534,10 +5531,10 @@
         <v>76</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H108" s="11" t="s">
         <v>18</v>
@@ -5546,7 +5543,7 @@
         <v>27</v>
       </c>
       <c r="J108" s="21" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K108" s="9"/>
       <c r="L108" s="9"/>
@@ -5559,7 +5556,7 @@
         <v>29</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D109" s="11" t="s">
         <v>129</v>
@@ -5580,7 +5577,7 @@
         <v>27</v>
       </c>
       <c r="J109" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K109" s="9"/>
       <c r="L109" s="9"/>
@@ -5593,7 +5590,7 @@
         <v>37</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D110" s="11" t="s">
         <v>75</v>
@@ -5602,10 +5599,10 @@
         <v>76</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G110" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H110" s="11" t="s">
         <v>18</v>
@@ -5614,10 +5611,10 @@
         <v>27</v>
       </c>
       <c r="J110" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="K110" s="21" t="s">
         <v>398</v>
-      </c>
-      <c r="K110" s="21" t="s">
-        <v>399</v>
       </c>
       <c r="L110" s="9"/>
     </row>
@@ -5632,16 +5629,16 @@
         <v>30</v>
       </c>
       <c r="D111" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="E111" s="19" t="s">
         <v>338</v>
       </c>
-      <c r="E111" s="19" t="s">
+      <c r="F111" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="F111" s="11" t="s">
-        <v>340</v>
-      </c>
       <c r="G111" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H111" s="11" t="s">
         <v>85</v>
@@ -5650,10 +5647,10 @@
         <v>27</v>
       </c>
       <c r="J111" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="K111" s="21" t="s">
         <v>400</v>
-      </c>
-      <c r="K111" s="21" t="s">
-        <v>401</v>
       </c>
       <c r="L111" s="9"/>
     </row>
@@ -5674,10 +5671,10 @@
         <v>76</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G112" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H112" s="11" t="s">
         <v>85</v>
@@ -5686,10 +5683,10 @@
         <v>27</v>
       </c>
       <c r="J112" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="K112" s="21" t="s">
         <v>402</v>
-      </c>
-      <c r="K112" s="21" t="s">
-        <v>403</v>
       </c>
       <c r="L112" s="9"/>
     </row>
@@ -5701,7 +5698,7 @@
         <v>37</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>75</v>
@@ -5710,7 +5707,7 @@
         <v>76</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G113" s="13" t="s">
         <v>69</v>
@@ -5722,10 +5719,10 @@
         <v>27</v>
       </c>
       <c r="J113" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="K113" s="22" t="s">
         <v>405</v>
-      </c>
-      <c r="K113" s="22" t="s">
-        <v>406</v>
       </c>
       <c r="L113" s="9"/>
     </row>
@@ -5737,7 +5734,7 @@
         <v>62</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D114" s="11" t="s">
         <v>75</v>
@@ -5746,10 +5743,10 @@
         <v>76</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G114" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H114" s="11" t="s">
         <v>18</v>
@@ -5758,13 +5755,13 @@
         <v>27</v>
       </c>
       <c r="J114" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="K114" s="22" t="s">
         <v>408</v>
       </c>
-      <c r="K114" s="22" t="s">
+      <c r="L114" s="23" t="s">
         <v>409</v>
-      </c>
-      <c r="L114" s="23" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
@@ -5787,7 +5784,7 @@
         <v>150</v>
       </c>
       <c r="G115" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H115" s="11" t="s">
         <v>18</v>
@@ -5796,10 +5793,10 @@
         <v>27</v>
       </c>
       <c r="J115" s="21" t="s">
+        <v>410</v>
+      </c>
+      <c r="K115" s="21" t="s">
         <v>411</v>
-      </c>
-      <c r="K115" s="21" t="s">
-        <v>412</v>
       </c>
       <c r="L115" s="9"/>
     </row>
@@ -5820,7 +5817,7 @@
         <v>76</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G116" s="13" t="s">
         <v>164</v>
@@ -5832,10 +5829,10 @@
         <v>27</v>
       </c>
       <c r="J116" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="K116" s="9" t="s">
         <v>402</v>
-      </c>
-      <c r="K116" s="9" t="s">
-        <v>403</v>
       </c>
       <c r="L116" s="9"/>
     </row>
@@ -5847,16 +5844,16 @@
         <v>62</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E117" s="19" t="s">
         <v>183</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G117" s="13" t="s">
         <v>164</v>
@@ -5868,10 +5865,10 @@
         <v>27</v>
       </c>
       <c r="J117" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="K117" s="9" t="s">
         <v>415</v>
-      </c>
-      <c r="K117" s="9" t="s">
-        <v>416</v>
       </c>
       <c r="L117" s="9"/>
     </row>
@@ -5883,7 +5880,7 @@
         <v>54</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D118" s="11" t="s">
         <v>75</v>
@@ -5892,10 +5889,10 @@
         <v>76</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G118" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H118" s="11" t="s">
         <v>18</v>
@@ -5904,10 +5901,10 @@
         <v>27</v>
       </c>
       <c r="J118" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="K118" s="21" t="s">
         <v>418</v>
-      </c>
-      <c r="K118" s="21" t="s">
-        <v>419</v>
       </c>
       <c r="L118" s="9"/>
     </row>
@@ -5940,7 +5937,7 @@
         <v>27</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K119" s="9"/>
       <c r="L119" s="9"/>
@@ -5965,7 +5962,7 @@
         <v>130</v>
       </c>
       <c r="G120" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H120" s="11" t="s">
         <v>85</v>
@@ -5974,10 +5971,10 @@
         <v>27</v>
       </c>
       <c r="J120" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="K120" s="7" t="s">
         <v>421</v>
-      </c>
-      <c r="K120" s="7" t="s">
-        <v>422</v>
       </c>
       <c r="L120" s="9"/>
     </row>
@@ -5989,7 +5986,7 @@
         <v>12</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D121" s="9" t="s">
         <v>162</v>
@@ -5998,7 +5995,7 @@
         <v>76</v>
       </c>
       <c r="F121" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G121" s="7" t="s">
         <v>164</v>
@@ -6010,7 +6007,7 @@
         <v>27</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K121" s="9"/>
       <c r="L121" s="9"/>

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -537,7 +537,7 @@
     <t>Immortalized Tour</t>
   </si>
   <si>
-    <t>Breaking Benjamin, Alter Bridge, Saint Asonia</t>
+    <t>Nothing More, Chevelle</t>
   </si>
   <si>
     <t>Red Hot Chili Peppers</t>
@@ -2913,7 +2913,7 @@
       <c r="J34" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="K34" s="21" t="s">
+      <c r="K34" s="22" t="s">
         <v>174</v>
       </c>
       <c r="L34" s="9"/>

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -960,7 +960,7 @@
     <t>Lunatic Luau 2022</t>
   </si>
   <si>
-    <t>Distrubed, The Pretty Reckless, Living Colour, Dirty Honey, Bad Wolves, Ayron Jones</t>
+    <t>Disturbed, The Pretty Reckless, Living Colour, Dirty Honey, Bad Wolves, Ayron Jones</t>
   </si>
   <si>
     <t>Existential Reckoning Tour 2022</t>

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="426">
   <si>
     <t>Date</t>
   </si>
@@ -111,7 +111,7 @@
     <t>Snocore 99 Tour</t>
   </si>
   <si>
-    <t>Mr Bungle, Incubus</t>
+    <t>Mr. Bungle, Incubus</t>
   </si>
   <si>
     <t>Co-headline tour with Mr. Bungle</t>
@@ -546,7 +546,7 @@
     <t>The Getaway World Tour</t>
   </si>
   <si>
-    <t>Babymetal</t>
+    <t>BABYMETAL</t>
   </si>
   <si>
     <t>Metallica</t>
@@ -558,7 +558,7 @@
     <t>WorldWired Tour</t>
   </si>
   <si>
-    <t>Avenged Sevenfold, Volbeat</t>
+    <t>Volbeat, Local H, Mix Master Mike</t>
   </si>
   <si>
     <t>Fairfax</t>
@@ -666,7 +666,7 @@
     <t>Rock on the Range 2018</t>
   </si>
   <si>
-    <t>Alice in Chains, A Perfect Circle, Breaking Benjamin, Machine Gun Kelly, Greta Van Fleet, 10 Years, The Bronx, Underoath, Quicksand, Hawthorne Heights, Turnstile, Senses Fail, The Fever 333, I See Stars, Body Count, Atreyu, Power Trip, Dance Gavin Dance, Mutoid Man, Spirit Animal</t>
+    <t>Alice in Chains, A Perfect Circle, Breaking Benjamin, Machine Gun Kelly, Greta Van Fleet, 10 Years, The Bronx, Underoath, Quicksand, Hawthorne Heights, Turnstile, Senses Fail, Fever 333, I See Stars, Body Count, Atreyu, Power Trip, Dance Gavin Dance, Mutoid Man, Spirit Animal</t>
   </si>
   <si>
     <t>Glamping! First Festival!</t>
@@ -807,7 +807,7 @@
     <t>Ember Tour</t>
   </si>
   <si>
-    <t>Chevelle, Three Days Grace, Dorothy, Diamente</t>
+    <t>Chevelle, Three Days Grace, Dorothy, DIAMANTE</t>
   </si>
   <si>
     <t>Ghost</t>
@@ -840,7 +840,7 @@
     <t>Fear Inoculum Tour</t>
   </si>
   <si>
-    <t>Author and Punisher</t>
+    <t>Killing Joke</t>
   </si>
   <si>
     <t>Josh R., Bill B.</t>
@@ -855,6 +855,9 @@
     <t>T-Mobile Arena</t>
   </si>
   <si>
+    <t>Author &amp; Punisher</t>
+  </si>
+  <si>
     <t>Lily K.</t>
   </si>
   <si>
@@ -888,7 +891,7 @@
     <t>Welcome To Rockville Festival - Day 2</t>
   </si>
   <si>
-    <t>Metallica, Social Distortion, Pennywise, Ice Nine Kills, Ayron Jones, Austin Meade, Rob Zombie, Chevelle, Beartooth, Starset, Zero 9:36, Whit3 Collr, Wage War, Butcher Babies, Amigo the Devil, Bad Omens, Tallah, Eva Under Fire, Zero 9:36, Whit3 Collr, Divided Truth, ReBirth, Tragic, VENTRUSS, The Coursing, As You Were</t>
+    <t>Metallica, Social Distortion, Pennywise, Ice Nine Kills, Ayron Jones, Austin Meade, Rob Zombie, Chevelle, Beartooth, Starset, Wage War, Butcher Babies, Amigo the Devil, Bad Omens, Tallah, Eva Under Fire, Zero 9:36, Whit3 Collr, Divided Truth, ReBirth, Tragic, VENTRUSS, The Coursing, As You Were</t>
   </si>
   <si>
     <t>Welcome To Rockville Festival- Day 3</t>
@@ -945,7 +948,7 @@
     <t>Boy Harsher</t>
   </si>
   <si>
-    <t>Lunatic Luau</t>
+    <t>Lunatic Luau Festival</t>
   </si>
   <si>
     <t>Virginia Beach</t>
@@ -1053,7 +1056,7 @@
     <t>Blue Ridge Rock Fest 2023</t>
   </si>
   <si>
-    <t>Slipknot, Danzig, Motionless In White, Sleep Token, Knocked Loose, Lorna Shore, Polyphia, Testament, VV, Electric Callboy, Coal Chamber, Flyleaf, The Black Dahlia Murder, Job For Cowboy, After The Burial, Woe Is Me, Like Moths To Flames, The Acacia Strain, Of Mice &amp; Men, Chelsea Grin, Catch Your Breath, Black S. Cherry, Upon A Burning Body, Afterlife, Struggle Jennings, Angelmaker, Crown the Empire, Conquer Divide, TrustCompany, Savage Hands, Demun Jones, Archers, Starbenders, Oliver Anthony</t>
+    <t>Slipknot, Danzig, Motionless in White, Sleep Token, Knocked Loose, Lorna Shore, Polyphia, Testament, VV, Electric Callboy, Coal Chamber, Flyleaf, The Black Dahlia Murder, Job For Cowboy, After The Burial, Woe Is Me, Like Moths to Flames, The Acacia Strain, Of Mice &amp; Men, Chelsea Grin, Catch Your Breath, Black S. Cherry, Upon A Burning Body, Afterlife, Struggle Jennings, Angelmaker, Crown the Empire, Conquer Divide, TrustCompany, Savage Hands, Demun Jones, Archers, Starbenders, Oliver Anthony</t>
   </si>
   <si>
     <t>Blue Ride Disaster Shitshow: https://digitalbeatmag.com/a-2023-blue-ridge-rock-fest-review/</t>
@@ -1128,7 +1131,7 @@
     <t>Disturbed, Evanescence, Mudvayne, Theory of a Deadman, P.O.D., Drowning Pool, Nita Strauss, Judas Priest, Kerry King, The Ghost Inside, Nova Twins, Taipei Houston, Bob Vylan, Tim Montana, Cypress Hill, Electric Callboy, Enter Shikari, The Chats, Magnolia Park, TX2, Lø Spirit, Machine Head, August Burns Red, Frank Carter &amp; The Rattlesnakes, Fire from the Gods, Miss May I, Catch Your Breath, SiM, HotBox</t>
   </si>
   <si>
-    <t>The Original Misfits, Falling In Reverse, Seether, Anthrax, Dirty Honey, Nonpoint, Point North, Rise Against, Sum 41, Black Veil Brides, Movements, Terror, Scowl, Gel, Code Orange, Mr. Bungle, Drain, Militarie Gun, Rain City Drive, The Chisel, Gideon, Avatar, Atreyu, Soulfly, Kublai Khan TX, New Years Day, Fleshwater, I See Stars, Fuming Mouth</t>
+    <t>The Original Misfits, Falling in Reverse, Seether, Anthrax, Dirty Honey, Nonpoint, Point North, Rise Against, Sum 41, Black Veil Brides, Movements, Terror, Scowl, Gel, Code Orange, Mr. Bungle, Drain, Militarie Gun, Rain City Drive, The Chisel, Gideon, Avatar, Atreyu, Soulfly, Kublai Khan TX, New Years Day, Fleshwater, I See Stars, Fuming Mouth</t>
   </si>
   <si>
     <t>Pantera, Staind, Breaking Benjamin, Starset, Living Colour, Saint Asonia, Flat Black, Sleep Token, In This Moment, Flyleaf with Lacey Sturm, Kittie, Destroy Boys, Calva Louise, VUKOVI, Polyphia, The Amity Affliction, Currents, Spite, Bodysnatcher, Thrown, Dying Wish, Slaughter to Prevail, In Flames, Lacuna Coil, Harm's Way, Empire State Bastard, Imminence, Mike's Dead</t>
@@ -1140,7 +1143,7 @@
     <t>Unlimited Love Tour</t>
   </si>
   <si>
-    <t>IRONTOM</t>
+    <t>Ice Cube</t>
   </si>
   <si>
     <t>Loaded: The Greatest Hits 1994-2023 Tour</t>
@@ -1152,7 +1155,7 @@
     <t>Jubilee Tour</t>
   </si>
   <si>
-    <t>LIVE, Soul Asylum</t>
+    <t>Live, Soul Asylum</t>
   </si>
   <si>
     <t>Co-headline tour with Live.</t>
@@ -1179,13 +1182,13 @@
     <t>From Zero World Tour</t>
   </si>
   <si>
-    <t>Jean Dawson</t>
+    <t>grandson</t>
   </si>
   <si>
     <t>Dark Matter World Tour</t>
   </si>
   <si>
-    <t>Teen Jesus and the Jean Teaser</t>
+    <t>Teen Jesus and the Jean Teasers</t>
   </si>
   <si>
     <t>Bank of America Stadium</t>
@@ -1239,7 +1242,7 @@
     <t>I Can't Hear You Tour</t>
   </si>
   <si>
-    <t>Health, Daycare, Destroy Boys</t>
+    <t>Health, Ecca Vandal, Like Roses</t>
   </si>
   <si>
     <t>Co-headline tour with Health.</t>
@@ -1248,7 +1251,7 @@
     <t>Lucro Sucio: Los Ojos del Vacio Tour</t>
   </si>
   <si>
-    <t>Teri Gender Bender</t>
+    <t>Feliz y Dada, Kianî Medina</t>
   </si>
   <si>
     <t>Candlebox</t>
@@ -1842,7 +1845,7 @@
       <c r="J4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="7" t="s">
         <v>32</v>
       </c>
       <c r="L4" s="15" t="s">
@@ -2949,7 +2952,7 @@
       <c r="J35" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="K35" s="21" t="s">
+      <c r="K35" s="22" t="s">
         <v>177</v>
       </c>
       <c r="L35" s="9"/>
@@ -2985,7 +2988,7 @@
       <c r="J36" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="K36" s="21" t="s">
+      <c r="K36" s="22" t="s">
         <v>181</v>
       </c>
       <c r="L36" s="9"/>
@@ -4010,7 +4013,7 @@
         <v>274</v>
       </c>
       <c r="K65" s="28" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="L65" s="9"/>
     </row>
@@ -4034,7 +4037,7 @@
         <v>163</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H66" s="11" t="s">
         <v>85</v>
@@ -4046,7 +4049,7 @@
         <v>242</v>
       </c>
       <c r="K66" s="28" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L66" s="9"/>
     </row>
@@ -4058,7 +4061,7 @@
         <v>62</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>75</v>
@@ -4079,7 +4082,7 @@
         <v>27</v>
       </c>
       <c r="J67" s="21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L67" s="9"/>
     </row>
@@ -4112,7 +4115,7 @@
         <v>27</v>
       </c>
       <c r="J68" s="21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L68" s="9"/>
     </row>
@@ -4124,16 +4127,16 @@
         <v>37</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E69" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>164</v>
@@ -4145,10 +4148,10 @@
         <v>27</v>
       </c>
       <c r="J69" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K69" s="28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L69" s="7"/>
     </row>
@@ -4160,16 +4163,16 @@
         <v>12</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E70" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>164</v>
@@ -4181,10 +4184,10 @@
         <v>27</v>
       </c>
       <c r="J70" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K70" s="28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L70" s="7"/>
     </row>
@@ -4196,16 +4199,16 @@
         <v>62</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E71" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>164</v>
@@ -4217,10 +4220,10 @@
         <v>27</v>
       </c>
       <c r="J71" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K71" s="28" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L71" s="7"/>
     </row>
@@ -4232,16 +4235,16 @@
         <v>21</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E72" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>164</v>
@@ -4253,10 +4256,10 @@
         <v>27</v>
       </c>
       <c r="J72" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K72" s="28" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L72" s="7"/>
     </row>
@@ -4268,7 +4271,7 @@
         <v>12</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>75</v>
@@ -4280,7 +4283,7 @@
         <v>103</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H73" s="11" t="s">
         <v>85</v>
@@ -4289,7 +4292,7 @@
         <v>27</v>
       </c>
       <c r="J73" s="21" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L73" s="9"/>
     </row>
@@ -4304,13 +4307,13 @@
         <v>144</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G74" s="13" t="s">
         <v>233</v>
@@ -4325,7 +4328,7 @@
         <v>274</v>
       </c>
       <c r="K74" s="28" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L74" s="9"/>
     </row>
@@ -4337,7 +4340,7 @@
         <v>12</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D75" s="11" t="s">
         <v>162</v>
@@ -4358,10 +4361,10 @@
         <v>27</v>
       </c>
       <c r="J75" s="21" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K75" s="28" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L75" s="9"/>
     </row>
@@ -4376,13 +4379,13 @@
         <v>144</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E76" s="19" t="s">
         <v>213</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G76" s="13" t="s">
         <v>233</v>
@@ -4397,7 +4400,7 @@
         <v>274</v>
       </c>
       <c r="K76" s="28" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L76" s="9"/>
     </row>
@@ -4430,10 +4433,10 @@
         <v>27</v>
       </c>
       <c r="J77" s="21" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K77" s="28" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L77" s="9"/>
     </row>
@@ -4444,20 +4447,20 @@
       <c r="B78" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C78" s="11" t="s">
-        <v>310</v>
+      <c r="C78" s="13" t="s">
+        <v>311</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E78" s="19" t="s">
         <v>183</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H78" s="11" t="s">
         <v>18</v>
@@ -4466,10 +4469,10 @@
         <v>27</v>
       </c>
       <c r="J78" s="13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K78" s="22" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L78" s="9"/>
     </row>
@@ -4502,10 +4505,10 @@
         <v>27</v>
       </c>
       <c r="J79" s="21" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K79" s="28" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L79" s="9"/>
     </row>
@@ -4517,7 +4520,7 @@
         <v>21</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D80" s="11" t="s">
         <v>75</v>
@@ -4529,7 +4532,7 @@
         <v>103</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H80" s="11" t="s">
         <v>85</v>
@@ -4538,10 +4541,10 @@
         <v>27</v>
       </c>
       <c r="J80" s="21" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K80" s="28" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L80" s="9"/>
     </row>
@@ -4565,7 +4568,7 @@
         <v>103</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H81" s="11" t="s">
         <v>18</v>
@@ -4574,7 +4577,7 @@
         <v>27</v>
       </c>
       <c r="J81" s="21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L81" s="9"/>
     </row>
@@ -4586,16 +4589,16 @@
         <v>21</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G82" s="13" t="s">
         <v>233</v>
@@ -4607,10 +4610,10 @@
         <v>27</v>
       </c>
       <c r="J82" s="21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K82" s="28" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L82" s="9"/>
     </row>
@@ -4622,7 +4625,7 @@
         <v>29</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D83" s="11" t="s">
         <v>75</v>
@@ -4643,13 +4646,13 @@
         <v>27</v>
       </c>
       <c r="J83" s="21" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K83" s="28" t="s">
         <v>261</v>
       </c>
       <c r="L83" s="23" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
@@ -4681,10 +4684,10 @@
         <v>27</v>
       </c>
       <c r="J84" s="21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K84" s="28" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L84" s="9"/>
     </row>
@@ -4696,16 +4699,16 @@
         <v>21</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E85" s="19" t="s">
         <v>116</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G85" s="13" t="s">
         <v>164</v>
@@ -4717,10 +4720,10 @@
         <v>27</v>
       </c>
       <c r="J85" s="22" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K85" s="28" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L85" s="7"/>
     </row>
@@ -4735,13 +4738,13 @@
         <v>178</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G86" s="13" t="s">
         <v>233</v>
@@ -4753,10 +4756,10 @@
         <v>27</v>
       </c>
       <c r="J86" s="21" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K86" s="28" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L86" s="9"/>
     </row>
@@ -4768,16 +4771,16 @@
         <v>37</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E87" s="19" t="s">
         <v>183</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>164</v>
@@ -4789,13 +4792,13 @@
         <v>27</v>
       </c>
       <c r="J87" s="22" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K87" s="28" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
@@ -4806,7 +4809,7 @@
         <v>62</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D88" s="11" t="s">
         <v>277</v>
@@ -4815,7 +4818,7 @@
         <v>278</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G88" s="13" t="s">
         <v>231</v>
@@ -4827,7 +4830,7 @@
         <v>27</v>
       </c>
       <c r="J88" s="21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L88" s="9"/>
     </row>
@@ -4839,7 +4842,7 @@
         <v>21</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D89" s="11" t="s">
         <v>75</v>
@@ -4860,10 +4863,10 @@
         <v>27</v>
       </c>
       <c r="J89" s="21" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K89" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L89" s="9"/>
     </row>
@@ -4875,7 +4878,7 @@
         <v>37</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>75</v>
@@ -4896,10 +4899,10 @@
         <v>27</v>
       </c>
       <c r="J90" s="21" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K90" s="28" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L90" s="9"/>
     </row>
@@ -4911,7 +4914,7 @@
         <v>12</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D91" s="11" t="s">
         <v>129</v>
@@ -4923,7 +4926,7 @@
         <v>130</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H91" s="11" t="s">
         <v>18</v>
@@ -4932,10 +4935,10 @@
         <v>27</v>
       </c>
       <c r="J91" s="21" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K91" s="28" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L91" s="9"/>
     </row>
@@ -4968,10 +4971,10 @@
         <v>27</v>
       </c>
       <c r="J92" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K92" s="28" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L92" s="9"/>
     </row>
@@ -5004,10 +5007,10 @@
         <v>27</v>
       </c>
       <c r="J93" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K93" s="28" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L93" s="9"/>
     </row>
@@ -5019,7 +5022,7 @@
         <v>12</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D94" s="11" t="s">
         <v>75</v>
@@ -5028,7 +5031,7 @@
         <v>76</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G94" s="13" t="s">
         <v>164</v>
@@ -5040,10 +5043,10 @@
         <v>27</v>
       </c>
       <c r="J94" s="21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K94" s="28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L94" s="9"/>
     </row>
@@ -5055,7 +5058,7 @@
         <v>21</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D95" s="11" t="s">
         <v>75</v>
@@ -5076,7 +5079,7 @@
         <v>27</v>
       </c>
       <c r="J95" s="21" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L95" s="21"/>
     </row>
@@ -5088,7 +5091,7 @@
         <v>37</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D96" s="11" t="s">
         <v>212</v>
@@ -5097,7 +5100,7 @@
         <v>213</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G96" s="13" t="s">
         <v>164</v>
@@ -5109,10 +5112,10 @@
         <v>27</v>
       </c>
       <c r="J96" s="29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K96" s="28" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L96" s="30"/>
     </row>
@@ -5124,7 +5127,7 @@
         <v>12</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>212</v>
@@ -5133,7 +5136,7 @@
         <v>213</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G97" s="13" t="s">
         <v>164</v>
@@ -5145,10 +5148,10 @@
         <v>27</v>
       </c>
       <c r="J97" s="29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K97" s="28" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L97" s="30"/>
     </row>
@@ -5160,7 +5163,7 @@
         <v>62</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D98" s="11" t="s">
         <v>212</v>
@@ -5169,7 +5172,7 @@
         <v>213</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G98" s="13" t="s">
         <v>164</v>
@@ -5181,10 +5184,10 @@
         <v>27</v>
       </c>
       <c r="J98" s="29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K98" s="28" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L98" s="30"/>
     </row>
@@ -5196,7 +5199,7 @@
         <v>21</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D99" s="11" t="s">
         <v>212</v>
@@ -5205,7 +5208,7 @@
         <v>213</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G99" s="13" t="s">
         <v>164</v>
@@ -5217,10 +5220,10 @@
         <v>27</v>
       </c>
       <c r="J99" s="29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K99" s="28" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L99" s="30"/>
     </row>
@@ -5253,10 +5256,10 @@
         <v>27</v>
       </c>
       <c r="J100" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="K100" s="21" t="s">
         <v>375</v>
+      </c>
+      <c r="K100" s="22" t="s">
+        <v>376</v>
       </c>
       <c r="L100" s="9"/>
     </row>
@@ -5268,7 +5271,7 @@
         <v>29</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D101" s="11" t="s">
         <v>75</v>
@@ -5289,10 +5292,10 @@
         <v>27</v>
       </c>
       <c r="J101" s="21" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K101" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L101" s="9"/>
     </row>
@@ -5325,13 +5328,13 @@
         <v>27</v>
       </c>
       <c r="J102" s="21" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K102" s="22" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L102" s="23" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
@@ -5342,7 +5345,7 @@
         <v>89</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D103" s="11" t="s">
         <v>75</v>
@@ -5363,10 +5366,10 @@
         <v>27</v>
       </c>
       <c r="J103" s="21" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K103" s="21" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L103" s="9"/>
     </row>
@@ -5378,7 +5381,7 @@
         <v>54</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>140</v>
@@ -5399,7 +5402,7 @@
         <v>27</v>
       </c>
       <c r="J104" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K104" s="9" t="s">
         <v>71</v>
@@ -5414,7 +5417,7 @@
         <v>29</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D105" s="11" t="s">
         <v>75</v>
@@ -5423,7 +5426,7 @@
         <v>76</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G105" s="13" t="s">
         <v>276</v>
@@ -5435,10 +5438,10 @@
         <v>27</v>
       </c>
       <c r="J105" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="K105" s="21" t="s">
         <v>388</v>
+      </c>
+      <c r="K105" s="22" t="s">
+        <v>389</v>
       </c>
       <c r="L105" s="9"/>
     </row>
@@ -5459,7 +5462,7 @@
         <v>76</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G106" s="13" t="s">
         <v>164</v>
@@ -5471,10 +5474,10 @@
         <v>27</v>
       </c>
       <c r="J106" s="21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K106" s="22" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L106" s="9"/>
     </row>
@@ -5495,7 +5498,7 @@
         <v>76</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G107" s="13" t="s">
         <v>276</v>
@@ -5507,10 +5510,10 @@
         <v>27</v>
       </c>
       <c r="J107" s="21" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K107" s="21" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L107" s="9"/>
     </row>
@@ -5531,10 +5534,10 @@
         <v>76</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H108" s="11" t="s">
         <v>18</v>
@@ -5543,7 +5546,7 @@
         <v>27</v>
       </c>
       <c r="J108" s="21" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K108" s="9"/>
       <c r="L108" s="9"/>
@@ -5556,7 +5559,7 @@
         <v>29</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D109" s="11" t="s">
         <v>129</v>
@@ -5577,7 +5580,7 @@
         <v>27</v>
       </c>
       <c r="J109" s="21" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K109" s="9"/>
       <c r="L109" s="9"/>
@@ -5590,7 +5593,7 @@
         <v>37</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D110" s="11" t="s">
         <v>75</v>
@@ -5599,10 +5602,10 @@
         <v>76</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G110" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H110" s="11" t="s">
         <v>18</v>
@@ -5611,10 +5614,10 @@
         <v>27</v>
       </c>
       <c r="J110" s="21" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K110" s="21" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L110" s="9"/>
     </row>
@@ -5629,13 +5632,13 @@
         <v>30</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E111" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G111" s="13" t="s">
         <v>233</v>
@@ -5647,10 +5650,10 @@
         <v>27</v>
       </c>
       <c r="J111" s="21" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K111" s="21" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L111" s="9"/>
     </row>
@@ -5671,7 +5674,7 @@
         <v>76</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G112" s="13" t="s">
         <v>276</v>
@@ -5683,10 +5686,10 @@
         <v>27</v>
       </c>
       <c r="J112" s="21" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K112" s="21" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L112" s="9"/>
     </row>
@@ -5698,7 +5701,7 @@
         <v>37</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>75</v>
@@ -5707,7 +5710,7 @@
         <v>76</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G113" s="13" t="s">
         <v>69</v>
@@ -5719,10 +5722,10 @@
         <v>27</v>
       </c>
       <c r="J113" s="21" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K113" s="22" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L113" s="9"/>
     </row>
@@ -5734,7 +5737,7 @@
         <v>62</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D114" s="11" t="s">
         <v>75</v>
@@ -5755,13 +5758,13 @@
         <v>27</v>
       </c>
       <c r="J114" s="21" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K114" s="22" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L114" s="23" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
@@ -5793,10 +5796,10 @@
         <v>27</v>
       </c>
       <c r="J115" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="K115" s="21" t="s">
         <v>411</v>
+      </c>
+      <c r="K115" s="22" t="s">
+        <v>412</v>
       </c>
       <c r="L115" s="9"/>
     </row>
@@ -5829,10 +5832,10 @@
         <v>27</v>
       </c>
       <c r="J116" s="21" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K116" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L116" s="9"/>
     </row>
@@ -5844,16 +5847,16 @@
         <v>62</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E117" s="19" t="s">
         <v>183</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G117" s="13" t="s">
         <v>164</v>
@@ -5865,10 +5868,10 @@
         <v>27</v>
       </c>
       <c r="J117" s="21" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K117" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L117" s="9"/>
     </row>
@@ -5880,7 +5883,7 @@
         <v>54</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D118" s="11" t="s">
         <v>75</v>
@@ -5889,7 +5892,7 @@
         <v>76</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G118" s="13" t="s">
         <v>233</v>
@@ -5901,10 +5904,10 @@
         <v>27</v>
       </c>
       <c r="J118" s="21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K118" s="21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L118" s="9"/>
     </row>
@@ -5937,7 +5940,7 @@
         <v>27</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K119" s="9"/>
       <c r="L119" s="9"/>
@@ -5971,10 +5974,10 @@
         <v>27</v>
       </c>
       <c r="J120" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K120" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L120" s="9"/>
     </row>
@@ -5986,7 +5989,7 @@
         <v>12</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D121" s="9" t="s">
         <v>162</v>
@@ -5995,7 +5998,7 @@
         <v>76</v>
       </c>
       <c r="F121" s="9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G121" s="7" t="s">
         <v>164</v>
@@ -6007,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K121" s="9"/>
       <c r="L121" s="9"/>

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="427">
   <si>
     <t>Date</t>
   </si>
@@ -75,7 +75,7 @@
     <t>College and University Independant Tour</t>
   </si>
   <si>
-    <t>Greg Humphrys</t>
+    <t>Hobex</t>
   </si>
   <si>
     <t>Sunday</t>
@@ -591,7 +591,7 @@
     <t>2017 Summer Tour</t>
   </si>
   <si>
-    <t>Clutch, The Fungi Band</t>
+    <t>Clutch</t>
   </si>
   <si>
     <t>Winston Salem</t>
@@ -768,7 +768,7 @@
     <t>Motionless in White, Badflower, The Damned Things, Wage War, Crobot, Sylar, Shvpes, Dirty Honey, Alien Weaponry, Hyde, Tetrarch, Dead Girls Academy</t>
   </si>
   <si>
-    <t>Note: Tool, Judas Priest, The Cult, Bush, Black Label Society, Circa Survive, Yelawolf, Grandson, Memphis May Fire, and Starset were all cancelled or cut short due to the storm evacuation.</t>
+    <t>Note: Tool, Judas Priest, The Cult, Bush, Black Label Society, Circa Survive, Yelawolf, grandson, Memphis May Fire, and Starset were all cancelled or cut short due to the storm evacuation.</t>
   </si>
   <si>
     <t>Epicenter Festival - Day 3</t>
@@ -885,7 +885,7 @@
     <t>Welcome to Rockville 2021</t>
   </si>
   <si>
-    <t>Slipknot, Cypress Hill, Grandson, Dead Sara, Spiritbox, Dana Dentata, A Day to Remember, Gojira, Dorothy, Teenage Wrist, Siiickbrain, Brass Against, NASCAR Aloe, Jeris Johnson, Blame My Youth, Contracult Collective, Them Evils, Revision, Revised, The Alpha Complex, A War Within, Scarlett O'hara, Dead Reckoning, Shadow the Earth, As You Were</t>
+    <t>Slipknot, Cypress Hill, grandson, Dead Sara, Spiritbox, Dana Dentata, A Day to Remember, Gojira, Dorothy, Teenage Wrist, Siiickbrain, Brass Against, NASCAR Aloe, Jeris Johnson, Blame My Youth, Contracult Collective, Them Evils, Revision, Revised, The Alpha Complex, A War Within, Scarlett O'hara, Dead Reckoning, Shadow the Earth, As You Were</t>
   </si>
   <si>
     <t>Welcome To Rockville Festival - Day 2</t>
@@ -1026,7 +1026,7 @@
     <t>Welcome to Rockville 2023</t>
   </si>
   <si>
-    <t>Tool, Deftones, Incubus, The Mars Volta, Coheed &amp; Cambria, Pennywise, Ghostemane, Grandson, Sueco, Filter, Deafheaven, Anti-Flag, Senses Fail, New Years Day, Nothing,Nowhere, Angel Dust, Nova Twins, Point North, Bob Vylan, Capital Theatre, Uncured, Reddstar</t>
+    <t>Tool, Deftones, Incubus, The Mars Volta, Coheed &amp; Cambria, Pennywise, Ghostemane, grandson, Sueco, Filter, Deafheaven, Anti-Flag, Senses Fail, New Years Day, Nothing,Nowhere, Angel Dust, Nova Twins, Point North, Bob Vylan, Capital Theatre, Uncured, Reddstar</t>
   </si>
   <si>
     <t>East Rutherford</t>
@@ -1281,7 +1281,10 @@
     <t>Normal Isn't Tour</t>
   </si>
   <si>
-    <t>Dave Hill, Puddles Pity Party (guest appearance)</t>
+    <t>Dave Hill</t>
+  </si>
+  <si>
+    <t>Puddles Pity Party (guest appearance)</t>
   </si>
   <si>
     <t>AVTT/PTTN</t>
@@ -3096,7 +3099,7 @@
       <c r="J39" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="K39" s="21" t="s">
+      <c r="K39" s="22" t="s">
         <v>192</v>
       </c>
       <c r="L39" s="9"/>
@@ -5979,7 +5982,9 @@
       <c r="K120" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="L120" s="9"/>
+      <c r="L120" s="7" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="10">
@@ -5989,7 +5994,7 @@
         <v>12</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D121" s="9" t="s">
         <v>162</v>
@@ -5998,7 +6003,7 @@
         <v>76</v>
       </c>
       <c r="F121" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G121" s="7" t="s">
         <v>164</v>
@@ -6010,7 +6015,7 @@
         <v>27</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K121" s="9"/>
       <c r="L121" s="9"/>

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -3090,8 +3090,8 @@
       <c r="G39" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="H39" s="11" t="s">
-        <v>18</v>
+      <c r="H39" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="I39" s="20" t="s">
         <v>27</v>
@@ -3590,8 +3590,8 @@
       <c r="G53" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="H53" s="11" t="s">
-        <v>18</v>
+      <c r="H53" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="I53" s="20" t="s">
         <v>27</v>

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -1304,7 +1304,7 @@
     <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1373,6 +1373,11 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1388,7 +1393,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1465,6 +1470,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
@@ -5625,11 +5633,11 @@
       <c r="L110" s="9"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="10">
-        <v>45896.0</v>
-      </c>
-      <c r="B111" s="18" t="s">
-        <v>89</v>
+      <c r="A111" s="6">
+        <v>45897.0</v>
+      </c>
+      <c r="B111" s="26" t="s">
+        <v>37</v>
       </c>
       <c r="C111" s="11" t="s">
         <v>30</v>
@@ -5649,7 +5657,7 @@
       <c r="H111" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="I111" s="24" t="s">
+      <c r="I111" s="31" t="s">
         <v>27</v>
       </c>
       <c r="J111" s="21" t="s">
@@ -8541,7 +8549,7 @@
       <c r="L301" s="9"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="31"/>
+      <c r="A302" s="32"/>
       <c r="B302" s="9"/>
       <c r="C302" s="9"/>
       <c r="D302" s="9"/>
@@ -8555,7 +8563,7 @@
       <c r="L302" s="9"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="31"/>
+      <c r="A303" s="32"/>
       <c r="B303" s="9"/>
       <c r="C303" s="9"/>
       <c r="D303" s="9"/>
@@ -8569,7 +8577,7 @@
       <c r="L303" s="9"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="31"/>
+      <c r="A304" s="32"/>
       <c r="B304" s="9"/>
       <c r="C304" s="9"/>
       <c r="D304" s="9"/>
@@ -8583,7 +8591,7 @@
       <c r="L304" s="9"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="31"/>
+      <c r="A305" s="32"/>
       <c r="B305" s="9"/>
       <c r="C305" s="9"/>
       <c r="D305" s="9"/>
@@ -8597,7 +8605,7 @@
       <c r="L305" s="9"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="31"/>
+      <c r="A306" s="32"/>
       <c r="B306" s="9"/>
       <c r="C306" s="9"/>
       <c r="D306" s="9"/>
@@ -8611,7 +8619,7 @@
       <c r="L306" s="9"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="31"/>
+      <c r="A307" s="32"/>
       <c r="B307" s="9"/>
       <c r="C307" s="9"/>
       <c r="D307" s="9"/>
@@ -8625,7 +8633,7 @@
       <c r="L307" s="9"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="31"/>
+      <c r="A308" s="32"/>
       <c r="B308" s="9"/>
       <c r="C308" s="9"/>
       <c r="D308" s="9"/>
@@ -8639,7 +8647,7 @@
       <c r="L308" s="9"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="31"/>
+      <c r="A309" s="32"/>
       <c r="B309" s="9"/>
       <c r="C309" s="9"/>
       <c r="D309" s="9"/>
@@ -8653,7 +8661,7 @@
       <c r="L309" s="9"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="31"/>
+      <c r="A310" s="32"/>
       <c r="B310" s="9"/>
       <c r="C310" s="9"/>
       <c r="D310" s="9"/>
@@ -8667,7 +8675,7 @@
       <c r="L310" s="9"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="31"/>
+      <c r="A311" s="32"/>
       <c r="B311" s="9"/>
       <c r="C311" s="9"/>
       <c r="D311" s="9"/>
@@ -8681,7 +8689,7 @@
       <c r="L311" s="9"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="31"/>
+      <c r="A312" s="32"/>
       <c r="B312" s="9"/>
       <c r="C312" s="9"/>
       <c r="D312" s="9"/>
@@ -8695,7 +8703,7 @@
       <c r="L312" s="9"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="31"/>
+      <c r="A313" s="32"/>
       <c r="B313" s="9"/>
       <c r="C313" s="9"/>
       <c r="D313" s="9"/>
@@ -8709,7 +8717,7 @@
       <c r="L313" s="9"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="31"/>
+      <c r="A314" s="32"/>
       <c r="B314" s="9"/>
       <c r="C314" s="9"/>
       <c r="D314" s="9"/>
@@ -8723,7 +8731,7 @@
       <c r="L314" s="9"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="31"/>
+      <c r="A315" s="32"/>
       <c r="B315" s="9"/>
       <c r="C315" s="9"/>
       <c r="D315" s="9"/>
@@ -8737,7 +8745,7 @@
       <c r="L315" s="9"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="31"/>
+      <c r="A316" s="32"/>
       <c r="B316" s="9"/>
       <c r="C316" s="9"/>
       <c r="D316" s="9"/>
@@ -8751,7 +8759,7 @@
       <c r="L316" s="9"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="31"/>
+      <c r="A317" s="32"/>
       <c r="B317" s="9"/>
       <c r="C317" s="9"/>
       <c r="D317" s="9"/>
@@ -8765,7 +8773,7 @@
       <c r="L317" s="9"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="A318" s="31"/>
+      <c r="A318" s="32"/>
       <c r="B318" s="9"/>
       <c r="C318" s="9"/>
       <c r="D318" s="9"/>
@@ -8779,7 +8787,7 @@
       <c r="L318" s="9"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="A319" s="31"/>
+      <c r="A319" s="32"/>
       <c r="B319" s="9"/>
       <c r="C319" s="9"/>
       <c r="D319" s="9"/>
@@ -8793,7 +8801,7 @@
       <c r="L319" s="9"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="31"/>
+      <c r="A320" s="32"/>
       <c r="B320" s="9"/>
       <c r="C320" s="9"/>
       <c r="D320" s="9"/>
@@ -8807,7 +8815,7 @@
       <c r="L320" s="9"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="A321" s="31"/>
+      <c r="A321" s="32"/>
       <c r="B321" s="9"/>
       <c r="C321" s="9"/>
       <c r="D321" s="9"/>
@@ -8821,7 +8829,7 @@
       <c r="L321" s="9"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="31"/>
+      <c r="A322" s="32"/>
       <c r="B322" s="9"/>
       <c r="C322" s="9"/>
       <c r="D322" s="9"/>
@@ -8835,7 +8843,7 @@
       <c r="L322" s="9"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="31"/>
+      <c r="A323" s="32"/>
       <c r="B323" s="9"/>
       <c r="C323" s="9"/>
       <c r="D323" s="9"/>
@@ -8849,7 +8857,7 @@
       <c r="L323" s="9"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="31"/>
+      <c r="A324" s="32"/>
       <c r="B324" s="9"/>
       <c r="C324" s="9"/>
       <c r="D324" s="9"/>
@@ -8863,7 +8871,7 @@
       <c r="L324" s="9"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="A325" s="31"/>
+      <c r="A325" s="32"/>
       <c r="B325" s="9"/>
       <c r="C325" s="9"/>
       <c r="D325" s="9"/>
@@ -8877,7 +8885,7 @@
       <c r="L325" s="9"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="31"/>
+      <c r="A326" s="32"/>
       <c r="B326" s="9"/>
       <c r="C326" s="9"/>
       <c r="D326" s="9"/>
@@ -8891,7 +8899,7 @@
       <c r="L326" s="9"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="A327" s="31"/>
+      <c r="A327" s="32"/>
       <c r="B327" s="9"/>
       <c r="C327" s="9"/>
       <c r="D327" s="9"/>
@@ -8905,7 +8913,7 @@
       <c r="L327" s="9"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="A328" s="31"/>
+      <c r="A328" s="32"/>
       <c r="B328" s="9"/>
       <c r="C328" s="9"/>
       <c r="D328" s="9"/>
@@ -8919,7 +8927,7 @@
       <c r="L328" s="9"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="31"/>
+      <c r="A329" s="32"/>
       <c r="B329" s="9"/>
       <c r="C329" s="9"/>
       <c r="D329" s="9"/>
@@ -8933,7 +8941,7 @@
       <c r="L329" s="9"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="31"/>
+      <c r="A330" s="32"/>
       <c r="B330" s="9"/>
       <c r="C330" s="9"/>
       <c r="D330" s="9"/>
@@ -8947,7 +8955,7 @@
       <c r="L330" s="9"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="A331" s="31"/>
+      <c r="A331" s="32"/>
       <c r="B331" s="9"/>
       <c r="C331" s="9"/>
       <c r="D331" s="9"/>
@@ -8961,7 +8969,7 @@
       <c r="L331" s="9"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="31"/>
+      <c r="A332" s="32"/>
       <c r="B332" s="9"/>
       <c r="C332" s="9"/>
       <c r="D332" s="9"/>
@@ -8975,7 +8983,7 @@
       <c r="L332" s="9"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="31"/>
+      <c r="A333" s="32"/>
       <c r="B333" s="9"/>
       <c r="C333" s="9"/>
       <c r="D333" s="9"/>
@@ -8989,7 +8997,7 @@
       <c r="L333" s="9"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="A334" s="31"/>
+      <c r="A334" s="32"/>
       <c r="B334" s="9"/>
       <c r="C334" s="9"/>
       <c r="D334" s="9"/>
@@ -9003,7 +9011,7 @@
       <c r="L334" s="9"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="31"/>
+      <c r="A335" s="32"/>
       <c r="B335" s="9"/>
       <c r="C335" s="9"/>
       <c r="D335" s="9"/>
@@ -9017,7 +9025,7 @@
       <c r="L335" s="9"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="31"/>
+      <c r="A336" s="32"/>
       <c r="B336" s="9"/>
       <c r="C336" s="9"/>
       <c r="D336" s="9"/>
@@ -9031,7 +9039,7 @@
       <c r="L336" s="9"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="31"/>
+      <c r="A337" s="32"/>
       <c r="B337" s="9"/>
       <c r="C337" s="9"/>
       <c r="D337" s="9"/>
@@ -9045,7 +9053,7 @@
       <c r="L337" s="9"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="31"/>
+      <c r="A338" s="32"/>
       <c r="B338" s="9"/>
       <c r="C338" s="9"/>
       <c r="D338" s="9"/>
@@ -9059,7 +9067,7 @@
       <c r="L338" s="9"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="31"/>
+      <c r="A339" s="32"/>
       <c r="B339" s="9"/>
       <c r="C339" s="9"/>
       <c r="D339" s="9"/>
@@ -9073,7 +9081,7 @@
       <c r="L339" s="9"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="31"/>
+      <c r="A340" s="32"/>
       <c r="B340" s="9"/>
       <c r="C340" s="9"/>
       <c r="D340" s="9"/>
@@ -9087,7 +9095,7 @@
       <c r="L340" s="9"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="A341" s="31"/>
+      <c r="A341" s="32"/>
       <c r="B341" s="9"/>
       <c r="C341" s="9"/>
       <c r="D341" s="9"/>
@@ -9101,7 +9109,7 @@
       <c r="L341" s="9"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="A342" s="31"/>
+      <c r="A342" s="32"/>
       <c r="B342" s="9"/>
       <c r="C342" s="9"/>
       <c r="D342" s="9"/>
@@ -9115,7 +9123,7 @@
       <c r="L342" s="9"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="31"/>
+      <c r="A343" s="32"/>
       <c r="B343" s="9"/>
       <c r="C343" s="9"/>
       <c r="D343" s="9"/>
@@ -9129,7 +9137,7 @@
       <c r="L343" s="9"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="A344" s="31"/>
+      <c r="A344" s="32"/>
       <c r="B344" s="9"/>
       <c r="C344" s="9"/>
       <c r="D344" s="9"/>
@@ -9143,7 +9151,7 @@
       <c r="L344" s="9"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="A345" s="31"/>
+      <c r="A345" s="32"/>
       <c r="B345" s="9"/>
       <c r="C345" s="9"/>
       <c r="D345" s="9"/>
@@ -9157,7 +9165,7 @@
       <c r="L345" s="9"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="A346" s="31"/>
+      <c r="A346" s="32"/>
       <c r="B346" s="9"/>
       <c r="C346" s="9"/>
       <c r="D346" s="9"/>
@@ -9171,7 +9179,7 @@
       <c r="L346" s="9"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="A347" s="31"/>
+      <c r="A347" s="32"/>
       <c r="B347" s="9"/>
       <c r="C347" s="9"/>
       <c r="D347" s="9"/>
@@ -9185,7 +9193,7 @@
       <c r="L347" s="9"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="A348" s="31"/>
+      <c r="A348" s="32"/>
       <c r="B348" s="9"/>
       <c r="C348" s="9"/>
       <c r="D348" s="9"/>
@@ -9199,7 +9207,7 @@
       <c r="L348" s="9"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="A349" s="31"/>
+      <c r="A349" s="32"/>
       <c r="B349" s="9"/>
       <c r="C349" s="9"/>
       <c r="D349" s="9"/>
@@ -9213,7 +9221,7 @@
       <c r="L349" s="9"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="31"/>
+      <c r="A350" s="32"/>
       <c r="B350" s="9"/>
       <c r="C350" s="9"/>
       <c r="D350" s="9"/>
@@ -9227,7 +9235,7 @@
       <c r="L350" s="9"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="31"/>
+      <c r="A351" s="32"/>
       <c r="B351" s="9"/>
       <c r="C351" s="9"/>
       <c r="D351" s="9"/>
@@ -9241,7 +9249,7 @@
       <c r="L351" s="9"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="31"/>
+      <c r="A352" s="32"/>
       <c r="B352" s="9"/>
       <c r="C352" s="9"/>
       <c r="D352" s="9"/>
@@ -9255,7 +9263,7 @@
       <c r="L352" s="9"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="31"/>
+      <c r="A353" s="32"/>
       <c r="B353" s="9"/>
       <c r="C353" s="9"/>
       <c r="D353" s="9"/>
@@ -9269,7 +9277,7 @@
       <c r="L353" s="9"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="31"/>
+      <c r="A354" s="32"/>
       <c r="B354" s="9"/>
       <c r="C354" s="9"/>
       <c r="D354" s="9"/>
@@ -9283,7 +9291,7 @@
       <c r="L354" s="9"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="31"/>
+      <c r="A355" s="32"/>
       <c r="B355" s="9"/>
       <c r="C355" s="9"/>
       <c r="D355" s="9"/>
@@ -9297,7 +9305,7 @@
       <c r="L355" s="9"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="31"/>
+      <c r="A356" s="32"/>
       <c r="B356" s="9"/>
       <c r="C356" s="9"/>
       <c r="D356" s="9"/>
@@ -9311,7 +9319,7 @@
       <c r="L356" s="9"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="31"/>
+      <c r="A357" s="32"/>
       <c r="B357" s="9"/>
       <c r="C357" s="9"/>
       <c r="D357" s="9"/>
@@ -9325,7 +9333,7 @@
       <c r="L357" s="9"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="31"/>
+      <c r="A358" s="32"/>
       <c r="B358" s="9"/>
       <c r="C358" s="9"/>
       <c r="D358" s="9"/>
@@ -9339,7 +9347,7 @@
       <c r="L358" s="9"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="31"/>
+      <c r="A359" s="32"/>
       <c r="B359" s="9"/>
       <c r="C359" s="9"/>
       <c r="D359" s="9"/>
@@ -9353,7 +9361,7 @@
       <c r="L359" s="9"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="31"/>
+      <c r="A360" s="32"/>
       <c r="B360" s="9"/>
       <c r="C360" s="9"/>
       <c r="D360" s="9"/>
@@ -9367,7 +9375,7 @@
       <c r="L360" s="9"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="31"/>
+      <c r="A361" s="32"/>
       <c r="B361" s="9"/>
       <c r="C361" s="9"/>
       <c r="D361" s="9"/>
@@ -9381,7 +9389,7 @@
       <c r="L361" s="9"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="31"/>
+      <c r="A362" s="32"/>
       <c r="B362" s="9"/>
       <c r="C362" s="9"/>
       <c r="D362" s="9"/>
@@ -9395,7 +9403,7 @@
       <c r="L362" s="9"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="31"/>
+      <c r="A363" s="32"/>
       <c r="B363" s="9"/>
       <c r="C363" s="9"/>
       <c r="D363" s="9"/>
@@ -9409,7 +9417,7 @@
       <c r="L363" s="9"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="31"/>
+      <c r="A364" s="32"/>
       <c r="B364" s="9"/>
       <c r="C364" s="9"/>
       <c r="D364" s="9"/>
@@ -9423,7 +9431,7 @@
       <c r="L364" s="9"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="31"/>
+      <c r="A365" s="32"/>
       <c r="B365" s="9"/>
       <c r="C365" s="9"/>
       <c r="D365" s="9"/>
@@ -9437,7 +9445,7 @@
       <c r="L365" s="9"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="31"/>
+      <c r="A366" s="32"/>
       <c r="B366" s="9"/>
       <c r="C366" s="9"/>
       <c r="D366" s="9"/>
@@ -9451,7 +9459,7 @@
       <c r="L366" s="9"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="31"/>
+      <c r="A367" s="32"/>
       <c r="B367" s="9"/>
       <c r="C367" s="9"/>
       <c r="D367" s="9"/>
@@ -9465,7 +9473,7 @@
       <c r="L367" s="9"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="31"/>
+      <c r="A368" s="32"/>
       <c r="B368" s="9"/>
       <c r="C368" s="9"/>
       <c r="D368" s="9"/>
@@ -9479,7 +9487,7 @@
       <c r="L368" s="9"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="31"/>
+      <c r="A369" s="32"/>
       <c r="B369" s="9"/>
       <c r="C369" s="9"/>
       <c r="D369" s="9"/>
@@ -9493,7 +9501,7 @@
       <c r="L369" s="9"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="31"/>
+      <c r="A370" s="32"/>
       <c r="B370" s="9"/>
       <c r="C370" s="9"/>
       <c r="D370" s="9"/>
@@ -9507,7 +9515,7 @@
       <c r="L370" s="9"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="31"/>
+      <c r="A371" s="32"/>
       <c r="B371" s="9"/>
       <c r="C371" s="9"/>
       <c r="D371" s="9"/>
@@ -9521,7 +9529,7 @@
       <c r="L371" s="9"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="31"/>
+      <c r="A372" s="32"/>
       <c r="B372" s="9"/>
       <c r="C372" s="9"/>
       <c r="D372" s="9"/>
@@ -9535,7 +9543,7 @@
       <c r="L372" s="9"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="31"/>
+      <c r="A373" s="32"/>
       <c r="B373" s="9"/>
       <c r="C373" s="9"/>
       <c r="D373" s="9"/>
@@ -9549,7 +9557,7 @@
       <c r="L373" s="9"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="31"/>
+      <c r="A374" s="32"/>
       <c r="B374" s="9"/>
       <c r="C374" s="9"/>
       <c r="D374" s="9"/>
@@ -9563,7 +9571,7 @@
       <c r="L374" s="9"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="31"/>
+      <c r="A375" s="32"/>
       <c r="B375" s="9"/>
       <c r="C375" s="9"/>
       <c r="D375" s="9"/>
@@ -9577,7 +9585,7 @@
       <c r="L375" s="9"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="31"/>
+      <c r="A376" s="32"/>
       <c r="B376" s="9"/>
       <c r="C376" s="9"/>
       <c r="D376" s="9"/>
@@ -9591,7 +9599,7 @@
       <c r="L376" s="9"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="31"/>
+      <c r="A377" s="32"/>
       <c r="B377" s="9"/>
       <c r="C377" s="9"/>
       <c r="D377" s="9"/>
@@ -9605,7 +9613,7 @@
       <c r="L377" s="9"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="31"/>
+      <c r="A378" s="32"/>
       <c r="B378" s="9"/>
       <c r="C378" s="9"/>
       <c r="D378" s="9"/>
@@ -9619,7 +9627,7 @@
       <c r="L378" s="9"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="A379" s="31"/>
+      <c r="A379" s="32"/>
       <c r="B379" s="9"/>
       <c r="C379" s="9"/>
       <c r="D379" s="9"/>
@@ -9633,7 +9641,7 @@
       <c r="L379" s="9"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="31"/>
+      <c r="A380" s="32"/>
       <c r="B380" s="9"/>
       <c r="C380" s="9"/>
       <c r="D380" s="9"/>
@@ -9647,7 +9655,7 @@
       <c r="L380" s="9"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="A381" s="31"/>
+      <c r="A381" s="32"/>
       <c r="B381" s="9"/>
       <c r="C381" s="9"/>
       <c r="D381" s="9"/>
@@ -9661,7 +9669,7 @@
       <c r="L381" s="9"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="31"/>
+      <c r="A382" s="32"/>
       <c r="B382" s="9"/>
       <c r="C382" s="9"/>
       <c r="D382" s="9"/>
@@ -9675,7 +9683,7 @@
       <c r="L382" s="9"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="31"/>
+      <c r="A383" s="32"/>
       <c r="B383" s="9"/>
       <c r="C383" s="9"/>
       <c r="D383" s="9"/>
@@ -9689,7 +9697,7 @@
       <c r="L383" s="9"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="A384" s="31"/>
+      <c r="A384" s="32"/>
       <c r="B384" s="9"/>
       <c r="C384" s="9"/>
       <c r="D384" s="9"/>
@@ -9703,7 +9711,7 @@
       <c r="L384" s="9"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="31"/>
+      <c r="A385" s="32"/>
       <c r="B385" s="9"/>
       <c r="C385" s="9"/>
       <c r="D385" s="9"/>
@@ -9717,7 +9725,7 @@
       <c r="L385" s="9"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="31"/>
+      <c r="A386" s="32"/>
       <c r="B386" s="9"/>
       <c r="C386" s="9"/>
       <c r="D386" s="9"/>
@@ -9731,7 +9739,7 @@
       <c r="L386" s="9"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="A387" s="31"/>
+      <c r="A387" s="32"/>
       <c r="B387" s="9"/>
       <c r="C387" s="9"/>
       <c r="D387" s="9"/>
@@ -9745,7 +9753,7 @@
       <c r="L387" s="9"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="A388" s="31"/>
+      <c r="A388" s="32"/>
       <c r="B388" s="9"/>
       <c r="C388" s="9"/>
       <c r="D388" s="9"/>
@@ -9759,7 +9767,7 @@
       <c r="L388" s="9"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="A389" s="31"/>
+      <c r="A389" s="32"/>
       <c r="B389" s="9"/>
       <c r="C389" s="9"/>
       <c r="D389" s="9"/>
@@ -9773,7 +9781,7 @@
       <c r="L389" s="9"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="31"/>
+      <c r="A390" s="32"/>
       <c r="B390" s="9"/>
       <c r="C390" s="9"/>
       <c r="D390" s="9"/>
@@ -9787,7 +9795,7 @@
       <c r="L390" s="9"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="31"/>
+      <c r="A391" s="32"/>
       <c r="B391" s="9"/>
       <c r="C391" s="9"/>
       <c r="D391" s="9"/>
@@ -9801,7 +9809,7 @@
       <c r="L391" s="9"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="A392" s="31"/>
+      <c r="A392" s="32"/>
       <c r="B392" s="9"/>
       <c r="C392" s="9"/>
       <c r="D392" s="9"/>
@@ -9815,7 +9823,7 @@
       <c r="L392" s="9"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="31"/>
+      <c r="A393" s="32"/>
       <c r="B393" s="9"/>
       <c r="C393" s="9"/>
       <c r="D393" s="9"/>
@@ -9829,7 +9837,7 @@
       <c r="L393" s="9"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="A394" s="31"/>
+      <c r="A394" s="32"/>
       <c r="B394" s="9"/>
       <c r="C394" s="9"/>
       <c r="D394" s="9"/>
@@ -9843,7 +9851,7 @@
       <c r="L394" s="9"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="31"/>
+      <c r="A395" s="32"/>
       <c r="B395" s="9"/>
       <c r="C395" s="9"/>
       <c r="D395" s="9"/>
@@ -9857,7 +9865,7 @@
       <c r="L395" s="9"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="31"/>
+      <c r="A396" s="32"/>
       <c r="B396" s="9"/>
       <c r="C396" s="9"/>
       <c r="D396" s="9"/>
@@ -9871,7 +9879,7 @@
       <c r="L396" s="9"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="A397" s="31"/>
+      <c r="A397" s="32"/>
       <c r="B397" s="9"/>
       <c r="C397" s="9"/>
       <c r="D397" s="9"/>
@@ -9885,7 +9893,7 @@
       <c r="L397" s="9"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="A398" s="31"/>
+      <c r="A398" s="32"/>
       <c r="B398" s="9"/>
       <c r="C398" s="9"/>
       <c r="D398" s="9"/>
@@ -9899,7 +9907,7 @@
       <c r="L398" s="9"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="31"/>
+      <c r="A399" s="32"/>
       <c r="B399" s="9"/>
       <c r="C399" s="9"/>
       <c r="D399" s="9"/>
@@ -9913,7 +9921,7 @@
       <c r="L399" s="9"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="A400" s="31"/>
+      <c r="A400" s="32"/>
       <c r="B400" s="9"/>
       <c r="C400" s="9"/>
       <c r="D400" s="9"/>
@@ -9927,7 +9935,7 @@
       <c r="L400" s="9"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="31"/>
+      <c r="A401" s="32"/>
       <c r="B401" s="9"/>
       <c r="C401" s="9"/>
       <c r="D401" s="9"/>
@@ -9941,7 +9949,7 @@
       <c r="L401" s="9"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="31"/>
+      <c r="A402" s="32"/>
       <c r="B402" s="9"/>
       <c r="C402" s="9"/>
       <c r="D402" s="9"/>
@@ -9955,7 +9963,7 @@
       <c r="L402" s="9"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="A403" s="31"/>
+      <c r="A403" s="32"/>
       <c r="B403" s="9"/>
       <c r="C403" s="9"/>
       <c r="D403" s="9"/>
@@ -9969,7 +9977,7 @@
       <c r="L403" s="9"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="A404" s="31"/>
+      <c r="A404" s="32"/>
       <c r="B404" s="9"/>
       <c r="C404" s="9"/>
       <c r="D404" s="9"/>
@@ -9983,7 +9991,7 @@
       <c r="L404" s="9"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="A405" s="31"/>
+      <c r="A405" s="32"/>
       <c r="B405" s="9"/>
       <c r="C405" s="9"/>
       <c r="D405" s="9"/>
@@ -9997,7 +10005,7 @@
       <c r="L405" s="9"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="A406" s="31"/>
+      <c r="A406" s="32"/>
       <c r="B406" s="9"/>
       <c r="C406" s="9"/>
       <c r="D406" s="9"/>
@@ -10011,7 +10019,7 @@
       <c r="L406" s="9"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="A407" s="31"/>
+      <c r="A407" s="32"/>
       <c r="B407" s="9"/>
       <c r="C407" s="9"/>
       <c r="D407" s="9"/>
@@ -10025,7 +10033,7 @@
       <c r="L407" s="9"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="A408" s="31"/>
+      <c r="A408" s="32"/>
       <c r="B408" s="9"/>
       <c r="C408" s="9"/>
       <c r="D408" s="9"/>
@@ -10039,7 +10047,7 @@
       <c r="L408" s="9"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="A409" s="31"/>
+      <c r="A409" s="32"/>
       <c r="B409" s="9"/>
       <c r="C409" s="9"/>
       <c r="D409" s="9"/>
@@ -10053,7 +10061,7 @@
       <c r="L409" s="9"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="A410" s="31"/>
+      <c r="A410" s="32"/>
       <c r="B410" s="9"/>
       <c r="C410" s="9"/>
       <c r="D410" s="9"/>
@@ -10067,7 +10075,7 @@
       <c r="L410" s="9"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="A411" s="31"/>
+      <c r="A411" s="32"/>
       <c r="B411" s="9"/>
       <c r="C411" s="9"/>
       <c r="D411" s="9"/>
@@ -10081,7 +10089,7 @@
       <c r="L411" s="9"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="A412" s="31"/>
+      <c r="A412" s="32"/>
       <c r="B412" s="9"/>
       <c r="C412" s="9"/>
       <c r="D412" s="9"/>
@@ -10095,7 +10103,7 @@
       <c r="L412" s="9"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="31"/>
+      <c r="A413" s="32"/>
       <c r="B413" s="9"/>
       <c r="C413" s="9"/>
       <c r="D413" s="9"/>
@@ -10109,7 +10117,7 @@
       <c r="L413" s="9"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="A414" s="31"/>
+      <c r="A414" s="32"/>
       <c r="B414" s="9"/>
       <c r="C414" s="9"/>
       <c r="D414" s="9"/>
@@ -10123,7 +10131,7 @@
       <c r="L414" s="9"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="A415" s="31"/>
+      <c r="A415" s="32"/>
       <c r="B415" s="9"/>
       <c r="C415" s="9"/>
       <c r="D415" s="9"/>
@@ -10137,7 +10145,7 @@
       <c r="L415" s="9"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="31"/>
+      <c r="A416" s="32"/>
       <c r="B416" s="9"/>
       <c r="C416" s="9"/>
       <c r="D416" s="9"/>
@@ -10151,7 +10159,7 @@
       <c r="L416" s="9"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="A417" s="31"/>
+      <c r="A417" s="32"/>
       <c r="B417" s="9"/>
       <c r="C417" s="9"/>
       <c r="D417" s="9"/>
@@ -10165,7 +10173,7 @@
       <c r="L417" s="9"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="A418" s="31"/>
+      <c r="A418" s="32"/>
       <c r="B418" s="9"/>
       <c r="C418" s="9"/>
       <c r="D418" s="9"/>
@@ -10179,7 +10187,7 @@
       <c r="L418" s="9"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="A419" s="31"/>
+      <c r="A419" s="32"/>
       <c r="B419" s="9"/>
       <c r="C419" s="9"/>
       <c r="D419" s="9"/>
@@ -10193,7 +10201,7 @@
       <c r="L419" s="9"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="A420" s="31"/>
+      <c r="A420" s="32"/>
       <c r="B420" s="9"/>
       <c r="C420" s="9"/>
       <c r="D420" s="9"/>
@@ -10207,7 +10215,7 @@
       <c r="L420" s="9"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="A421" s="31"/>
+      <c r="A421" s="32"/>
       <c r="B421" s="9"/>
       <c r="C421" s="9"/>
       <c r="D421" s="9"/>
@@ -10221,7 +10229,7 @@
       <c r="L421" s="9"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="31"/>
+      <c r="A422" s="32"/>
       <c r="B422" s="9"/>
       <c r="C422" s="9"/>
       <c r="D422" s="9"/>
@@ -10235,7 +10243,7 @@
       <c r="L422" s="9"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="A423" s="31"/>
+      <c r="A423" s="32"/>
       <c r="B423" s="9"/>
       <c r="C423" s="9"/>
       <c r="D423" s="9"/>
@@ -10249,7 +10257,7 @@
       <c r="L423" s="9"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="A424" s="31"/>
+      <c r="A424" s="32"/>
       <c r="B424" s="9"/>
       <c r="C424" s="9"/>
       <c r="D424" s="9"/>
@@ -10263,7 +10271,7 @@
       <c r="L424" s="9"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="31"/>
+      <c r="A425" s="32"/>
       <c r="B425" s="9"/>
       <c r="C425" s="9"/>
       <c r="D425" s="9"/>
@@ -10277,7 +10285,7 @@
       <c r="L425" s="9"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="31"/>
+      <c r="A426" s="32"/>
       <c r="B426" s="9"/>
       <c r="C426" s="9"/>
       <c r="D426" s="9"/>
@@ -10291,7 +10299,7 @@
       <c r="L426" s="9"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="31"/>
+      <c r="A427" s="32"/>
       <c r="B427" s="9"/>
       <c r="C427" s="9"/>
       <c r="D427" s="9"/>
@@ -10305,7 +10313,7 @@
       <c r="L427" s="9"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="31"/>
+      <c r="A428" s="32"/>
       <c r="B428" s="9"/>
       <c r="C428" s="9"/>
       <c r="D428" s="9"/>
@@ -10319,7 +10327,7 @@
       <c r="L428" s="9"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="A429" s="31"/>
+      <c r="A429" s="32"/>
       <c r="B429" s="9"/>
       <c r="C429" s="9"/>
       <c r="D429" s="9"/>
@@ -10333,7 +10341,7 @@
       <c r="L429" s="9"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="31"/>
+      <c r="A430" s="32"/>
       <c r="B430" s="9"/>
       <c r="C430" s="9"/>
       <c r="D430" s="9"/>
@@ -10347,7 +10355,7 @@
       <c r="L430" s="9"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="31"/>
+      <c r="A431" s="32"/>
       <c r="B431" s="9"/>
       <c r="C431" s="9"/>
       <c r="D431" s="9"/>
@@ -10361,7 +10369,7 @@
       <c r="L431" s="9"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="31"/>
+      <c r="A432" s="32"/>
       <c r="B432" s="9"/>
       <c r="C432" s="9"/>
       <c r="D432" s="9"/>
@@ -10375,7 +10383,7 @@
       <c r="L432" s="9"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="31"/>
+      <c r="A433" s="32"/>
       <c r="B433" s="9"/>
       <c r="C433" s="9"/>
       <c r="D433" s="9"/>
@@ -10389,7 +10397,7 @@
       <c r="L433" s="9"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="31"/>
+      <c r="A434" s="32"/>
       <c r="B434" s="9"/>
       <c r="C434" s="9"/>
       <c r="D434" s="9"/>
@@ -10403,7 +10411,7 @@
       <c r="L434" s="9"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="31"/>
+      <c r="A435" s="32"/>
       <c r="B435" s="9"/>
       <c r="C435" s="9"/>
       <c r="D435" s="9"/>
@@ -10417,7 +10425,7 @@
       <c r="L435" s="9"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="31"/>
+      <c r="A436" s="32"/>
       <c r="B436" s="9"/>
       <c r="C436" s="9"/>
       <c r="D436" s="9"/>
@@ -10431,7 +10439,7 @@
       <c r="L436" s="9"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="31"/>
+      <c r="A437" s="32"/>
       <c r="B437" s="9"/>
       <c r="C437" s="9"/>
       <c r="D437" s="9"/>
@@ -10445,7 +10453,7 @@
       <c r="L437" s="9"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="31"/>
+      <c r="A438" s="32"/>
       <c r="B438" s="9"/>
       <c r="C438" s="9"/>
       <c r="D438" s="9"/>
@@ -10459,7 +10467,7 @@
       <c r="L438" s="9"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="31"/>
+      <c r="A439" s="32"/>
       <c r="B439" s="9"/>
       <c r="C439" s="9"/>
       <c r="D439" s="9"/>
@@ -10473,7 +10481,7 @@
       <c r="L439" s="9"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="31"/>
+      <c r="A440" s="32"/>
       <c r="B440" s="9"/>
       <c r="C440" s="9"/>
       <c r="D440" s="9"/>
@@ -10487,7 +10495,7 @@
       <c r="L440" s="9"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="31"/>
+      <c r="A441" s="32"/>
       <c r="B441" s="9"/>
       <c r="C441" s="9"/>
       <c r="D441" s="9"/>
@@ -10501,7 +10509,7 @@
       <c r="L441" s="9"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="31"/>
+      <c r="A442" s="32"/>
       <c r="B442" s="9"/>
       <c r="C442" s="9"/>
       <c r="D442" s="9"/>
@@ -10515,7 +10523,7 @@
       <c r="L442" s="9"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="31"/>
+      <c r="A443" s="32"/>
       <c r="B443" s="9"/>
       <c r="C443" s="9"/>
       <c r="D443" s="9"/>
@@ -10529,7 +10537,7 @@
       <c r="L443" s="9"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="31"/>
+      <c r="A444" s="32"/>
       <c r="B444" s="9"/>
       <c r="C444" s="9"/>
       <c r="D444" s="9"/>
@@ -10543,7 +10551,7 @@
       <c r="L444" s="9"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="31"/>
+      <c r="A445" s="32"/>
       <c r="B445" s="9"/>
       <c r="C445" s="9"/>
       <c r="D445" s="9"/>
@@ -10557,7 +10565,7 @@
       <c r="L445" s="9"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="31"/>
+      <c r="A446" s="32"/>
       <c r="B446" s="9"/>
       <c r="C446" s="9"/>
       <c r="D446" s="9"/>
@@ -10571,7 +10579,7 @@
       <c r="L446" s="9"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="A447" s="31"/>
+      <c r="A447" s="32"/>
       <c r="B447" s="9"/>
       <c r="C447" s="9"/>
       <c r="D447" s="9"/>
@@ -10585,7 +10593,7 @@
       <c r="L447" s="9"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="A448" s="31"/>
+      <c r="A448" s="32"/>
       <c r="B448" s="9"/>
       <c r="C448" s="9"/>
       <c r="D448" s="9"/>
@@ -10599,7 +10607,7 @@
       <c r="L448" s="9"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="A449" s="31"/>
+      <c r="A449" s="32"/>
       <c r="B449" s="9"/>
       <c r="C449" s="9"/>
       <c r="D449" s="9"/>
@@ -10613,7 +10621,7 @@
       <c r="L449" s="9"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="A450" s="31"/>
+      <c r="A450" s="32"/>
       <c r="B450" s="9"/>
       <c r="C450" s="9"/>
       <c r="D450" s="9"/>
@@ -10627,7 +10635,7 @@
       <c r="L450" s="9"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="31"/>
+      <c r="A451" s="32"/>
       <c r="B451" s="9"/>
       <c r="C451" s="9"/>
       <c r="D451" s="9"/>
@@ -10641,7 +10649,7 @@
       <c r="L451" s="9"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="A452" s="31"/>
+      <c r="A452" s="32"/>
       <c r="B452" s="9"/>
       <c r="C452" s="9"/>
       <c r="D452" s="9"/>
@@ -10655,7 +10663,7 @@
       <c r="L452" s="9"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="31"/>
+      <c r="A453" s="32"/>
       <c r="B453" s="9"/>
       <c r="C453" s="9"/>
       <c r="D453" s="9"/>
@@ -10669,7 +10677,7 @@
       <c r="L453" s="9"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="A454" s="31"/>
+      <c r="A454" s="32"/>
       <c r="B454" s="9"/>
       <c r="C454" s="9"/>
       <c r="D454" s="9"/>
@@ -10683,7 +10691,7 @@
       <c r="L454" s="9"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="A455" s="31"/>
+      <c r="A455" s="32"/>
       <c r="B455" s="9"/>
       <c r="C455" s="9"/>
       <c r="D455" s="9"/>
@@ -10697,7 +10705,7 @@
       <c r="L455" s="9"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="31"/>
+      <c r="A456" s="32"/>
       <c r="B456" s="9"/>
       <c r="C456" s="9"/>
       <c r="D456" s="9"/>
@@ -10711,7 +10719,7 @@
       <c r="L456" s="9"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="A457" s="31"/>
+      <c r="A457" s="32"/>
       <c r="B457" s="9"/>
       <c r="C457" s="9"/>
       <c r="D457" s="9"/>
@@ -10725,7 +10733,7 @@
       <c r="L457" s="9"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="A458" s="31"/>
+      <c r="A458" s="32"/>
       <c r="B458" s="9"/>
       <c r="C458" s="9"/>
       <c r="D458" s="9"/>
@@ -10739,7 +10747,7 @@
       <c r="L458" s="9"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="A459" s="31"/>
+      <c r="A459" s="32"/>
       <c r="B459" s="9"/>
       <c r="C459" s="9"/>
       <c r="D459" s="9"/>
@@ -10753,7 +10761,7 @@
       <c r="L459" s="9"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="A460" s="31"/>
+      <c r="A460" s="32"/>
       <c r="B460" s="9"/>
       <c r="C460" s="9"/>
       <c r="D460" s="9"/>
@@ -10767,7 +10775,7 @@
       <c r="L460" s="9"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="31"/>
+      <c r="A461" s="32"/>
       <c r="B461" s="9"/>
       <c r="C461" s="9"/>
       <c r="D461" s="9"/>
@@ -10781,7 +10789,7 @@
       <c r="L461" s="9"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="31"/>
+      <c r="A462" s="32"/>
       <c r="B462" s="9"/>
       <c r="C462" s="9"/>
       <c r="D462" s="9"/>
@@ -10795,7 +10803,7 @@
       <c r="L462" s="9"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="A463" s="31"/>
+      <c r="A463" s="32"/>
       <c r="B463" s="9"/>
       <c r="C463" s="9"/>
       <c r="D463" s="9"/>
@@ -10809,7 +10817,7 @@
       <c r="L463" s="9"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="31"/>
+      <c r="A464" s="32"/>
       <c r="B464" s="9"/>
       <c r="C464" s="9"/>
       <c r="D464" s="9"/>
@@ -10823,7 +10831,7 @@
       <c r="L464" s="9"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="31"/>
+      <c r="A465" s="32"/>
       <c r="B465" s="9"/>
       <c r="C465" s="9"/>
       <c r="D465" s="9"/>
@@ -10837,7 +10845,7 @@
       <c r="L465" s="9"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="31"/>
+      <c r="A466" s="32"/>
       <c r="B466" s="9"/>
       <c r="C466" s="9"/>
       <c r="D466" s="9"/>
@@ -10851,7 +10859,7 @@
       <c r="L466" s="9"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="A467" s="31"/>
+      <c r="A467" s="32"/>
       <c r="B467" s="9"/>
       <c r="C467" s="9"/>
       <c r="D467" s="9"/>
@@ -10865,7 +10873,7 @@
       <c r="L467" s="9"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="31"/>
+      <c r="A468" s="32"/>
       <c r="B468" s="9"/>
       <c r="C468" s="9"/>
       <c r="D468" s="9"/>
@@ -10879,7 +10887,7 @@
       <c r="L468" s="9"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="31"/>
+      <c r="A469" s="32"/>
       <c r="B469" s="9"/>
       <c r="C469" s="9"/>
       <c r="D469" s="9"/>
@@ -10893,7 +10901,7 @@
       <c r="L469" s="9"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="31"/>
+      <c r="A470" s="32"/>
       <c r="B470" s="9"/>
       <c r="C470" s="9"/>
       <c r="D470" s="9"/>
@@ -10907,7 +10915,7 @@
       <c r="L470" s="9"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="31"/>
+      <c r="A471" s="32"/>
       <c r="B471" s="9"/>
       <c r="C471" s="9"/>
       <c r="D471" s="9"/>
@@ -10921,7 +10929,7 @@
       <c r="L471" s="9"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="A472" s="31"/>
+      <c r="A472" s="32"/>
       <c r="B472" s="9"/>
       <c r="C472" s="9"/>
       <c r="D472" s="9"/>
@@ -10935,7 +10943,7 @@
       <c r="L472" s="9"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="31"/>
+      <c r="A473" s="32"/>
       <c r="B473" s="9"/>
       <c r="C473" s="9"/>
       <c r="D473" s="9"/>
@@ -10949,7 +10957,7 @@
       <c r="L473" s="9"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="A474" s="31"/>
+      <c r="A474" s="32"/>
       <c r="B474" s="9"/>
       <c r="C474" s="9"/>
       <c r="D474" s="9"/>
@@ -10963,7 +10971,7 @@
       <c r="L474" s="9"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="31"/>
+      <c r="A475" s="32"/>
       <c r="B475" s="9"/>
       <c r="C475" s="9"/>
       <c r="D475" s="9"/>
@@ -10977,7 +10985,7 @@
       <c r="L475" s="9"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="31"/>
+      <c r="A476" s="32"/>
       <c r="B476" s="9"/>
       <c r="C476" s="9"/>
       <c r="D476" s="9"/>
@@ -10991,7 +10999,7 @@
       <c r="L476" s="9"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="31"/>
+      <c r="A477" s="32"/>
       <c r="B477" s="9"/>
       <c r="C477" s="9"/>
       <c r="D477" s="9"/>
@@ -11005,7 +11013,7 @@
       <c r="L477" s="9"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="31"/>
+      <c r="A478" s="32"/>
       <c r="B478" s="9"/>
       <c r="C478" s="9"/>
       <c r="D478" s="9"/>
@@ -11019,7 +11027,7 @@
       <c r="L478" s="9"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="A479" s="31"/>
+      <c r="A479" s="32"/>
       <c r="B479" s="9"/>
       <c r="C479" s="9"/>
       <c r="D479" s="9"/>
@@ -11033,7 +11041,7 @@
       <c r="L479" s="9"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="A480" s="31"/>
+      <c r="A480" s="32"/>
       <c r="B480" s="9"/>
       <c r="C480" s="9"/>
       <c r="D480" s="9"/>
@@ -11047,7 +11055,7 @@
       <c r="L480" s="9"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="A481" s="31"/>
+      <c r="A481" s="32"/>
       <c r="B481" s="9"/>
       <c r="C481" s="9"/>
       <c r="D481" s="9"/>
@@ -11061,7 +11069,7 @@
       <c r="L481" s="9"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="A482" s="31"/>
+      <c r="A482" s="32"/>
       <c r="B482" s="9"/>
       <c r="C482" s="9"/>
       <c r="D482" s="9"/>
@@ -11075,7 +11083,7 @@
       <c r="L482" s="9"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="A483" s="31"/>
+      <c r="A483" s="32"/>
       <c r="B483" s="9"/>
       <c r="C483" s="9"/>
       <c r="D483" s="9"/>
@@ -11089,7 +11097,7 @@
       <c r="L483" s="9"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="A484" s="31"/>
+      <c r="A484" s="32"/>
       <c r="B484" s="9"/>
       <c r="C484" s="9"/>
       <c r="D484" s="9"/>
@@ -11103,7 +11111,7 @@
       <c r="L484" s="9"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="A485" s="31"/>
+      <c r="A485" s="32"/>
       <c r="B485" s="9"/>
       <c r="C485" s="9"/>
       <c r="D485" s="9"/>
@@ -11117,7 +11125,7 @@
       <c r="L485" s="9"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="A486" s="31"/>
+      <c r="A486" s="32"/>
       <c r="B486" s="9"/>
       <c r="C486" s="9"/>
       <c r="D486" s="9"/>
@@ -11131,7 +11139,7 @@
       <c r="L486" s="9"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="A487" s="31"/>
+      <c r="A487" s="32"/>
       <c r="B487" s="9"/>
       <c r="C487" s="9"/>
       <c r="D487" s="9"/>
@@ -11145,7 +11153,7 @@
       <c r="L487" s="9"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="A488" s="31"/>
+      <c r="A488" s="32"/>
       <c r="B488" s="9"/>
       <c r="C488" s="9"/>
       <c r="D488" s="9"/>
@@ -11159,7 +11167,7 @@
       <c r="L488" s="9"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="A489" s="31"/>
+      <c r="A489" s="32"/>
       <c r="B489" s="9"/>
       <c r="C489" s="9"/>
       <c r="D489" s="9"/>
@@ -11173,7 +11181,7 @@
       <c r="L489" s="9"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="A490" s="31"/>
+      <c r="A490" s="32"/>
       <c r="B490" s="9"/>
       <c r="C490" s="9"/>
       <c r="D490" s="9"/>
@@ -11187,7 +11195,7 @@
       <c r="L490" s="9"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="A491" s="31"/>
+      <c r="A491" s="32"/>
       <c r="B491" s="9"/>
       <c r="C491" s="9"/>
       <c r="D491" s="9"/>
@@ -11201,7 +11209,7 @@
       <c r="L491" s="9"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="A492" s="31"/>
+      <c r="A492" s="32"/>
       <c r="B492" s="9"/>
       <c r="C492" s="9"/>
       <c r="D492" s="9"/>
@@ -11215,7 +11223,7 @@
       <c r="L492" s="9"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="A493" s="31"/>
+      <c r="A493" s="32"/>
       <c r="B493" s="9"/>
       <c r="C493" s="9"/>
       <c r="D493" s="9"/>
@@ -11229,7 +11237,7 @@
       <c r="L493" s="9"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="A494" s="31"/>
+      <c r="A494" s="32"/>
       <c r="B494" s="9"/>
       <c r="C494" s="9"/>
       <c r="D494" s="9"/>
@@ -11243,7 +11251,7 @@
       <c r="L494" s="9"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="A495" s="31"/>
+      <c r="A495" s="32"/>
       <c r="B495" s="9"/>
       <c r="C495" s="9"/>
       <c r="D495" s="9"/>
@@ -11257,7 +11265,7 @@
       <c r="L495" s="9"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="A496" s="31"/>
+      <c r="A496" s="32"/>
       <c r="B496" s="9"/>
       <c r="C496" s="9"/>
       <c r="D496" s="9"/>
@@ -11271,7 +11279,7 @@
       <c r="L496" s="9"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="A497" s="31"/>
+      <c r="A497" s="32"/>
       <c r="B497" s="9"/>
       <c r="C497" s="9"/>
       <c r="D497" s="9"/>
@@ -11285,7 +11293,7 @@
       <c r="L497" s="9"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="A498" s="31"/>
+      <c r="A498" s="32"/>
       <c r="B498" s="9"/>
       <c r="C498" s="9"/>
       <c r="D498" s="9"/>
@@ -11299,7 +11307,7 @@
       <c r="L498" s="9"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="A499" s="31"/>
+      <c r="A499" s="32"/>
       <c r="B499" s="9"/>
       <c r="C499" s="9"/>
       <c r="D499" s="9"/>
@@ -11313,7 +11321,7 @@
       <c r="L499" s="9"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="A500" s="31"/>
+      <c r="A500" s="32"/>
       <c r="B500" s="9"/>
       <c r="C500" s="9"/>
       <c r="D500" s="9"/>
@@ -11327,7 +11335,7 @@
       <c r="L500" s="9"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="A501" s="31"/>
+      <c r="A501" s="32"/>
       <c r="B501" s="9"/>
       <c r="C501" s="9"/>
       <c r="D501" s="9"/>
@@ -11341,7 +11349,7 @@
       <c r="L501" s="9"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="A502" s="31"/>
+      <c r="A502" s="32"/>
       <c r="B502" s="9"/>
       <c r="C502" s="9"/>
       <c r="D502" s="9"/>
@@ -11355,7 +11363,7 @@
       <c r="L502" s="9"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="A503" s="31"/>
+      <c r="A503" s="32"/>
       <c r="B503" s="9"/>
       <c r="C503" s="9"/>
       <c r="D503" s="9"/>
@@ -11369,7 +11377,7 @@
       <c r="L503" s="9"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="A504" s="31"/>
+      <c r="A504" s="32"/>
       <c r="B504" s="9"/>
       <c r="C504" s="9"/>
       <c r="D504" s="9"/>
@@ -11383,7 +11391,7 @@
       <c r="L504" s="9"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="A505" s="31"/>
+      <c r="A505" s="32"/>
       <c r="B505" s="9"/>
       <c r="C505" s="9"/>
       <c r="D505" s="9"/>
@@ -11397,7 +11405,7 @@
       <c r="L505" s="9"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="A506" s="31"/>
+      <c r="A506" s="32"/>
       <c r="B506" s="9"/>
       <c r="C506" s="9"/>
       <c r="D506" s="9"/>
@@ -11411,7 +11419,7 @@
       <c r="L506" s="9"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="A507" s="31"/>
+      <c r="A507" s="32"/>
       <c r="B507" s="9"/>
       <c r="C507" s="9"/>
       <c r="D507" s="9"/>
@@ -11425,7 +11433,7 @@
       <c r="L507" s="9"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="A508" s="31"/>
+      <c r="A508" s="32"/>
       <c r="B508" s="9"/>
       <c r="C508" s="9"/>
       <c r="D508" s="9"/>
@@ -11439,7 +11447,7 @@
       <c r="L508" s="9"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="A509" s="31"/>
+      <c r="A509" s="32"/>
       <c r="B509" s="9"/>
       <c r="C509" s="9"/>
       <c r="D509" s="9"/>
@@ -11453,7 +11461,7 @@
       <c r="L509" s="9"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="A510" s="31"/>
+      <c r="A510" s="32"/>
       <c r="B510" s="9"/>
       <c r="C510" s="9"/>
       <c r="D510" s="9"/>
@@ -11467,7 +11475,7 @@
       <c r="L510" s="9"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="A511" s="31"/>
+      <c r="A511" s="32"/>
       <c r="B511" s="9"/>
       <c r="C511" s="9"/>
       <c r="D511" s="9"/>
@@ -11481,7 +11489,7 @@
       <c r="L511" s="9"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="A512" s="31"/>
+      <c r="A512" s="32"/>
       <c r="B512" s="9"/>
       <c r="C512" s="9"/>
       <c r="D512" s="9"/>
@@ -11495,7 +11503,7 @@
       <c r="L512" s="9"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="A513" s="31"/>
+      <c r="A513" s="32"/>
       <c r="B513" s="9"/>
       <c r="C513" s="9"/>
       <c r="D513" s="9"/>
@@ -11509,7 +11517,7 @@
       <c r="L513" s="9"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="A514" s="31"/>
+      <c r="A514" s="32"/>
       <c r="B514" s="9"/>
       <c r="C514" s="9"/>
       <c r="D514" s="9"/>
@@ -11523,7 +11531,7 @@
       <c r="L514" s="9"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="A515" s="31"/>
+      <c r="A515" s="32"/>
       <c r="B515" s="9"/>
       <c r="C515" s="9"/>
       <c r="D515" s="9"/>
@@ -11537,7 +11545,7 @@
       <c r="L515" s="9"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="A516" s="31"/>
+      <c r="A516" s="32"/>
       <c r="B516" s="9"/>
       <c r="C516" s="9"/>
       <c r="D516" s="9"/>
@@ -11551,7 +11559,7 @@
       <c r="L516" s="9"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="A517" s="31"/>
+      <c r="A517" s="32"/>
       <c r="B517" s="9"/>
       <c r="C517" s="9"/>
       <c r="D517" s="9"/>
@@ -11565,7 +11573,7 @@
       <c r="L517" s="9"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="A518" s="31"/>
+      <c r="A518" s="32"/>
       <c r="B518" s="9"/>
       <c r="C518" s="9"/>
       <c r="D518" s="9"/>
@@ -11579,7 +11587,7 @@
       <c r="L518" s="9"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="A519" s="31"/>
+      <c r="A519" s="32"/>
       <c r="B519" s="9"/>
       <c r="C519" s="9"/>
       <c r="D519" s="9"/>
@@ -11593,7 +11601,7 @@
       <c r="L519" s="9"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="A520" s="31"/>
+      <c r="A520" s="32"/>
       <c r="B520" s="9"/>
       <c r="C520" s="9"/>
       <c r="D520" s="9"/>
@@ -11607,7 +11615,7 @@
       <c r="L520" s="9"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="A521" s="31"/>
+      <c r="A521" s="32"/>
       <c r="B521" s="9"/>
       <c r="C521" s="9"/>
       <c r="D521" s="9"/>
@@ -11621,7 +11629,7 @@
       <c r="L521" s="9"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="A522" s="31"/>
+      <c r="A522" s="32"/>
       <c r="B522" s="9"/>
       <c r="C522" s="9"/>
       <c r="D522" s="9"/>
@@ -11635,7 +11643,7 @@
       <c r="L522" s="9"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="A523" s="31"/>
+      <c r="A523" s="32"/>
       <c r="B523" s="9"/>
       <c r="C523" s="9"/>
       <c r="D523" s="9"/>
@@ -11649,7 +11657,7 @@
       <c r="L523" s="9"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="A524" s="31"/>
+      <c r="A524" s="32"/>
       <c r="B524" s="9"/>
       <c r="C524" s="9"/>
       <c r="D524" s="9"/>
@@ -11663,7 +11671,7 @@
       <c r="L524" s="9"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="A525" s="31"/>
+      <c r="A525" s="32"/>
       <c r="B525" s="9"/>
       <c r="C525" s="9"/>
       <c r="D525" s="9"/>
@@ -11677,7 +11685,7 @@
       <c r="L525" s="9"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="A526" s="31"/>
+      <c r="A526" s="32"/>
       <c r="B526" s="9"/>
       <c r="C526" s="9"/>
       <c r="D526" s="9"/>
@@ -11691,7 +11699,7 @@
       <c r="L526" s="9"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="A527" s="31"/>
+      <c r="A527" s="32"/>
       <c r="B527" s="9"/>
       <c r="C527" s="9"/>
       <c r="D527" s="9"/>
@@ -11705,7 +11713,7 @@
       <c r="L527" s="9"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="A528" s="31"/>
+      <c r="A528" s="32"/>
       <c r="B528" s="9"/>
       <c r="C528" s="9"/>
       <c r="D528" s="9"/>
@@ -11719,7 +11727,7 @@
       <c r="L528" s="9"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="A529" s="31"/>
+      <c r="A529" s="32"/>
       <c r="B529" s="9"/>
       <c r="C529" s="9"/>
       <c r="D529" s="9"/>
@@ -11733,7 +11741,7 @@
       <c r="L529" s="9"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="A530" s="31"/>
+      <c r="A530" s="32"/>
       <c r="B530" s="9"/>
       <c r="C530" s="9"/>
       <c r="D530" s="9"/>
@@ -11747,7 +11755,7 @@
       <c r="L530" s="9"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="A531" s="31"/>
+      <c r="A531" s="32"/>
       <c r="B531" s="9"/>
       <c r="C531" s="9"/>
       <c r="D531" s="9"/>
@@ -11761,7 +11769,7 @@
       <c r="L531" s="9"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="A532" s="31"/>
+      <c r="A532" s="32"/>
       <c r="B532" s="9"/>
       <c r="C532" s="9"/>
       <c r="D532" s="9"/>
@@ -11775,7 +11783,7 @@
       <c r="L532" s="9"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="A533" s="31"/>
+      <c r="A533" s="32"/>
       <c r="B533" s="9"/>
       <c r="C533" s="9"/>
       <c r="D533" s="9"/>
@@ -11789,7 +11797,7 @@
       <c r="L533" s="9"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="A534" s="31"/>
+      <c r="A534" s="32"/>
       <c r="B534" s="9"/>
       <c r="C534" s="9"/>
       <c r="D534" s="9"/>
@@ -11803,7 +11811,7 @@
       <c r="L534" s="9"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="A535" s="31"/>
+      <c r="A535" s="32"/>
       <c r="B535" s="9"/>
       <c r="C535" s="9"/>
       <c r="D535" s="9"/>
@@ -11817,7 +11825,7 @@
       <c r="L535" s="9"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="A536" s="31"/>
+      <c r="A536" s="32"/>
       <c r="B536" s="9"/>
       <c r="C536" s="9"/>
       <c r="D536" s="9"/>
@@ -11831,7 +11839,7 @@
       <c r="L536" s="9"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="A537" s="31"/>
+      <c r="A537" s="32"/>
       <c r="B537" s="9"/>
       <c r="C537" s="9"/>
       <c r="D537" s="9"/>
@@ -11845,7 +11853,7 @@
       <c r="L537" s="9"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="A538" s="31"/>
+      <c r="A538" s="32"/>
       <c r="B538" s="9"/>
       <c r="C538" s="9"/>
       <c r="D538" s="9"/>
@@ -11859,7 +11867,7 @@
       <c r="L538" s="9"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="A539" s="31"/>
+      <c r="A539" s="32"/>
       <c r="B539" s="9"/>
       <c r="C539" s="9"/>
       <c r="D539" s="9"/>
@@ -11873,7 +11881,7 @@
       <c r="L539" s="9"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="A540" s="31"/>
+      <c r="A540" s="32"/>
       <c r="B540" s="9"/>
       <c r="C540" s="9"/>
       <c r="D540" s="9"/>
@@ -11887,7 +11895,7 @@
       <c r="L540" s="9"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="A541" s="31"/>
+      <c r="A541" s="32"/>
       <c r="B541" s="9"/>
       <c r="C541" s="9"/>
       <c r="D541" s="9"/>
@@ -11901,7 +11909,7 @@
       <c r="L541" s="9"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="A542" s="31"/>
+      <c r="A542" s="32"/>
       <c r="B542" s="9"/>
       <c r="C542" s="9"/>
       <c r="D542" s="9"/>
@@ -11915,7 +11923,7 @@
       <c r="L542" s="9"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="A543" s="31"/>
+      <c r="A543" s="32"/>
       <c r="B543" s="9"/>
       <c r="C543" s="9"/>
       <c r="D543" s="9"/>
@@ -11929,7 +11937,7 @@
       <c r="L543" s="9"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="A544" s="31"/>
+      <c r="A544" s="32"/>
       <c r="B544" s="9"/>
       <c r="C544" s="9"/>
       <c r="D544" s="9"/>
@@ -11943,7 +11951,7 @@
       <c r="L544" s="9"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="A545" s="31"/>
+      <c r="A545" s="32"/>
       <c r="B545" s="9"/>
       <c r="C545" s="9"/>
       <c r="D545" s="9"/>
@@ -11957,7 +11965,7 @@
       <c r="L545" s="9"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="A546" s="31"/>
+      <c r="A546" s="32"/>
       <c r="B546" s="9"/>
       <c r="C546" s="9"/>
       <c r="D546" s="9"/>
@@ -11971,7 +11979,7 @@
       <c r="L546" s="9"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="A547" s="31"/>
+      <c r="A547" s="32"/>
       <c r="B547" s="9"/>
       <c r="C547" s="9"/>
       <c r="D547" s="9"/>
@@ -11985,7 +11993,7 @@
       <c r="L547" s="9"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="A548" s="31"/>
+      <c r="A548" s="32"/>
       <c r="B548" s="9"/>
       <c r="C548" s="9"/>
       <c r="D548" s="9"/>
@@ -11999,7 +12007,7 @@
       <c r="L548" s="9"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="A549" s="31"/>
+      <c r="A549" s="32"/>
       <c r="B549" s="9"/>
       <c r="C549" s="9"/>
       <c r="D549" s="9"/>
@@ -12013,7 +12021,7 @@
       <c r="L549" s="9"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="A550" s="31"/>
+      <c r="A550" s="32"/>
       <c r="B550" s="9"/>
       <c r="C550" s="9"/>
       <c r="D550" s="9"/>
@@ -12027,7 +12035,7 @@
       <c r="L550" s="9"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="A551" s="31"/>
+      <c r="A551" s="32"/>
       <c r="B551" s="9"/>
       <c r="C551" s="9"/>
       <c r="D551" s="9"/>
@@ -12041,7 +12049,7 @@
       <c r="L551" s="9"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="A552" s="31"/>
+      <c r="A552" s="32"/>
       <c r="B552" s="9"/>
       <c r="C552" s="9"/>
       <c r="D552" s="9"/>
@@ -12055,7 +12063,7 @@
       <c r="L552" s="9"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="A553" s="31"/>
+      <c r="A553" s="32"/>
       <c r="B553" s="9"/>
       <c r="C553" s="9"/>
       <c r="D553" s="9"/>
@@ -12069,7 +12077,7 @@
       <c r="L553" s="9"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="A554" s="31"/>
+      <c r="A554" s="32"/>
       <c r="B554" s="9"/>
       <c r="C554" s="9"/>
       <c r="D554" s="9"/>
@@ -12083,7 +12091,7 @@
       <c r="L554" s="9"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="A555" s="31"/>
+      <c r="A555" s="32"/>
       <c r="B555" s="9"/>
       <c r="C555" s="9"/>
       <c r="D555" s="9"/>
@@ -12097,7 +12105,7 @@
       <c r="L555" s="9"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="A556" s="31"/>
+      <c r="A556" s="32"/>
       <c r="B556" s="9"/>
       <c r="C556" s="9"/>
       <c r="D556" s="9"/>
@@ -12111,7 +12119,7 @@
       <c r="L556" s="9"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="A557" s="31"/>
+      <c r="A557" s="32"/>
       <c r="B557" s="9"/>
       <c r="C557" s="9"/>
       <c r="D557" s="9"/>
@@ -12125,7 +12133,7 @@
       <c r="L557" s="9"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="A558" s="31"/>
+      <c r="A558" s="32"/>
       <c r="B558" s="9"/>
       <c r="C558" s="9"/>
       <c r="D558" s="9"/>
@@ -12139,7 +12147,7 @@
       <c r="L558" s="9"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="A559" s="31"/>
+      <c r="A559" s="32"/>
       <c r="B559" s="9"/>
       <c r="C559" s="9"/>
       <c r="D559" s="9"/>
@@ -12153,7 +12161,7 @@
       <c r="L559" s="9"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="A560" s="31"/>
+      <c r="A560" s="32"/>
       <c r="B560" s="9"/>
       <c r="C560" s="9"/>
       <c r="D560" s="9"/>
@@ -12167,7 +12175,7 @@
       <c r="L560" s="9"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="A561" s="31"/>
+      <c r="A561" s="32"/>
       <c r="B561" s="9"/>
       <c r="C561" s="9"/>
       <c r="D561" s="9"/>
@@ -12181,7 +12189,7 @@
       <c r="L561" s="9"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="A562" s="31"/>
+      <c r="A562" s="32"/>
       <c r="B562" s="9"/>
       <c r="C562" s="9"/>
       <c r="D562" s="9"/>
@@ -12195,7 +12203,7 @@
       <c r="L562" s="9"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="A563" s="31"/>
+      <c r="A563" s="32"/>
       <c r="B563" s="9"/>
       <c r="C563" s="9"/>
       <c r="D563" s="9"/>
@@ -12209,7 +12217,7 @@
       <c r="L563" s="9"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="A564" s="31"/>
+      <c r="A564" s="32"/>
       <c r="B564" s="9"/>
       <c r="C564" s="9"/>
       <c r="D564" s="9"/>
@@ -12223,7 +12231,7 @@
       <c r="L564" s="9"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="A565" s="31"/>
+      <c r="A565" s="32"/>
       <c r="B565" s="9"/>
       <c r="C565" s="9"/>
       <c r="D565" s="9"/>
@@ -12237,7 +12245,7 @@
       <c r="L565" s="9"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="A566" s="31"/>
+      <c r="A566" s="32"/>
       <c r="B566" s="9"/>
       <c r="C566" s="9"/>
       <c r="D566" s="9"/>
@@ -12251,7 +12259,7 @@
       <c r="L566" s="9"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="A567" s="31"/>
+      <c r="A567" s="32"/>
       <c r="B567" s="9"/>
       <c r="C567" s="9"/>
       <c r="D567" s="9"/>
@@ -12265,7 +12273,7 @@
       <c r="L567" s="9"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="A568" s="31"/>
+      <c r="A568" s="32"/>
       <c r="B568" s="9"/>
       <c r="C568" s="9"/>
       <c r="D568" s="9"/>
@@ -12279,7 +12287,7 @@
       <c r="L568" s="9"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="A569" s="31"/>
+      <c r="A569" s="32"/>
       <c r="B569" s="9"/>
       <c r="C569" s="9"/>
       <c r="D569" s="9"/>
@@ -12293,7 +12301,7 @@
       <c r="L569" s="9"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="A570" s="31"/>
+      <c r="A570" s="32"/>
       <c r="B570" s="9"/>
       <c r="C570" s="9"/>
       <c r="D570" s="9"/>
@@ -12307,7 +12315,7 @@
       <c r="L570" s="9"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="A571" s="31"/>
+      <c r="A571" s="32"/>
       <c r="B571" s="9"/>
       <c r="C571" s="9"/>
       <c r="D571" s="9"/>
@@ -12321,7 +12329,7 @@
       <c r="L571" s="9"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="A572" s="31"/>
+      <c r="A572" s="32"/>
       <c r="B572" s="9"/>
       <c r="C572" s="9"/>
       <c r="D572" s="9"/>
@@ -12335,7 +12343,7 @@
       <c r="L572" s="9"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="A573" s="31"/>
+      <c r="A573" s="32"/>
       <c r="B573" s="9"/>
       <c r="C573" s="9"/>
       <c r="D573" s="9"/>
@@ -12349,7 +12357,7 @@
       <c r="L573" s="9"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="A574" s="31"/>
+      <c r="A574" s="32"/>
       <c r="B574" s="9"/>
       <c r="C574" s="9"/>
       <c r="D574" s="9"/>
@@ -12363,7 +12371,7 @@
       <c r="L574" s="9"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="A575" s="31"/>
+      <c r="A575" s="32"/>
       <c r="B575" s="9"/>
       <c r="C575" s="9"/>
       <c r="D575" s="9"/>
@@ -12377,7 +12385,7 @@
       <c r="L575" s="9"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="A576" s="31"/>
+      <c r="A576" s="32"/>
       <c r="B576" s="9"/>
       <c r="C576" s="9"/>
       <c r="D576" s="9"/>
@@ -12391,7 +12399,7 @@
       <c r="L576" s="9"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="A577" s="31"/>
+      <c r="A577" s="32"/>
       <c r="B577" s="9"/>
       <c r="C577" s="9"/>
       <c r="D577" s="9"/>
@@ -12405,7 +12413,7 @@
       <c r="L577" s="9"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="A578" s="31"/>
+      <c r="A578" s="32"/>
       <c r="B578" s="9"/>
       <c r="C578" s="9"/>
       <c r="D578" s="9"/>
@@ -12419,7 +12427,7 @@
       <c r="L578" s="9"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="A579" s="31"/>
+      <c r="A579" s="32"/>
       <c r="B579" s="9"/>
       <c r="C579" s="9"/>
       <c r="D579" s="9"/>
@@ -12433,7 +12441,7 @@
       <c r="L579" s="9"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="A580" s="31"/>
+      <c r="A580" s="32"/>
       <c r="B580" s="9"/>
       <c r="C580" s="9"/>
       <c r="D580" s="9"/>
@@ -12447,7 +12455,7 @@
       <c r="L580" s="9"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="A581" s="31"/>
+      <c r="A581" s="32"/>
       <c r="B581" s="9"/>
       <c r="C581" s="9"/>
       <c r="D581" s="9"/>
@@ -12461,7 +12469,7 @@
       <c r="L581" s="9"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="A582" s="31"/>
+      <c r="A582" s="32"/>
       <c r="B582" s="9"/>
       <c r="C582" s="9"/>
       <c r="D582" s="9"/>
@@ -12475,7 +12483,7 @@
       <c r="L582" s="9"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="A583" s="31"/>
+      <c r="A583" s="32"/>
       <c r="B583" s="9"/>
       <c r="C583" s="9"/>
       <c r="D583" s="9"/>
@@ -12489,7 +12497,7 @@
       <c r="L583" s="9"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="A584" s="31"/>
+      <c r="A584" s="32"/>
       <c r="B584" s="9"/>
       <c r="C584" s="9"/>
       <c r="D584" s="9"/>
@@ -12503,7 +12511,7 @@
       <c r="L584" s="9"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="A585" s="31"/>
+      <c r="A585" s="32"/>
       <c r="B585" s="9"/>
       <c r="C585" s="9"/>
       <c r="D585" s="9"/>
@@ -12517,7 +12525,7 @@
       <c r="L585" s="9"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="A586" s="31"/>
+      <c r="A586" s="32"/>
       <c r="B586" s="9"/>
       <c r="C586" s="9"/>
       <c r="D586" s="9"/>
@@ -12531,7 +12539,7 @@
       <c r="L586" s="9"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="A587" s="31"/>
+      <c r="A587" s="32"/>
       <c r="B587" s="9"/>
       <c r="C587" s="9"/>
       <c r="D587" s="9"/>
@@ -12545,7 +12553,7 @@
       <c r="L587" s="9"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="A588" s="31"/>
+      <c r="A588" s="32"/>
       <c r="B588" s="9"/>
       <c r="C588" s="9"/>
       <c r="D588" s="9"/>
@@ -12559,7 +12567,7 @@
       <c r="L588" s="9"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="A589" s="31"/>
+      <c r="A589" s="32"/>
       <c r="B589" s="9"/>
       <c r="C589" s="9"/>
       <c r="D589" s="9"/>
@@ -12573,7 +12581,7 @@
       <c r="L589" s="9"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="A590" s="31"/>
+      <c r="A590" s="32"/>
       <c r="B590" s="9"/>
       <c r="C590" s="9"/>
       <c r="D590" s="9"/>
@@ -12587,7 +12595,7 @@
       <c r="L590" s="9"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="A591" s="31"/>
+      <c r="A591" s="32"/>
       <c r="B591" s="9"/>
       <c r="C591" s="9"/>
       <c r="D591" s="9"/>
@@ -12601,7 +12609,7 @@
       <c r="L591" s="9"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="A592" s="31"/>
+      <c r="A592" s="32"/>
       <c r="B592" s="9"/>
       <c r="C592" s="9"/>
       <c r="D592" s="9"/>
@@ -12615,7 +12623,7 @@
       <c r="L592" s="9"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="A593" s="31"/>
+      <c r="A593" s="32"/>
       <c r="B593" s="9"/>
       <c r="C593" s="9"/>
       <c r="D593" s="9"/>
@@ -12629,7 +12637,7 @@
       <c r="L593" s="9"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="A594" s="31"/>
+      <c r="A594" s="32"/>
       <c r="B594" s="9"/>
       <c r="C594" s="9"/>
       <c r="D594" s="9"/>
@@ -12643,7 +12651,7 @@
       <c r="L594" s="9"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="A595" s="31"/>
+      <c r="A595" s="32"/>
       <c r="B595" s="9"/>
       <c r="C595" s="9"/>
       <c r="D595" s="9"/>
@@ -12657,7 +12665,7 @@
       <c r="L595" s="9"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="A596" s="31"/>
+      <c r="A596" s="32"/>
       <c r="B596" s="9"/>
       <c r="C596" s="9"/>
       <c r="D596" s="9"/>
@@ -12671,7 +12679,7 @@
       <c r="L596" s="9"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="A597" s="31"/>
+      <c r="A597" s="32"/>
       <c r="B597" s="9"/>
       <c r="C597" s="9"/>
       <c r="D597" s="9"/>
@@ -12685,7 +12693,7 @@
       <c r="L597" s="9"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="A598" s="31"/>
+      <c r="A598" s="32"/>
       <c r="B598" s="9"/>
       <c r="C598" s="9"/>
       <c r="D598" s="9"/>
@@ -12699,7 +12707,7 @@
       <c r="L598" s="9"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="A599" s="31"/>
+      <c r="A599" s="32"/>
       <c r="B599" s="9"/>
       <c r="C599" s="9"/>
       <c r="D599" s="9"/>
@@ -12713,7 +12721,7 @@
       <c r="L599" s="9"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="A600" s="31"/>
+      <c r="A600" s="32"/>
       <c r="B600" s="9"/>
       <c r="C600" s="9"/>
       <c r="D600" s="9"/>
@@ -12727,7 +12735,7 @@
       <c r="L600" s="9"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="A601" s="31"/>
+      <c r="A601" s="32"/>
       <c r="B601" s="9"/>
       <c r="C601" s="9"/>
       <c r="D601" s="9"/>
@@ -12741,7 +12749,7 @@
       <c r="L601" s="9"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="A602" s="31"/>
+      <c r="A602" s="32"/>
       <c r="B602" s="9"/>
       <c r="C602" s="9"/>
       <c r="D602" s="9"/>
@@ -12755,7 +12763,7 @@
       <c r="L602" s="9"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="A603" s="31"/>
+      <c r="A603" s="32"/>
       <c r="B603" s="9"/>
       <c r="C603" s="9"/>
       <c r="D603" s="9"/>
@@ -12769,7 +12777,7 @@
       <c r="L603" s="9"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="A604" s="31"/>
+      <c r="A604" s="32"/>
       <c r="B604" s="9"/>
       <c r="C604" s="9"/>
       <c r="D604" s="9"/>
@@ -12783,7 +12791,7 @@
       <c r="L604" s="9"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="A605" s="31"/>
+      <c r="A605" s="32"/>
       <c r="B605" s="9"/>
       <c r="C605" s="9"/>
       <c r="D605" s="9"/>
@@ -12797,7 +12805,7 @@
       <c r="L605" s="9"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="A606" s="31"/>
+      <c r="A606" s="32"/>
       <c r="B606" s="9"/>
       <c r="C606" s="9"/>
       <c r="D606" s="9"/>
@@ -12811,7 +12819,7 @@
       <c r="L606" s="9"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="A607" s="31"/>
+      <c r="A607" s="32"/>
       <c r="B607" s="9"/>
       <c r="C607" s="9"/>
       <c r="D607" s="9"/>
@@ -12825,7 +12833,7 @@
       <c r="L607" s="9"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="A608" s="31"/>
+      <c r="A608" s="32"/>
       <c r="B608" s="9"/>
       <c r="C608" s="9"/>
       <c r="D608" s="9"/>
@@ -12839,7 +12847,7 @@
       <c r="L608" s="9"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="A609" s="31"/>
+      <c r="A609" s="32"/>
       <c r="B609" s="9"/>
       <c r="C609" s="9"/>
       <c r="D609" s="9"/>
@@ -12853,7 +12861,7 @@
       <c r="L609" s="9"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="A610" s="31"/>
+      <c r="A610" s="32"/>
       <c r="B610" s="9"/>
       <c r="C610" s="9"/>
       <c r="D610" s="9"/>
@@ -12867,7 +12875,7 @@
       <c r="L610" s="9"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="A611" s="31"/>
+      <c r="A611" s="32"/>
       <c r="B611" s="9"/>
       <c r="C611" s="9"/>
       <c r="D611" s="9"/>
@@ -12881,7 +12889,7 @@
       <c r="L611" s="9"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="A612" s="31"/>
+      <c r="A612" s="32"/>
       <c r="B612" s="9"/>
       <c r="C612" s="9"/>
       <c r="D612" s="9"/>
@@ -12895,7 +12903,7 @@
       <c r="L612" s="9"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="A613" s="31"/>
+      <c r="A613" s="32"/>
       <c r="B613" s="9"/>
       <c r="C613" s="9"/>
       <c r="D613" s="9"/>
@@ -12909,7 +12917,7 @@
       <c r="L613" s="9"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="A614" s="31"/>
+      <c r="A614" s="32"/>
       <c r="B614" s="9"/>
       <c r="C614" s="9"/>
       <c r="D614" s="9"/>
@@ -12923,7 +12931,7 @@
       <c r="L614" s="9"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="A615" s="31"/>
+      <c r="A615" s="32"/>
       <c r="B615" s="9"/>
       <c r="C615" s="9"/>
       <c r="D615" s="9"/>
@@ -12937,7 +12945,7 @@
       <c r="L615" s="9"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="A616" s="31"/>
+      <c r="A616" s="32"/>
       <c r="B616" s="9"/>
       <c r="C616" s="9"/>
       <c r="D616" s="9"/>
@@ -12951,7 +12959,7 @@
       <c r="L616" s="9"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="A617" s="31"/>
+      <c r="A617" s="32"/>
       <c r="B617" s="9"/>
       <c r="C617" s="9"/>
       <c r="D617" s="9"/>
@@ -12965,7 +12973,7 @@
       <c r="L617" s="9"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="A618" s="31"/>
+      <c r="A618" s="32"/>
       <c r="B618" s="9"/>
       <c r="C618" s="9"/>
       <c r="D618" s="9"/>
@@ -12979,7 +12987,7 @@
       <c r="L618" s="9"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="A619" s="31"/>
+      <c r="A619" s="32"/>
       <c r="B619" s="9"/>
       <c r="C619" s="9"/>
       <c r="D619" s="9"/>
@@ -12993,7 +13001,7 @@
       <c r="L619" s="9"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="A620" s="31"/>
+      <c r="A620" s="32"/>
       <c r="B620" s="9"/>
       <c r="C620" s="9"/>
       <c r="D620" s="9"/>
@@ -13007,7 +13015,7 @@
       <c r="L620" s="9"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="A621" s="31"/>
+      <c r="A621" s="32"/>
       <c r="B621" s="9"/>
       <c r="C621" s="9"/>
       <c r="D621" s="9"/>
@@ -13021,7 +13029,7 @@
       <c r="L621" s="9"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="A622" s="31"/>
+      <c r="A622" s="32"/>
       <c r="B622" s="9"/>
       <c r="C622" s="9"/>
       <c r="D622" s="9"/>
@@ -13035,7 +13043,7 @@
       <c r="L622" s="9"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="A623" s="31"/>
+      <c r="A623" s="32"/>
       <c r="B623" s="9"/>
       <c r="C623" s="9"/>
       <c r="D623" s="9"/>
@@ -13049,7 +13057,7 @@
       <c r="L623" s="9"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="A624" s="31"/>
+      <c r="A624" s="32"/>
       <c r="B624" s="9"/>
       <c r="C624" s="9"/>
       <c r="D624" s="9"/>
@@ -13063,7 +13071,7 @@
       <c r="L624" s="9"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="A625" s="31"/>
+      <c r="A625" s="32"/>
       <c r="B625" s="9"/>
       <c r="C625" s="9"/>
       <c r="D625" s="9"/>
@@ -13077,7 +13085,7 @@
       <c r="L625" s="9"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="A626" s="31"/>
+      <c r="A626" s="32"/>
       <c r="B626" s="9"/>
       <c r="C626" s="9"/>
       <c r="D626" s="9"/>
@@ -13091,7 +13099,7 @@
       <c r="L626" s="9"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="A627" s="31"/>
+      <c r="A627" s="32"/>
       <c r="B627" s="9"/>
       <c r="C627" s="9"/>
       <c r="D627" s="9"/>
@@ -13105,7 +13113,7 @@
       <c r="L627" s="9"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="A628" s="31"/>
+      <c r="A628" s="32"/>
       <c r="B628" s="9"/>
       <c r="C628" s="9"/>
       <c r="D628" s="9"/>
@@ -13119,7 +13127,7 @@
       <c r="L628" s="9"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="A629" s="31"/>
+      <c r="A629" s="32"/>
       <c r="B629" s="9"/>
       <c r="C629" s="9"/>
       <c r="D629" s="9"/>
@@ -13133,7 +13141,7 @@
       <c r="L629" s="9"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="A630" s="31"/>
+      <c r="A630" s="32"/>
       <c r="B630" s="9"/>
       <c r="C630" s="9"/>
       <c r="D630" s="9"/>
@@ -13147,7 +13155,7 @@
       <c r="L630" s="9"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="A631" s="31"/>
+      <c r="A631" s="32"/>
       <c r="B631" s="9"/>
       <c r="C631" s="9"/>
       <c r="D631" s="9"/>
@@ -13161,7 +13169,7 @@
       <c r="L631" s="9"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="A632" s="31"/>
+      <c r="A632" s="32"/>
       <c r="B632" s="9"/>
       <c r="C632" s="9"/>
       <c r="D632" s="9"/>
@@ -13175,7 +13183,7 @@
       <c r="L632" s="9"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="A633" s="31"/>
+      <c r="A633" s="32"/>
       <c r="B633" s="9"/>
       <c r="C633" s="9"/>
       <c r="D633" s="9"/>
@@ -13189,7 +13197,7 @@
       <c r="L633" s="9"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="A634" s="31"/>
+      <c r="A634" s="32"/>
       <c r="B634" s="9"/>
       <c r="C634" s="9"/>
       <c r="D634" s="9"/>
@@ -13203,7 +13211,7 @@
       <c r="L634" s="9"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="A635" s="31"/>
+      <c r="A635" s="32"/>
       <c r="B635" s="9"/>
       <c r="C635" s="9"/>
       <c r="D635" s="9"/>
@@ -13217,7 +13225,7 @@
       <c r="L635" s="9"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="A636" s="31"/>
+      <c r="A636" s="32"/>
       <c r="B636" s="9"/>
       <c r="C636" s="9"/>
       <c r="D636" s="9"/>
@@ -13231,7 +13239,7 @@
       <c r="L636" s="9"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="A637" s="31"/>
+      <c r="A637" s="32"/>
       <c r="B637" s="9"/>
       <c r="C637" s="9"/>
       <c r="D637" s="9"/>
@@ -13245,7 +13253,7 @@
       <c r="L637" s="9"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="A638" s="31"/>
+      <c r="A638" s="32"/>
       <c r="B638" s="9"/>
       <c r="C638" s="9"/>
       <c r="D638" s="9"/>
@@ -13259,7 +13267,7 @@
       <c r="L638" s="9"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="A639" s="31"/>
+      <c r="A639" s="32"/>
       <c r="B639" s="9"/>
       <c r="C639" s="9"/>
       <c r="D639" s="9"/>
@@ -13273,7 +13281,7 @@
       <c r="L639" s="9"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="A640" s="31"/>
+      <c r="A640" s="32"/>
       <c r="B640" s="9"/>
       <c r="C640" s="9"/>
       <c r="D640" s="9"/>
@@ -13287,7 +13295,7 @@
       <c r="L640" s="9"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="A641" s="31"/>
+      <c r="A641" s="32"/>
       <c r="B641" s="9"/>
       <c r="C641" s="9"/>
       <c r="D641" s="9"/>
@@ -13301,7 +13309,7 @@
       <c r="L641" s="9"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="A642" s="31"/>
+      <c r="A642" s="32"/>
       <c r="B642" s="9"/>
       <c r="C642" s="9"/>
       <c r="D642" s="9"/>
@@ -13315,7 +13323,7 @@
       <c r="L642" s="9"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="A643" s="31"/>
+      <c r="A643" s="32"/>
       <c r="B643" s="9"/>
       <c r="C643" s="9"/>
       <c r="D643" s="9"/>
@@ -13329,7 +13337,7 @@
       <c r="L643" s="9"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="A644" s="31"/>
+      <c r="A644" s="32"/>
       <c r="B644" s="9"/>
       <c r="C644" s="9"/>
       <c r="D644" s="9"/>
@@ -13343,7 +13351,7 @@
       <c r="L644" s="9"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="A645" s="31"/>
+      <c r="A645" s="32"/>
       <c r="B645" s="9"/>
       <c r="C645" s="9"/>
       <c r="D645" s="9"/>
@@ -13357,7 +13365,7 @@
       <c r="L645" s="9"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="A646" s="31"/>
+      <c r="A646" s="32"/>
       <c r="B646" s="9"/>
       <c r="C646" s="9"/>
       <c r="D646" s="9"/>
@@ -13371,7 +13379,7 @@
       <c r="L646" s="9"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="A647" s="31"/>
+      <c r="A647" s="32"/>
       <c r="B647" s="9"/>
       <c r="C647" s="9"/>
       <c r="D647" s="9"/>
@@ -13385,7 +13393,7 @@
       <c r="L647" s="9"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="A648" s="31"/>
+      <c r="A648" s="32"/>
       <c r="B648" s="9"/>
       <c r="C648" s="9"/>
       <c r="D648" s="9"/>
@@ -13399,7 +13407,7 @@
       <c r="L648" s="9"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="A649" s="31"/>
+      <c r="A649" s="32"/>
       <c r="B649" s="9"/>
       <c r="C649" s="9"/>
       <c r="D649" s="9"/>
@@ -13413,7 +13421,7 @@
       <c r="L649" s="9"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="A650" s="31"/>
+      <c r="A650" s="32"/>
       <c r="B650" s="9"/>
       <c r="C650" s="9"/>
       <c r="D650" s="9"/>
@@ -13427,7 +13435,7 @@
       <c r="L650" s="9"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="A651" s="31"/>
+      <c r="A651" s="32"/>
       <c r="B651" s="9"/>
       <c r="C651" s="9"/>
       <c r="D651" s="9"/>
@@ -13441,7 +13449,7 @@
       <c r="L651" s="9"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="A652" s="31"/>
+      <c r="A652" s="32"/>
       <c r="B652" s="9"/>
       <c r="C652" s="9"/>
       <c r="D652" s="9"/>
@@ -13455,7 +13463,7 @@
       <c r="L652" s="9"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="A653" s="31"/>
+      <c r="A653" s="32"/>
       <c r="B653" s="9"/>
       <c r="C653" s="9"/>
       <c r="D653" s="9"/>
@@ -13469,7 +13477,7 @@
       <c r="L653" s="9"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="A654" s="31"/>
+      <c r="A654" s="32"/>
       <c r="B654" s="9"/>
       <c r="C654" s="9"/>
       <c r="D654" s="9"/>
@@ -13483,7 +13491,7 @@
       <c r="L654" s="9"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="A655" s="31"/>
+      <c r="A655" s="32"/>
       <c r="B655" s="9"/>
       <c r="C655" s="9"/>
       <c r="D655" s="9"/>
@@ -13497,7 +13505,7 @@
       <c r="L655" s="9"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="A656" s="31"/>
+      <c r="A656" s="32"/>
       <c r="B656" s="9"/>
       <c r="C656" s="9"/>
       <c r="D656" s="9"/>
@@ -13511,7 +13519,7 @@
       <c r="L656" s="9"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="A657" s="31"/>
+      <c r="A657" s="32"/>
       <c r="B657" s="9"/>
       <c r="C657" s="9"/>
       <c r="D657" s="9"/>
@@ -13525,7 +13533,7 @@
       <c r="L657" s="9"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="A658" s="31"/>
+      <c r="A658" s="32"/>
       <c r="B658" s="9"/>
       <c r="C658" s="9"/>
       <c r="D658" s="9"/>
@@ -13539,7 +13547,7 @@
       <c r="L658" s="9"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="A659" s="31"/>
+      <c r="A659" s="32"/>
       <c r="B659" s="9"/>
       <c r="C659" s="9"/>
       <c r="D659" s="9"/>
@@ -13553,7 +13561,7 @@
       <c r="L659" s="9"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="A660" s="31"/>
+      <c r="A660" s="32"/>
       <c r="B660" s="9"/>
       <c r="C660" s="9"/>
       <c r="D660" s="9"/>
@@ -13567,7 +13575,7 @@
       <c r="L660" s="9"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="A661" s="31"/>
+      <c r="A661" s="32"/>
       <c r="B661" s="9"/>
       <c r="C661" s="9"/>
       <c r="D661" s="9"/>
@@ -13581,7 +13589,7 @@
       <c r="L661" s="9"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="A662" s="31"/>
+      <c r="A662" s="32"/>
       <c r="B662" s="9"/>
       <c r="C662" s="9"/>
       <c r="D662" s="9"/>
@@ -13595,7 +13603,7 @@
       <c r="L662" s="9"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="A663" s="31"/>
+      <c r="A663" s="32"/>
       <c r="B663" s="9"/>
       <c r="C663" s="9"/>
       <c r="D663" s="9"/>
@@ -13609,7 +13617,7 @@
       <c r="L663" s="9"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="A664" s="31"/>
+      <c r="A664" s="32"/>
       <c r="B664" s="9"/>
       <c r="C664" s="9"/>
       <c r="D664" s="9"/>
@@ -13623,7 +13631,7 @@
       <c r="L664" s="9"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="A665" s="31"/>
+      <c r="A665" s="32"/>
       <c r="B665" s="9"/>
       <c r="C665" s="9"/>
       <c r="D665" s="9"/>
@@ -13637,7 +13645,7 @@
       <c r="L665" s="9"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="A666" s="31"/>
+      <c r="A666" s="32"/>
       <c r="B666" s="9"/>
       <c r="C666" s="9"/>
       <c r="D666" s="9"/>
@@ -13651,7 +13659,7 @@
       <c r="L666" s="9"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="A667" s="31"/>
+      <c r="A667" s="32"/>
       <c r="B667" s="9"/>
       <c r="C667" s="9"/>
       <c r="D667" s="9"/>
@@ -13665,7 +13673,7 @@
       <c r="L667" s="9"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="A668" s="31"/>
+      <c r="A668" s="32"/>
       <c r="B668" s="9"/>
       <c r="C668" s="9"/>
       <c r="D668" s="9"/>
@@ -13679,7 +13687,7 @@
       <c r="L668" s="9"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="A669" s="31"/>
+      <c r="A669" s="32"/>
       <c r="B669" s="9"/>
       <c r="C669" s="9"/>
       <c r="D669" s="9"/>
@@ -13693,7 +13701,7 @@
       <c r="L669" s="9"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="A670" s="31"/>
+      <c r="A670" s="32"/>
       <c r="B670" s="9"/>
       <c r="C670" s="9"/>
       <c r="D670" s="9"/>
@@ -13707,7 +13715,7 @@
       <c r="L670" s="9"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="A671" s="31"/>
+      <c r="A671" s="32"/>
       <c r="B671" s="9"/>
       <c r="C671" s="9"/>
       <c r="D671" s="9"/>
@@ -13721,7 +13729,7 @@
       <c r="L671" s="9"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="A672" s="31"/>
+      <c r="A672" s="32"/>
       <c r="B672" s="9"/>
       <c r="C672" s="9"/>
       <c r="D672" s="9"/>
@@ -13735,7 +13743,7 @@
       <c r="L672" s="9"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="A673" s="31"/>
+      <c r="A673" s="32"/>
       <c r="B673" s="9"/>
       <c r="C673" s="9"/>
       <c r="D673" s="9"/>
@@ -13749,7 +13757,7 @@
       <c r="L673" s="9"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="A674" s="31"/>
+      <c r="A674" s="32"/>
       <c r="B674" s="9"/>
       <c r="C674" s="9"/>
       <c r="D674" s="9"/>
@@ -13763,7 +13771,7 @@
       <c r="L674" s="9"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="A675" s="31"/>
+      <c r="A675" s="32"/>
       <c r="B675" s="9"/>
       <c r="C675" s="9"/>
       <c r="D675" s="9"/>
@@ -13777,7 +13785,7 @@
       <c r="L675" s="9"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="A676" s="31"/>
+      <c r="A676" s="32"/>
       <c r="B676" s="9"/>
       <c r="C676" s="9"/>
       <c r="D676" s="9"/>
@@ -13791,7 +13799,7 @@
       <c r="L676" s="9"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="A677" s="31"/>
+      <c r="A677" s="32"/>
       <c r="B677" s="9"/>
       <c r="C677" s="9"/>
       <c r="D677" s="9"/>
@@ -13805,7 +13813,7 @@
       <c r="L677" s="9"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="A678" s="31"/>
+      <c r="A678" s="32"/>
       <c r="B678" s="9"/>
       <c r="C678" s="9"/>
       <c r="D678" s="9"/>
@@ -13819,7 +13827,7 @@
       <c r="L678" s="9"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="A679" s="31"/>
+      <c r="A679" s="32"/>
       <c r="B679" s="9"/>
       <c r="C679" s="9"/>
       <c r="D679" s="9"/>
@@ -13833,7 +13841,7 @@
       <c r="L679" s="9"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="A680" s="31"/>
+      <c r="A680" s="32"/>
       <c r="B680" s="9"/>
       <c r="C680" s="9"/>
       <c r="D680" s="9"/>
@@ -13847,7 +13855,7 @@
       <c r="L680" s="9"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="A681" s="31"/>
+      <c r="A681" s="32"/>
       <c r="B681" s="9"/>
       <c r="C681" s="9"/>
       <c r="D681" s="9"/>
@@ -13861,7 +13869,7 @@
       <c r="L681" s="9"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="A682" s="31"/>
+      <c r="A682" s="32"/>
       <c r="B682" s="9"/>
       <c r="C682" s="9"/>
       <c r="D682" s="9"/>
@@ -13875,7 +13883,7 @@
       <c r="L682" s="9"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="A683" s="31"/>
+      <c r="A683" s="32"/>
       <c r="B683" s="9"/>
       <c r="C683" s="9"/>
       <c r="D683" s="9"/>
@@ -13889,7 +13897,7 @@
       <c r="L683" s="9"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="A684" s="31"/>
+      <c r="A684" s="32"/>
       <c r="B684" s="9"/>
       <c r="C684" s="9"/>
       <c r="D684" s="9"/>
@@ -13903,7 +13911,7 @@
       <c r="L684" s="9"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="A685" s="31"/>
+      <c r="A685" s="32"/>
       <c r="B685" s="9"/>
       <c r="C685" s="9"/>
       <c r="D685" s="9"/>
@@ -13917,7 +13925,7 @@
       <c r="L685" s="9"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="A686" s="31"/>
+      <c r="A686" s="32"/>
       <c r="B686" s="9"/>
       <c r="C686" s="9"/>
       <c r="D686" s="9"/>
@@ -13931,7 +13939,7 @@
       <c r="L686" s="9"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="A687" s="31"/>
+      <c r="A687" s="32"/>
       <c r="B687" s="9"/>
       <c r="C687" s="9"/>
       <c r="D687" s="9"/>
@@ -13945,7 +13953,7 @@
       <c r="L687" s="9"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="A688" s="31"/>
+      <c r="A688" s="32"/>
       <c r="B688" s="9"/>
       <c r="C688" s="9"/>
       <c r="D688" s="9"/>
@@ -13959,7 +13967,7 @@
       <c r="L688" s="9"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="A689" s="31"/>
+      <c r="A689" s="32"/>
       <c r="B689" s="9"/>
       <c r="C689" s="9"/>
       <c r="D689" s="9"/>
@@ -13973,7 +13981,7 @@
       <c r="L689" s="9"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="A690" s="31"/>
+      <c r="A690" s="32"/>
       <c r="B690" s="9"/>
       <c r="C690" s="9"/>
       <c r="D690" s="9"/>
@@ -13987,7 +13995,7 @@
       <c r="L690" s="9"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="A691" s="31"/>
+      <c r="A691" s="32"/>
       <c r="B691" s="9"/>
       <c r="C691" s="9"/>
       <c r="D691" s="9"/>
@@ -14001,7 +14009,7 @@
       <c r="L691" s="9"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="A692" s="31"/>
+      <c r="A692" s="32"/>
       <c r="B692" s="9"/>
       <c r="C692" s="9"/>
       <c r="D692" s="9"/>
@@ -14015,7 +14023,7 @@
       <c r="L692" s="9"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="A693" s="31"/>
+      <c r="A693" s="32"/>
       <c r="B693" s="9"/>
       <c r="C693" s="9"/>
       <c r="D693" s="9"/>
@@ -14029,7 +14037,7 @@
       <c r="L693" s="9"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="A694" s="31"/>
+      <c r="A694" s="32"/>
       <c r="B694" s="9"/>
       <c r="C694" s="9"/>
       <c r="D694" s="9"/>
@@ -14043,7 +14051,7 @@
       <c r="L694" s="9"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="A695" s="31"/>
+      <c r="A695" s="32"/>
       <c r="B695" s="9"/>
       <c r="C695" s="9"/>
       <c r="D695" s="9"/>
@@ -14057,7 +14065,7 @@
       <c r="L695" s="9"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="A696" s="31"/>
+      <c r="A696" s="32"/>
       <c r="B696" s="9"/>
       <c r="C696" s="9"/>
       <c r="D696" s="9"/>
@@ -14071,7 +14079,7 @@
       <c r="L696" s="9"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="A697" s="31"/>
+      <c r="A697" s="32"/>
       <c r="B697" s="9"/>
       <c r="C697" s="9"/>
       <c r="D697" s="9"/>
@@ -14085,7 +14093,7 @@
       <c r="L697" s="9"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="A698" s="31"/>
+      <c r="A698" s="32"/>
       <c r="B698" s="9"/>
       <c r="C698" s="9"/>
       <c r="D698" s="9"/>
@@ -14099,7 +14107,7 @@
       <c r="L698" s="9"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="A699" s="31"/>
+      <c r="A699" s="32"/>
       <c r="B699" s="9"/>
       <c r="C699" s="9"/>
       <c r="D699" s="9"/>
@@ -14113,7 +14121,7 @@
       <c r="L699" s="9"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="A700" s="31"/>
+      <c r="A700" s="32"/>
       <c r="B700" s="9"/>
       <c r="C700" s="9"/>
       <c r="D700" s="9"/>
@@ -14127,7 +14135,7 @@
       <c r="L700" s="9"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="A701" s="31"/>
+      <c r="A701" s="32"/>
       <c r="B701" s="9"/>
       <c r="C701" s="9"/>
       <c r="D701" s="9"/>
@@ -14141,7 +14149,7 @@
       <c r="L701" s="9"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="A702" s="31"/>
+      <c r="A702" s="32"/>
       <c r="B702" s="9"/>
       <c r="C702" s="9"/>
       <c r="D702" s="9"/>
@@ -14155,7 +14163,7 @@
       <c r="L702" s="9"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="A703" s="31"/>
+      <c r="A703" s="32"/>
       <c r="B703" s="9"/>
       <c r="C703" s="9"/>
       <c r="D703" s="9"/>
@@ -14169,7 +14177,7 @@
       <c r="L703" s="9"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="A704" s="31"/>
+      <c r="A704" s="32"/>
       <c r="B704" s="9"/>
       <c r="C704" s="9"/>
       <c r="D704" s="9"/>
@@ -14183,7 +14191,7 @@
       <c r="L704" s="9"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="A705" s="31"/>
+      <c r="A705" s="32"/>
       <c r="B705" s="9"/>
       <c r="C705" s="9"/>
       <c r="D705" s="9"/>
@@ -14197,7 +14205,7 @@
       <c r="L705" s="9"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="A706" s="31"/>
+      <c r="A706" s="32"/>
       <c r="B706" s="9"/>
       <c r="C706" s="9"/>
       <c r="D706" s="9"/>
@@ -14211,7 +14219,7 @@
       <c r="L706" s="9"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="A707" s="31"/>
+      <c r="A707" s="32"/>
       <c r="B707" s="9"/>
       <c r="C707" s="9"/>
       <c r="D707" s="9"/>
@@ -14225,7 +14233,7 @@
       <c r="L707" s="9"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="A708" s="31"/>
+      <c r="A708" s="32"/>
       <c r="B708" s="9"/>
       <c r="C708" s="9"/>
       <c r="D708" s="9"/>
@@ -14239,7 +14247,7 @@
       <c r="L708" s="9"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="A709" s="31"/>
+      <c r="A709" s="32"/>
       <c r="B709" s="9"/>
       <c r="C709" s="9"/>
       <c r="D709" s="9"/>
@@ -14253,7 +14261,7 @@
       <c r="L709" s="9"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="A710" s="31"/>
+      <c r="A710" s="32"/>
       <c r="B710" s="9"/>
       <c r="C710" s="9"/>
       <c r="D710" s="9"/>
@@ -14267,7 +14275,7 @@
       <c r="L710" s="9"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="A711" s="31"/>
+      <c r="A711" s="32"/>
       <c r="B711" s="9"/>
       <c r="C711" s="9"/>
       <c r="D711" s="9"/>
@@ -14281,7 +14289,7 @@
       <c r="L711" s="9"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="A712" s="31"/>
+      <c r="A712" s="32"/>
       <c r="B712" s="9"/>
       <c r="C712" s="9"/>
       <c r="D712" s="9"/>
@@ -14295,7 +14303,7 @@
       <c r="L712" s="9"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="A713" s="31"/>
+      <c r="A713" s="32"/>
       <c r="B713" s="9"/>
       <c r="C713" s="9"/>
       <c r="D713" s="9"/>
@@ -14309,7 +14317,7 @@
       <c r="L713" s="9"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="A714" s="31"/>
+      <c r="A714" s="32"/>
       <c r="B714" s="9"/>
       <c r="C714" s="9"/>
       <c r="D714" s="9"/>
@@ -14323,7 +14331,7 @@
       <c r="L714" s="9"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="A715" s="31"/>
+      <c r="A715" s="32"/>
       <c r="B715" s="9"/>
       <c r="C715" s="9"/>
       <c r="D715" s="9"/>
@@ -14337,7 +14345,7 @@
       <c r="L715" s="9"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="A716" s="31"/>
+      <c r="A716" s="32"/>
       <c r="B716" s="9"/>
       <c r="C716" s="9"/>
       <c r="D716" s="9"/>
@@ -14351,7 +14359,7 @@
       <c r="L716" s="9"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="A717" s="31"/>
+      <c r="A717" s="32"/>
       <c r="B717" s="9"/>
       <c r="C717" s="9"/>
       <c r="D717" s="9"/>
@@ -14365,7 +14373,7 @@
       <c r="L717" s="9"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="A718" s="31"/>
+      <c r="A718" s="32"/>
       <c r="B718" s="9"/>
       <c r="C718" s="9"/>
       <c r="D718" s="9"/>
@@ -14379,7 +14387,7 @@
       <c r="L718" s="9"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="A719" s="31"/>
+      <c r="A719" s="32"/>
       <c r="B719" s="9"/>
       <c r="C719" s="9"/>
       <c r="D719" s="9"/>
@@ -14393,7 +14401,7 @@
       <c r="L719" s="9"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="A720" s="31"/>
+      <c r="A720" s="32"/>
       <c r="B720" s="9"/>
       <c r="C720" s="9"/>
       <c r="D720" s="9"/>
@@ -14407,7 +14415,7 @@
       <c r="L720" s="9"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="A721" s="31"/>
+      <c r="A721" s="32"/>
       <c r="B721" s="9"/>
       <c r="C721" s="9"/>
       <c r="D721" s="9"/>
@@ -14421,7 +14429,7 @@
       <c r="L721" s="9"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="A722" s="31"/>
+      <c r="A722" s="32"/>
       <c r="B722" s="9"/>
       <c r="C722" s="9"/>
       <c r="D722" s="9"/>
@@ -14435,7 +14443,7 @@
       <c r="L722" s="9"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="A723" s="31"/>
+      <c r="A723" s="32"/>
       <c r="B723" s="9"/>
       <c r="C723" s="9"/>
       <c r="D723" s="9"/>
@@ -14449,7 +14457,7 @@
       <c r="L723" s="9"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="A724" s="31"/>
+      <c r="A724" s="32"/>
       <c r="B724" s="9"/>
       <c r="C724" s="9"/>
       <c r="D724" s="9"/>
@@ -14463,7 +14471,7 @@
       <c r="L724" s="9"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="A725" s="31"/>
+      <c r="A725" s="32"/>
       <c r="B725" s="9"/>
       <c r="C725" s="9"/>
       <c r="D725" s="9"/>
@@ -14477,7 +14485,7 @@
       <c r="L725" s="9"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="A726" s="31"/>
+      <c r="A726" s="32"/>
       <c r="B726" s="9"/>
       <c r="C726" s="9"/>
       <c r="D726" s="9"/>
@@ -14491,7 +14499,7 @@
       <c r="L726" s="9"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="A727" s="31"/>
+      <c r="A727" s="32"/>
       <c r="B727" s="9"/>
       <c r="C727" s="9"/>
       <c r="D727" s="9"/>
@@ -14505,7 +14513,7 @@
       <c r="L727" s="9"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="A728" s="31"/>
+      <c r="A728" s="32"/>
       <c r="B728" s="9"/>
       <c r="C728" s="9"/>
       <c r="D728" s="9"/>
@@ -14519,7 +14527,7 @@
       <c r="L728" s="9"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="A729" s="31"/>
+      <c r="A729" s="32"/>
       <c r="B729" s="9"/>
       <c r="C729" s="9"/>
       <c r="D729" s="9"/>
@@ -14533,7 +14541,7 @@
       <c r="L729" s="9"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="A730" s="31"/>
+      <c r="A730" s="32"/>
       <c r="B730" s="9"/>
       <c r="C730" s="9"/>
       <c r="D730" s="9"/>
@@ -14547,7 +14555,7 @@
       <c r="L730" s="9"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="A731" s="31"/>
+      <c r="A731" s="32"/>
       <c r="B731" s="9"/>
       <c r="C731" s="9"/>
       <c r="D731" s="9"/>
@@ -14561,7 +14569,7 @@
       <c r="L731" s="9"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="A732" s="31"/>
+      <c r="A732" s="32"/>
       <c r="B732" s="9"/>
       <c r="C732" s="9"/>
       <c r="D732" s="9"/>
@@ -14575,7 +14583,7 @@
       <c r="L732" s="9"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="A733" s="31"/>
+      <c r="A733" s="32"/>
       <c r="B733" s="9"/>
       <c r="C733" s="9"/>
       <c r="D733" s="9"/>
@@ -14589,7 +14597,7 @@
       <c r="L733" s="9"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="A734" s="31"/>
+      <c r="A734" s="32"/>
       <c r="B734" s="9"/>
       <c r="C734" s="9"/>
       <c r="D734" s="9"/>
@@ -14603,7 +14611,7 @@
       <c r="L734" s="9"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="A735" s="31"/>
+      <c r="A735" s="32"/>
       <c r="B735" s="9"/>
       <c r="C735" s="9"/>
       <c r="D735" s="9"/>
@@ -14617,7 +14625,7 @@
       <c r="L735" s="9"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="A736" s="31"/>
+      <c r="A736" s="32"/>
       <c r="B736" s="9"/>
       <c r="C736" s="9"/>
       <c r="D736" s="9"/>
@@ -14631,7 +14639,7 @@
       <c r="L736" s="9"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="A737" s="31"/>
+      <c r="A737" s="32"/>
       <c r="B737" s="9"/>
       <c r="C737" s="9"/>
       <c r="D737" s="9"/>
@@ -14645,7 +14653,7 @@
       <c r="L737" s="9"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="A738" s="31"/>
+      <c r="A738" s="32"/>
       <c r="B738" s="9"/>
       <c r="C738" s="9"/>
       <c r="D738" s="9"/>
@@ -14659,7 +14667,7 @@
       <c r="L738" s="9"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="A739" s="31"/>
+      <c r="A739" s="32"/>
       <c r="B739" s="9"/>
       <c r="C739" s="9"/>
       <c r="D739" s="9"/>
@@ -14673,7 +14681,7 @@
       <c r="L739" s="9"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="A740" s="31"/>
+      <c r="A740" s="32"/>
       <c r="B740" s="9"/>
       <c r="C740" s="9"/>
       <c r="D740" s="9"/>
@@ -14687,7 +14695,7 @@
       <c r="L740" s="9"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="A741" s="31"/>
+      <c r="A741" s="32"/>
       <c r="B741" s="9"/>
       <c r="C741" s="9"/>
       <c r="D741" s="9"/>
@@ -14701,7 +14709,7 @@
       <c r="L741" s="9"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="A742" s="31"/>
+      <c r="A742" s="32"/>
       <c r="B742" s="9"/>
       <c r="C742" s="9"/>
       <c r="D742" s="9"/>
@@ -14715,7 +14723,7 @@
       <c r="L742" s="9"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="A743" s="31"/>
+      <c r="A743" s="32"/>
       <c r="B743" s="9"/>
       <c r="C743" s="9"/>
       <c r="D743" s="9"/>
@@ -14729,7 +14737,7 @@
       <c r="L743" s="9"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="A744" s="31"/>
+      <c r="A744" s="32"/>
       <c r="B744" s="9"/>
       <c r="C744" s="9"/>
       <c r="D744" s="9"/>
@@ -14743,7 +14751,7 @@
       <c r="L744" s="9"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="A745" s="31"/>
+      <c r="A745" s="32"/>
       <c r="B745" s="9"/>
       <c r="C745" s="9"/>
       <c r="D745" s="9"/>
@@ -14757,7 +14765,7 @@
       <c r="L745" s="9"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="A746" s="31"/>
+      <c r="A746" s="32"/>
       <c r="B746" s="9"/>
       <c r="C746" s="9"/>
       <c r="D746" s="9"/>
@@ -14771,7 +14779,7 @@
       <c r="L746" s="9"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="A747" s="31"/>
+      <c r="A747" s="32"/>
       <c r="B747" s="9"/>
       <c r="C747" s="9"/>
       <c r="D747" s="9"/>
@@ -14785,7 +14793,7 @@
       <c r="L747" s="9"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="A748" s="31"/>
+      <c r="A748" s="32"/>
       <c r="B748" s="9"/>
       <c r="C748" s="9"/>
       <c r="D748" s="9"/>
@@ -14799,7 +14807,7 @@
       <c r="L748" s="9"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="A749" s="31"/>
+      <c r="A749" s="32"/>
       <c r="B749" s="9"/>
       <c r="C749" s="9"/>
       <c r="D749" s="9"/>
@@ -14813,7 +14821,7 @@
       <c r="L749" s="9"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="A750" s="31"/>
+      <c r="A750" s="32"/>
       <c r="B750" s="9"/>
       <c r="C750" s="9"/>
       <c r="D750" s="9"/>
@@ -14827,7 +14835,7 @@
       <c r="L750" s="9"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="A751" s="31"/>
+      <c r="A751" s="32"/>
       <c r="B751" s="9"/>
       <c r="C751" s="9"/>
       <c r="D751" s="9"/>
@@ -14841,7 +14849,7 @@
       <c r="L751" s="9"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="A752" s="31"/>
+      <c r="A752" s="32"/>
       <c r="B752" s="9"/>
       <c r="C752" s="9"/>
       <c r="D752" s="9"/>
@@ -14855,7 +14863,7 @@
       <c r="L752" s="9"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="A753" s="31"/>
+      <c r="A753" s="32"/>
       <c r="B753" s="9"/>
       <c r="C753" s="9"/>
       <c r="D753" s="9"/>
@@ -14869,7 +14877,7 @@
       <c r="L753" s="9"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="A754" s="31"/>
+      <c r="A754" s="32"/>
       <c r="B754" s="9"/>
       <c r="C754" s="9"/>
       <c r="D754" s="9"/>
@@ -14883,7 +14891,7 @@
       <c r="L754" s="9"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="A755" s="31"/>
+      <c r="A755" s="32"/>
       <c r="B755" s="9"/>
       <c r="C755" s="9"/>
       <c r="D755" s="9"/>
@@ -14897,7 +14905,7 @@
       <c r="L755" s="9"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="A756" s="31"/>
+      <c r="A756" s="32"/>
       <c r="B756" s="9"/>
       <c r="C756" s="9"/>
       <c r="D756" s="9"/>
@@ -14911,7 +14919,7 @@
       <c r="L756" s="9"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="A757" s="31"/>
+      <c r="A757" s="32"/>
       <c r="B757" s="9"/>
       <c r="C757" s="9"/>
       <c r="D757" s="9"/>
@@ -14925,7 +14933,7 @@
       <c r="L757" s="9"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="A758" s="31"/>
+      <c r="A758" s="32"/>
       <c r="B758" s="9"/>
       <c r="C758" s="9"/>
       <c r="D758" s="9"/>
@@ -14939,7 +14947,7 @@
       <c r="L758" s="9"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="A759" s="31"/>
+      <c r="A759" s="32"/>
       <c r="B759" s="9"/>
       <c r="C759" s="9"/>
       <c r="D759" s="9"/>
@@ -14953,7 +14961,7 @@
       <c r="L759" s="9"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="A760" s="31"/>
+      <c r="A760" s="32"/>
       <c r="B760" s="9"/>
       <c r="C760" s="9"/>
       <c r="D760" s="9"/>
@@ -14967,7 +14975,7 @@
       <c r="L760" s="9"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="A761" s="31"/>
+      <c r="A761" s="32"/>
       <c r="B761" s="9"/>
       <c r="C761" s="9"/>
       <c r="D761" s="9"/>
@@ -14981,7 +14989,7 @@
       <c r="L761" s="9"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="A762" s="31"/>
+      <c r="A762" s="32"/>
       <c r="B762" s="9"/>
       <c r="C762" s="9"/>
       <c r="D762" s="9"/>
@@ -14995,7 +15003,7 @@
       <c r="L762" s="9"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="A763" s="31"/>
+      <c r="A763" s="32"/>
       <c r="B763" s="9"/>
       <c r="C763" s="9"/>
       <c r="D763" s="9"/>
@@ -15009,7 +15017,7 @@
       <c r="L763" s="9"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="A764" s="31"/>
+      <c r="A764" s="32"/>
       <c r="B764" s="9"/>
       <c r="C764" s="9"/>
       <c r="D764" s="9"/>
@@ -15023,7 +15031,7 @@
       <c r="L764" s="9"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="A765" s="31"/>
+      <c r="A765" s="32"/>
       <c r="B765" s="9"/>
       <c r="C765" s="9"/>
       <c r="D765" s="9"/>
@@ -15037,7 +15045,7 @@
       <c r="L765" s="9"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="A766" s="31"/>
+      <c r="A766" s="32"/>
       <c r="B766" s="9"/>
       <c r="C766" s="9"/>
       <c r="D766" s="9"/>
@@ -15051,7 +15059,7 @@
       <c r="L766" s="9"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="A767" s="31"/>
+      <c r="A767" s="32"/>
       <c r="B767" s="9"/>
       <c r="C767" s="9"/>
       <c r="D767" s="9"/>
@@ -15065,7 +15073,7 @@
       <c r="L767" s="9"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="A768" s="31"/>
+      <c r="A768" s="32"/>
       <c r="B768" s="9"/>
       <c r="C768" s="9"/>
       <c r="D768" s="9"/>
@@ -15079,7 +15087,7 @@
       <c r="L768" s="9"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="A769" s="31"/>
+      <c r="A769" s="32"/>
       <c r="B769" s="9"/>
       <c r="C769" s="9"/>
       <c r="D769" s="9"/>
@@ -15093,7 +15101,7 @@
       <c r="L769" s="9"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="A770" s="31"/>
+      <c r="A770" s="32"/>
       <c r="B770" s="9"/>
       <c r="C770" s="9"/>
       <c r="D770" s="9"/>
@@ -15107,7 +15115,7 @@
       <c r="L770" s="9"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="A771" s="31"/>
+      <c r="A771" s="32"/>
       <c r="B771" s="9"/>
       <c r="C771" s="9"/>
       <c r="D771" s="9"/>
@@ -15121,7 +15129,7 @@
       <c r="L771" s="9"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="A772" s="31"/>
+      <c r="A772" s="32"/>
       <c r="B772" s="9"/>
       <c r="C772" s="9"/>
       <c r="D772" s="9"/>
@@ -15135,7 +15143,7 @@
       <c r="L772" s="9"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="A773" s="31"/>
+      <c r="A773" s="32"/>
       <c r="B773" s="9"/>
       <c r="C773" s="9"/>
       <c r="D773" s="9"/>
@@ -15149,7 +15157,7 @@
       <c r="L773" s="9"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="A774" s="31"/>
+      <c r="A774" s="32"/>
       <c r="B774" s="9"/>
       <c r="C774" s="9"/>
       <c r="D774" s="9"/>
@@ -15163,7 +15171,7 @@
       <c r="L774" s="9"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="A775" s="31"/>
+      <c r="A775" s="32"/>
       <c r="B775" s="9"/>
       <c r="C775" s="9"/>
       <c r="D775" s="9"/>
@@ -15177,7 +15185,7 @@
       <c r="L775" s="9"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="A776" s="31"/>
+      <c r="A776" s="32"/>
       <c r="B776" s="9"/>
       <c r="C776" s="9"/>
       <c r="D776" s="9"/>
@@ -15191,7 +15199,7 @@
       <c r="L776" s="9"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="A777" s="31"/>
+      <c r="A777" s="32"/>
       <c r="B777" s="9"/>
       <c r="C777" s="9"/>
       <c r="D777" s="9"/>
@@ -15205,7 +15213,7 @@
       <c r="L777" s="9"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="A778" s="31"/>
+      <c r="A778" s="32"/>
       <c r="B778" s="9"/>
       <c r="C778" s="9"/>
       <c r="D778" s="9"/>
@@ -15219,7 +15227,7 @@
       <c r="L778" s="9"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="A779" s="31"/>
+      <c r="A779" s="32"/>
       <c r="B779" s="9"/>
       <c r="C779" s="9"/>
       <c r="D779" s="9"/>
@@ -15233,7 +15241,7 @@
       <c r="L779" s="9"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="A780" s="31"/>
+      <c r="A780" s="32"/>
       <c r="B780" s="9"/>
       <c r="C780" s="9"/>
       <c r="D780" s="9"/>
@@ -15247,7 +15255,7 @@
       <c r="L780" s="9"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="A781" s="31"/>
+      <c r="A781" s="32"/>
       <c r="B781" s="9"/>
       <c r="C781" s="9"/>
       <c r="D781" s="9"/>
@@ -15261,7 +15269,7 @@
       <c r="L781" s="9"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="A782" s="31"/>
+      <c r="A782" s="32"/>
       <c r="B782" s="9"/>
       <c r="C782" s="9"/>
       <c r="D782" s="9"/>
@@ -15275,7 +15283,7 @@
       <c r="L782" s="9"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="A783" s="31"/>
+      <c r="A783" s="32"/>
       <c r="B783" s="9"/>
       <c r="C783" s="9"/>
       <c r="D783" s="9"/>
@@ -15289,7 +15297,7 @@
       <c r="L783" s="9"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="A784" s="31"/>
+      <c r="A784" s="32"/>
       <c r="B784" s="9"/>
       <c r="C784" s="9"/>
       <c r="D784" s="9"/>
@@ -15303,7 +15311,7 @@
       <c r="L784" s="9"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="A785" s="31"/>
+      <c r="A785" s="32"/>
       <c r="B785" s="9"/>
       <c r="C785" s="9"/>
       <c r="D785" s="9"/>
@@ -15317,7 +15325,7 @@
       <c r="L785" s="9"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="A786" s="31"/>
+      <c r="A786" s="32"/>
       <c r="B786" s="9"/>
       <c r="C786" s="9"/>
       <c r="D786" s="9"/>
@@ -15331,7 +15339,7 @@
       <c r="L786" s="9"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="A787" s="31"/>
+      <c r="A787" s="32"/>
       <c r="B787" s="9"/>
       <c r="C787" s="9"/>
       <c r="D787" s="9"/>
@@ -15345,7 +15353,7 @@
       <c r="L787" s="9"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="A788" s="31"/>
+      <c r="A788" s="32"/>
       <c r="B788" s="9"/>
       <c r="C788" s="9"/>
       <c r="D788" s="9"/>
@@ -15359,7 +15367,7 @@
       <c r="L788" s="9"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="A789" s="31"/>
+      <c r="A789" s="32"/>
       <c r="B789" s="9"/>
       <c r="C789" s="9"/>
       <c r="D789" s="9"/>
@@ -15373,7 +15381,7 @@
       <c r="L789" s="9"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="A790" s="31"/>
+      <c r="A790" s="32"/>
       <c r="B790" s="9"/>
       <c r="C790" s="9"/>
       <c r="D790" s="9"/>
@@ -15387,7 +15395,7 @@
       <c r="L790" s="9"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="A791" s="31"/>
+      <c r="A791" s="32"/>
       <c r="B791" s="9"/>
       <c r="C791" s="9"/>
       <c r="D791" s="9"/>
@@ -15401,7 +15409,7 @@
       <c r="L791" s="9"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="A792" s="31"/>
+      <c r="A792" s="32"/>
       <c r="B792" s="9"/>
       <c r="C792" s="9"/>
       <c r="D792" s="9"/>
@@ -15415,7 +15423,7 @@
       <c r="L792" s="9"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="A793" s="31"/>
+      <c r="A793" s="32"/>
       <c r="B793" s="9"/>
       <c r="C793" s="9"/>
       <c r="D793" s="9"/>
@@ -15429,7 +15437,7 @@
       <c r="L793" s="9"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="A794" s="31"/>
+      <c r="A794" s="32"/>
       <c r="B794" s="9"/>
       <c r="C794" s="9"/>
       <c r="D794" s="9"/>
@@ -15443,7 +15451,7 @@
       <c r="L794" s="9"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="A795" s="31"/>
+      <c r="A795" s="32"/>
       <c r="B795" s="9"/>
       <c r="C795" s="9"/>
       <c r="D795" s="9"/>
@@ -15457,7 +15465,7 @@
       <c r="L795" s="9"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="A796" s="31"/>
+      <c r="A796" s="32"/>
       <c r="B796" s="9"/>
       <c r="C796" s="9"/>
       <c r="D796" s="9"/>
@@ -15471,7 +15479,7 @@
       <c r="L796" s="9"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="A797" s="31"/>
+      <c r="A797" s="32"/>
       <c r="B797" s="9"/>
       <c r="C797" s="9"/>
       <c r="D797" s="9"/>
@@ -15485,7 +15493,7 @@
       <c r="L797" s="9"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="A798" s="31"/>
+      <c r="A798" s="32"/>
       <c r="B798" s="9"/>
       <c r="C798" s="9"/>
       <c r="D798" s="9"/>
@@ -15499,7 +15507,7 @@
       <c r="L798" s="9"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="A799" s="31"/>
+      <c r="A799" s="32"/>
       <c r="B799" s="9"/>
       <c r="C799" s="9"/>
       <c r="D799" s="9"/>
@@ -15513,7 +15521,7 @@
       <c r="L799" s="9"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="A800" s="31"/>
+      <c r="A800" s="32"/>
       <c r="B800" s="9"/>
       <c r="C800" s="9"/>
       <c r="D800" s="9"/>
@@ -15527,7 +15535,7 @@
       <c r="L800" s="9"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="A801" s="31"/>
+      <c r="A801" s="32"/>
       <c r="B801" s="9"/>
       <c r="C801" s="9"/>
       <c r="D801" s="9"/>
@@ -15541,7 +15549,7 @@
       <c r="L801" s="9"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="31"/>
+      <c r="A802" s="32"/>
       <c r="B802" s="9"/>
       <c r="C802" s="9"/>
       <c r="D802" s="9"/>
@@ -15555,7 +15563,7 @@
       <c r="L802" s="9"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="A803" s="31"/>
+      <c r="A803" s="32"/>
       <c r="B803" s="9"/>
       <c r="C803" s="9"/>
       <c r="D803" s="9"/>
@@ -15569,7 +15577,7 @@
       <c r="L803" s="9"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="A804" s="31"/>
+      <c r="A804" s="32"/>
       <c r="B804" s="9"/>
       <c r="C804" s="9"/>
       <c r="D804" s="9"/>
@@ -15583,7 +15591,7 @@
       <c r="L804" s="9"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="A805" s="31"/>
+      <c r="A805" s="32"/>
       <c r="B805" s="9"/>
       <c r="C805" s="9"/>
       <c r="D805" s="9"/>
@@ -15597,7 +15605,7 @@
       <c r="L805" s="9"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="A806" s="31"/>
+      <c r="A806" s="32"/>
       <c r="B806" s="9"/>
       <c r="C806" s="9"/>
       <c r="D806" s="9"/>
@@ -15611,7 +15619,7 @@
       <c r="L806" s="9"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="A807" s="31"/>
+      <c r="A807" s="32"/>
       <c r="B807" s="9"/>
       <c r="C807" s="9"/>
       <c r="D807" s="9"/>
@@ -15625,7 +15633,7 @@
       <c r="L807" s="9"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="A808" s="31"/>
+      <c r="A808" s="32"/>
       <c r="B808" s="9"/>
       <c r="C808" s="9"/>
       <c r="D808" s="9"/>
@@ -15639,7 +15647,7 @@
       <c r="L808" s="9"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="A809" s="31"/>
+      <c r="A809" s="32"/>
       <c r="B809" s="9"/>
       <c r="C809" s="9"/>
       <c r="D809" s="9"/>
@@ -15653,7 +15661,7 @@
       <c r="L809" s="9"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="A810" s="31"/>
+      <c r="A810" s="32"/>
       <c r="B810" s="9"/>
       <c r="C810" s="9"/>
       <c r="D810" s="9"/>
@@ -15667,7 +15675,7 @@
       <c r="L810" s="9"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="A811" s="31"/>
+      <c r="A811" s="32"/>
       <c r="B811" s="9"/>
       <c r="C811" s="9"/>
       <c r="D811" s="9"/>
@@ -15681,7 +15689,7 @@
       <c r="L811" s="9"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="A812" s="31"/>
+      <c r="A812" s="32"/>
       <c r="B812" s="9"/>
       <c r="C812" s="9"/>
       <c r="D812" s="9"/>
@@ -15695,7 +15703,7 @@
       <c r="L812" s="9"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="A813" s="31"/>
+      <c r="A813" s="32"/>
       <c r="B813" s="9"/>
       <c r="C813" s="9"/>
       <c r="D813" s="9"/>
@@ -15709,7 +15717,7 @@
       <c r="L813" s="9"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="A814" s="31"/>
+      <c r="A814" s="32"/>
       <c r="B814" s="9"/>
       <c r="C814" s="9"/>
       <c r="D814" s="9"/>
@@ -15723,7 +15731,7 @@
       <c r="L814" s="9"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="A815" s="31"/>
+      <c r="A815" s="32"/>
       <c r="B815" s="9"/>
       <c r="C815" s="9"/>
       <c r="D815" s="9"/>
@@ -15737,7 +15745,7 @@
       <c r="L815" s="9"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="A816" s="31"/>
+      <c r="A816" s="32"/>
       <c r="B816" s="9"/>
       <c r="C816" s="9"/>
       <c r="D816" s="9"/>
@@ -15751,7 +15759,7 @@
       <c r="L816" s="9"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="A817" s="31"/>
+      <c r="A817" s="32"/>
       <c r="B817" s="9"/>
       <c r="C817" s="9"/>
       <c r="D817" s="9"/>
@@ -15765,7 +15773,7 @@
       <c r="L817" s="9"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="A818" s="31"/>
+      <c r="A818" s="32"/>
       <c r="B818" s="9"/>
       <c r="C818" s="9"/>
       <c r="D818" s="9"/>
@@ -15779,7 +15787,7 @@
       <c r="L818" s="9"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="A819" s="31"/>
+      <c r="A819" s="32"/>
       <c r="B819" s="9"/>
       <c r="C819" s="9"/>
       <c r="D819" s="9"/>
@@ -15793,7 +15801,7 @@
       <c r="L819" s="9"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="A820" s="31"/>
+      <c r="A820" s="32"/>
       <c r="B820" s="9"/>
       <c r="C820" s="9"/>
       <c r="D820" s="9"/>
@@ -15807,7 +15815,7 @@
       <c r="L820" s="9"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="A821" s="31"/>
+      <c r="A821" s="32"/>
       <c r="B821" s="9"/>
       <c r="C821" s="9"/>
       <c r="D821" s="9"/>
@@ -15821,7 +15829,7 @@
       <c r="L821" s="9"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="A822" s="31"/>
+      <c r="A822" s="32"/>
       <c r="B822" s="9"/>
       <c r="C822" s="9"/>
       <c r="D822" s="9"/>
@@ -15835,7 +15843,7 @@
       <c r="L822" s="9"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="A823" s="31"/>
+      <c r="A823" s="32"/>
       <c r="B823" s="9"/>
       <c r="C823" s="9"/>
       <c r="D823" s="9"/>
@@ -15849,7 +15857,7 @@
       <c r="L823" s="9"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="A824" s="31"/>
+      <c r="A824" s="32"/>
       <c r="B824" s="9"/>
       <c r="C824" s="9"/>
       <c r="D824" s="9"/>
@@ -15863,7 +15871,7 @@
       <c r="L824" s="9"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="A825" s="31"/>
+      <c r="A825" s="32"/>
       <c r="B825" s="9"/>
       <c r="C825" s="9"/>
       <c r="D825" s="9"/>
@@ -15877,7 +15885,7 @@
       <c r="L825" s="9"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="A826" s="31"/>
+      <c r="A826" s="32"/>
       <c r="B826" s="9"/>
       <c r="C826" s="9"/>
       <c r="D826" s="9"/>
@@ -15891,7 +15899,7 @@
       <c r="L826" s="9"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="A827" s="31"/>
+      <c r="A827" s="32"/>
       <c r="B827" s="9"/>
       <c r="C827" s="9"/>
       <c r="D827" s="9"/>
@@ -15905,7 +15913,7 @@
       <c r="L827" s="9"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="A828" s="31"/>
+      <c r="A828" s="32"/>
       <c r="B828" s="9"/>
       <c r="C828" s="9"/>
       <c r="D828" s="9"/>
@@ -15919,7 +15927,7 @@
       <c r="L828" s="9"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="A829" s="31"/>
+      <c r="A829" s="32"/>
       <c r="B829" s="9"/>
       <c r="C829" s="9"/>
       <c r="D829" s="9"/>
@@ -15933,7 +15941,7 @@
       <c r="L829" s="9"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="A830" s="31"/>
+      <c r="A830" s="32"/>
       <c r="B830" s="9"/>
       <c r="C830" s="9"/>
       <c r="D830" s="9"/>
@@ -15947,7 +15955,7 @@
       <c r="L830" s="9"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="A831" s="31"/>
+      <c r="A831" s="32"/>
       <c r="B831" s="9"/>
       <c r="C831" s="9"/>
       <c r="D831" s="9"/>
@@ -15961,7 +15969,7 @@
       <c r="L831" s="9"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="A832" s="31"/>
+      <c r="A832" s="32"/>
       <c r="B832" s="9"/>
       <c r="C832" s="9"/>
       <c r="D832" s="9"/>
@@ -15975,7 +15983,7 @@
       <c r="L832" s="9"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="A833" s="31"/>
+      <c r="A833" s="32"/>
       <c r="B833" s="9"/>
       <c r="C833" s="9"/>
       <c r="D833" s="9"/>
@@ -15989,7 +15997,7 @@
       <c r="L833" s="9"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="A834" s="31"/>
+      <c r="A834" s="32"/>
       <c r="B834" s="9"/>
       <c r="C834" s="9"/>
       <c r="D834" s="9"/>
@@ -16003,7 +16011,7 @@
       <c r="L834" s="9"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="A835" s="31"/>
+      <c r="A835" s="32"/>
       <c r="B835" s="9"/>
       <c r="C835" s="9"/>
       <c r="D835" s="9"/>
@@ -16017,7 +16025,7 @@
       <c r="L835" s="9"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="A836" s="31"/>
+      <c r="A836" s="32"/>
       <c r="B836" s="9"/>
       <c r="C836" s="9"/>
       <c r="D836" s="9"/>
@@ -16031,7 +16039,7 @@
       <c r="L836" s="9"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="A837" s="31"/>
+      <c r="A837" s="32"/>
       <c r="B837" s="9"/>
       <c r="C837" s="9"/>
       <c r="D837" s="9"/>
@@ -16045,7 +16053,7 @@
       <c r="L837" s="9"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="A838" s="31"/>
+      <c r="A838" s="32"/>
       <c r="B838" s="9"/>
       <c r="C838" s="9"/>
       <c r="D838" s="9"/>
@@ -16059,7 +16067,7 @@
       <c r="L838" s="9"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="A839" s="31"/>
+      <c r="A839" s="32"/>
       <c r="B839" s="9"/>
       <c r="C839" s="9"/>
       <c r="D839" s="9"/>
@@ -16073,7 +16081,7 @@
       <c r="L839" s="9"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="A840" s="31"/>
+      <c r="A840" s="32"/>
       <c r="B840" s="9"/>
       <c r="C840" s="9"/>
       <c r="D840" s="9"/>
@@ -16087,7 +16095,7 @@
       <c r="L840" s="9"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="A841" s="31"/>
+      <c r="A841" s="32"/>
       <c r="B841" s="9"/>
       <c r="C841" s="9"/>
       <c r="D841" s="9"/>
@@ -16101,7 +16109,7 @@
       <c r="L841" s="9"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="A842" s="31"/>
+      <c r="A842" s="32"/>
       <c r="B842" s="9"/>
       <c r="C842" s="9"/>
       <c r="D842" s="9"/>
@@ -16115,7 +16123,7 @@
       <c r="L842" s="9"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="A843" s="31"/>
+      <c r="A843" s="32"/>
       <c r="B843" s="9"/>
       <c r="C843" s="9"/>
       <c r="D843" s="9"/>
@@ -16129,7 +16137,7 @@
       <c r="L843" s="9"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="A844" s="31"/>
+      <c r="A844" s="32"/>
       <c r="B844" s="9"/>
       <c r="C844" s="9"/>
       <c r="D844" s="9"/>
@@ -16143,7 +16151,7 @@
       <c r="L844" s="9"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="A845" s="31"/>
+      <c r="A845" s="32"/>
       <c r="B845" s="9"/>
       <c r="C845" s="9"/>
       <c r="D845" s="9"/>
@@ -16157,7 +16165,7 @@
       <c r="L845" s="9"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="A846" s="31"/>
+      <c r="A846" s="32"/>
       <c r="B846" s="9"/>
       <c r="C846" s="9"/>
       <c r="D846" s="9"/>
@@ -16171,7 +16179,7 @@
       <c r="L846" s="9"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="A847" s="31"/>
+      <c r="A847" s="32"/>
       <c r="B847" s="9"/>
       <c r="C847" s="9"/>
       <c r="D847" s="9"/>
@@ -16185,7 +16193,7 @@
       <c r="L847" s="9"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="A848" s="31"/>
+      <c r="A848" s="32"/>
       <c r="B848" s="9"/>
       <c r="C848" s="9"/>
       <c r="D848" s="9"/>
@@ -16199,7 +16207,7 @@
       <c r="L848" s="9"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="A849" s="31"/>
+      <c r="A849" s="32"/>
       <c r="B849" s="9"/>
       <c r="C849" s="9"/>
       <c r="D849" s="9"/>
@@ -16213,7 +16221,7 @@
       <c r="L849" s="9"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="A850" s="31"/>
+      <c r="A850" s="32"/>
       <c r="B850" s="9"/>
       <c r="C850" s="9"/>
       <c r="D850" s="9"/>
@@ -16227,7 +16235,7 @@
       <c r="L850" s="9"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="A851" s="31"/>
+      <c r="A851" s="32"/>
       <c r="B851" s="9"/>
       <c r="C851" s="9"/>
       <c r="D851" s="9"/>
@@ -16241,7 +16249,7 @@
       <c r="L851" s="9"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="A852" s="31"/>
+      <c r="A852" s="32"/>
       <c r="B852" s="9"/>
       <c r="C852" s="9"/>
       <c r="D852" s="9"/>
@@ -16255,7 +16263,7 @@
       <c r="L852" s="9"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="A853" s="31"/>
+      <c r="A853" s="32"/>
       <c r="B853" s="9"/>
       <c r="C853" s="9"/>
       <c r="D853" s="9"/>
@@ -16269,7 +16277,7 @@
       <c r="L853" s="9"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="A854" s="31"/>
+      <c r="A854" s="32"/>
       <c r="B854" s="9"/>
       <c r="C854" s="9"/>
       <c r="D854" s="9"/>
@@ -16283,7 +16291,7 @@
       <c r="L854" s="9"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="31"/>
+      <c r="A855" s="32"/>
       <c r="B855" s="9"/>
       <c r="C855" s="9"/>
       <c r="D855" s="9"/>
@@ -16297,7 +16305,7 @@
       <c r="L855" s="9"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="A856" s="31"/>
+      <c r="A856" s="32"/>
       <c r="B856" s="9"/>
       <c r="C856" s="9"/>
       <c r="D856" s="9"/>
@@ -16311,7 +16319,7 @@
       <c r="L856" s="9"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="A857" s="31"/>
+      <c r="A857" s="32"/>
       <c r="B857" s="9"/>
       <c r="C857" s="9"/>
       <c r="D857" s="9"/>
@@ -16325,7 +16333,7 @@
       <c r="L857" s="9"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="A858" s="31"/>
+      <c r="A858" s="32"/>
       <c r="B858" s="9"/>
       <c r="C858" s="9"/>
       <c r="D858" s="9"/>
@@ -16339,7 +16347,7 @@
       <c r="L858" s="9"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="A859" s="31"/>
+      <c r="A859" s="32"/>
       <c r="B859" s="9"/>
       <c r="C859" s="9"/>
       <c r="D859" s="9"/>
@@ -16353,7 +16361,7 @@
       <c r="L859" s="9"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="A860" s="31"/>
+      <c r="A860" s="32"/>
       <c r="B860" s="9"/>
       <c r="C860" s="9"/>
       <c r="D860" s="9"/>
@@ -16367,7 +16375,7 @@
       <c r="L860" s="9"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="A861" s="31"/>
+      <c r="A861" s="32"/>
       <c r="B861" s="9"/>
       <c r="C861" s="9"/>
       <c r="D861" s="9"/>
@@ -16381,7 +16389,7 @@
       <c r="L861" s="9"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="31"/>
+      <c r="A862" s="32"/>
       <c r="B862" s="9"/>
       <c r="C862" s="9"/>
       <c r="D862" s="9"/>
@@ -16395,7 +16403,7 @@
       <c r="L862" s="9"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="A863" s="31"/>
+      <c r="A863" s="32"/>
       <c r="B863" s="9"/>
       <c r="C863" s="9"/>
       <c r="D863" s="9"/>
@@ -16409,7 +16417,7 @@
       <c r="L863" s="9"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="A864" s="31"/>
+      <c r="A864" s="32"/>
       <c r="B864" s="9"/>
       <c r="C864" s="9"/>
       <c r="D864" s="9"/>
@@ -16423,7 +16431,7 @@
       <c r="L864" s="9"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="A865" s="31"/>
+      <c r="A865" s="32"/>
       <c r="B865" s="9"/>
       <c r="C865" s="9"/>
       <c r="D865" s="9"/>
@@ -16437,7 +16445,7 @@
       <c r="L865" s="9"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="A866" s="31"/>
+      <c r="A866" s="32"/>
       <c r="B866" s="9"/>
       <c r="C866" s="9"/>
       <c r="D866" s="9"/>
@@ -16451,7 +16459,7 @@
       <c r="L866" s="9"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="A867" s="31"/>
+      <c r="A867" s="32"/>
       <c r="B867" s="9"/>
       <c r="C867" s="9"/>
       <c r="D867" s="9"/>
@@ -16465,7 +16473,7 @@
       <c r="L867" s="9"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="A868" s="31"/>
+      <c r="A868" s="32"/>
       <c r="B868" s="9"/>
       <c r="C868" s="9"/>
       <c r="D868" s="9"/>
@@ -16479,7 +16487,7 @@
       <c r="L868" s="9"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="31"/>
+      <c r="A869" s="32"/>
       <c r="B869" s="9"/>
       <c r="C869" s="9"/>
       <c r="D869" s="9"/>
@@ -16493,7 +16501,7 @@
       <c r="L869" s="9"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="A870" s="31"/>
+      <c r="A870" s="32"/>
       <c r="B870" s="9"/>
       <c r="C870" s="9"/>
       <c r="D870" s="9"/>
@@ -16507,7 +16515,7 @@
       <c r="L870" s="9"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="A871" s="31"/>
+      <c r="A871" s="32"/>
       <c r="B871" s="9"/>
       <c r="C871" s="9"/>
       <c r="D871" s="9"/>
@@ -16521,7 +16529,7 @@
       <c r="L871" s="9"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="A872" s="31"/>
+      <c r="A872" s="32"/>
       <c r="B872" s="9"/>
       <c r="C872" s="9"/>
       <c r="D872" s="9"/>
@@ -16535,7 +16543,7 @@
       <c r="L872" s="9"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="A873" s="31"/>
+      <c r="A873" s="32"/>
       <c r="B873" s="9"/>
       <c r="C873" s="9"/>
       <c r="D873" s="9"/>
@@ -16549,7 +16557,7 @@
       <c r="L873" s="9"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="A874" s="31"/>
+      <c r="A874" s="32"/>
       <c r="B874" s="9"/>
       <c r="C874" s="9"/>
       <c r="D874" s="9"/>
@@ -16563,7 +16571,7 @@
       <c r="L874" s="9"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="A875" s="31"/>
+      <c r="A875" s="32"/>
       <c r="B875" s="9"/>
       <c r="C875" s="9"/>
       <c r="D875" s="9"/>
@@ -16577,7 +16585,7 @@
       <c r="L875" s="9"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="A876" s="31"/>
+      <c r="A876" s="32"/>
       <c r="B876" s="9"/>
       <c r="C876" s="9"/>
       <c r="D876" s="9"/>
@@ -16591,7 +16599,7 @@
       <c r="L876" s="9"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="A877" s="31"/>
+      <c r="A877" s="32"/>
       <c r="B877" s="9"/>
       <c r="C877" s="9"/>
       <c r="D877" s="9"/>
@@ -16605,7 +16613,7 @@
       <c r="L877" s="9"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="A878" s="31"/>
+      <c r="A878" s="32"/>
       <c r="B878" s="9"/>
       <c r="C878" s="9"/>
       <c r="D878" s="9"/>
@@ -16619,7 +16627,7 @@
       <c r="L878" s="9"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="A879" s="31"/>
+      <c r="A879" s="32"/>
       <c r="B879" s="9"/>
       <c r="C879" s="9"/>
       <c r="D879" s="9"/>
@@ -16633,7 +16641,7 @@
       <c r="L879" s="9"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="A880" s="31"/>
+      <c r="A880" s="32"/>
       <c r="B880" s="9"/>
       <c r="C880" s="9"/>
       <c r="D880" s="9"/>
@@ -16647,7 +16655,7 @@
       <c r="L880" s="9"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="A881" s="31"/>
+      <c r="A881" s="32"/>
       <c r="B881" s="9"/>
       <c r="C881" s="9"/>
       <c r="D881" s="9"/>
@@ -16661,7 +16669,7 @@
       <c r="L881" s="9"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="A882" s="31"/>
+      <c r="A882" s="32"/>
       <c r="B882" s="9"/>
       <c r="C882" s="9"/>
       <c r="D882" s="9"/>
@@ -16675,7 +16683,7 @@
       <c r="L882" s="9"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="A883" s="31"/>
+      <c r="A883" s="32"/>
       <c r="B883" s="9"/>
       <c r="C883" s="9"/>
       <c r="D883" s="9"/>
@@ -16689,7 +16697,7 @@
       <c r="L883" s="9"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="A884" s="31"/>
+      <c r="A884" s="32"/>
       <c r="B884" s="9"/>
       <c r="C884" s="9"/>
       <c r="D884" s="9"/>
@@ -16703,7 +16711,7 @@
       <c r="L884" s="9"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="A885" s="31"/>
+      <c r="A885" s="32"/>
       <c r="B885" s="9"/>
       <c r="C885" s="9"/>
       <c r="D885" s="9"/>
@@ -16717,7 +16725,7 @@
       <c r="L885" s="9"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="A886" s="31"/>
+      <c r="A886" s="32"/>
       <c r="B886" s="9"/>
       <c r="C886" s="9"/>
       <c r="D886" s="9"/>
@@ -16731,7 +16739,7 @@
       <c r="L886" s="9"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="A887" s="31"/>
+      <c r="A887" s="32"/>
       <c r="B887" s="9"/>
       <c r="C887" s="9"/>
       <c r="D887" s="9"/>
@@ -16745,7 +16753,7 @@
       <c r="L887" s="9"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="A888" s="31"/>
+      <c r="A888" s="32"/>
       <c r="B888" s="9"/>
       <c r="C888" s="9"/>
       <c r="D888" s="9"/>
@@ -16759,7 +16767,7 @@
       <c r="L888" s="9"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="A889" s="31"/>
+      <c r="A889" s="32"/>
       <c r="B889" s="9"/>
       <c r="C889" s="9"/>
       <c r="D889" s="9"/>
@@ -16773,7 +16781,7 @@
       <c r="L889" s="9"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="A890" s="31"/>
+      <c r="A890" s="32"/>
       <c r="B890" s="9"/>
       <c r="C890" s="9"/>
       <c r="D890" s="9"/>
@@ -16787,7 +16795,7 @@
       <c r="L890" s="9"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="A891" s="31"/>
+      <c r="A891" s="32"/>
       <c r="B891" s="9"/>
       <c r="C891" s="9"/>
       <c r="D891" s="9"/>
@@ -16801,7 +16809,7 @@
       <c r="L891" s="9"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="A892" s="31"/>
+      <c r="A892" s="32"/>
       <c r="B892" s="9"/>
       <c r="C892" s="9"/>
       <c r="D892" s="9"/>
@@ -16815,7 +16823,7 @@
       <c r="L892" s="9"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="A893" s="31"/>
+      <c r="A893" s="32"/>
       <c r="B893" s="9"/>
       <c r="C893" s="9"/>
       <c r="D893" s="9"/>
@@ -16829,7 +16837,7 @@
       <c r="L893" s="9"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="A894" s="31"/>
+      <c r="A894" s="32"/>
       <c r="B894" s="9"/>
       <c r="C894" s="9"/>
       <c r="D894" s="9"/>
@@ -16843,7 +16851,7 @@
       <c r="L894" s="9"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="A895" s="31"/>
+      <c r="A895" s="32"/>
       <c r="B895" s="9"/>
       <c r="C895" s="9"/>
       <c r="D895" s="9"/>
@@ -16857,7 +16865,7 @@
       <c r="L895" s="9"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="A896" s="31"/>
+      <c r="A896" s="32"/>
       <c r="B896" s="9"/>
       <c r="C896" s="9"/>
       <c r="D896" s="9"/>
@@ -16871,7 +16879,7 @@
       <c r="L896" s="9"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="A897" s="31"/>
+      <c r="A897" s="32"/>
       <c r="B897" s="9"/>
       <c r="C897" s="9"/>
       <c r="D897" s="9"/>
@@ -16885,7 +16893,7 @@
       <c r="L897" s="9"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="A898" s="31"/>
+      <c r="A898" s="32"/>
       <c r="B898" s="9"/>
       <c r="C898" s="9"/>
       <c r="D898" s="9"/>
@@ -16899,7 +16907,7 @@
       <c r="L898" s="9"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="A899" s="31"/>
+      <c r="A899" s="32"/>
       <c r="B899" s="9"/>
       <c r="C899" s="9"/>
       <c r="D899" s="9"/>
@@ -16913,7 +16921,7 @@
       <c r="L899" s="9"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="A900" s="31"/>
+      <c r="A900" s="32"/>
       <c r="B900" s="9"/>
       <c r="C900" s="9"/>
       <c r="D900" s="9"/>
@@ -16927,7 +16935,7 @@
       <c r="L900" s="9"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="A901" s="31"/>
+      <c r="A901" s="32"/>
       <c r="B901" s="9"/>
       <c r="C901" s="9"/>
       <c r="D901" s="9"/>
@@ -16941,7 +16949,7 @@
       <c r="L901" s="9"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="A902" s="31"/>
+      <c r="A902" s="32"/>
       <c r="B902" s="9"/>
       <c r="C902" s="9"/>
       <c r="D902" s="9"/>
@@ -16955,7 +16963,7 @@
       <c r="L902" s="9"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="A903" s="31"/>
+      <c r="A903" s="32"/>
       <c r="B903" s="9"/>
       <c r="C903" s="9"/>
       <c r="D903" s="9"/>
@@ -16969,7 +16977,7 @@
       <c r="L903" s="9"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="A904" s="31"/>
+      <c r="A904" s="32"/>
       <c r="B904" s="9"/>
       <c r="C904" s="9"/>
       <c r="D904" s="9"/>
@@ -16983,7 +16991,7 @@
       <c r="L904" s="9"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="A905" s="31"/>
+      <c r="A905" s="32"/>
       <c r="B905" s="9"/>
       <c r="C905" s="9"/>
       <c r="D905" s="9"/>
@@ -16997,7 +17005,7 @@
       <c r="L905" s="9"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="A906" s="31"/>
+      <c r="A906" s="32"/>
       <c r="B906" s="9"/>
       <c r="C906" s="9"/>
       <c r="D906" s="9"/>
@@ -17011,7 +17019,7 @@
       <c r="L906" s="9"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="A907" s="31"/>
+      <c r="A907" s="32"/>
       <c r="B907" s="9"/>
       <c r="C907" s="9"/>
       <c r="D907" s="9"/>
@@ -17025,7 +17033,7 @@
       <c r="L907" s="9"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="A908" s="31"/>
+      <c r="A908" s="32"/>
       <c r="B908" s="9"/>
       <c r="C908" s="9"/>
       <c r="D908" s="9"/>
@@ -17039,7 +17047,7 @@
       <c r="L908" s="9"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="A909" s="31"/>
+      <c r="A909" s="32"/>
       <c r="B909" s="9"/>
       <c r="C909" s="9"/>
       <c r="D909" s="9"/>
@@ -17053,7 +17061,7 @@
       <c r="L909" s="9"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="A910" s="31"/>
+      <c r="A910" s="32"/>
       <c r="B910" s="9"/>
       <c r="C910" s="9"/>
       <c r="D910" s="9"/>
@@ -17067,7 +17075,7 @@
       <c r="L910" s="9"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="A911" s="31"/>
+      <c r="A911" s="32"/>
       <c r="B911" s="9"/>
       <c r="C911" s="9"/>
       <c r="D911" s="9"/>
@@ -17081,7 +17089,7 @@
       <c r="L911" s="9"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="A912" s="31"/>
+      <c r="A912" s="32"/>
       <c r="B912" s="9"/>
       <c r="C912" s="9"/>
       <c r="D912" s="9"/>
@@ -17095,7 +17103,7 @@
       <c r="L912" s="9"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="A913" s="31"/>
+      <c r="A913" s="32"/>
       <c r="B913" s="9"/>
       <c r="C913" s="9"/>
       <c r="D913" s="9"/>
@@ -17109,7 +17117,7 @@
       <c r="L913" s="9"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="A914" s="31"/>
+      <c r="A914" s="32"/>
       <c r="B914" s="9"/>
       <c r="C914" s="9"/>
       <c r="D914" s="9"/>
@@ -17123,7 +17131,7 @@
       <c r="L914" s="9"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="A915" s="31"/>
+      <c r="A915" s="32"/>
       <c r="B915" s="9"/>
       <c r="C915" s="9"/>
       <c r="D915" s="9"/>
@@ -17137,7 +17145,7 @@
       <c r="L915" s="9"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="A916" s="31"/>
+      <c r="A916" s="32"/>
       <c r="B916" s="9"/>
       <c r="C916" s="9"/>
       <c r="D916" s="9"/>
@@ -17151,7 +17159,7 @@
       <c r="L916" s="9"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="A917" s="31"/>
+      <c r="A917" s="32"/>
       <c r="B917" s="9"/>
       <c r="C917" s="9"/>
       <c r="D917" s="9"/>
@@ -17165,7 +17173,7 @@
       <c r="L917" s="9"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="A918" s="31"/>
+      <c r="A918" s="32"/>
       <c r="B918" s="9"/>
       <c r="C918" s="9"/>
       <c r="D918" s="9"/>
@@ -17179,7 +17187,7 @@
       <c r="L918" s="9"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="A919" s="31"/>
+      <c r="A919" s="32"/>
       <c r="B919" s="9"/>
       <c r="C919" s="9"/>
       <c r="D919" s="9"/>
@@ -17193,7 +17201,7 @@
       <c r="L919" s="9"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="A920" s="31"/>
+      <c r="A920" s="32"/>
       <c r="B920" s="9"/>
       <c r="C920" s="9"/>
       <c r="D920" s="9"/>
@@ -17207,7 +17215,7 @@
       <c r="L920" s="9"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="A921" s="31"/>
+      <c r="A921" s="32"/>
       <c r="B921" s="9"/>
       <c r="C921" s="9"/>
       <c r="D921" s="9"/>
@@ -17221,7 +17229,7 @@
       <c r="L921" s="9"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="A922" s="31"/>
+      <c r="A922" s="32"/>
       <c r="B922" s="9"/>
       <c r="C922" s="9"/>
       <c r="D922" s="9"/>
@@ -17235,7 +17243,7 @@
       <c r="L922" s="9"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="A923" s="31"/>
+      <c r="A923" s="32"/>
       <c r="B923" s="9"/>
       <c r="C923" s="9"/>
       <c r="D923" s="9"/>
@@ -17249,7 +17257,7 @@
       <c r="L923" s="9"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="A924" s="31"/>
+      <c r="A924" s="32"/>
       <c r="B924" s="9"/>
       <c r="C924" s="9"/>
       <c r="D924" s="9"/>
@@ -17263,7 +17271,7 @@
       <c r="L924" s="9"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="A925" s="31"/>
+      <c r="A925" s="32"/>
       <c r="B925" s="9"/>
       <c r="C925" s="9"/>
       <c r="D925" s="9"/>
@@ -17277,7 +17285,7 @@
       <c r="L925" s="9"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="A926" s="31"/>
+      <c r="A926" s="32"/>
       <c r="B926" s="9"/>
       <c r="C926" s="9"/>
       <c r="D926" s="9"/>
@@ -17291,7 +17299,7 @@
       <c r="L926" s="9"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="A927" s="31"/>
+      <c r="A927" s="32"/>
       <c r="B927" s="9"/>
       <c r="C927" s="9"/>
       <c r="D927" s="9"/>
@@ -17305,7 +17313,7 @@
       <c r="L927" s="9"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="A928" s="31"/>
+      <c r="A928" s="32"/>
       <c r="B928" s="9"/>
       <c r="C928" s="9"/>
       <c r="D928" s="9"/>
@@ -17319,7 +17327,7 @@
       <c r="L928" s="9"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="A929" s="31"/>
+      <c r="A929" s="32"/>
       <c r="B929" s="9"/>
       <c r="C929" s="9"/>
       <c r="D929" s="9"/>
@@ -17333,7 +17341,7 @@
       <c r="L929" s="9"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="A930" s="31"/>
+      <c r="A930" s="32"/>
       <c r="B930" s="9"/>
       <c r="C930" s="9"/>
       <c r="D930" s="9"/>
@@ -17347,7 +17355,7 @@
       <c r="L930" s="9"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="A931" s="31"/>
+      <c r="A931" s="32"/>
       <c r="B931" s="9"/>
       <c r="C931" s="9"/>
       <c r="D931" s="9"/>
@@ -17361,7 +17369,7 @@
       <c r="L931" s="9"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="31"/>
+      <c r="A932" s="32"/>
       <c r="B932" s="9"/>
       <c r="C932" s="9"/>
       <c r="D932" s="9"/>
@@ -17375,7 +17383,7 @@
       <c r="L932" s="9"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="A933" s="31"/>
+      <c r="A933" s="32"/>
       <c r="B933" s="9"/>
       <c r="C933" s="9"/>
       <c r="D933" s="9"/>
@@ -17389,7 +17397,7 @@
       <c r="L933" s="9"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="A934" s="31"/>
+      <c r="A934" s="32"/>
       <c r="B934" s="9"/>
       <c r="C934" s="9"/>
       <c r="D934" s="9"/>
@@ -17403,7 +17411,7 @@
       <c r="L934" s="9"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="A935" s="31"/>
+      <c r="A935" s="32"/>
       <c r="B935" s="9"/>
       <c r="C935" s="9"/>
       <c r="D935" s="9"/>
@@ -17417,7 +17425,7 @@
       <c r="L935" s="9"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="A936" s="31"/>
+      <c r="A936" s="32"/>
       <c r="B936" s="9"/>
       <c r="C936" s="9"/>
       <c r="D936" s="9"/>
@@ -17431,7 +17439,7 @@
       <c r="L936" s="9"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="A937" s="31"/>
+      <c r="A937" s="32"/>
       <c r="B937" s="9"/>
       <c r="C937" s="9"/>
       <c r="D937" s="9"/>
@@ -17445,7 +17453,7 @@
       <c r="L937" s="9"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="A938" s="31"/>
+      <c r="A938" s="32"/>
       <c r="B938" s="9"/>
       <c r="C938" s="9"/>
       <c r="D938" s="9"/>
@@ -17459,7 +17467,7 @@
       <c r="L938" s="9"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="A939" s="31"/>
+      <c r="A939" s="32"/>
       <c r="B939" s="9"/>
       <c r="C939" s="9"/>
       <c r="D939" s="9"/>
@@ -17473,7 +17481,7 @@
       <c r="L939" s="9"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="A940" s="31"/>
+      <c r="A940" s="32"/>
       <c r="B940" s="9"/>
       <c r="C940" s="9"/>
       <c r="D940" s="9"/>
@@ -17487,7 +17495,7 @@
       <c r="L940" s="9"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="A941" s="31"/>
+      <c r="A941" s="32"/>
       <c r="B941" s="9"/>
       <c r="C941" s="9"/>
       <c r="D941" s="9"/>
@@ -17501,7 +17509,7 @@
       <c r="L941" s="9"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="A942" s="31"/>
+      <c r="A942" s="32"/>
       <c r="B942" s="9"/>
       <c r="C942" s="9"/>
       <c r="D942" s="9"/>
@@ -17515,7 +17523,7 @@
       <c r="L942" s="9"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="A943" s="31"/>
+      <c r="A943" s="32"/>
       <c r="B943" s="9"/>
       <c r="C943" s="9"/>
       <c r="D943" s="9"/>
@@ -17529,7 +17537,7 @@
       <c r="L943" s="9"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="A944" s="31"/>
+      <c r="A944" s="32"/>
       <c r="B944" s="9"/>
       <c r="C944" s="9"/>
       <c r="D944" s="9"/>
@@ -17543,7 +17551,7 @@
       <c r="L944" s="9"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="A945" s="31"/>
+      <c r="A945" s="32"/>
       <c r="B945" s="9"/>
       <c r="C945" s="9"/>
       <c r="D945" s="9"/>
@@ -17557,7 +17565,7 @@
       <c r="L945" s="9"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="A946" s="31"/>
+      <c r="A946" s="32"/>
       <c r="B946" s="9"/>
       <c r="C946" s="9"/>
       <c r="D946" s="9"/>
@@ -17571,7 +17579,7 @@
       <c r="L946" s="9"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="A947" s="31"/>
+      <c r="A947" s="32"/>
       <c r="B947" s="9"/>
       <c r="C947" s="9"/>
       <c r="D947" s="9"/>
@@ -17585,7 +17593,7 @@
       <c r="L947" s="9"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="A948" s="31"/>
+      <c r="A948" s="32"/>
       <c r="B948" s="9"/>
       <c r="C948" s="9"/>
       <c r="D948" s="9"/>
@@ -17599,7 +17607,7 @@
       <c r="L948" s="9"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="A949" s="31"/>
+      <c r="A949" s="32"/>
       <c r="B949" s="9"/>
       <c r="C949" s="9"/>
       <c r="D949" s="9"/>
@@ -17613,7 +17621,7 @@
       <c r="L949" s="9"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="A950" s="31"/>
+      <c r="A950" s="32"/>
       <c r="B950" s="9"/>
       <c r="C950" s="9"/>
       <c r="D950" s="9"/>
@@ -17627,7 +17635,7 @@
       <c r="L950" s="9"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="A951" s="31"/>
+      <c r="A951" s="32"/>
       <c r="B951" s="9"/>
       <c r="C951" s="9"/>
       <c r="D951" s="9"/>
@@ -17641,7 +17649,7 @@
       <c r="L951" s="9"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="A952" s="31"/>
+      <c r="A952" s="32"/>
       <c r="B952" s="9"/>
       <c r="C952" s="9"/>
       <c r="D952" s="9"/>
@@ -17655,7 +17663,7 @@
       <c r="L952" s="9"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="A953" s="31"/>
+      <c r="A953" s="32"/>
       <c r="B953" s="9"/>
       <c r="C953" s="9"/>
       <c r="D953" s="9"/>
@@ -17669,7 +17677,7 @@
       <c r="L953" s="9"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="31"/>
+      <c r="A954" s="32"/>
       <c r="B954" s="9"/>
       <c r="C954" s="9"/>
       <c r="D954" s="9"/>
@@ -17683,7 +17691,7 @@
       <c r="L954" s="9"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="31"/>
+      <c r="A955" s="32"/>
       <c r="B955" s="9"/>
       <c r="C955" s="9"/>
       <c r="D955" s="9"/>
@@ -17697,7 +17705,7 @@
       <c r="L955" s="9"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="31"/>
+      <c r="A956" s="32"/>
       <c r="B956" s="9"/>
       <c r="C956" s="9"/>
       <c r="D956" s="9"/>
@@ -17711,7 +17719,7 @@
       <c r="L956" s="9"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="31"/>
+      <c r="A957" s="32"/>
       <c r="B957" s="9"/>
       <c r="C957" s="9"/>
       <c r="D957" s="9"/>
@@ -17725,7 +17733,7 @@
       <c r="L957" s="9"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="31"/>
+      <c r="A958" s="32"/>
       <c r="B958" s="9"/>
       <c r="C958" s="9"/>
       <c r="D958" s="9"/>
@@ -17739,7 +17747,7 @@
       <c r="L958" s="9"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="31"/>
+      <c r="A959" s="32"/>
       <c r="B959" s="9"/>
       <c r="C959" s="9"/>
       <c r="D959" s="9"/>
@@ -17753,7 +17761,7 @@
       <c r="L959" s="9"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="31"/>
+      <c r="A960" s="32"/>
       <c r="B960" s="9"/>
       <c r="C960" s="9"/>
       <c r="D960" s="9"/>
@@ -17767,7 +17775,7 @@
       <c r="L960" s="9"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="31"/>
+      <c r="A961" s="32"/>
       <c r="B961" s="9"/>
       <c r="C961" s="9"/>
       <c r="D961" s="9"/>
@@ -17781,7 +17789,7 @@
       <c r="L961" s="9"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="31"/>
+      <c r="A962" s="32"/>
       <c r="B962" s="9"/>
       <c r="C962" s="9"/>
       <c r="D962" s="9"/>
@@ -17795,7 +17803,7 @@
       <c r="L962" s="9"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="31"/>
+      <c r="A963" s="32"/>
       <c r="B963" s="9"/>
       <c r="C963" s="9"/>
       <c r="D963" s="9"/>
@@ -17809,7 +17817,7 @@
       <c r="L963" s="9"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="31"/>
+      <c r="A964" s="32"/>
       <c r="B964" s="9"/>
       <c r="C964" s="9"/>
       <c r="D964" s="9"/>
@@ -17823,7 +17831,7 @@
       <c r="L964" s="9"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="A965" s="31"/>
+      <c r="A965" s="32"/>
       <c r="B965" s="9"/>
       <c r="C965" s="9"/>
       <c r="D965" s="9"/>
@@ -17837,7 +17845,7 @@
       <c r="L965" s="9"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="A966" s="31"/>
+      <c r="A966" s="32"/>
       <c r="B966" s="9"/>
       <c r="C966" s="9"/>
       <c r="D966" s="9"/>
@@ -17851,7 +17859,7 @@
       <c r="L966" s="9"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="31"/>
+      <c r="A967" s="32"/>
       <c r="B967" s="9"/>
       <c r="C967" s="9"/>
       <c r="D967" s="9"/>
@@ -17865,7 +17873,7 @@
       <c r="L967" s="9"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="A968" s="31"/>
+      <c r="A968" s="32"/>
       <c r="B968" s="9"/>
       <c r="C968" s="9"/>
       <c r="D968" s="9"/>
@@ -17879,7 +17887,7 @@
       <c r="L968" s="9"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="A969" s="31"/>
+      <c r="A969" s="32"/>
       <c r="B969" s="9"/>
       <c r="C969" s="9"/>
       <c r="D969" s="9"/>
@@ -17893,7 +17901,7 @@
       <c r="L969" s="9"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="A970" s="31"/>
+      <c r="A970" s="32"/>
       <c r="B970" s="9"/>
       <c r="C970" s="9"/>
       <c r="D970" s="9"/>
@@ -17907,7 +17915,7 @@
       <c r="L970" s="9"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="A971" s="31"/>
+      <c r="A971" s="32"/>
       <c r="B971" s="9"/>
       <c r="C971" s="9"/>
       <c r="D971" s="9"/>
@@ -17921,7 +17929,7 @@
       <c r="L971" s="9"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="31"/>
+      <c r="A972" s="32"/>
       <c r="B972" s="9"/>
       <c r="C972" s="9"/>
       <c r="D972" s="9"/>
@@ -17935,7 +17943,7 @@
       <c r="L972" s="9"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="31"/>
+      <c r="A973" s="32"/>
       <c r="B973" s="9"/>
       <c r="C973" s="9"/>
       <c r="D973" s="9"/>
@@ -17949,7 +17957,7 @@
       <c r="L973" s="9"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="31"/>
+      <c r="A974" s="32"/>
       <c r="B974" s="9"/>
       <c r="C974" s="9"/>
       <c r="D974" s="9"/>
@@ -17963,7 +17971,7 @@
       <c r="L974" s="9"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="31"/>
+      <c r="A975" s="32"/>
       <c r="B975" s="9"/>
       <c r="C975" s="9"/>
       <c r="D975" s="9"/>
@@ -17977,7 +17985,7 @@
       <c r="L975" s="9"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="31"/>
+      <c r="A976" s="32"/>
       <c r="B976" s="9"/>
       <c r="C976" s="9"/>
       <c r="D976" s="9"/>
@@ -17991,7 +17999,7 @@
       <c r="L976" s="9"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="31"/>
+      <c r="A977" s="32"/>
       <c r="B977" s="9"/>
       <c r="C977" s="9"/>
       <c r="D977" s="9"/>
@@ -18005,7 +18013,7 @@
       <c r="L977" s="9"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="31"/>
+      <c r="A978" s="32"/>
       <c r="B978" s="9"/>
       <c r="C978" s="9"/>
       <c r="D978" s="9"/>
@@ -18019,7 +18027,7 @@
       <c r="L978" s="9"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="31"/>
+      <c r="A979" s="32"/>
       <c r="B979" s="9"/>
       <c r="C979" s="9"/>
       <c r="D979" s="9"/>
@@ -18033,7 +18041,7 @@
       <c r="L979" s="9"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="31"/>
+      <c r="A980" s="32"/>
       <c r="B980" s="9"/>
       <c r="C980" s="9"/>
       <c r="D980" s="9"/>
@@ -18047,7 +18055,7 @@
       <c r="L980" s="9"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="31"/>
+      <c r="A981" s="32"/>
       <c r="B981" s="9"/>
       <c r="C981" s="9"/>
       <c r="D981" s="9"/>
@@ -18061,7 +18069,7 @@
       <c r="L981" s="9"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="31"/>
+      <c r="A982" s="32"/>
       <c r="B982" s="9"/>
       <c r="C982" s="9"/>
       <c r="D982" s="9"/>
@@ -18075,7 +18083,7 @@
       <c r="L982" s="9"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="31"/>
+      <c r="A983" s="32"/>
       <c r="B983" s="9"/>
       <c r="C983" s="9"/>
       <c r="D983" s="9"/>
@@ -18089,7 +18097,7 @@
       <c r="L983" s="9"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="31"/>
+      <c r="A984" s="32"/>
       <c r="B984" s="9"/>
       <c r="C984" s="9"/>
       <c r="D984" s="9"/>
@@ -18103,7 +18111,7 @@
       <c r="L984" s="9"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="31"/>
+      <c r="A985" s="32"/>
       <c r="B985" s="9"/>
       <c r="C985" s="9"/>
       <c r="D985" s="9"/>
@@ -18117,7 +18125,7 @@
       <c r="L985" s="9"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="31"/>
+      <c r="A986" s="32"/>
       <c r="B986" s="9"/>
       <c r="C986" s="9"/>
       <c r="D986" s="9"/>
@@ -18131,7 +18139,7 @@
       <c r="L986" s="9"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="31"/>
+      <c r="A987" s="32"/>
       <c r="B987" s="9"/>
       <c r="C987" s="9"/>
       <c r="D987" s="9"/>
@@ -18145,7 +18153,7 @@
       <c r="L987" s="9"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="31"/>
+      <c r="A988" s="32"/>
       <c r="B988" s="9"/>
       <c r="C988" s="9"/>
       <c r="D988" s="9"/>
@@ -18159,7 +18167,7 @@
       <c r="L988" s="9"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="31"/>
+      <c r="A989" s="32"/>
       <c r="B989" s="9"/>
       <c r="C989" s="9"/>
       <c r="D989" s="9"/>
@@ -18173,7 +18181,7 @@
       <c r="L989" s="9"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="31"/>
+      <c r="A990" s="32"/>
       <c r="B990" s="9"/>
       <c r="C990" s="9"/>
       <c r="D990" s="9"/>
@@ -18187,7 +18195,7 @@
       <c r="L990" s="9"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="31"/>
+      <c r="A991" s="32"/>
       <c r="B991" s="9"/>
       <c r="C991" s="9"/>
       <c r="D991" s="9"/>
@@ -18201,7 +18209,7 @@
       <c r="L991" s="9"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="31"/>
+      <c r="A992" s="32"/>
       <c r="B992" s="9"/>
       <c r="C992" s="9"/>
       <c r="D992" s="9"/>
@@ -18215,7 +18223,7 @@
       <c r="L992" s="9"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="31"/>
+      <c r="A993" s="32"/>
       <c r="B993" s="9"/>
       <c r="C993" s="9"/>
       <c r="D993" s="9"/>
@@ -18229,7 +18237,7 @@
       <c r="L993" s="9"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="31"/>
+      <c r="A994" s="32"/>
       <c r="B994" s="9"/>
       <c r="C994" s="9"/>
       <c r="D994" s="9"/>
@@ -18243,7 +18251,7 @@
       <c r="L994" s="9"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="31"/>
+      <c r="A995" s="32"/>
       <c r="B995" s="9"/>
       <c r="C995" s="9"/>
       <c r="D995" s="9"/>
@@ -18257,7 +18265,7 @@
       <c r="L995" s="9"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="31"/>
+      <c r="A996" s="32"/>
       <c r="B996" s="9"/>
       <c r="C996" s="9"/>
       <c r="D996" s="9"/>
@@ -18271,7 +18279,7 @@
       <c r="L996" s="9"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="31"/>
+      <c r="A997" s="32"/>
       <c r="B997" s="9"/>
       <c r="C997" s="9"/>
       <c r="D997" s="9"/>
@@ -18285,7 +18293,7 @@
       <c r="L997" s="9"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="31"/>
+      <c r="A998" s="32"/>
       <c r="B998" s="9"/>
       <c r="C998" s="9"/>
       <c r="D998" s="9"/>
@@ -18299,7 +18307,7 @@
       <c r="L998" s="9"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="31"/>
+      <c r="A999" s="32"/>
       <c r="B999" s="9"/>
       <c r="C999" s="9"/>
       <c r="D999" s="9"/>
@@ -18313,7 +18321,7 @@
       <c r="L999" s="9"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="31"/>
+      <c r="A1000" s="32"/>
       <c r="B1000" s="9"/>
       <c r="C1000" s="9"/>
       <c r="D1000" s="9"/>
@@ -18327,7 +18335,7 @@
       <c r="L1000" s="9"/>
     </row>
     <row r="1001" ht="15.75" customHeight="1">
-      <c r="A1001" s="31"/>
+      <c r="A1001" s="32"/>
       <c r="B1001" s="9"/>
       <c r="C1001" s="9"/>
       <c r="D1001" s="9"/>
@@ -18341,7 +18349,7 @@
       <c r="L1001" s="9"/>
     </row>
     <row r="1002" ht="15.75" customHeight="1">
-      <c r="A1002" s="31"/>
+      <c r="A1002" s="32"/>
       <c r="B1002" s="9"/>
       <c r="C1002" s="9"/>
       <c r="D1002" s="9"/>
@@ -18355,7 +18363,7 @@
       <c r="L1002" s="9"/>
     </row>
     <row r="1003" ht="15.75" customHeight="1">
-      <c r="A1003" s="31"/>
+      <c r="A1003" s="32"/>
       <c r="B1003" s="9"/>
       <c r="C1003" s="9"/>
       <c r="D1003" s="9"/>
@@ -18369,7 +18377,7 @@
       <c r="L1003" s="9"/>
     </row>
     <row r="1004" ht="15.75" customHeight="1">
-      <c r="A1004" s="31"/>
+      <c r="A1004" s="32"/>
       <c r="B1004" s="9"/>
       <c r="C1004" s="9"/>
       <c r="D1004" s="9"/>
@@ -18383,7 +18391,7 @@
       <c r="L1004" s="9"/>
     </row>
     <row r="1005" ht="15.75" customHeight="1">
-      <c r="A1005" s="31"/>
+      <c r="A1005" s="32"/>
       <c r="B1005" s="9"/>
       <c r="C1005" s="9"/>
       <c r="D1005" s="9"/>
@@ -18397,7 +18405,7 @@
       <c r="L1005" s="9"/>
     </row>
     <row r="1006" ht="15.75" customHeight="1">
-      <c r="A1006" s="31"/>
+      <c r="A1006" s="32"/>
       <c r="B1006" s="9"/>
       <c r="C1006" s="9"/>
       <c r="D1006" s="9"/>
@@ -18411,7 +18419,7 @@
       <c r="L1006" s="9"/>
     </row>
     <row r="1007" ht="15.75" customHeight="1">
-      <c r="A1007" s="31"/>
+      <c r="A1007" s="32"/>
       <c r="B1007" s="9"/>
       <c r="C1007" s="9"/>
       <c r="D1007" s="9"/>
@@ -18425,7 +18433,7 @@
       <c r="L1007" s="9"/>
     </row>
     <row r="1008" ht="15.75" customHeight="1">
-      <c r="A1008" s="31"/>
+      <c r="A1008" s="32"/>
       <c r="B1008" s="9"/>
       <c r="C1008" s="9"/>
       <c r="D1008" s="9"/>
@@ -18439,7 +18447,7 @@
       <c r="L1008" s="9"/>
     </row>
     <row r="1009" ht="15.75" customHeight="1">
-      <c r="A1009" s="31"/>
+      <c r="A1009" s="32"/>
       <c r="B1009" s="9"/>
       <c r="C1009" s="9"/>
       <c r="D1009" s="9"/>

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Attended Show List" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Attended Show List'!$A$1:$M$121</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Attended Show List'!$A$1:$M$122</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="432">
   <si>
     <t>Date</t>
   </si>
@@ -1239,13 +1239,13 @@
     <t>Pierce the Veil</t>
   </si>
   <si>
-    <t>I Can't Hear You Tour</t>
-  </si>
-  <si>
-    <t>Health, Ecca Vandal, Like Roses</t>
-  </si>
-  <si>
-    <t>Co-headline tour with Health.</t>
+    <t>Co-Headline tour with Pierce the Veil</t>
+  </si>
+  <si>
+    <t>Pierce the Veil, Ecca Vandal, Like Roses</t>
+  </si>
+  <si>
+    <t>Co-headlining tour with Pierce the Veil</t>
   </si>
   <si>
     <t>Lucro Sucio: Los Ojos del Vacio Tour</t>
@@ -1294,6 +1294,21 @@
   </si>
   <si>
     <t>AVVT/PTTN Tour</t>
+  </si>
+  <si>
+    <t>Truliant Ampitheatre</t>
+  </si>
+  <si>
+    <t>Setlist link</t>
+  </si>
+  <si>
+    <t>The Rise of Rock Tour 2026</t>
+  </si>
+  <si>
+    <t>Godsmack, Dorothy</t>
+  </si>
+  <si>
+    <t>Co-headling tour with Godsmack</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1319,7 @@
     <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1378,6 +1393,11 @@
       <u/>
       <color rgb="FF0000FF"/>
     </font>
+    <font>
+      <color rgb="FF0563C1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1393,7 +1413,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1473,6 +1493,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
@@ -5768,13 +5791,13 @@
       <c r="I114" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="J114" s="21" t="s">
+      <c r="J114" s="22" t="s">
         <v>408</v>
       </c>
       <c r="K114" s="22" t="s">
         <v>409</v>
       </c>
-      <c r="L114" s="23" t="s">
+      <c r="L114" s="32" t="s">
         <v>410</v>
       </c>
     </row>
@@ -6029,18 +6052,42 @@
       <c r="L121" s="9"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="10"/>
-      <c r="B122" s="9"/>
-      <c r="C122" s="9"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="16"/>
-      <c r="F122" s="9"/>
-      <c r="G122" s="9"/>
-      <c r="H122" s="9"/>
-      <c r="I122" s="9"/>
-      <c r="J122" s="9"/>
-      <c r="K122" s="9"/>
-      <c r="L122" s="9"/>
+      <c r="A122" s="6">
+        <v>46156.0</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="G122" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="H122" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I122" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="J122" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="K122" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="L122" s="7" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
@@ -8549,7 +8596,7 @@
       <c r="L301" s="9"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="32"/>
+      <c r="A302" s="33"/>
       <c r="B302" s="9"/>
       <c r="C302" s="9"/>
       <c r="D302" s="9"/>
@@ -8563,7 +8610,7 @@
       <c r="L302" s="9"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="32"/>
+      <c r="A303" s="33"/>
       <c r="B303" s="9"/>
       <c r="C303" s="9"/>
       <c r="D303" s="9"/>
@@ -8577,7 +8624,7 @@
       <c r="L303" s="9"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="32"/>
+      <c r="A304" s="33"/>
       <c r="B304" s="9"/>
       <c r="C304" s="9"/>
       <c r="D304" s="9"/>
@@ -8591,7 +8638,7 @@
       <c r="L304" s="9"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="32"/>
+      <c r="A305" s="33"/>
       <c r="B305" s="9"/>
       <c r="C305" s="9"/>
       <c r="D305" s="9"/>
@@ -8605,7 +8652,7 @@
       <c r="L305" s="9"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="32"/>
+      <c r="A306" s="33"/>
       <c r="B306" s="9"/>
       <c r="C306" s="9"/>
       <c r="D306" s="9"/>
@@ -8619,7 +8666,7 @@
       <c r="L306" s="9"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="32"/>
+      <c r="A307" s="33"/>
       <c r="B307" s="9"/>
       <c r="C307" s="9"/>
       <c r="D307" s="9"/>
@@ -8633,7 +8680,7 @@
       <c r="L307" s="9"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="32"/>
+      <c r="A308" s="33"/>
       <c r="B308" s="9"/>
       <c r="C308" s="9"/>
       <c r="D308" s="9"/>
@@ -8647,7 +8694,7 @@
       <c r="L308" s="9"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="32"/>
+      <c r="A309" s="33"/>
       <c r="B309" s="9"/>
       <c r="C309" s="9"/>
       <c r="D309" s="9"/>
@@ -8661,7 +8708,7 @@
       <c r="L309" s="9"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="32"/>
+      <c r="A310" s="33"/>
       <c r="B310" s="9"/>
       <c r="C310" s="9"/>
       <c r="D310" s="9"/>
@@ -8675,7 +8722,7 @@
       <c r="L310" s="9"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="32"/>
+      <c r="A311" s="33"/>
       <c r="B311" s="9"/>
       <c r="C311" s="9"/>
       <c r="D311" s="9"/>
@@ -8689,7 +8736,7 @@
       <c r="L311" s="9"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="32"/>
+      <c r="A312" s="33"/>
       <c r="B312" s="9"/>
       <c r="C312" s="9"/>
       <c r="D312" s="9"/>
@@ -8703,7 +8750,7 @@
       <c r="L312" s="9"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="32"/>
+      <c r="A313" s="33"/>
       <c r="B313" s="9"/>
       <c r="C313" s="9"/>
       <c r="D313" s="9"/>
@@ -8717,7 +8764,7 @@
       <c r="L313" s="9"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="32"/>
+      <c r="A314" s="33"/>
       <c r="B314" s="9"/>
       <c r="C314" s="9"/>
       <c r="D314" s="9"/>
@@ -8731,7 +8778,7 @@
       <c r="L314" s="9"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="32"/>
+      <c r="A315" s="33"/>
       <c r="B315" s="9"/>
       <c r="C315" s="9"/>
       <c r="D315" s="9"/>
@@ -8745,7 +8792,7 @@
       <c r="L315" s="9"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="32"/>
+      <c r="A316" s="33"/>
       <c r="B316" s="9"/>
       <c r="C316" s="9"/>
       <c r="D316" s="9"/>
@@ -8759,7 +8806,7 @@
       <c r="L316" s="9"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="32"/>
+      <c r="A317" s="33"/>
       <c r="B317" s="9"/>
       <c r="C317" s="9"/>
       <c r="D317" s="9"/>
@@ -8773,7 +8820,7 @@
       <c r="L317" s="9"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="A318" s="32"/>
+      <c r="A318" s="33"/>
       <c r="B318" s="9"/>
       <c r="C318" s="9"/>
       <c r="D318" s="9"/>
@@ -8787,7 +8834,7 @@
       <c r="L318" s="9"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="A319" s="32"/>
+      <c r="A319" s="33"/>
       <c r="B319" s="9"/>
       <c r="C319" s="9"/>
       <c r="D319" s="9"/>
@@ -8801,7 +8848,7 @@
       <c r="L319" s="9"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="32"/>
+      <c r="A320" s="33"/>
       <c r="B320" s="9"/>
       <c r="C320" s="9"/>
       <c r="D320" s="9"/>
@@ -8815,7 +8862,7 @@
       <c r="L320" s="9"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="A321" s="32"/>
+      <c r="A321" s="33"/>
       <c r="B321" s="9"/>
       <c r="C321" s="9"/>
       <c r="D321" s="9"/>
@@ -8829,7 +8876,7 @@
       <c r="L321" s="9"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="32"/>
+      <c r="A322" s="33"/>
       <c r="B322" s="9"/>
       <c r="C322" s="9"/>
       <c r="D322" s="9"/>
@@ -8843,7 +8890,7 @@
       <c r="L322" s="9"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="32"/>
+      <c r="A323" s="33"/>
       <c r="B323" s="9"/>
       <c r="C323" s="9"/>
       <c r="D323" s="9"/>
@@ -8857,7 +8904,7 @@
       <c r="L323" s="9"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="32"/>
+      <c r="A324" s="33"/>
       <c r="B324" s="9"/>
       <c r="C324" s="9"/>
       <c r="D324" s="9"/>
@@ -8871,7 +8918,7 @@
       <c r="L324" s="9"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="A325" s="32"/>
+      <c r="A325" s="33"/>
       <c r="B325" s="9"/>
       <c r="C325" s="9"/>
       <c r="D325" s="9"/>
@@ -8885,7 +8932,7 @@
       <c r="L325" s="9"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="32"/>
+      <c r="A326" s="33"/>
       <c r="B326" s="9"/>
       <c r="C326" s="9"/>
       <c r="D326" s="9"/>
@@ -8899,7 +8946,7 @@
       <c r="L326" s="9"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="A327" s="32"/>
+      <c r="A327" s="33"/>
       <c r="B327" s="9"/>
       <c r="C327" s="9"/>
       <c r="D327" s="9"/>
@@ -8913,7 +8960,7 @@
       <c r="L327" s="9"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="A328" s="32"/>
+      <c r="A328" s="33"/>
       <c r="B328" s="9"/>
       <c r="C328" s="9"/>
       <c r="D328" s="9"/>
@@ -8927,7 +8974,7 @@
       <c r="L328" s="9"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="32"/>
+      <c r="A329" s="33"/>
       <c r="B329" s="9"/>
       <c r="C329" s="9"/>
       <c r="D329" s="9"/>
@@ -8941,7 +8988,7 @@
       <c r="L329" s="9"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="32"/>
+      <c r="A330" s="33"/>
       <c r="B330" s="9"/>
       <c r="C330" s="9"/>
       <c r="D330" s="9"/>
@@ -8955,7 +9002,7 @@
       <c r="L330" s="9"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="A331" s="32"/>
+      <c r="A331" s="33"/>
       <c r="B331" s="9"/>
       <c r="C331" s="9"/>
       <c r="D331" s="9"/>
@@ -8969,7 +9016,7 @@
       <c r="L331" s="9"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="32"/>
+      <c r="A332" s="33"/>
       <c r="B332" s="9"/>
       <c r="C332" s="9"/>
       <c r="D332" s="9"/>
@@ -8983,7 +9030,7 @@
       <c r="L332" s="9"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="32"/>
+      <c r="A333" s="33"/>
       <c r="B333" s="9"/>
       <c r="C333" s="9"/>
       <c r="D333" s="9"/>
@@ -8997,7 +9044,7 @@
       <c r="L333" s="9"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="A334" s="32"/>
+      <c r="A334" s="33"/>
       <c r="B334" s="9"/>
       <c r="C334" s="9"/>
       <c r="D334" s="9"/>
@@ -9011,7 +9058,7 @@
       <c r="L334" s="9"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="32"/>
+      <c r="A335" s="33"/>
       <c r="B335" s="9"/>
       <c r="C335" s="9"/>
       <c r="D335" s="9"/>
@@ -9025,7 +9072,7 @@
       <c r="L335" s="9"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="32"/>
+      <c r="A336" s="33"/>
       <c r="B336" s="9"/>
       <c r="C336" s="9"/>
       <c r="D336" s="9"/>
@@ -9039,7 +9086,7 @@
       <c r="L336" s="9"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="32"/>
+      <c r="A337" s="33"/>
       <c r="B337" s="9"/>
       <c r="C337" s="9"/>
       <c r="D337" s="9"/>
@@ -9053,7 +9100,7 @@
       <c r="L337" s="9"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="32"/>
+      <c r="A338" s="33"/>
       <c r="B338" s="9"/>
       <c r="C338" s="9"/>
       <c r="D338" s="9"/>
@@ -9067,7 +9114,7 @@
       <c r="L338" s="9"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="32"/>
+      <c r="A339" s="33"/>
       <c r="B339" s="9"/>
       <c r="C339" s="9"/>
       <c r="D339" s="9"/>
@@ -9081,7 +9128,7 @@
       <c r="L339" s="9"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="32"/>
+      <c r="A340" s="33"/>
       <c r="B340" s="9"/>
       <c r="C340" s="9"/>
       <c r="D340" s="9"/>
@@ -9095,7 +9142,7 @@
       <c r="L340" s="9"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="A341" s="32"/>
+      <c r="A341" s="33"/>
       <c r="B341" s="9"/>
       <c r="C341" s="9"/>
       <c r="D341" s="9"/>
@@ -9109,7 +9156,7 @@
       <c r="L341" s="9"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="A342" s="32"/>
+      <c r="A342" s="33"/>
       <c r="B342" s="9"/>
       <c r="C342" s="9"/>
       <c r="D342" s="9"/>
@@ -9123,7 +9170,7 @@
       <c r="L342" s="9"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="32"/>
+      <c r="A343" s="33"/>
       <c r="B343" s="9"/>
       <c r="C343" s="9"/>
       <c r="D343" s="9"/>
@@ -9137,7 +9184,7 @@
       <c r="L343" s="9"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="A344" s="32"/>
+      <c r="A344" s="33"/>
       <c r="B344" s="9"/>
       <c r="C344" s="9"/>
       <c r="D344" s="9"/>
@@ -9151,7 +9198,7 @@
       <c r="L344" s="9"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="A345" s="32"/>
+      <c r="A345" s="33"/>
       <c r="B345" s="9"/>
       <c r="C345" s="9"/>
       <c r="D345" s="9"/>
@@ -9165,7 +9212,7 @@
       <c r="L345" s="9"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="A346" s="32"/>
+      <c r="A346" s="33"/>
       <c r="B346" s="9"/>
       <c r="C346" s="9"/>
       <c r="D346" s="9"/>
@@ -9179,7 +9226,7 @@
       <c r="L346" s="9"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="A347" s="32"/>
+      <c r="A347" s="33"/>
       <c r="B347" s="9"/>
       <c r="C347" s="9"/>
       <c r="D347" s="9"/>
@@ -9193,7 +9240,7 @@
       <c r="L347" s="9"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="A348" s="32"/>
+      <c r="A348" s="33"/>
       <c r="B348" s="9"/>
       <c r="C348" s="9"/>
       <c r="D348" s="9"/>
@@ -9207,7 +9254,7 @@
       <c r="L348" s="9"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="A349" s="32"/>
+      <c r="A349" s="33"/>
       <c r="B349" s="9"/>
       <c r="C349" s="9"/>
       <c r="D349" s="9"/>
@@ -9221,7 +9268,7 @@
       <c r="L349" s="9"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="32"/>
+      <c r="A350" s="33"/>
       <c r="B350" s="9"/>
       <c r="C350" s="9"/>
       <c r="D350" s="9"/>
@@ -9235,7 +9282,7 @@
       <c r="L350" s="9"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="32"/>
+      <c r="A351" s="33"/>
       <c r="B351" s="9"/>
       <c r="C351" s="9"/>
       <c r="D351" s="9"/>
@@ -9249,7 +9296,7 @@
       <c r="L351" s="9"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="32"/>
+      <c r="A352" s="33"/>
       <c r="B352" s="9"/>
       <c r="C352" s="9"/>
       <c r="D352" s="9"/>
@@ -9263,7 +9310,7 @@
       <c r="L352" s="9"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="32"/>
+      <c r="A353" s="33"/>
       <c r="B353" s="9"/>
       <c r="C353" s="9"/>
       <c r="D353" s="9"/>
@@ -9277,7 +9324,7 @@
       <c r="L353" s="9"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="32"/>
+      <c r="A354" s="33"/>
       <c r="B354" s="9"/>
       <c r="C354" s="9"/>
       <c r="D354" s="9"/>
@@ -9291,7 +9338,7 @@
       <c r="L354" s="9"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="32"/>
+      <c r="A355" s="33"/>
       <c r="B355" s="9"/>
       <c r="C355" s="9"/>
       <c r="D355" s="9"/>
@@ -9305,7 +9352,7 @@
       <c r="L355" s="9"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="32"/>
+      <c r="A356" s="33"/>
       <c r="B356" s="9"/>
       <c r="C356" s="9"/>
       <c r="D356" s="9"/>
@@ -9319,7 +9366,7 @@
       <c r="L356" s="9"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="32"/>
+      <c r="A357" s="33"/>
       <c r="B357" s="9"/>
       <c r="C357" s="9"/>
       <c r="D357" s="9"/>
@@ -9333,7 +9380,7 @@
       <c r="L357" s="9"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="32"/>
+      <c r="A358" s="33"/>
       <c r="B358" s="9"/>
       <c r="C358" s="9"/>
       <c r="D358" s="9"/>
@@ -9347,7 +9394,7 @@
       <c r="L358" s="9"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="32"/>
+      <c r="A359" s="33"/>
       <c r="B359" s="9"/>
       <c r="C359" s="9"/>
       <c r="D359" s="9"/>
@@ -9361,7 +9408,7 @@
       <c r="L359" s="9"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="32"/>
+      <c r="A360" s="33"/>
       <c r="B360" s="9"/>
       <c r="C360" s="9"/>
       <c r="D360" s="9"/>
@@ -9375,7 +9422,7 @@
       <c r="L360" s="9"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="32"/>
+      <c r="A361" s="33"/>
       <c r="B361" s="9"/>
       <c r="C361" s="9"/>
       <c r="D361" s="9"/>
@@ -9389,7 +9436,7 @@
       <c r="L361" s="9"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="32"/>
+      <c r="A362" s="33"/>
       <c r="B362" s="9"/>
       <c r="C362" s="9"/>
       <c r="D362" s="9"/>
@@ -9403,7 +9450,7 @@
       <c r="L362" s="9"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="32"/>
+      <c r="A363" s="33"/>
       <c r="B363" s="9"/>
       <c r="C363" s="9"/>
       <c r="D363" s="9"/>
@@ -9417,7 +9464,7 @@
       <c r="L363" s="9"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="32"/>
+      <c r="A364" s="33"/>
       <c r="B364" s="9"/>
       <c r="C364" s="9"/>
       <c r="D364" s="9"/>
@@ -9431,7 +9478,7 @@
       <c r="L364" s="9"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="32"/>
+      <c r="A365" s="33"/>
       <c r="B365" s="9"/>
       <c r="C365" s="9"/>
       <c r="D365" s="9"/>
@@ -9445,7 +9492,7 @@
       <c r="L365" s="9"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="32"/>
+      <c r="A366" s="33"/>
       <c r="B366" s="9"/>
       <c r="C366" s="9"/>
       <c r="D366" s="9"/>
@@ -9459,7 +9506,7 @@
       <c r="L366" s="9"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="32"/>
+      <c r="A367" s="33"/>
       <c r="B367" s="9"/>
       <c r="C367" s="9"/>
       <c r="D367" s="9"/>
@@ -9473,7 +9520,7 @@
       <c r="L367" s="9"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="32"/>
+      <c r="A368" s="33"/>
       <c r="B368" s="9"/>
       <c r="C368" s="9"/>
       <c r="D368" s="9"/>
@@ -9487,7 +9534,7 @@
       <c r="L368" s="9"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="32"/>
+      <c r="A369" s="33"/>
       <c r="B369" s="9"/>
       <c r="C369" s="9"/>
       <c r="D369" s="9"/>
@@ -9501,7 +9548,7 @@
       <c r="L369" s="9"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="32"/>
+      <c r="A370" s="33"/>
       <c r="B370" s="9"/>
       <c r="C370" s="9"/>
       <c r="D370" s="9"/>
@@ -9515,7 +9562,7 @@
       <c r="L370" s="9"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="32"/>
+      <c r="A371" s="33"/>
       <c r="B371" s="9"/>
       <c r="C371" s="9"/>
       <c r="D371" s="9"/>
@@ -9529,7 +9576,7 @@
       <c r="L371" s="9"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="32"/>
+      <c r="A372" s="33"/>
       <c r="B372" s="9"/>
       <c r="C372" s="9"/>
       <c r="D372" s="9"/>
@@ -9543,7 +9590,7 @@
       <c r="L372" s="9"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="32"/>
+      <c r="A373" s="33"/>
       <c r="B373" s="9"/>
       <c r="C373" s="9"/>
       <c r="D373" s="9"/>
@@ -9557,7 +9604,7 @@
       <c r="L373" s="9"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="32"/>
+      <c r="A374" s="33"/>
       <c r="B374" s="9"/>
       <c r="C374" s="9"/>
       <c r="D374" s="9"/>
@@ -9571,7 +9618,7 @@
       <c r="L374" s="9"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="32"/>
+      <c r="A375" s="33"/>
       <c r="B375" s="9"/>
       <c r="C375" s="9"/>
       <c r="D375" s="9"/>
@@ -9585,7 +9632,7 @@
       <c r="L375" s="9"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="32"/>
+      <c r="A376" s="33"/>
       <c r="B376" s="9"/>
       <c r="C376" s="9"/>
       <c r="D376" s="9"/>
@@ -9599,7 +9646,7 @@
       <c r="L376" s="9"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="32"/>
+      <c r="A377" s="33"/>
       <c r="B377" s="9"/>
       <c r="C377" s="9"/>
       <c r="D377" s="9"/>
@@ -9613,7 +9660,7 @@
       <c r="L377" s="9"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="32"/>
+      <c r="A378" s="33"/>
       <c r="B378" s="9"/>
       <c r="C378" s="9"/>
       <c r="D378" s="9"/>
@@ -9627,7 +9674,7 @@
       <c r="L378" s="9"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="A379" s="32"/>
+      <c r="A379" s="33"/>
       <c r="B379" s="9"/>
       <c r="C379" s="9"/>
       <c r="D379" s="9"/>
@@ -9641,7 +9688,7 @@
       <c r="L379" s="9"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="32"/>
+      <c r="A380" s="33"/>
       <c r="B380" s="9"/>
       <c r="C380" s="9"/>
       <c r="D380" s="9"/>
@@ -9655,7 +9702,7 @@
       <c r="L380" s="9"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="A381" s="32"/>
+      <c r="A381" s="33"/>
       <c r="B381" s="9"/>
       <c r="C381" s="9"/>
       <c r="D381" s="9"/>
@@ -9669,7 +9716,7 @@
       <c r="L381" s="9"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="32"/>
+      <c r="A382" s="33"/>
       <c r="B382" s="9"/>
       <c r="C382" s="9"/>
       <c r="D382" s="9"/>
@@ -9683,7 +9730,7 @@
       <c r="L382" s="9"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="32"/>
+      <c r="A383" s="33"/>
       <c r="B383" s="9"/>
       <c r="C383" s="9"/>
       <c r="D383" s="9"/>
@@ -9697,7 +9744,7 @@
       <c r="L383" s="9"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="A384" s="32"/>
+      <c r="A384" s="33"/>
       <c r="B384" s="9"/>
       <c r="C384" s="9"/>
       <c r="D384" s="9"/>
@@ -9711,7 +9758,7 @@
       <c r="L384" s="9"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="32"/>
+      <c r="A385" s="33"/>
       <c r="B385" s="9"/>
       <c r="C385" s="9"/>
       <c r="D385" s="9"/>
@@ -9725,7 +9772,7 @@
       <c r="L385" s="9"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="32"/>
+      <c r="A386" s="33"/>
       <c r="B386" s="9"/>
       <c r="C386" s="9"/>
       <c r="D386" s="9"/>
@@ -9739,7 +9786,7 @@
       <c r="L386" s="9"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="A387" s="32"/>
+      <c r="A387" s="33"/>
       <c r="B387" s="9"/>
       <c r="C387" s="9"/>
       <c r="D387" s="9"/>
@@ -9753,7 +9800,7 @@
       <c r="L387" s="9"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="A388" s="32"/>
+      <c r="A388" s="33"/>
       <c r="B388" s="9"/>
       <c r="C388" s="9"/>
       <c r="D388" s="9"/>
@@ -9767,7 +9814,7 @@
       <c r="L388" s="9"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="A389" s="32"/>
+      <c r="A389" s="33"/>
       <c r="B389" s="9"/>
       <c r="C389" s="9"/>
       <c r="D389" s="9"/>
@@ -9781,7 +9828,7 @@
       <c r="L389" s="9"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="32"/>
+      <c r="A390" s="33"/>
       <c r="B390" s="9"/>
       <c r="C390" s="9"/>
       <c r="D390" s="9"/>
@@ -9795,7 +9842,7 @@
       <c r="L390" s="9"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="32"/>
+      <c r="A391" s="33"/>
       <c r="B391" s="9"/>
       <c r="C391" s="9"/>
       <c r="D391" s="9"/>
@@ -9809,7 +9856,7 @@
       <c r="L391" s="9"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="A392" s="32"/>
+      <c r="A392" s="33"/>
       <c r="B392" s="9"/>
       <c r="C392" s="9"/>
       <c r="D392" s="9"/>
@@ -9823,7 +9870,7 @@
       <c r="L392" s="9"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="32"/>
+      <c r="A393" s="33"/>
       <c r="B393" s="9"/>
       <c r="C393" s="9"/>
       <c r="D393" s="9"/>
@@ -9837,7 +9884,7 @@
       <c r="L393" s="9"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="A394" s="32"/>
+      <c r="A394" s="33"/>
       <c r="B394" s="9"/>
       <c r="C394" s="9"/>
       <c r="D394" s="9"/>
@@ -9851,7 +9898,7 @@
       <c r="L394" s="9"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="32"/>
+      <c r="A395" s="33"/>
       <c r="B395" s="9"/>
       <c r="C395" s="9"/>
       <c r="D395" s="9"/>
@@ -9865,7 +9912,7 @@
       <c r="L395" s="9"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="32"/>
+      <c r="A396" s="33"/>
       <c r="B396" s="9"/>
       <c r="C396" s="9"/>
       <c r="D396" s="9"/>
@@ -9879,7 +9926,7 @@
       <c r="L396" s="9"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="A397" s="32"/>
+      <c r="A397" s="33"/>
       <c r="B397" s="9"/>
       <c r="C397" s="9"/>
       <c r="D397" s="9"/>
@@ -9893,7 +9940,7 @@
       <c r="L397" s="9"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="A398" s="32"/>
+      <c r="A398" s="33"/>
       <c r="B398" s="9"/>
       <c r="C398" s="9"/>
       <c r="D398" s="9"/>
@@ -9907,7 +9954,7 @@
       <c r="L398" s="9"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="32"/>
+      <c r="A399" s="33"/>
       <c r="B399" s="9"/>
       <c r="C399" s="9"/>
       <c r="D399" s="9"/>
@@ -9921,7 +9968,7 @@
       <c r="L399" s="9"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="A400" s="32"/>
+      <c r="A400" s="33"/>
       <c r="B400" s="9"/>
       <c r="C400" s="9"/>
       <c r="D400" s="9"/>
@@ -9935,7 +9982,7 @@
       <c r="L400" s="9"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="32"/>
+      <c r="A401" s="33"/>
       <c r="B401" s="9"/>
       <c r="C401" s="9"/>
       <c r="D401" s="9"/>
@@ -9949,7 +9996,7 @@
       <c r="L401" s="9"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="32"/>
+      <c r="A402" s="33"/>
       <c r="B402" s="9"/>
       <c r="C402" s="9"/>
       <c r="D402" s="9"/>
@@ -9963,7 +10010,7 @@
       <c r="L402" s="9"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="A403" s="32"/>
+      <c r="A403" s="33"/>
       <c r="B403" s="9"/>
       <c r="C403" s="9"/>
       <c r="D403" s="9"/>
@@ -9977,7 +10024,7 @@
       <c r="L403" s="9"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="A404" s="32"/>
+      <c r="A404" s="33"/>
       <c r="B404" s="9"/>
       <c r="C404" s="9"/>
       <c r="D404" s="9"/>
@@ -9991,7 +10038,7 @@
       <c r="L404" s="9"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="A405" s="32"/>
+      <c r="A405" s="33"/>
       <c r="B405" s="9"/>
       <c r="C405" s="9"/>
       <c r="D405" s="9"/>
@@ -10005,7 +10052,7 @@
       <c r="L405" s="9"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="A406" s="32"/>
+      <c r="A406" s="33"/>
       <c r="B406" s="9"/>
       <c r="C406" s="9"/>
       <c r="D406" s="9"/>
@@ -10019,7 +10066,7 @@
       <c r="L406" s="9"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="A407" s="32"/>
+      <c r="A407" s="33"/>
       <c r="B407" s="9"/>
       <c r="C407" s="9"/>
       <c r="D407" s="9"/>
@@ -10033,7 +10080,7 @@
       <c r="L407" s="9"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="A408" s="32"/>
+      <c r="A408" s="33"/>
       <c r="B408" s="9"/>
       <c r="C408" s="9"/>
       <c r="D408" s="9"/>
@@ -10047,7 +10094,7 @@
       <c r="L408" s="9"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="A409" s="32"/>
+      <c r="A409" s="33"/>
       <c r="B409" s="9"/>
       <c r="C409" s="9"/>
       <c r="D409" s="9"/>
@@ -10061,7 +10108,7 @@
       <c r="L409" s="9"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="A410" s="32"/>
+      <c r="A410" s="33"/>
       <c r="B410" s="9"/>
       <c r="C410" s="9"/>
       <c r="D410" s="9"/>
@@ -10075,7 +10122,7 @@
       <c r="L410" s="9"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="A411" s="32"/>
+      <c r="A411" s="33"/>
       <c r="B411" s="9"/>
       <c r="C411" s="9"/>
       <c r="D411" s="9"/>
@@ -10089,7 +10136,7 @@
       <c r="L411" s="9"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="A412" s="32"/>
+      <c r="A412" s="33"/>
       <c r="B412" s="9"/>
       <c r="C412" s="9"/>
       <c r="D412" s="9"/>
@@ -10103,7 +10150,7 @@
       <c r="L412" s="9"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="32"/>
+      <c r="A413" s="33"/>
       <c r="B413" s="9"/>
       <c r="C413" s="9"/>
       <c r="D413" s="9"/>
@@ -10117,7 +10164,7 @@
       <c r="L413" s="9"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="A414" s="32"/>
+      <c r="A414" s="33"/>
       <c r="B414" s="9"/>
       <c r="C414" s="9"/>
       <c r="D414" s="9"/>
@@ -10131,7 +10178,7 @@
       <c r="L414" s="9"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="A415" s="32"/>
+      <c r="A415" s="33"/>
       <c r="B415" s="9"/>
       <c r="C415" s="9"/>
       <c r="D415" s="9"/>
@@ -10145,7 +10192,7 @@
       <c r="L415" s="9"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="32"/>
+      <c r="A416" s="33"/>
       <c r="B416" s="9"/>
       <c r="C416" s="9"/>
       <c r="D416" s="9"/>
@@ -10159,7 +10206,7 @@
       <c r="L416" s="9"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="A417" s="32"/>
+      <c r="A417" s="33"/>
       <c r="B417" s="9"/>
       <c r="C417" s="9"/>
       <c r="D417" s="9"/>
@@ -10173,7 +10220,7 @@
       <c r="L417" s="9"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="A418" s="32"/>
+      <c r="A418" s="33"/>
       <c r="B418" s="9"/>
       <c r="C418" s="9"/>
       <c r="D418" s="9"/>
@@ -10187,7 +10234,7 @@
       <c r="L418" s="9"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="A419" s="32"/>
+      <c r="A419" s="33"/>
       <c r="B419" s="9"/>
       <c r="C419" s="9"/>
       <c r="D419" s="9"/>
@@ -10201,7 +10248,7 @@
       <c r="L419" s="9"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="A420" s="32"/>
+      <c r="A420" s="33"/>
       <c r="B420" s="9"/>
       <c r="C420" s="9"/>
       <c r="D420" s="9"/>
@@ -10215,7 +10262,7 @@
       <c r="L420" s="9"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="A421" s="32"/>
+      <c r="A421" s="33"/>
       <c r="B421" s="9"/>
       <c r="C421" s="9"/>
       <c r="D421" s="9"/>
@@ -10229,7 +10276,7 @@
       <c r="L421" s="9"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="32"/>
+      <c r="A422" s="33"/>
       <c r="B422" s="9"/>
       <c r="C422" s="9"/>
       <c r="D422" s="9"/>
@@ -10243,7 +10290,7 @@
       <c r="L422" s="9"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="A423" s="32"/>
+      <c r="A423" s="33"/>
       <c r="B423" s="9"/>
       <c r="C423" s="9"/>
       <c r="D423" s="9"/>
@@ -10257,7 +10304,7 @@
       <c r="L423" s="9"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="A424" s="32"/>
+      <c r="A424" s="33"/>
       <c r="B424" s="9"/>
       <c r="C424" s="9"/>
       <c r="D424" s="9"/>
@@ -10271,7 +10318,7 @@
       <c r="L424" s="9"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="32"/>
+      <c r="A425" s="33"/>
       <c r="B425" s="9"/>
       <c r="C425" s="9"/>
       <c r="D425" s="9"/>
@@ -10285,7 +10332,7 @@
       <c r="L425" s="9"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="32"/>
+      <c r="A426" s="33"/>
       <c r="B426" s="9"/>
       <c r="C426" s="9"/>
       <c r="D426" s="9"/>
@@ -10299,7 +10346,7 @@
       <c r="L426" s="9"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="32"/>
+      <c r="A427" s="33"/>
       <c r="B427" s="9"/>
       <c r="C427" s="9"/>
       <c r="D427" s="9"/>
@@ -10313,7 +10360,7 @@
       <c r="L427" s="9"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="32"/>
+      <c r="A428" s="33"/>
       <c r="B428" s="9"/>
       <c r="C428" s="9"/>
       <c r="D428" s="9"/>
@@ -10327,7 +10374,7 @@
       <c r="L428" s="9"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="A429" s="32"/>
+      <c r="A429" s="33"/>
       <c r="B429" s="9"/>
       <c r="C429" s="9"/>
       <c r="D429" s="9"/>
@@ -10341,7 +10388,7 @@
       <c r="L429" s="9"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="32"/>
+      <c r="A430" s="33"/>
       <c r="B430" s="9"/>
       <c r="C430" s="9"/>
       <c r="D430" s="9"/>
@@ -10355,7 +10402,7 @@
       <c r="L430" s="9"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="32"/>
+      <c r="A431" s="33"/>
       <c r="B431" s="9"/>
       <c r="C431" s="9"/>
       <c r="D431" s="9"/>
@@ -10369,7 +10416,7 @@
       <c r="L431" s="9"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="32"/>
+      <c r="A432" s="33"/>
       <c r="B432" s="9"/>
       <c r="C432" s="9"/>
       <c r="D432" s="9"/>
@@ -10383,7 +10430,7 @@
       <c r="L432" s="9"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="32"/>
+      <c r="A433" s="33"/>
       <c r="B433" s="9"/>
       <c r="C433" s="9"/>
       <c r="D433" s="9"/>
@@ -10397,7 +10444,7 @@
       <c r="L433" s="9"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="32"/>
+      <c r="A434" s="33"/>
       <c r="B434" s="9"/>
       <c r="C434" s="9"/>
       <c r="D434" s="9"/>
@@ -10411,7 +10458,7 @@
       <c r="L434" s="9"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="32"/>
+      <c r="A435" s="33"/>
       <c r="B435" s="9"/>
       <c r="C435" s="9"/>
       <c r="D435" s="9"/>
@@ -10425,7 +10472,7 @@
       <c r="L435" s="9"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="32"/>
+      <c r="A436" s="33"/>
       <c r="B436" s="9"/>
       <c r="C436" s="9"/>
       <c r="D436" s="9"/>
@@ -10439,7 +10486,7 @@
       <c r="L436" s="9"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="32"/>
+      <c r="A437" s="33"/>
       <c r="B437" s="9"/>
       <c r="C437" s="9"/>
       <c r="D437" s="9"/>
@@ -10453,7 +10500,7 @@
       <c r="L437" s="9"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="32"/>
+      <c r="A438" s="33"/>
       <c r="B438" s="9"/>
       <c r="C438" s="9"/>
       <c r="D438" s="9"/>
@@ -10467,7 +10514,7 @@
       <c r="L438" s="9"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="32"/>
+      <c r="A439" s="33"/>
       <c r="B439" s="9"/>
       <c r="C439" s="9"/>
       <c r="D439" s="9"/>
@@ -10481,7 +10528,7 @@
       <c r="L439" s="9"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="32"/>
+      <c r="A440" s="33"/>
       <c r="B440" s="9"/>
       <c r="C440" s="9"/>
       <c r="D440" s="9"/>
@@ -10495,7 +10542,7 @@
       <c r="L440" s="9"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="32"/>
+      <c r="A441" s="33"/>
       <c r="B441" s="9"/>
       <c r="C441" s="9"/>
       <c r="D441" s="9"/>
@@ -10509,7 +10556,7 @@
       <c r="L441" s="9"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="32"/>
+      <c r="A442" s="33"/>
       <c r="B442" s="9"/>
       <c r="C442" s="9"/>
       <c r="D442" s="9"/>
@@ -10523,7 +10570,7 @@
       <c r="L442" s="9"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="32"/>
+      <c r="A443" s="33"/>
       <c r="B443" s="9"/>
       <c r="C443" s="9"/>
       <c r="D443" s="9"/>
@@ -10537,7 +10584,7 @@
       <c r="L443" s="9"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="32"/>
+      <c r="A444" s="33"/>
       <c r="B444" s="9"/>
       <c r="C444" s="9"/>
       <c r="D444" s="9"/>
@@ -10551,7 +10598,7 @@
       <c r="L444" s="9"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="32"/>
+      <c r="A445" s="33"/>
       <c r="B445" s="9"/>
       <c r="C445" s="9"/>
       <c r="D445" s="9"/>
@@ -10565,7 +10612,7 @@
       <c r="L445" s="9"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="32"/>
+      <c r="A446" s="33"/>
       <c r="B446" s="9"/>
       <c r="C446" s="9"/>
       <c r="D446" s="9"/>
@@ -10579,7 +10626,7 @@
       <c r="L446" s="9"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="A447" s="32"/>
+      <c r="A447" s="33"/>
       <c r="B447" s="9"/>
       <c r="C447" s="9"/>
       <c r="D447" s="9"/>
@@ -10593,7 +10640,7 @@
       <c r="L447" s="9"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="A448" s="32"/>
+      <c r="A448" s="33"/>
       <c r="B448" s="9"/>
       <c r="C448" s="9"/>
       <c r="D448" s="9"/>
@@ -10607,7 +10654,7 @@
       <c r="L448" s="9"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="A449" s="32"/>
+      <c r="A449" s="33"/>
       <c r="B449" s="9"/>
       <c r="C449" s="9"/>
       <c r="D449" s="9"/>
@@ -10621,7 +10668,7 @@
       <c r="L449" s="9"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="A450" s="32"/>
+      <c r="A450" s="33"/>
       <c r="B450" s="9"/>
       <c r="C450" s="9"/>
       <c r="D450" s="9"/>
@@ -10635,7 +10682,7 @@
       <c r="L450" s="9"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="32"/>
+      <c r="A451" s="33"/>
       <c r="B451" s="9"/>
       <c r="C451" s="9"/>
       <c r="D451" s="9"/>
@@ -10649,7 +10696,7 @@
       <c r="L451" s="9"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="A452" s="32"/>
+      <c r="A452" s="33"/>
       <c r="B452" s="9"/>
       <c r="C452" s="9"/>
       <c r="D452" s="9"/>
@@ -10663,7 +10710,7 @@
       <c r="L452" s="9"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="32"/>
+      <c r="A453" s="33"/>
       <c r="B453" s="9"/>
       <c r="C453" s="9"/>
       <c r="D453" s="9"/>
@@ -10677,7 +10724,7 @@
       <c r="L453" s="9"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="A454" s="32"/>
+      <c r="A454" s="33"/>
       <c r="B454" s="9"/>
       <c r="C454" s="9"/>
       <c r="D454" s="9"/>
@@ -10691,7 +10738,7 @@
       <c r="L454" s="9"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="A455" s="32"/>
+      <c r="A455" s="33"/>
       <c r="B455" s="9"/>
       <c r="C455" s="9"/>
       <c r="D455" s="9"/>
@@ -10705,7 +10752,7 @@
       <c r="L455" s="9"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="32"/>
+      <c r="A456" s="33"/>
       <c r="B456" s="9"/>
       <c r="C456" s="9"/>
       <c r="D456" s="9"/>
@@ -10719,7 +10766,7 @@
       <c r="L456" s="9"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="A457" s="32"/>
+      <c r="A457" s="33"/>
       <c r="B457" s="9"/>
       <c r="C457" s="9"/>
       <c r="D457" s="9"/>
@@ -10733,7 +10780,7 @@
       <c r="L457" s="9"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="A458" s="32"/>
+      <c r="A458" s="33"/>
       <c r="B458" s="9"/>
       <c r="C458" s="9"/>
       <c r="D458" s="9"/>
@@ -10747,7 +10794,7 @@
       <c r="L458" s="9"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="A459" s="32"/>
+      <c r="A459" s="33"/>
       <c r="B459" s="9"/>
       <c r="C459" s="9"/>
       <c r="D459" s="9"/>
@@ -10761,7 +10808,7 @@
       <c r="L459" s="9"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="A460" s="32"/>
+      <c r="A460" s="33"/>
       <c r="B460" s="9"/>
       <c r="C460" s="9"/>
       <c r="D460" s="9"/>
@@ -10775,7 +10822,7 @@
       <c r="L460" s="9"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="32"/>
+      <c r="A461" s="33"/>
       <c r="B461" s="9"/>
       <c r="C461" s="9"/>
       <c r="D461" s="9"/>
@@ -10789,7 +10836,7 @@
       <c r="L461" s="9"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="32"/>
+      <c r="A462" s="33"/>
       <c r="B462" s="9"/>
       <c r="C462" s="9"/>
       <c r="D462" s="9"/>
@@ -10803,7 +10850,7 @@
       <c r="L462" s="9"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="A463" s="32"/>
+      <c r="A463" s="33"/>
       <c r="B463" s="9"/>
       <c r="C463" s="9"/>
       <c r="D463" s="9"/>
@@ -10817,7 +10864,7 @@
       <c r="L463" s="9"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="32"/>
+      <c r="A464" s="33"/>
       <c r="B464" s="9"/>
       <c r="C464" s="9"/>
       <c r="D464" s="9"/>
@@ -10831,7 +10878,7 @@
       <c r="L464" s="9"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="32"/>
+      <c r="A465" s="33"/>
       <c r="B465" s="9"/>
       <c r="C465" s="9"/>
       <c r="D465" s="9"/>
@@ -10845,7 +10892,7 @@
       <c r="L465" s="9"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="32"/>
+      <c r="A466" s="33"/>
       <c r="B466" s="9"/>
       <c r="C466" s="9"/>
       <c r="D466" s="9"/>
@@ -10859,7 +10906,7 @@
       <c r="L466" s="9"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="A467" s="32"/>
+      <c r="A467" s="33"/>
       <c r="B467" s="9"/>
       <c r="C467" s="9"/>
       <c r="D467" s="9"/>
@@ -10873,7 +10920,7 @@
       <c r="L467" s="9"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="32"/>
+      <c r="A468" s="33"/>
       <c r="B468" s="9"/>
       <c r="C468" s="9"/>
       <c r="D468" s="9"/>
@@ -10887,7 +10934,7 @@
       <c r="L468" s="9"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="32"/>
+      <c r="A469" s="33"/>
       <c r="B469" s="9"/>
       <c r="C469" s="9"/>
       <c r="D469" s="9"/>
@@ -10901,7 +10948,7 @@
       <c r="L469" s="9"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="32"/>
+      <c r="A470" s="33"/>
       <c r="B470" s="9"/>
       <c r="C470" s="9"/>
       <c r="D470" s="9"/>
@@ -10915,7 +10962,7 @@
       <c r="L470" s="9"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="32"/>
+      <c r="A471" s="33"/>
       <c r="B471" s="9"/>
       <c r="C471" s="9"/>
       <c r="D471" s="9"/>
@@ -10929,7 +10976,7 @@
       <c r="L471" s="9"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="A472" s="32"/>
+      <c r="A472" s="33"/>
       <c r="B472" s="9"/>
       <c r="C472" s="9"/>
       <c r="D472" s="9"/>
@@ -10943,7 +10990,7 @@
       <c r="L472" s="9"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="32"/>
+      <c r="A473" s="33"/>
       <c r="B473" s="9"/>
       <c r="C473" s="9"/>
       <c r="D473" s="9"/>
@@ -10957,7 +11004,7 @@
       <c r="L473" s="9"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="A474" s="32"/>
+      <c r="A474" s="33"/>
       <c r="B474" s="9"/>
       <c r="C474" s="9"/>
       <c r="D474" s="9"/>
@@ -10971,7 +11018,7 @@
       <c r="L474" s="9"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="32"/>
+      <c r="A475" s="33"/>
       <c r="B475" s="9"/>
       <c r="C475" s="9"/>
       <c r="D475" s="9"/>
@@ -10985,7 +11032,7 @@
       <c r="L475" s="9"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="32"/>
+      <c r="A476" s="33"/>
       <c r="B476" s="9"/>
       <c r="C476" s="9"/>
       <c r="D476" s="9"/>
@@ -10999,7 +11046,7 @@
       <c r="L476" s="9"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="32"/>
+      <c r="A477" s="33"/>
       <c r="B477" s="9"/>
       <c r="C477" s="9"/>
       <c r="D477" s="9"/>
@@ -11013,7 +11060,7 @@
       <c r="L477" s="9"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="32"/>
+      <c r="A478" s="33"/>
       <c r="B478" s="9"/>
       <c r="C478" s="9"/>
       <c r="D478" s="9"/>
@@ -11027,7 +11074,7 @@
       <c r="L478" s="9"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="A479" s="32"/>
+      <c r="A479" s="33"/>
       <c r="B479" s="9"/>
       <c r="C479" s="9"/>
       <c r="D479" s="9"/>
@@ -11041,7 +11088,7 @@
       <c r="L479" s="9"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="A480" s="32"/>
+      <c r="A480" s="33"/>
       <c r="B480" s="9"/>
       <c r="C480" s="9"/>
       <c r="D480" s="9"/>
@@ -11055,7 +11102,7 @@
       <c r="L480" s="9"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="A481" s="32"/>
+      <c r="A481" s="33"/>
       <c r="B481" s="9"/>
       <c r="C481" s="9"/>
       <c r="D481" s="9"/>
@@ -11069,7 +11116,7 @@
       <c r="L481" s="9"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="A482" s="32"/>
+      <c r="A482" s="33"/>
       <c r="B482" s="9"/>
       <c r="C482" s="9"/>
       <c r="D482" s="9"/>
@@ -11083,7 +11130,7 @@
       <c r="L482" s="9"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="A483" s="32"/>
+      <c r="A483" s="33"/>
       <c r="B483" s="9"/>
       <c r="C483" s="9"/>
       <c r="D483" s="9"/>
@@ -11097,7 +11144,7 @@
       <c r="L483" s="9"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="A484" s="32"/>
+      <c r="A484" s="33"/>
       <c r="B484" s="9"/>
       <c r="C484" s="9"/>
       <c r="D484" s="9"/>
@@ -11111,7 +11158,7 @@
       <c r="L484" s="9"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="A485" s="32"/>
+      <c r="A485" s="33"/>
       <c r="B485" s="9"/>
       <c r="C485" s="9"/>
       <c r="D485" s="9"/>
@@ -11125,7 +11172,7 @@
       <c r="L485" s="9"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="A486" s="32"/>
+      <c r="A486" s="33"/>
       <c r="B486" s="9"/>
       <c r="C486" s="9"/>
       <c r="D486" s="9"/>
@@ -11139,7 +11186,7 @@
       <c r="L486" s="9"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="A487" s="32"/>
+      <c r="A487" s="33"/>
       <c r="B487" s="9"/>
       <c r="C487" s="9"/>
       <c r="D487" s="9"/>
@@ -11153,7 +11200,7 @@
       <c r="L487" s="9"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="A488" s="32"/>
+      <c r="A488" s="33"/>
       <c r="B488" s="9"/>
       <c r="C488" s="9"/>
       <c r="D488" s="9"/>
@@ -11167,7 +11214,7 @@
       <c r="L488" s="9"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="A489" s="32"/>
+      <c r="A489" s="33"/>
       <c r="B489" s="9"/>
       <c r="C489" s="9"/>
       <c r="D489" s="9"/>
@@ -11181,7 +11228,7 @@
       <c r="L489" s="9"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="A490" s="32"/>
+      <c r="A490" s="33"/>
       <c r="B490" s="9"/>
       <c r="C490" s="9"/>
       <c r="D490" s="9"/>
@@ -11195,7 +11242,7 @@
       <c r="L490" s="9"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="A491" s="32"/>
+      <c r="A491" s="33"/>
       <c r="B491" s="9"/>
       <c r="C491" s="9"/>
       <c r="D491" s="9"/>
@@ -11209,7 +11256,7 @@
       <c r="L491" s="9"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="A492" s="32"/>
+      <c r="A492" s="33"/>
       <c r="B492" s="9"/>
       <c r="C492" s="9"/>
       <c r="D492" s="9"/>
@@ -11223,7 +11270,7 @@
       <c r="L492" s="9"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="A493" s="32"/>
+      <c r="A493" s="33"/>
       <c r="B493" s="9"/>
       <c r="C493" s="9"/>
       <c r="D493" s="9"/>
@@ -11237,7 +11284,7 @@
       <c r="L493" s="9"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="A494" s="32"/>
+      <c r="A494" s="33"/>
       <c r="B494" s="9"/>
       <c r="C494" s="9"/>
       <c r="D494" s="9"/>
@@ -11251,7 +11298,7 @@
       <c r="L494" s="9"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="A495" s="32"/>
+      <c r="A495" s="33"/>
       <c r="B495" s="9"/>
       <c r="C495" s="9"/>
       <c r="D495" s="9"/>
@@ -11265,7 +11312,7 @@
       <c r="L495" s="9"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="A496" s="32"/>
+      <c r="A496" s="33"/>
       <c r="B496" s="9"/>
       <c r="C496" s="9"/>
       <c r="D496" s="9"/>
@@ -11279,7 +11326,7 @@
       <c r="L496" s="9"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="A497" s="32"/>
+      <c r="A497" s="33"/>
       <c r="B497" s="9"/>
       <c r="C497" s="9"/>
       <c r="D497" s="9"/>
@@ -11293,7 +11340,7 @@
       <c r="L497" s="9"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="A498" s="32"/>
+      <c r="A498" s="33"/>
       <c r="B498" s="9"/>
       <c r="C498" s="9"/>
       <c r="D498" s="9"/>
@@ -11307,7 +11354,7 @@
       <c r="L498" s="9"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="A499" s="32"/>
+      <c r="A499" s="33"/>
       <c r="B499" s="9"/>
       <c r="C499" s="9"/>
       <c r="D499" s="9"/>
@@ -11321,7 +11368,7 @@
       <c r="L499" s="9"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="A500" s="32"/>
+      <c r="A500" s="33"/>
       <c r="B500" s="9"/>
       <c r="C500" s="9"/>
       <c r="D500" s="9"/>
@@ -11335,7 +11382,7 @@
       <c r="L500" s="9"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="A501" s="32"/>
+      <c r="A501" s="33"/>
       <c r="B501" s="9"/>
       <c r="C501" s="9"/>
       <c r="D501" s="9"/>
@@ -11349,7 +11396,7 @@
       <c r="L501" s="9"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="A502" s="32"/>
+      <c r="A502" s="33"/>
       <c r="B502" s="9"/>
       <c r="C502" s="9"/>
       <c r="D502" s="9"/>
@@ -11363,7 +11410,7 @@
       <c r="L502" s="9"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="A503" s="32"/>
+      <c r="A503" s="33"/>
       <c r="B503" s="9"/>
       <c r="C503" s="9"/>
       <c r="D503" s="9"/>
@@ -11377,7 +11424,7 @@
       <c r="L503" s="9"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="A504" s="32"/>
+      <c r="A504" s="33"/>
       <c r="B504" s="9"/>
       <c r="C504" s="9"/>
       <c r="D504" s="9"/>
@@ -11391,7 +11438,7 @@
       <c r="L504" s="9"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="A505" s="32"/>
+      <c r="A505" s="33"/>
       <c r="B505" s="9"/>
       <c r="C505" s="9"/>
       <c r="D505" s="9"/>
@@ -11405,7 +11452,7 @@
       <c r="L505" s="9"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="A506" s="32"/>
+      <c r="A506" s="33"/>
       <c r="B506" s="9"/>
       <c r="C506" s="9"/>
       <c r="D506" s="9"/>
@@ -11419,7 +11466,7 @@
       <c r="L506" s="9"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="A507" s="32"/>
+      <c r="A507" s="33"/>
       <c r="B507" s="9"/>
       <c r="C507" s="9"/>
       <c r="D507" s="9"/>
@@ -11433,7 +11480,7 @@
       <c r="L507" s="9"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="A508" s="32"/>
+      <c r="A508" s="33"/>
       <c r="B508" s="9"/>
       <c r="C508" s="9"/>
       <c r="D508" s="9"/>
@@ -11447,7 +11494,7 @@
       <c r="L508" s="9"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="A509" s="32"/>
+      <c r="A509" s="33"/>
       <c r="B509" s="9"/>
       <c r="C509" s="9"/>
       <c r="D509" s="9"/>
@@ -11461,7 +11508,7 @@
       <c r="L509" s="9"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="A510" s="32"/>
+      <c r="A510" s="33"/>
       <c r="B510" s="9"/>
       <c r="C510" s="9"/>
       <c r="D510" s="9"/>
@@ -11475,7 +11522,7 @@
       <c r="L510" s="9"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="A511" s="32"/>
+      <c r="A511" s="33"/>
       <c r="B511" s="9"/>
       <c r="C511" s="9"/>
       <c r="D511" s="9"/>
@@ -11489,7 +11536,7 @@
       <c r="L511" s="9"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="A512" s="32"/>
+      <c r="A512" s="33"/>
       <c r="B512" s="9"/>
       <c r="C512" s="9"/>
       <c r="D512" s="9"/>
@@ -11503,7 +11550,7 @@
       <c r="L512" s="9"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="A513" s="32"/>
+      <c r="A513" s="33"/>
       <c r="B513" s="9"/>
       <c r="C513" s="9"/>
       <c r="D513" s="9"/>
@@ -11517,7 +11564,7 @@
       <c r="L513" s="9"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="A514" s="32"/>
+      <c r="A514" s="33"/>
       <c r="B514" s="9"/>
       <c r="C514" s="9"/>
       <c r="D514" s="9"/>
@@ -11531,7 +11578,7 @@
       <c r="L514" s="9"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="A515" s="32"/>
+      <c r="A515" s="33"/>
       <c r="B515" s="9"/>
       <c r="C515" s="9"/>
       <c r="D515" s="9"/>
@@ -11545,7 +11592,7 @@
       <c r="L515" s="9"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="A516" s="32"/>
+      <c r="A516" s="33"/>
       <c r="B516" s="9"/>
       <c r="C516" s="9"/>
       <c r="D516" s="9"/>
@@ -11559,7 +11606,7 @@
       <c r="L516" s="9"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="A517" s="32"/>
+      <c r="A517" s="33"/>
       <c r="B517" s="9"/>
       <c r="C517" s="9"/>
       <c r="D517" s="9"/>
@@ -11573,7 +11620,7 @@
       <c r="L517" s="9"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="A518" s="32"/>
+      <c r="A518" s="33"/>
       <c r="B518" s="9"/>
       <c r="C518" s="9"/>
       <c r="D518" s="9"/>
@@ -11587,7 +11634,7 @@
       <c r="L518" s="9"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="A519" s="32"/>
+      <c r="A519" s="33"/>
       <c r="B519" s="9"/>
       <c r="C519" s="9"/>
       <c r="D519" s="9"/>
@@ -11601,7 +11648,7 @@
       <c r="L519" s="9"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="A520" s="32"/>
+      <c r="A520" s="33"/>
       <c r="B520" s="9"/>
       <c r="C520" s="9"/>
       <c r="D520" s="9"/>
@@ -11615,7 +11662,7 @@
       <c r="L520" s="9"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="A521" s="32"/>
+      <c r="A521" s="33"/>
       <c r="B521" s="9"/>
       <c r="C521" s="9"/>
       <c r="D521" s="9"/>
@@ -11629,7 +11676,7 @@
       <c r="L521" s="9"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="A522" s="32"/>
+      <c r="A522" s="33"/>
       <c r="B522" s="9"/>
       <c r="C522" s="9"/>
       <c r="D522" s="9"/>
@@ -11643,7 +11690,7 @@
       <c r="L522" s="9"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="A523" s="32"/>
+      <c r="A523" s="33"/>
       <c r="B523" s="9"/>
       <c r="C523" s="9"/>
       <c r="D523" s="9"/>
@@ -11657,7 +11704,7 @@
       <c r="L523" s="9"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="A524" s="32"/>
+      <c r="A524" s="33"/>
       <c r="B524" s="9"/>
       <c r="C524" s="9"/>
       <c r="D524" s="9"/>
@@ -11671,7 +11718,7 @@
       <c r="L524" s="9"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="A525" s="32"/>
+      <c r="A525" s="33"/>
       <c r="B525" s="9"/>
       <c r="C525" s="9"/>
       <c r="D525" s="9"/>
@@ -11685,7 +11732,7 @@
       <c r="L525" s="9"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="A526" s="32"/>
+      <c r="A526" s="33"/>
       <c r="B526" s="9"/>
       <c r="C526" s="9"/>
       <c r="D526" s="9"/>
@@ -11699,7 +11746,7 @@
       <c r="L526" s="9"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="A527" s="32"/>
+      <c r="A527" s="33"/>
       <c r="B527" s="9"/>
       <c r="C527" s="9"/>
       <c r="D527" s="9"/>
@@ -11713,7 +11760,7 @@
       <c r="L527" s="9"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="A528" s="32"/>
+      <c r="A528" s="33"/>
       <c r="B528" s="9"/>
       <c r="C528" s="9"/>
       <c r="D528" s="9"/>
@@ -11727,7 +11774,7 @@
       <c r="L528" s="9"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="A529" s="32"/>
+      <c r="A529" s="33"/>
       <c r="B529" s="9"/>
       <c r="C529" s="9"/>
       <c r="D529" s="9"/>
@@ -11741,7 +11788,7 @@
       <c r="L529" s="9"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="A530" s="32"/>
+      <c r="A530" s="33"/>
       <c r="B530" s="9"/>
       <c r="C530" s="9"/>
       <c r="D530" s="9"/>
@@ -11755,7 +11802,7 @@
       <c r="L530" s="9"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="A531" s="32"/>
+      <c r="A531" s="33"/>
       <c r="B531" s="9"/>
       <c r="C531" s="9"/>
       <c r="D531" s="9"/>
@@ -11769,7 +11816,7 @@
       <c r="L531" s="9"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="A532" s="32"/>
+      <c r="A532" s="33"/>
       <c r="B532" s="9"/>
       <c r="C532" s="9"/>
       <c r="D532" s="9"/>
@@ -11783,7 +11830,7 @@
       <c r="L532" s="9"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="A533" s="32"/>
+      <c r="A533" s="33"/>
       <c r="B533" s="9"/>
       <c r="C533" s="9"/>
       <c r="D533" s="9"/>
@@ -11797,7 +11844,7 @@
       <c r="L533" s="9"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="A534" s="32"/>
+      <c r="A534" s="33"/>
       <c r="B534" s="9"/>
       <c r="C534" s="9"/>
       <c r="D534" s="9"/>
@@ -11811,7 +11858,7 @@
       <c r="L534" s="9"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="A535" s="32"/>
+      <c r="A535" s="33"/>
       <c r="B535" s="9"/>
       <c r="C535" s="9"/>
       <c r="D535" s="9"/>
@@ -11825,7 +11872,7 @@
       <c r="L535" s="9"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="A536" s="32"/>
+      <c r="A536" s="33"/>
       <c r="B536" s="9"/>
       <c r="C536" s="9"/>
       <c r="D536" s="9"/>
@@ -11839,7 +11886,7 @@
       <c r="L536" s="9"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="A537" s="32"/>
+      <c r="A537" s="33"/>
       <c r="B537" s="9"/>
       <c r="C537" s="9"/>
       <c r="D537" s="9"/>
@@ -11853,7 +11900,7 @@
       <c r="L537" s="9"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="A538" s="32"/>
+      <c r="A538" s="33"/>
       <c r="B538" s="9"/>
       <c r="C538" s="9"/>
       <c r="D538" s="9"/>
@@ -11867,7 +11914,7 @@
       <c r="L538" s="9"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="A539" s="32"/>
+      <c r="A539" s="33"/>
       <c r="B539" s="9"/>
       <c r="C539" s="9"/>
       <c r="D539" s="9"/>
@@ -11881,7 +11928,7 @@
       <c r="L539" s="9"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="A540" s="32"/>
+      <c r="A540" s="33"/>
       <c r="B540" s="9"/>
       <c r="C540" s="9"/>
       <c r="D540" s="9"/>
@@ -11895,7 +11942,7 @@
       <c r="L540" s="9"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="A541" s="32"/>
+      <c r="A541" s="33"/>
       <c r="B541" s="9"/>
       <c r="C541" s="9"/>
       <c r="D541" s="9"/>
@@ -11909,7 +11956,7 @@
       <c r="L541" s="9"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="A542" s="32"/>
+      <c r="A542" s="33"/>
       <c r="B542" s="9"/>
       <c r="C542" s="9"/>
       <c r="D542" s="9"/>
@@ -11923,7 +11970,7 @@
       <c r="L542" s="9"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="A543" s="32"/>
+      <c r="A543" s="33"/>
       <c r="B543" s="9"/>
       <c r="C543" s="9"/>
       <c r="D543" s="9"/>
@@ -11937,7 +11984,7 @@
       <c r="L543" s="9"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="A544" s="32"/>
+      <c r="A544" s="33"/>
       <c r="B544" s="9"/>
       <c r="C544" s="9"/>
       <c r="D544" s="9"/>
@@ -11951,7 +11998,7 @@
       <c r="L544" s="9"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="A545" s="32"/>
+      <c r="A545" s="33"/>
       <c r="B545" s="9"/>
       <c r="C545" s="9"/>
       <c r="D545" s="9"/>
@@ -11965,7 +12012,7 @@
       <c r="L545" s="9"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="A546" s="32"/>
+      <c r="A546" s="33"/>
       <c r="B546" s="9"/>
       <c r="C546" s="9"/>
       <c r="D546" s="9"/>
@@ -11979,7 +12026,7 @@
       <c r="L546" s="9"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="A547" s="32"/>
+      <c r="A547" s="33"/>
       <c r="B547" s="9"/>
       <c r="C547" s="9"/>
       <c r="D547" s="9"/>
@@ -11993,7 +12040,7 @@
       <c r="L547" s="9"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="A548" s="32"/>
+      <c r="A548" s="33"/>
       <c r="B548" s="9"/>
       <c r="C548" s="9"/>
       <c r="D548" s="9"/>
@@ -12007,7 +12054,7 @@
       <c r="L548" s="9"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="A549" s="32"/>
+      <c r="A549" s="33"/>
       <c r="B549" s="9"/>
       <c r="C549" s="9"/>
       <c r="D549" s="9"/>
@@ -12021,7 +12068,7 @@
       <c r="L549" s="9"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="A550" s="32"/>
+      <c r="A550" s="33"/>
       <c r="B550" s="9"/>
       <c r="C550" s="9"/>
       <c r="D550" s="9"/>
@@ -12035,7 +12082,7 @@
       <c r="L550" s="9"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="A551" s="32"/>
+      <c r="A551" s="33"/>
       <c r="B551" s="9"/>
       <c r="C551" s="9"/>
       <c r="D551" s="9"/>
@@ -12049,7 +12096,7 @@
       <c r="L551" s="9"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="A552" s="32"/>
+      <c r="A552" s="33"/>
       <c r="B552" s="9"/>
       <c r="C552" s="9"/>
       <c r="D552" s="9"/>
@@ -12063,7 +12110,7 @@
       <c r="L552" s="9"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="A553" s="32"/>
+      <c r="A553" s="33"/>
       <c r="B553" s="9"/>
       <c r="C553" s="9"/>
       <c r="D553" s="9"/>
@@ -12077,7 +12124,7 @@
       <c r="L553" s="9"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="A554" s="32"/>
+      <c r="A554" s="33"/>
       <c r="B554" s="9"/>
       <c r="C554" s="9"/>
       <c r="D554" s="9"/>
@@ -12091,7 +12138,7 @@
       <c r="L554" s="9"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="A555" s="32"/>
+      <c r="A555" s="33"/>
       <c r="B555" s="9"/>
       <c r="C555" s="9"/>
       <c r="D555" s="9"/>
@@ -12105,7 +12152,7 @@
       <c r="L555" s="9"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="A556" s="32"/>
+      <c r="A556" s="33"/>
       <c r="B556" s="9"/>
       <c r="C556" s="9"/>
       <c r="D556" s="9"/>
@@ -12119,7 +12166,7 @@
       <c r="L556" s="9"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="A557" s="32"/>
+      <c r="A557" s="33"/>
       <c r="B557" s="9"/>
       <c r="C557" s="9"/>
       <c r="D557" s="9"/>
@@ -12133,7 +12180,7 @@
       <c r="L557" s="9"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="A558" s="32"/>
+      <c r="A558" s="33"/>
       <c r="B558" s="9"/>
       <c r="C558" s="9"/>
       <c r="D558" s="9"/>
@@ -12147,7 +12194,7 @@
       <c r="L558" s="9"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="A559" s="32"/>
+      <c r="A559" s="33"/>
       <c r="B559" s="9"/>
       <c r="C559" s="9"/>
       <c r="D559" s="9"/>
@@ -12161,7 +12208,7 @@
       <c r="L559" s="9"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="A560" s="32"/>
+      <c r="A560" s="33"/>
       <c r="B560" s="9"/>
       <c r="C560" s="9"/>
       <c r="D560" s="9"/>
@@ -12175,7 +12222,7 @@
       <c r="L560" s="9"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="A561" s="32"/>
+      <c r="A561" s="33"/>
       <c r="B561" s="9"/>
       <c r="C561" s="9"/>
       <c r="D561" s="9"/>
@@ -12189,7 +12236,7 @@
       <c r="L561" s="9"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="A562" s="32"/>
+      <c r="A562" s="33"/>
       <c r="B562" s="9"/>
       <c r="C562" s="9"/>
       <c r="D562" s="9"/>
@@ -12203,7 +12250,7 @@
       <c r="L562" s="9"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="A563" s="32"/>
+      <c r="A563" s="33"/>
       <c r="B563" s="9"/>
       <c r="C563" s="9"/>
       <c r="D563" s="9"/>
@@ -12217,7 +12264,7 @@
       <c r="L563" s="9"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="A564" s="32"/>
+      <c r="A564" s="33"/>
       <c r="B564" s="9"/>
       <c r="C564" s="9"/>
       <c r="D564" s="9"/>
@@ -12231,7 +12278,7 @@
       <c r="L564" s="9"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="A565" s="32"/>
+      <c r="A565" s="33"/>
       <c r="B565" s="9"/>
       <c r="C565" s="9"/>
       <c r="D565" s="9"/>
@@ -12245,7 +12292,7 @@
       <c r="L565" s="9"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="A566" s="32"/>
+      <c r="A566" s="33"/>
       <c r="B566" s="9"/>
       <c r="C566" s="9"/>
       <c r="D566" s="9"/>
@@ -12259,7 +12306,7 @@
       <c r="L566" s="9"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="A567" s="32"/>
+      <c r="A567" s="33"/>
       <c r="B567" s="9"/>
       <c r="C567" s="9"/>
       <c r="D567" s="9"/>
@@ -12273,7 +12320,7 @@
       <c r="L567" s="9"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="A568" s="32"/>
+      <c r="A568" s="33"/>
       <c r="B568" s="9"/>
       <c r="C568" s="9"/>
       <c r="D568" s="9"/>
@@ -12287,7 +12334,7 @@
       <c r="L568" s="9"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="A569" s="32"/>
+      <c r="A569" s="33"/>
       <c r="B569" s="9"/>
       <c r="C569" s="9"/>
       <c r="D569" s="9"/>
@@ -12301,7 +12348,7 @@
       <c r="L569" s="9"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="A570" s="32"/>
+      <c r="A570" s="33"/>
       <c r="B570" s="9"/>
       <c r="C570" s="9"/>
       <c r="D570" s="9"/>
@@ -12315,7 +12362,7 @@
       <c r="L570" s="9"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="A571" s="32"/>
+      <c r="A571" s="33"/>
       <c r="B571" s="9"/>
       <c r="C571" s="9"/>
       <c r="D571" s="9"/>
@@ -12329,7 +12376,7 @@
       <c r="L571" s="9"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="A572" s="32"/>
+      <c r="A572" s="33"/>
       <c r="B572" s="9"/>
       <c r="C572" s="9"/>
       <c r="D572" s="9"/>
@@ -12343,7 +12390,7 @@
       <c r="L572" s="9"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="A573" s="32"/>
+      <c r="A573" s="33"/>
       <c r="B573" s="9"/>
       <c r="C573" s="9"/>
       <c r="D573" s="9"/>
@@ -12357,7 +12404,7 @@
       <c r="L573" s="9"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="A574" s="32"/>
+      <c r="A574" s="33"/>
       <c r="B574" s="9"/>
       <c r="C574" s="9"/>
       <c r="D574" s="9"/>
@@ -12371,7 +12418,7 @@
       <c r="L574" s="9"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="A575" s="32"/>
+      <c r="A575" s="33"/>
       <c r="B575" s="9"/>
       <c r="C575" s="9"/>
       <c r="D575" s="9"/>
@@ -12385,7 +12432,7 @@
       <c r="L575" s="9"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="A576" s="32"/>
+      <c r="A576" s="33"/>
       <c r="B576" s="9"/>
       <c r="C576" s="9"/>
       <c r="D576" s="9"/>
@@ -12399,7 +12446,7 @@
       <c r="L576" s="9"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="A577" s="32"/>
+      <c r="A577" s="33"/>
       <c r="B577" s="9"/>
       <c r="C577" s="9"/>
       <c r="D577" s="9"/>
@@ -12413,7 +12460,7 @@
       <c r="L577" s="9"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="A578" s="32"/>
+      <c r="A578" s="33"/>
       <c r="B578" s="9"/>
       <c r="C578" s="9"/>
       <c r="D578" s="9"/>
@@ -12427,7 +12474,7 @@
       <c r="L578" s="9"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="A579" s="32"/>
+      <c r="A579" s="33"/>
       <c r="B579" s="9"/>
       <c r="C579" s="9"/>
       <c r="D579" s="9"/>
@@ -12441,7 +12488,7 @@
       <c r="L579" s="9"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="A580" s="32"/>
+      <c r="A580" s="33"/>
       <c r="B580" s="9"/>
       <c r="C580" s="9"/>
       <c r="D580" s="9"/>
@@ -12455,7 +12502,7 @@
       <c r="L580" s="9"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="A581" s="32"/>
+      <c r="A581" s="33"/>
       <c r="B581" s="9"/>
       <c r="C581" s="9"/>
       <c r="D581" s="9"/>
@@ -12469,7 +12516,7 @@
       <c r="L581" s="9"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="A582" s="32"/>
+      <c r="A582" s="33"/>
       <c r="B582" s="9"/>
       <c r="C582" s="9"/>
       <c r="D582" s="9"/>
@@ -12483,7 +12530,7 @@
       <c r="L582" s="9"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="A583" s="32"/>
+      <c r="A583" s="33"/>
       <c r="B583" s="9"/>
       <c r="C583" s="9"/>
       <c r="D583" s="9"/>
@@ -12497,7 +12544,7 @@
       <c r="L583" s="9"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="A584" s="32"/>
+      <c r="A584" s="33"/>
       <c r="B584" s="9"/>
       <c r="C584" s="9"/>
       <c r="D584" s="9"/>
@@ -12511,7 +12558,7 @@
       <c r="L584" s="9"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="A585" s="32"/>
+      <c r="A585" s="33"/>
       <c r="B585" s="9"/>
       <c r="C585" s="9"/>
       <c r="D585" s="9"/>
@@ -12525,7 +12572,7 @@
       <c r="L585" s="9"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="A586" s="32"/>
+      <c r="A586" s="33"/>
       <c r="B586" s="9"/>
       <c r="C586" s="9"/>
       <c r="D586" s="9"/>
@@ -12539,7 +12586,7 @@
       <c r="L586" s="9"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="A587" s="32"/>
+      <c r="A587" s="33"/>
       <c r="B587" s="9"/>
       <c r="C587" s="9"/>
       <c r="D587" s="9"/>
@@ -12553,7 +12600,7 @@
       <c r="L587" s="9"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="A588" s="32"/>
+      <c r="A588" s="33"/>
       <c r="B588" s="9"/>
       <c r="C588" s="9"/>
       <c r="D588" s="9"/>
@@ -12567,7 +12614,7 @@
       <c r="L588" s="9"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="A589" s="32"/>
+      <c r="A589" s="33"/>
       <c r="B589" s="9"/>
       <c r="C589" s="9"/>
       <c r="D589" s="9"/>
@@ -12581,7 +12628,7 @@
       <c r="L589" s="9"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="A590" s="32"/>
+      <c r="A590" s="33"/>
       <c r="B590" s="9"/>
       <c r="C590" s="9"/>
       <c r="D590" s="9"/>
@@ -12595,7 +12642,7 @@
       <c r="L590" s="9"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="A591" s="32"/>
+      <c r="A591" s="33"/>
       <c r="B591" s="9"/>
       <c r="C591" s="9"/>
       <c r="D591" s="9"/>
@@ -12609,7 +12656,7 @@
       <c r="L591" s="9"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="A592" s="32"/>
+      <c r="A592" s="33"/>
       <c r="B592" s="9"/>
       <c r="C592" s="9"/>
       <c r="D592" s="9"/>
@@ -12623,7 +12670,7 @@
       <c r="L592" s="9"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="A593" s="32"/>
+      <c r="A593" s="33"/>
       <c r="B593" s="9"/>
       <c r="C593" s="9"/>
       <c r="D593" s="9"/>
@@ -12637,7 +12684,7 @@
       <c r="L593" s="9"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="A594" s="32"/>
+      <c r="A594" s="33"/>
       <c r="B594" s="9"/>
       <c r="C594" s="9"/>
       <c r="D594" s="9"/>
@@ -12651,7 +12698,7 @@
       <c r="L594" s="9"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="A595" s="32"/>
+      <c r="A595" s="33"/>
       <c r="B595" s="9"/>
       <c r="C595" s="9"/>
       <c r="D595" s="9"/>
@@ -12665,7 +12712,7 @@
       <c r="L595" s="9"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="A596" s="32"/>
+      <c r="A596" s="33"/>
       <c r="B596" s="9"/>
       <c r="C596" s="9"/>
       <c r="D596" s="9"/>
@@ -12679,7 +12726,7 @@
       <c r="L596" s="9"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="A597" s="32"/>
+      <c r="A597" s="33"/>
       <c r="B597" s="9"/>
       <c r="C597" s="9"/>
       <c r="D597" s="9"/>
@@ -12693,7 +12740,7 @@
       <c r="L597" s="9"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="A598" s="32"/>
+      <c r="A598" s="33"/>
       <c r="B598" s="9"/>
       <c r="C598" s="9"/>
       <c r="D598" s="9"/>
@@ -12707,7 +12754,7 @@
       <c r="L598" s="9"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="A599" s="32"/>
+      <c r="A599" s="33"/>
       <c r="B599" s="9"/>
       <c r="C599" s="9"/>
       <c r="D599" s="9"/>
@@ -12721,7 +12768,7 @@
       <c r="L599" s="9"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="A600" s="32"/>
+      <c r="A600" s="33"/>
       <c r="B600" s="9"/>
       <c r="C600" s="9"/>
       <c r="D600" s="9"/>
@@ -12735,7 +12782,7 @@
       <c r="L600" s="9"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="A601" s="32"/>
+      <c r="A601" s="33"/>
       <c r="B601" s="9"/>
       <c r="C601" s="9"/>
       <c r="D601" s="9"/>
@@ -12749,7 +12796,7 @@
       <c r="L601" s="9"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="A602" s="32"/>
+      <c r="A602" s="33"/>
       <c r="B602" s="9"/>
       <c r="C602" s="9"/>
       <c r="D602" s="9"/>
@@ -12763,7 +12810,7 @@
       <c r="L602" s="9"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="A603" s="32"/>
+      <c r="A603" s="33"/>
       <c r="B603" s="9"/>
       <c r="C603" s="9"/>
       <c r="D603" s="9"/>
@@ -12777,7 +12824,7 @@
       <c r="L603" s="9"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="A604" s="32"/>
+      <c r="A604" s="33"/>
       <c r="B604" s="9"/>
       <c r="C604" s="9"/>
       <c r="D604" s="9"/>
@@ -12791,7 +12838,7 @@
       <c r="L604" s="9"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="A605" s="32"/>
+      <c r="A605" s="33"/>
       <c r="B605" s="9"/>
       <c r="C605" s="9"/>
       <c r="D605" s="9"/>
@@ -12805,7 +12852,7 @@
       <c r="L605" s="9"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="A606" s="32"/>
+      <c r="A606" s="33"/>
       <c r="B606" s="9"/>
       <c r="C606" s="9"/>
       <c r="D606" s="9"/>
@@ -12819,7 +12866,7 @@
       <c r="L606" s="9"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="A607" s="32"/>
+      <c r="A607" s="33"/>
       <c r="B607" s="9"/>
       <c r="C607" s="9"/>
       <c r="D607" s="9"/>
@@ -12833,7 +12880,7 @@
       <c r="L607" s="9"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="A608" s="32"/>
+      <c r="A608" s="33"/>
       <c r="B608" s="9"/>
       <c r="C608" s="9"/>
       <c r="D608" s="9"/>
@@ -12847,7 +12894,7 @@
       <c r="L608" s="9"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="A609" s="32"/>
+      <c r="A609" s="33"/>
       <c r="B609" s="9"/>
       <c r="C609" s="9"/>
       <c r="D609" s="9"/>
@@ -12861,7 +12908,7 @@
       <c r="L609" s="9"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="A610" s="32"/>
+      <c r="A610" s="33"/>
       <c r="B610" s="9"/>
       <c r="C610" s="9"/>
       <c r="D610" s="9"/>
@@ -12875,7 +12922,7 @@
       <c r="L610" s="9"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="A611" s="32"/>
+      <c r="A611" s="33"/>
       <c r="B611" s="9"/>
       <c r="C611" s="9"/>
       <c r="D611" s="9"/>
@@ -12889,7 +12936,7 @@
       <c r="L611" s="9"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="A612" s="32"/>
+      <c r="A612" s="33"/>
       <c r="B612" s="9"/>
       <c r="C612" s="9"/>
       <c r="D612" s="9"/>
@@ -12903,7 +12950,7 @@
       <c r="L612" s="9"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="A613" s="32"/>
+      <c r="A613" s="33"/>
       <c r="B613" s="9"/>
       <c r="C613" s="9"/>
       <c r="D613" s="9"/>
@@ -12917,7 +12964,7 @@
       <c r="L613" s="9"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="A614" s="32"/>
+      <c r="A614" s="33"/>
       <c r="B614" s="9"/>
       <c r="C614" s="9"/>
       <c r="D614" s="9"/>
@@ -12931,7 +12978,7 @@
       <c r="L614" s="9"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="A615" s="32"/>
+      <c r="A615" s="33"/>
       <c r="B615" s="9"/>
       <c r="C615" s="9"/>
       <c r="D615" s="9"/>
@@ -12945,7 +12992,7 @@
       <c r="L615" s="9"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="A616" s="32"/>
+      <c r="A616" s="33"/>
       <c r="B616" s="9"/>
       <c r="C616" s="9"/>
       <c r="D616" s="9"/>
@@ -12959,7 +13006,7 @@
       <c r="L616" s="9"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="A617" s="32"/>
+      <c r="A617" s="33"/>
       <c r="B617" s="9"/>
       <c r="C617" s="9"/>
       <c r="D617" s="9"/>
@@ -12973,7 +13020,7 @@
       <c r="L617" s="9"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="A618" s="32"/>
+      <c r="A618" s="33"/>
       <c r="B618" s="9"/>
       <c r="C618" s="9"/>
       <c r="D618" s="9"/>
@@ -12987,7 +13034,7 @@
       <c r="L618" s="9"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="A619" s="32"/>
+      <c r="A619" s="33"/>
       <c r="B619" s="9"/>
       <c r="C619" s="9"/>
       <c r="D619" s="9"/>
@@ -13001,7 +13048,7 @@
       <c r="L619" s="9"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="A620" s="32"/>
+      <c r="A620" s="33"/>
       <c r="B620" s="9"/>
       <c r="C620" s="9"/>
       <c r="D620" s="9"/>
@@ -13015,7 +13062,7 @@
       <c r="L620" s="9"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="A621" s="32"/>
+      <c r="A621" s="33"/>
       <c r="B621" s="9"/>
       <c r="C621" s="9"/>
       <c r="D621" s="9"/>
@@ -13029,7 +13076,7 @@
       <c r="L621" s="9"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="A622" s="32"/>
+      <c r="A622" s="33"/>
       <c r="B622" s="9"/>
       <c r="C622" s="9"/>
       <c r="D622" s="9"/>
@@ -13043,7 +13090,7 @@
       <c r="L622" s="9"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="A623" s="32"/>
+      <c r="A623" s="33"/>
       <c r="B623" s="9"/>
       <c r="C623" s="9"/>
       <c r="D623" s="9"/>
@@ -13057,7 +13104,7 @@
       <c r="L623" s="9"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="A624" s="32"/>
+      <c r="A624" s="33"/>
       <c r="B624" s="9"/>
       <c r="C624" s="9"/>
       <c r="D624" s="9"/>
@@ -13071,7 +13118,7 @@
       <c r="L624" s="9"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="A625" s="32"/>
+      <c r="A625" s="33"/>
       <c r="B625" s="9"/>
       <c r="C625" s="9"/>
       <c r="D625" s="9"/>
@@ -13085,7 +13132,7 @@
       <c r="L625" s="9"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="A626" s="32"/>
+      <c r="A626" s="33"/>
       <c r="B626" s="9"/>
       <c r="C626" s="9"/>
       <c r="D626" s="9"/>
@@ -13099,7 +13146,7 @@
       <c r="L626" s="9"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="A627" s="32"/>
+      <c r="A627" s="33"/>
       <c r="B627" s="9"/>
       <c r="C627" s="9"/>
       <c r="D627" s="9"/>
@@ -13113,7 +13160,7 @@
       <c r="L627" s="9"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="A628" s="32"/>
+      <c r="A628" s="33"/>
       <c r="B628" s="9"/>
       <c r="C628" s="9"/>
       <c r="D628" s="9"/>
@@ -13127,7 +13174,7 @@
       <c r="L628" s="9"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="A629" s="32"/>
+      <c r="A629" s="33"/>
       <c r="B629" s="9"/>
       <c r="C629" s="9"/>
       <c r="D629" s="9"/>
@@ -13141,7 +13188,7 @@
       <c r="L629" s="9"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="A630" s="32"/>
+      <c r="A630" s="33"/>
       <c r="B630" s="9"/>
       <c r="C630" s="9"/>
       <c r="D630" s="9"/>
@@ -13155,7 +13202,7 @@
       <c r="L630" s="9"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="A631" s="32"/>
+      <c r="A631" s="33"/>
       <c r="B631" s="9"/>
       <c r="C631" s="9"/>
       <c r="D631" s="9"/>
@@ -13169,7 +13216,7 @@
       <c r="L631" s="9"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="A632" s="32"/>
+      <c r="A632" s="33"/>
       <c r="B632" s="9"/>
       <c r="C632" s="9"/>
       <c r="D632" s="9"/>
@@ -13183,7 +13230,7 @@
       <c r="L632" s="9"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="A633" s="32"/>
+      <c r="A633" s="33"/>
       <c r="B633" s="9"/>
       <c r="C633" s="9"/>
       <c r="D633" s="9"/>
@@ -13197,7 +13244,7 @@
       <c r="L633" s="9"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="A634" s="32"/>
+      <c r="A634" s="33"/>
       <c r="B634" s="9"/>
       <c r="C634" s="9"/>
       <c r="D634" s="9"/>
@@ -13211,7 +13258,7 @@
       <c r="L634" s="9"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="A635" s="32"/>
+      <c r="A635" s="33"/>
       <c r="B635" s="9"/>
       <c r="C635" s="9"/>
       <c r="D635" s="9"/>
@@ -13225,7 +13272,7 @@
       <c r="L635" s="9"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="A636" s="32"/>
+      <c r="A636" s="33"/>
       <c r="B636" s="9"/>
       <c r="C636" s="9"/>
       <c r="D636" s="9"/>
@@ -13239,7 +13286,7 @@
       <c r="L636" s="9"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="A637" s="32"/>
+      <c r="A637" s="33"/>
       <c r="B637" s="9"/>
       <c r="C637" s="9"/>
       <c r="D637" s="9"/>
@@ -13253,7 +13300,7 @@
       <c r="L637" s="9"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="A638" s="32"/>
+      <c r="A638" s="33"/>
       <c r="B638" s="9"/>
       <c r="C638" s="9"/>
       <c r="D638" s="9"/>
@@ -13267,7 +13314,7 @@
       <c r="L638" s="9"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="A639" s="32"/>
+      <c r="A639" s="33"/>
       <c r="B639" s="9"/>
       <c r="C639" s="9"/>
       <c r="D639" s="9"/>
@@ -13281,7 +13328,7 @@
       <c r="L639" s="9"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="A640" s="32"/>
+      <c r="A640" s="33"/>
       <c r="B640" s="9"/>
       <c r="C640" s="9"/>
       <c r="D640" s="9"/>
@@ -13295,7 +13342,7 @@
       <c r="L640" s="9"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="A641" s="32"/>
+      <c r="A641" s="33"/>
       <c r="B641" s="9"/>
       <c r="C641" s="9"/>
       <c r="D641" s="9"/>
@@ -13309,7 +13356,7 @@
       <c r="L641" s="9"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="A642" s="32"/>
+      <c r="A642" s="33"/>
       <c r="B642" s="9"/>
       <c r="C642" s="9"/>
       <c r="D642" s="9"/>
@@ -13323,7 +13370,7 @@
       <c r="L642" s="9"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="A643" s="32"/>
+      <c r="A643" s="33"/>
       <c r="B643" s="9"/>
       <c r="C643" s="9"/>
       <c r="D643" s="9"/>
@@ -13337,7 +13384,7 @@
       <c r="L643" s="9"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="A644" s="32"/>
+      <c r="A644" s="33"/>
       <c r="B644" s="9"/>
       <c r="C644" s="9"/>
       <c r="D644" s="9"/>
@@ -13351,7 +13398,7 @@
       <c r="L644" s="9"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="A645" s="32"/>
+      <c r="A645" s="33"/>
       <c r="B645" s="9"/>
       <c r="C645" s="9"/>
       <c r="D645" s="9"/>
@@ -13365,7 +13412,7 @@
       <c r="L645" s="9"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="A646" s="32"/>
+      <c r="A646" s="33"/>
       <c r="B646" s="9"/>
       <c r="C646" s="9"/>
       <c r="D646" s="9"/>
@@ -13379,7 +13426,7 @@
       <c r="L646" s="9"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="A647" s="32"/>
+      <c r="A647" s="33"/>
       <c r="B647" s="9"/>
       <c r="C647" s="9"/>
       <c r="D647" s="9"/>
@@ -13393,7 +13440,7 @@
       <c r="L647" s="9"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="A648" s="32"/>
+      <c r="A648" s="33"/>
       <c r="B648" s="9"/>
       <c r="C648" s="9"/>
       <c r="D648" s="9"/>
@@ -13407,7 +13454,7 @@
       <c r="L648" s="9"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="A649" s="32"/>
+      <c r="A649" s="33"/>
       <c r="B649" s="9"/>
       <c r="C649" s="9"/>
       <c r="D649" s="9"/>
@@ -13421,7 +13468,7 @@
       <c r="L649" s="9"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="A650" s="32"/>
+      <c r="A650" s="33"/>
       <c r="B650" s="9"/>
       <c r="C650" s="9"/>
       <c r="D650" s="9"/>
@@ -13435,7 +13482,7 @@
       <c r="L650" s="9"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="A651" s="32"/>
+      <c r="A651" s="33"/>
       <c r="B651" s="9"/>
       <c r="C651" s="9"/>
       <c r="D651" s="9"/>
@@ -13449,7 +13496,7 @@
       <c r="L651" s="9"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="A652" s="32"/>
+      <c r="A652" s="33"/>
       <c r="B652" s="9"/>
       <c r="C652" s="9"/>
       <c r="D652" s="9"/>
@@ -13463,7 +13510,7 @@
       <c r="L652" s="9"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="A653" s="32"/>
+      <c r="A653" s="33"/>
       <c r="B653" s="9"/>
       <c r="C653" s="9"/>
       <c r="D653" s="9"/>
@@ -13477,7 +13524,7 @@
       <c r="L653" s="9"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="A654" s="32"/>
+      <c r="A654" s="33"/>
       <c r="B654" s="9"/>
       <c r="C654" s="9"/>
       <c r="D654" s="9"/>
@@ -13491,7 +13538,7 @@
       <c r="L654" s="9"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="A655" s="32"/>
+      <c r="A655" s="33"/>
       <c r="B655" s="9"/>
       <c r="C655" s="9"/>
       <c r="D655" s="9"/>
@@ -13505,7 +13552,7 @@
       <c r="L655" s="9"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="A656" s="32"/>
+      <c r="A656" s="33"/>
       <c r="B656" s="9"/>
       <c r="C656" s="9"/>
       <c r="D656" s="9"/>
@@ -13519,7 +13566,7 @@
       <c r="L656" s="9"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="A657" s="32"/>
+      <c r="A657" s="33"/>
       <c r="B657" s="9"/>
       <c r="C657" s="9"/>
       <c r="D657" s="9"/>
@@ -13533,7 +13580,7 @@
       <c r="L657" s="9"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="A658" s="32"/>
+      <c r="A658" s="33"/>
       <c r="B658" s="9"/>
       <c r="C658" s="9"/>
       <c r="D658" s="9"/>
@@ -13547,7 +13594,7 @@
       <c r="L658" s="9"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="A659" s="32"/>
+      <c r="A659" s="33"/>
       <c r="B659" s="9"/>
       <c r="C659" s="9"/>
       <c r="D659" s="9"/>
@@ -13561,7 +13608,7 @@
       <c r="L659" s="9"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="A660" s="32"/>
+      <c r="A660" s="33"/>
       <c r="B660" s="9"/>
       <c r="C660" s="9"/>
       <c r="D660" s="9"/>
@@ -13575,7 +13622,7 @@
       <c r="L660" s="9"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="A661" s="32"/>
+      <c r="A661" s="33"/>
       <c r="B661" s="9"/>
       <c r="C661" s="9"/>
       <c r="D661" s="9"/>
@@ -13589,7 +13636,7 @@
       <c r="L661" s="9"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="A662" s="32"/>
+      <c r="A662" s="33"/>
       <c r="B662" s="9"/>
       <c r="C662" s="9"/>
       <c r="D662" s="9"/>
@@ -13603,7 +13650,7 @@
       <c r="L662" s="9"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="A663" s="32"/>
+      <c r="A663" s="33"/>
       <c r="B663" s="9"/>
       <c r="C663" s="9"/>
       <c r="D663" s="9"/>
@@ -13617,7 +13664,7 @@
       <c r="L663" s="9"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="A664" s="32"/>
+      <c r="A664" s="33"/>
       <c r="B664" s="9"/>
       <c r="C664" s="9"/>
       <c r="D664" s="9"/>
@@ -13631,7 +13678,7 @@
       <c r="L664" s="9"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="A665" s="32"/>
+      <c r="A665" s="33"/>
       <c r="B665" s="9"/>
       <c r="C665" s="9"/>
       <c r="D665" s="9"/>
@@ -13645,7 +13692,7 @@
       <c r="L665" s="9"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="A666" s="32"/>
+      <c r="A666" s="33"/>
       <c r="B666" s="9"/>
       <c r="C666" s="9"/>
       <c r="D666" s="9"/>
@@ -13659,7 +13706,7 @@
       <c r="L666" s="9"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="A667" s="32"/>
+      <c r="A667" s="33"/>
       <c r="B667" s="9"/>
       <c r="C667" s="9"/>
       <c r="D667" s="9"/>
@@ -13673,7 +13720,7 @@
       <c r="L667" s="9"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="A668" s="32"/>
+      <c r="A668" s="33"/>
       <c r="B668" s="9"/>
       <c r="C668" s="9"/>
       <c r="D668" s="9"/>
@@ -13687,7 +13734,7 @@
       <c r="L668" s="9"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="A669" s="32"/>
+      <c r="A669" s="33"/>
       <c r="B669" s="9"/>
       <c r="C669" s="9"/>
       <c r="D669" s="9"/>
@@ -13701,7 +13748,7 @@
       <c r="L669" s="9"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="A670" s="32"/>
+      <c r="A670" s="33"/>
       <c r="B670" s="9"/>
       <c r="C670" s="9"/>
       <c r="D670" s="9"/>
@@ -13715,7 +13762,7 @@
       <c r="L670" s="9"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="A671" s="32"/>
+      <c r="A671" s="33"/>
       <c r="B671" s="9"/>
       <c r="C671" s="9"/>
       <c r="D671" s="9"/>
@@ -13729,7 +13776,7 @@
       <c r="L671" s="9"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="A672" s="32"/>
+      <c r="A672" s="33"/>
       <c r="B672" s="9"/>
       <c r="C672" s="9"/>
       <c r="D672" s="9"/>
@@ -13743,7 +13790,7 @@
       <c r="L672" s="9"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="A673" s="32"/>
+      <c r="A673" s="33"/>
       <c r="B673" s="9"/>
       <c r="C673" s="9"/>
       <c r="D673" s="9"/>
@@ -13757,7 +13804,7 @@
       <c r="L673" s="9"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="A674" s="32"/>
+      <c r="A674" s="33"/>
       <c r="B674" s="9"/>
       <c r="C674" s="9"/>
       <c r="D674" s="9"/>
@@ -13771,7 +13818,7 @@
       <c r="L674" s="9"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="A675" s="32"/>
+      <c r="A675" s="33"/>
       <c r="B675" s="9"/>
       <c r="C675" s="9"/>
       <c r="D675" s="9"/>
@@ -13785,7 +13832,7 @@
       <c r="L675" s="9"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="A676" s="32"/>
+      <c r="A676" s="33"/>
       <c r="B676" s="9"/>
       <c r="C676" s="9"/>
       <c r="D676" s="9"/>
@@ -13799,7 +13846,7 @@
       <c r="L676" s="9"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="A677" s="32"/>
+      <c r="A677" s="33"/>
       <c r="B677" s="9"/>
       <c r="C677" s="9"/>
       <c r="D677" s="9"/>
@@ -13813,7 +13860,7 @@
       <c r="L677" s="9"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="A678" s="32"/>
+      <c r="A678" s="33"/>
       <c r="B678" s="9"/>
       <c r="C678" s="9"/>
       <c r="D678" s="9"/>
@@ -13827,7 +13874,7 @@
       <c r="L678" s="9"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="A679" s="32"/>
+      <c r="A679" s="33"/>
       <c r="B679" s="9"/>
       <c r="C679" s="9"/>
       <c r="D679" s="9"/>
@@ -13841,7 +13888,7 @@
       <c r="L679" s="9"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="A680" s="32"/>
+      <c r="A680" s="33"/>
       <c r="B680" s="9"/>
       <c r="C680" s="9"/>
       <c r="D680" s="9"/>
@@ -13855,7 +13902,7 @@
       <c r="L680" s="9"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="A681" s="32"/>
+      <c r="A681" s="33"/>
       <c r="B681" s="9"/>
       <c r="C681" s="9"/>
       <c r="D681" s="9"/>
@@ -13869,7 +13916,7 @@
       <c r="L681" s="9"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="A682" s="32"/>
+      <c r="A682" s="33"/>
       <c r="B682" s="9"/>
       <c r="C682" s="9"/>
       <c r="D682" s="9"/>
@@ -13883,7 +13930,7 @@
       <c r="L682" s="9"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="A683" s="32"/>
+      <c r="A683" s="33"/>
       <c r="B683" s="9"/>
       <c r="C683" s="9"/>
       <c r="D683" s="9"/>
@@ -13897,7 +13944,7 @@
       <c r="L683" s="9"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="A684" s="32"/>
+      <c r="A684" s="33"/>
       <c r="B684" s="9"/>
       <c r="C684" s="9"/>
       <c r="D684" s="9"/>
@@ -13911,7 +13958,7 @@
       <c r="L684" s="9"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="A685" s="32"/>
+      <c r="A685" s="33"/>
       <c r="B685" s="9"/>
       <c r="C685" s="9"/>
       <c r="D685" s="9"/>
@@ -13925,7 +13972,7 @@
       <c r="L685" s="9"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="A686" s="32"/>
+      <c r="A686" s="33"/>
       <c r="B686" s="9"/>
       <c r="C686" s="9"/>
       <c r="D686" s="9"/>
@@ -13939,7 +13986,7 @@
       <c r="L686" s="9"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="A687" s="32"/>
+      <c r="A687" s="33"/>
       <c r="B687" s="9"/>
       <c r="C687" s="9"/>
       <c r="D687" s="9"/>
@@ -13953,7 +14000,7 @@
       <c r="L687" s="9"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="A688" s="32"/>
+      <c r="A688" s="33"/>
       <c r="B688" s="9"/>
       <c r="C688" s="9"/>
       <c r="D688" s="9"/>
@@ -13967,7 +14014,7 @@
       <c r="L688" s="9"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="A689" s="32"/>
+      <c r="A689" s="33"/>
       <c r="B689" s="9"/>
       <c r="C689" s="9"/>
       <c r="D689" s="9"/>
@@ -13981,7 +14028,7 @@
       <c r="L689" s="9"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="A690" s="32"/>
+      <c r="A690" s="33"/>
       <c r="B690" s="9"/>
       <c r="C690" s="9"/>
       <c r="D690" s="9"/>
@@ -13995,7 +14042,7 @@
       <c r="L690" s="9"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="A691" s="32"/>
+      <c r="A691" s="33"/>
       <c r="B691" s="9"/>
       <c r="C691" s="9"/>
       <c r="D691" s="9"/>
@@ -14009,7 +14056,7 @@
       <c r="L691" s="9"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="A692" s="32"/>
+      <c r="A692" s="33"/>
       <c r="B692" s="9"/>
       <c r="C692" s="9"/>
       <c r="D692" s="9"/>
@@ -14023,7 +14070,7 @@
       <c r="L692" s="9"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="A693" s="32"/>
+      <c r="A693" s="33"/>
       <c r="B693" s="9"/>
       <c r="C693" s="9"/>
       <c r="D693" s="9"/>
@@ -14037,7 +14084,7 @@
       <c r="L693" s="9"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="A694" s="32"/>
+      <c r="A694" s="33"/>
       <c r="B694" s="9"/>
       <c r="C694" s="9"/>
       <c r="D694" s="9"/>
@@ -14051,7 +14098,7 @@
       <c r="L694" s="9"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="A695" s="32"/>
+      <c r="A695" s="33"/>
       <c r="B695" s="9"/>
       <c r="C695" s="9"/>
       <c r="D695" s="9"/>
@@ -14065,7 +14112,7 @@
       <c r="L695" s="9"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="A696" s="32"/>
+      <c r="A696" s="33"/>
       <c r="B696" s="9"/>
       <c r="C696" s="9"/>
       <c r="D696" s="9"/>
@@ -14079,7 +14126,7 @@
       <c r="L696" s="9"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="A697" s="32"/>
+      <c r="A697" s="33"/>
       <c r="B697" s="9"/>
       <c r="C697" s="9"/>
       <c r="D697" s="9"/>
@@ -14093,7 +14140,7 @@
       <c r="L697" s="9"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="A698" s="32"/>
+      <c r="A698" s="33"/>
       <c r="B698" s="9"/>
       <c r="C698" s="9"/>
       <c r="D698" s="9"/>
@@ -14107,7 +14154,7 @@
       <c r="L698" s="9"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="A699" s="32"/>
+      <c r="A699" s="33"/>
       <c r="B699" s="9"/>
       <c r="C699" s="9"/>
       <c r="D699" s="9"/>
@@ -14121,7 +14168,7 @@
       <c r="L699" s="9"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="A700" s="32"/>
+      <c r="A700" s="33"/>
       <c r="B700" s="9"/>
       <c r="C700" s="9"/>
       <c r="D700" s="9"/>
@@ -14135,7 +14182,7 @@
       <c r="L700" s="9"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="A701" s="32"/>
+      <c r="A701" s="33"/>
       <c r="B701" s="9"/>
       <c r="C701" s="9"/>
       <c r="D701" s="9"/>
@@ -14149,7 +14196,7 @@
       <c r="L701" s="9"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="A702" s="32"/>
+      <c r="A702" s="33"/>
       <c r="B702" s="9"/>
       <c r="C702" s="9"/>
       <c r="D702" s="9"/>
@@ -14163,7 +14210,7 @@
       <c r="L702" s="9"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="A703" s="32"/>
+      <c r="A703" s="33"/>
       <c r="B703" s="9"/>
       <c r="C703" s="9"/>
       <c r="D703" s="9"/>
@@ -14177,7 +14224,7 @@
       <c r="L703" s="9"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="A704" s="32"/>
+      <c r="A704" s="33"/>
       <c r="B704" s="9"/>
       <c r="C704" s="9"/>
       <c r="D704" s="9"/>
@@ -14191,7 +14238,7 @@
       <c r="L704" s="9"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="A705" s="32"/>
+      <c r="A705" s="33"/>
       <c r="B705" s="9"/>
       <c r="C705" s="9"/>
       <c r="D705" s="9"/>
@@ -14205,7 +14252,7 @@
       <c r="L705" s="9"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="A706" s="32"/>
+      <c r="A706" s="33"/>
       <c r="B706" s="9"/>
       <c r="C706" s="9"/>
       <c r="D706" s="9"/>
@@ -14219,7 +14266,7 @@
       <c r="L706" s="9"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="A707" s="32"/>
+      <c r="A707" s="33"/>
       <c r="B707" s="9"/>
       <c r="C707" s="9"/>
       <c r="D707" s="9"/>
@@ -14233,7 +14280,7 @@
       <c r="L707" s="9"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="A708" s="32"/>
+      <c r="A708" s="33"/>
       <c r="B708" s="9"/>
       <c r="C708" s="9"/>
       <c r="D708" s="9"/>
@@ -14247,7 +14294,7 @@
       <c r="L708" s="9"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="A709" s="32"/>
+      <c r="A709" s="33"/>
       <c r="B709" s="9"/>
       <c r="C709" s="9"/>
       <c r="D709" s="9"/>
@@ -14261,7 +14308,7 @@
       <c r="L709" s="9"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="A710" s="32"/>
+      <c r="A710" s="33"/>
       <c r="B710" s="9"/>
       <c r="C710" s="9"/>
       <c r="D710" s="9"/>
@@ -14275,7 +14322,7 @@
       <c r="L710" s="9"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="A711" s="32"/>
+      <c r="A711" s="33"/>
       <c r="B711" s="9"/>
       <c r="C711" s="9"/>
       <c r="D711" s="9"/>
@@ -14289,7 +14336,7 @@
       <c r="L711" s="9"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="A712" s="32"/>
+      <c r="A712" s="33"/>
       <c r="B712" s="9"/>
       <c r="C712" s="9"/>
       <c r="D712" s="9"/>
@@ -14303,7 +14350,7 @@
       <c r="L712" s="9"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="A713" s="32"/>
+      <c r="A713" s="33"/>
       <c r="B713" s="9"/>
       <c r="C713" s="9"/>
       <c r="D713" s="9"/>
@@ -14317,7 +14364,7 @@
       <c r="L713" s="9"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="A714" s="32"/>
+      <c r="A714" s="33"/>
       <c r="B714" s="9"/>
       <c r="C714" s="9"/>
       <c r="D714" s="9"/>
@@ -14331,7 +14378,7 @@
       <c r="L714" s="9"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="A715" s="32"/>
+      <c r="A715" s="33"/>
       <c r="B715" s="9"/>
       <c r="C715" s="9"/>
       <c r="D715" s="9"/>
@@ -14345,7 +14392,7 @@
       <c r="L715" s="9"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="A716" s="32"/>
+      <c r="A716" s="33"/>
       <c r="B716" s="9"/>
       <c r="C716" s="9"/>
       <c r="D716" s="9"/>
@@ -14359,7 +14406,7 @@
       <c r="L716" s="9"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="A717" s="32"/>
+      <c r="A717" s="33"/>
       <c r="B717" s="9"/>
       <c r="C717" s="9"/>
       <c r="D717" s="9"/>
@@ -14373,7 +14420,7 @@
       <c r="L717" s="9"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="A718" s="32"/>
+      <c r="A718" s="33"/>
       <c r="B718" s="9"/>
       <c r="C718" s="9"/>
       <c r="D718" s="9"/>
@@ -14387,7 +14434,7 @@
       <c r="L718" s="9"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="A719" s="32"/>
+      <c r="A719" s="33"/>
       <c r="B719" s="9"/>
       <c r="C719" s="9"/>
       <c r="D719" s="9"/>
@@ -14401,7 +14448,7 @@
       <c r="L719" s="9"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="A720" s="32"/>
+      <c r="A720" s="33"/>
       <c r="B720" s="9"/>
       <c r="C720" s="9"/>
       <c r="D720" s="9"/>
@@ -14415,7 +14462,7 @@
       <c r="L720" s="9"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="A721" s="32"/>
+      <c r="A721" s="33"/>
       <c r="B721" s="9"/>
       <c r="C721" s="9"/>
       <c r="D721" s="9"/>
@@ -14429,7 +14476,7 @@
       <c r="L721" s="9"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="A722" s="32"/>
+      <c r="A722" s="33"/>
       <c r="B722" s="9"/>
       <c r="C722" s="9"/>
       <c r="D722" s="9"/>
@@ -14443,7 +14490,7 @@
       <c r="L722" s="9"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="A723" s="32"/>
+      <c r="A723" s="33"/>
       <c r="B723" s="9"/>
       <c r="C723" s="9"/>
       <c r="D723" s="9"/>
@@ -14457,7 +14504,7 @@
       <c r="L723" s="9"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="A724" s="32"/>
+      <c r="A724" s="33"/>
       <c r="B724" s="9"/>
       <c r="C724" s="9"/>
       <c r="D724" s="9"/>
@@ -14471,7 +14518,7 @@
       <c r="L724" s="9"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="A725" s="32"/>
+      <c r="A725" s="33"/>
       <c r="B725" s="9"/>
       <c r="C725" s="9"/>
       <c r="D725" s="9"/>
@@ -14485,7 +14532,7 @@
       <c r="L725" s="9"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="A726" s="32"/>
+      <c r="A726" s="33"/>
       <c r="B726" s="9"/>
       <c r="C726" s="9"/>
       <c r="D726" s="9"/>
@@ -14499,7 +14546,7 @@
       <c r="L726" s="9"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="A727" s="32"/>
+      <c r="A727" s="33"/>
       <c r="B727" s="9"/>
       <c r="C727" s="9"/>
       <c r="D727" s="9"/>
@@ -14513,7 +14560,7 @@
       <c r="L727" s="9"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="A728" s="32"/>
+      <c r="A728" s="33"/>
       <c r="B728" s="9"/>
       <c r="C728" s="9"/>
       <c r="D728" s="9"/>
@@ -14527,7 +14574,7 @@
       <c r="L728" s="9"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="A729" s="32"/>
+      <c r="A729" s="33"/>
       <c r="B729" s="9"/>
       <c r="C729" s="9"/>
       <c r="D729" s="9"/>
@@ -14541,7 +14588,7 @@
       <c r="L729" s="9"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="A730" s="32"/>
+      <c r="A730" s="33"/>
       <c r="B730" s="9"/>
       <c r="C730" s="9"/>
       <c r="D730" s="9"/>
@@ -14555,7 +14602,7 @@
       <c r="L730" s="9"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="A731" s="32"/>
+      <c r="A731" s="33"/>
       <c r="B731" s="9"/>
       <c r="C731" s="9"/>
       <c r="D731" s="9"/>
@@ -14569,7 +14616,7 @@
       <c r="L731" s="9"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="A732" s="32"/>
+      <c r="A732" s="33"/>
       <c r="B732" s="9"/>
       <c r="C732" s="9"/>
       <c r="D732" s="9"/>
@@ -14583,7 +14630,7 @@
       <c r="L732" s="9"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="A733" s="32"/>
+      <c r="A733" s="33"/>
       <c r="B733" s="9"/>
       <c r="C733" s="9"/>
       <c r="D733" s="9"/>
@@ -14597,7 +14644,7 @@
       <c r="L733" s="9"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="A734" s="32"/>
+      <c r="A734" s="33"/>
       <c r="B734" s="9"/>
       <c r="C734" s="9"/>
       <c r="D734" s="9"/>
@@ -14611,7 +14658,7 @@
       <c r="L734" s="9"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="A735" s="32"/>
+      <c r="A735" s="33"/>
       <c r="B735" s="9"/>
       <c r="C735" s="9"/>
       <c r="D735" s="9"/>
@@ -14625,7 +14672,7 @@
       <c r="L735" s="9"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="A736" s="32"/>
+      <c r="A736" s="33"/>
       <c r="B736" s="9"/>
       <c r="C736" s="9"/>
       <c r="D736" s="9"/>
@@ -14639,7 +14686,7 @@
       <c r="L736" s="9"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="A737" s="32"/>
+      <c r="A737" s="33"/>
       <c r="B737" s="9"/>
       <c r="C737" s="9"/>
       <c r="D737" s="9"/>
@@ -14653,7 +14700,7 @@
       <c r="L737" s="9"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="A738" s="32"/>
+      <c r="A738" s="33"/>
       <c r="B738" s="9"/>
       <c r="C738" s="9"/>
       <c r="D738" s="9"/>
@@ -14667,7 +14714,7 @@
       <c r="L738" s="9"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="A739" s="32"/>
+      <c r="A739" s="33"/>
       <c r="B739" s="9"/>
       <c r="C739" s="9"/>
       <c r="D739" s="9"/>
@@ -14681,7 +14728,7 @@
       <c r="L739" s="9"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="A740" s="32"/>
+      <c r="A740" s="33"/>
       <c r="B740" s="9"/>
       <c r="C740" s="9"/>
       <c r="D740" s="9"/>
@@ -14695,7 +14742,7 @@
       <c r="L740" s="9"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="A741" s="32"/>
+      <c r="A741" s="33"/>
       <c r="B741" s="9"/>
       <c r="C741" s="9"/>
       <c r="D741" s="9"/>
@@ -14709,7 +14756,7 @@
       <c r="L741" s="9"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="A742" s="32"/>
+      <c r="A742" s="33"/>
       <c r="B742" s="9"/>
       <c r="C742" s="9"/>
       <c r="D742" s="9"/>
@@ -14723,7 +14770,7 @@
       <c r="L742" s="9"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="A743" s="32"/>
+      <c r="A743" s="33"/>
       <c r="B743" s="9"/>
       <c r="C743" s="9"/>
       <c r="D743" s="9"/>
@@ -14737,7 +14784,7 @@
       <c r="L743" s="9"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="A744" s="32"/>
+      <c r="A744" s="33"/>
       <c r="B744" s="9"/>
       <c r="C744" s="9"/>
       <c r="D744" s="9"/>
@@ -14751,7 +14798,7 @@
       <c r="L744" s="9"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="A745" s="32"/>
+      <c r="A745" s="33"/>
       <c r="B745" s="9"/>
       <c r="C745" s="9"/>
       <c r="D745" s="9"/>
@@ -14765,7 +14812,7 @@
       <c r="L745" s="9"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="A746" s="32"/>
+      <c r="A746" s="33"/>
       <c r="B746" s="9"/>
       <c r="C746" s="9"/>
       <c r="D746" s="9"/>
@@ -14779,7 +14826,7 @@
       <c r="L746" s="9"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="A747" s="32"/>
+      <c r="A747" s="33"/>
       <c r="B747" s="9"/>
       <c r="C747" s="9"/>
       <c r="D747" s="9"/>
@@ -14793,7 +14840,7 @@
       <c r="L747" s="9"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="A748" s="32"/>
+      <c r="A748" s="33"/>
       <c r="B748" s="9"/>
       <c r="C748" s="9"/>
       <c r="D748" s="9"/>
@@ -14807,7 +14854,7 @@
       <c r="L748" s="9"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="A749" s="32"/>
+      <c r="A749" s="33"/>
       <c r="B749" s="9"/>
       <c r="C749" s="9"/>
       <c r="D749" s="9"/>
@@ -14821,7 +14868,7 @@
       <c r="L749" s="9"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="A750" s="32"/>
+      <c r="A750" s="33"/>
       <c r="B750" s="9"/>
       <c r="C750" s="9"/>
       <c r="D750" s="9"/>
@@ -14835,7 +14882,7 @@
       <c r="L750" s="9"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="A751" s="32"/>
+      <c r="A751" s="33"/>
       <c r="B751" s="9"/>
       <c r="C751" s="9"/>
       <c r="D751" s="9"/>
@@ -14849,7 +14896,7 @@
       <c r="L751" s="9"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="A752" s="32"/>
+      <c r="A752" s="33"/>
       <c r="B752" s="9"/>
       <c r="C752" s="9"/>
       <c r="D752" s="9"/>
@@ -14863,7 +14910,7 @@
       <c r="L752" s="9"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="A753" s="32"/>
+      <c r="A753" s="33"/>
       <c r="B753" s="9"/>
       <c r="C753" s="9"/>
       <c r="D753" s="9"/>
@@ -14877,7 +14924,7 @@
       <c r="L753" s="9"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="A754" s="32"/>
+      <c r="A754" s="33"/>
       <c r="B754" s="9"/>
       <c r="C754" s="9"/>
       <c r="D754" s="9"/>
@@ -14891,7 +14938,7 @@
       <c r="L754" s="9"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="A755" s="32"/>
+      <c r="A755" s="33"/>
       <c r="B755" s="9"/>
       <c r="C755" s="9"/>
       <c r="D755" s="9"/>
@@ -14905,7 +14952,7 @@
       <c r="L755" s="9"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="A756" s="32"/>
+      <c r="A756" s="33"/>
       <c r="B756" s="9"/>
       <c r="C756" s="9"/>
       <c r="D756" s="9"/>
@@ -14919,7 +14966,7 @@
       <c r="L756" s="9"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="A757" s="32"/>
+      <c r="A757" s="33"/>
       <c r="B757" s="9"/>
       <c r="C757" s="9"/>
       <c r="D757" s="9"/>
@@ -14933,7 +14980,7 @@
       <c r="L757" s="9"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="A758" s="32"/>
+      <c r="A758" s="33"/>
       <c r="B758" s="9"/>
       <c r="C758" s="9"/>
       <c r="D758" s="9"/>
@@ -14947,7 +14994,7 @@
       <c r="L758" s="9"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="A759" s="32"/>
+      <c r="A759" s="33"/>
       <c r="B759" s="9"/>
       <c r="C759" s="9"/>
       <c r="D759" s="9"/>
@@ -14961,7 +15008,7 @@
       <c r="L759" s="9"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="A760" s="32"/>
+      <c r="A760" s="33"/>
       <c r="B760" s="9"/>
       <c r="C760" s="9"/>
       <c r="D760" s="9"/>
@@ -14975,7 +15022,7 @@
       <c r="L760" s="9"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="A761" s="32"/>
+      <c r="A761" s="33"/>
       <c r="B761" s="9"/>
       <c r="C761" s="9"/>
       <c r="D761" s="9"/>
@@ -14989,7 +15036,7 @@
       <c r="L761" s="9"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="A762" s="32"/>
+      <c r="A762" s="33"/>
       <c r="B762" s="9"/>
       <c r="C762" s="9"/>
       <c r="D762" s="9"/>
@@ -15003,7 +15050,7 @@
       <c r="L762" s="9"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="A763" s="32"/>
+      <c r="A763" s="33"/>
       <c r="B763" s="9"/>
       <c r="C763" s="9"/>
       <c r="D763" s="9"/>
@@ -15017,7 +15064,7 @@
       <c r="L763" s="9"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="A764" s="32"/>
+      <c r="A764" s="33"/>
       <c r="B764" s="9"/>
       <c r="C764" s="9"/>
       <c r="D764" s="9"/>
@@ -15031,7 +15078,7 @@
       <c r="L764" s="9"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="A765" s="32"/>
+      <c r="A765" s="33"/>
       <c r="B765" s="9"/>
       <c r="C765" s="9"/>
       <c r="D765" s="9"/>
@@ -15045,7 +15092,7 @@
       <c r="L765" s="9"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="A766" s="32"/>
+      <c r="A766" s="33"/>
       <c r="B766" s="9"/>
       <c r="C766" s="9"/>
       <c r="D766" s="9"/>
@@ -15059,7 +15106,7 @@
       <c r="L766" s="9"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="A767" s="32"/>
+      <c r="A767" s="33"/>
       <c r="B767" s="9"/>
       <c r="C767" s="9"/>
       <c r="D767" s="9"/>
@@ -15073,7 +15120,7 @@
       <c r="L767" s="9"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="A768" s="32"/>
+      <c r="A768" s="33"/>
       <c r="B768" s="9"/>
       <c r="C768" s="9"/>
       <c r="D768" s="9"/>
@@ -15087,7 +15134,7 @@
       <c r="L768" s="9"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="A769" s="32"/>
+      <c r="A769" s="33"/>
       <c r="B769" s="9"/>
       <c r="C769" s="9"/>
       <c r="D769" s="9"/>
@@ -15101,7 +15148,7 @@
       <c r="L769" s="9"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="A770" s="32"/>
+      <c r="A770" s="33"/>
       <c r="B770" s="9"/>
       <c r="C770" s="9"/>
       <c r="D770" s="9"/>
@@ -15115,7 +15162,7 @@
       <c r="L770" s="9"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="A771" s="32"/>
+      <c r="A771" s="33"/>
       <c r="B771" s="9"/>
       <c r="C771" s="9"/>
       <c r="D771" s="9"/>
@@ -15129,7 +15176,7 @@
       <c r="L771" s="9"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="A772" s="32"/>
+      <c r="A772" s="33"/>
       <c r="B772" s="9"/>
       <c r="C772" s="9"/>
       <c r="D772" s="9"/>
@@ -15143,7 +15190,7 @@
       <c r="L772" s="9"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="A773" s="32"/>
+      <c r="A773" s="33"/>
       <c r="B773" s="9"/>
       <c r="C773" s="9"/>
       <c r="D773" s="9"/>
@@ -15157,7 +15204,7 @@
       <c r="L773" s="9"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="A774" s="32"/>
+      <c r="A774" s="33"/>
       <c r="B774" s="9"/>
       <c r="C774" s="9"/>
       <c r="D774" s="9"/>
@@ -15171,7 +15218,7 @@
       <c r="L774" s="9"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="A775" s="32"/>
+      <c r="A775" s="33"/>
       <c r="B775" s="9"/>
       <c r="C775" s="9"/>
       <c r="D775" s="9"/>
@@ -15185,7 +15232,7 @@
       <c r="L775" s="9"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="A776" s="32"/>
+      <c r="A776" s="33"/>
       <c r="B776" s="9"/>
       <c r="C776" s="9"/>
       <c r="D776" s="9"/>
@@ -15199,7 +15246,7 @@
       <c r="L776" s="9"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="A777" s="32"/>
+      <c r="A777" s="33"/>
       <c r="B777" s="9"/>
       <c r="C777" s="9"/>
       <c r="D777" s="9"/>
@@ -15213,7 +15260,7 @@
       <c r="L777" s="9"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="A778" s="32"/>
+      <c r="A778" s="33"/>
       <c r="B778" s="9"/>
       <c r="C778" s="9"/>
       <c r="D778" s="9"/>
@@ -15227,7 +15274,7 @@
       <c r="L778" s="9"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="A779" s="32"/>
+      <c r="A779" s="33"/>
       <c r="B779" s="9"/>
       <c r="C779" s="9"/>
       <c r="D779" s="9"/>
@@ -15241,7 +15288,7 @@
       <c r="L779" s="9"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="A780" s="32"/>
+      <c r="A780" s="33"/>
       <c r="B780" s="9"/>
       <c r="C780" s="9"/>
       <c r="D780" s="9"/>
@@ -15255,7 +15302,7 @@
       <c r="L780" s="9"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="A781" s="32"/>
+      <c r="A781" s="33"/>
       <c r="B781" s="9"/>
       <c r="C781" s="9"/>
       <c r="D781" s="9"/>
@@ -15269,7 +15316,7 @@
       <c r="L781" s="9"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="A782" s="32"/>
+      <c r="A782" s="33"/>
       <c r="B782" s="9"/>
       <c r="C782" s="9"/>
       <c r="D782" s="9"/>
@@ -15283,7 +15330,7 @@
       <c r="L782" s="9"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="A783" s="32"/>
+      <c r="A783" s="33"/>
       <c r="B783" s="9"/>
       <c r="C783" s="9"/>
       <c r="D783" s="9"/>
@@ -15297,7 +15344,7 @@
       <c r="L783" s="9"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="A784" s="32"/>
+      <c r="A784" s="33"/>
       <c r="B784" s="9"/>
       <c r="C784" s="9"/>
       <c r="D784" s="9"/>
@@ -15311,7 +15358,7 @@
       <c r="L784" s="9"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="A785" s="32"/>
+      <c r="A785" s="33"/>
       <c r="B785" s="9"/>
       <c r="C785" s="9"/>
       <c r="D785" s="9"/>
@@ -15325,7 +15372,7 @@
       <c r="L785" s="9"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="A786" s="32"/>
+      <c r="A786" s="33"/>
       <c r="B786" s="9"/>
       <c r="C786" s="9"/>
       <c r="D786" s="9"/>
@@ -15339,7 +15386,7 @@
       <c r="L786" s="9"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="A787" s="32"/>
+      <c r="A787" s="33"/>
       <c r="B787" s="9"/>
       <c r="C787" s="9"/>
       <c r="D787" s="9"/>
@@ -15353,7 +15400,7 @@
       <c r="L787" s="9"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="A788" s="32"/>
+      <c r="A788" s="33"/>
       <c r="B788" s="9"/>
       <c r="C788" s="9"/>
       <c r="D788" s="9"/>
@@ -15367,7 +15414,7 @@
       <c r="L788" s="9"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="A789" s="32"/>
+      <c r="A789" s="33"/>
       <c r="B789" s="9"/>
       <c r="C789" s="9"/>
       <c r="D789" s="9"/>
@@ -15381,7 +15428,7 @@
       <c r="L789" s="9"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="A790" s="32"/>
+      <c r="A790" s="33"/>
       <c r="B790" s="9"/>
       <c r="C790" s="9"/>
       <c r="D790" s="9"/>
@@ -15395,7 +15442,7 @@
       <c r="L790" s="9"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="A791" s="32"/>
+      <c r="A791" s="33"/>
       <c r="B791" s="9"/>
       <c r="C791" s="9"/>
       <c r="D791" s="9"/>
@@ -15409,7 +15456,7 @@
       <c r="L791" s="9"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="A792" s="32"/>
+      <c r="A792" s="33"/>
       <c r="B792" s="9"/>
       <c r="C792" s="9"/>
       <c r="D792" s="9"/>
@@ -15423,7 +15470,7 @@
       <c r="L792" s="9"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="A793" s="32"/>
+      <c r="A793" s="33"/>
       <c r="B793" s="9"/>
       <c r="C793" s="9"/>
       <c r="D793" s="9"/>
@@ -15437,7 +15484,7 @@
       <c r="L793" s="9"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="A794" s="32"/>
+      <c r="A794" s="33"/>
       <c r="B794" s="9"/>
       <c r="C794" s="9"/>
       <c r="D794" s="9"/>
@@ -15451,7 +15498,7 @@
       <c r="L794" s="9"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="A795" s="32"/>
+      <c r="A795" s="33"/>
       <c r="B795" s="9"/>
       <c r="C795" s="9"/>
       <c r="D795" s="9"/>
@@ -15465,7 +15512,7 @@
       <c r="L795" s="9"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="A796" s="32"/>
+      <c r="A796" s="33"/>
       <c r="B796" s="9"/>
       <c r="C796" s="9"/>
       <c r="D796" s="9"/>
@@ -15479,7 +15526,7 @@
       <c r="L796" s="9"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="A797" s="32"/>
+      <c r="A797" s="33"/>
       <c r="B797" s="9"/>
       <c r="C797" s="9"/>
       <c r="D797" s="9"/>
@@ -15493,7 +15540,7 @@
       <c r="L797" s="9"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="A798" s="32"/>
+      <c r="A798" s="33"/>
       <c r="B798" s="9"/>
       <c r="C798" s="9"/>
       <c r="D798" s="9"/>
@@ -15507,7 +15554,7 @@
       <c r="L798" s="9"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="A799" s="32"/>
+      <c r="A799" s="33"/>
       <c r="B799" s="9"/>
       <c r="C799" s="9"/>
       <c r="D799" s="9"/>
@@ -15521,7 +15568,7 @@
       <c r="L799" s="9"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="A800" s="32"/>
+      <c r="A800" s="33"/>
       <c r="B800" s="9"/>
       <c r="C800" s="9"/>
       <c r="D800" s="9"/>
@@ -15535,7 +15582,7 @@
       <c r="L800" s="9"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="A801" s="32"/>
+      <c r="A801" s="33"/>
       <c r="B801" s="9"/>
       <c r="C801" s="9"/>
       <c r="D801" s="9"/>
@@ -15549,7 +15596,7 @@
       <c r="L801" s="9"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="32"/>
+      <c r="A802" s="33"/>
       <c r="B802" s="9"/>
       <c r="C802" s="9"/>
       <c r="D802" s="9"/>
@@ -15563,7 +15610,7 @@
       <c r="L802" s="9"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="A803" s="32"/>
+      <c r="A803" s="33"/>
       <c r="B803" s="9"/>
       <c r="C803" s="9"/>
       <c r="D803" s="9"/>
@@ -15577,7 +15624,7 @@
       <c r="L803" s="9"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="A804" s="32"/>
+      <c r="A804" s="33"/>
       <c r="B804" s="9"/>
       <c r="C804" s="9"/>
       <c r="D804" s="9"/>
@@ -15591,7 +15638,7 @@
       <c r="L804" s="9"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="A805" s="32"/>
+      <c r="A805" s="33"/>
       <c r="B805" s="9"/>
       <c r="C805" s="9"/>
       <c r="D805" s="9"/>
@@ -15605,7 +15652,7 @@
       <c r="L805" s="9"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="A806" s="32"/>
+      <c r="A806" s="33"/>
       <c r="B806" s="9"/>
       <c r="C806" s="9"/>
       <c r="D806" s="9"/>
@@ -15619,7 +15666,7 @@
       <c r="L806" s="9"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="A807" s="32"/>
+      <c r="A807" s="33"/>
       <c r="B807" s="9"/>
       <c r="C807" s="9"/>
       <c r="D807" s="9"/>
@@ -15633,7 +15680,7 @@
       <c r="L807" s="9"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="A808" s="32"/>
+      <c r="A808" s="33"/>
       <c r="B808" s="9"/>
       <c r="C808" s="9"/>
       <c r="D808" s="9"/>
@@ -15647,7 +15694,7 @@
       <c r="L808" s="9"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="A809" s="32"/>
+      <c r="A809" s="33"/>
       <c r="B809" s="9"/>
       <c r="C809" s="9"/>
       <c r="D809" s="9"/>
@@ -15661,7 +15708,7 @@
       <c r="L809" s="9"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="A810" s="32"/>
+      <c r="A810" s="33"/>
       <c r="B810" s="9"/>
       <c r="C810" s="9"/>
       <c r="D810" s="9"/>
@@ -15675,7 +15722,7 @@
       <c r="L810" s="9"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="A811" s="32"/>
+      <c r="A811" s="33"/>
       <c r="B811" s="9"/>
       <c r="C811" s="9"/>
       <c r="D811" s="9"/>
@@ -15689,7 +15736,7 @@
       <c r="L811" s="9"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="A812" s="32"/>
+      <c r="A812" s="33"/>
       <c r="B812" s="9"/>
       <c r="C812" s="9"/>
       <c r="D812" s="9"/>
@@ -15703,7 +15750,7 @@
       <c r="L812" s="9"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="A813" s="32"/>
+      <c r="A813" s="33"/>
       <c r="B813" s="9"/>
       <c r="C813" s="9"/>
       <c r="D813" s="9"/>
@@ -15717,7 +15764,7 @@
       <c r="L813" s="9"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="A814" s="32"/>
+      <c r="A814" s="33"/>
       <c r="B814" s="9"/>
       <c r="C814" s="9"/>
       <c r="D814" s="9"/>
@@ -15731,7 +15778,7 @@
       <c r="L814" s="9"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="A815" s="32"/>
+      <c r="A815" s="33"/>
       <c r="B815" s="9"/>
       <c r="C815" s="9"/>
       <c r="D815" s="9"/>
@@ -15745,7 +15792,7 @@
       <c r="L815" s="9"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="A816" s="32"/>
+      <c r="A816" s="33"/>
       <c r="B816" s="9"/>
       <c r="C816" s="9"/>
       <c r="D816" s="9"/>
@@ -15759,7 +15806,7 @@
       <c r="L816" s="9"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="A817" s="32"/>
+      <c r="A817" s="33"/>
       <c r="B817" s="9"/>
       <c r="C817" s="9"/>
       <c r="D817" s="9"/>
@@ -15773,7 +15820,7 @@
       <c r="L817" s="9"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="A818" s="32"/>
+      <c r="A818" s="33"/>
       <c r="B818" s="9"/>
       <c r="C818" s="9"/>
       <c r="D818" s="9"/>
@@ -15787,7 +15834,7 @@
       <c r="L818" s="9"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="A819" s="32"/>
+      <c r="A819" s="33"/>
       <c r="B819" s="9"/>
       <c r="C819" s="9"/>
       <c r="D819" s="9"/>
@@ -15801,7 +15848,7 @@
       <c r="L819" s="9"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="A820" s="32"/>
+      <c r="A820" s="33"/>
       <c r="B820" s="9"/>
       <c r="C820" s="9"/>
       <c r="D820" s="9"/>
@@ -15815,7 +15862,7 @@
       <c r="L820" s="9"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="A821" s="32"/>
+      <c r="A821" s="33"/>
       <c r="B821" s="9"/>
       <c r="C821" s="9"/>
       <c r="D821" s="9"/>
@@ -15829,7 +15876,7 @@
       <c r="L821" s="9"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="A822" s="32"/>
+      <c r="A822" s="33"/>
       <c r="B822" s="9"/>
       <c r="C822" s="9"/>
       <c r="D822" s="9"/>
@@ -15843,7 +15890,7 @@
       <c r="L822" s="9"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="A823" s="32"/>
+      <c r="A823" s="33"/>
       <c r="B823" s="9"/>
       <c r="C823" s="9"/>
       <c r="D823" s="9"/>
@@ -15857,7 +15904,7 @@
       <c r="L823" s="9"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="A824" s="32"/>
+      <c r="A824" s="33"/>
       <c r="B824" s="9"/>
       <c r="C824" s="9"/>
       <c r="D824" s="9"/>
@@ -15871,7 +15918,7 @@
       <c r="L824" s="9"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="A825" s="32"/>
+      <c r="A825" s="33"/>
       <c r="B825" s="9"/>
       <c r="C825" s="9"/>
       <c r="D825" s="9"/>
@@ -15885,7 +15932,7 @@
       <c r="L825" s="9"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="A826" s="32"/>
+      <c r="A826" s="33"/>
       <c r="B826" s="9"/>
       <c r="C826" s="9"/>
       <c r="D826" s="9"/>
@@ -15899,7 +15946,7 @@
       <c r="L826" s="9"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="A827" s="32"/>
+      <c r="A827" s="33"/>
       <c r="B827" s="9"/>
       <c r="C827" s="9"/>
       <c r="D827" s="9"/>
@@ -15913,7 +15960,7 @@
       <c r="L827" s="9"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="A828" s="32"/>
+      <c r="A828" s="33"/>
       <c r="B828" s="9"/>
       <c r="C828" s="9"/>
       <c r="D828" s="9"/>
@@ -15927,7 +15974,7 @@
       <c r="L828" s="9"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="A829" s="32"/>
+      <c r="A829" s="33"/>
       <c r="B829" s="9"/>
       <c r="C829" s="9"/>
       <c r="D829" s="9"/>
@@ -15941,7 +15988,7 @@
       <c r="L829" s="9"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="A830" s="32"/>
+      <c r="A830" s="33"/>
       <c r="B830" s="9"/>
       <c r="C830" s="9"/>
       <c r="D830" s="9"/>
@@ -15955,7 +16002,7 @@
       <c r="L830" s="9"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="A831" s="32"/>
+      <c r="A831" s="33"/>
       <c r="B831" s="9"/>
       <c r="C831" s="9"/>
       <c r="D831" s="9"/>
@@ -15969,7 +16016,7 @@
       <c r="L831" s="9"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="A832" s="32"/>
+      <c r="A832" s="33"/>
       <c r="B832" s="9"/>
       <c r="C832" s="9"/>
       <c r="D832" s="9"/>
@@ -15983,7 +16030,7 @@
       <c r="L832" s="9"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="A833" s="32"/>
+      <c r="A833" s="33"/>
       <c r="B833" s="9"/>
       <c r="C833" s="9"/>
       <c r="D833" s="9"/>
@@ -15997,7 +16044,7 @@
       <c r="L833" s="9"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="A834" s="32"/>
+      <c r="A834" s="33"/>
       <c r="B834" s="9"/>
       <c r="C834" s="9"/>
       <c r="D834" s="9"/>
@@ -16011,7 +16058,7 @@
       <c r="L834" s="9"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="A835" s="32"/>
+      <c r="A835" s="33"/>
       <c r="B835" s="9"/>
       <c r="C835" s="9"/>
       <c r="D835" s="9"/>
@@ -16025,7 +16072,7 @@
       <c r="L835" s="9"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="A836" s="32"/>
+      <c r="A836" s="33"/>
       <c r="B836" s="9"/>
       <c r="C836" s="9"/>
       <c r="D836" s="9"/>
@@ -16039,7 +16086,7 @@
       <c r="L836" s="9"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="A837" s="32"/>
+      <c r="A837" s="33"/>
       <c r="B837" s="9"/>
       <c r="C837" s="9"/>
       <c r="D837" s="9"/>
@@ -16053,7 +16100,7 @@
       <c r="L837" s="9"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="A838" s="32"/>
+      <c r="A838" s="33"/>
       <c r="B838" s="9"/>
       <c r="C838" s="9"/>
       <c r="D838" s="9"/>
@@ -16067,7 +16114,7 @@
       <c r="L838" s="9"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="A839" s="32"/>
+      <c r="A839" s="33"/>
       <c r="B839" s="9"/>
       <c r="C839" s="9"/>
       <c r="D839" s="9"/>
@@ -16081,7 +16128,7 @@
       <c r="L839" s="9"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="A840" s="32"/>
+      <c r="A840" s="33"/>
       <c r="B840" s="9"/>
       <c r="C840" s="9"/>
       <c r="D840" s="9"/>
@@ -16095,7 +16142,7 @@
       <c r="L840" s="9"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="A841" s="32"/>
+      <c r="A841" s="33"/>
       <c r="B841" s="9"/>
       <c r="C841" s="9"/>
       <c r="D841" s="9"/>
@@ -16109,7 +16156,7 @@
       <c r="L841" s="9"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="A842" s="32"/>
+      <c r="A842" s="33"/>
       <c r="B842" s="9"/>
       <c r="C842" s="9"/>
       <c r="D842" s="9"/>
@@ -16123,7 +16170,7 @@
       <c r="L842" s="9"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="A843" s="32"/>
+      <c r="A843" s="33"/>
       <c r="B843" s="9"/>
       <c r="C843" s="9"/>
       <c r="D843" s="9"/>
@@ -16137,7 +16184,7 @@
       <c r="L843" s="9"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="A844" s="32"/>
+      <c r="A844" s="33"/>
       <c r="B844" s="9"/>
       <c r="C844" s="9"/>
       <c r="D844" s="9"/>
@@ -16151,7 +16198,7 @@
       <c r="L844" s="9"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="A845" s="32"/>
+      <c r="A845" s="33"/>
       <c r="B845" s="9"/>
       <c r="C845" s="9"/>
       <c r="D845" s="9"/>
@@ -16165,7 +16212,7 @@
       <c r="L845" s="9"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="A846" s="32"/>
+      <c r="A846" s="33"/>
       <c r="B846" s="9"/>
       <c r="C846" s="9"/>
       <c r="D846" s="9"/>
@@ -16179,7 +16226,7 @@
       <c r="L846" s="9"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="A847" s="32"/>
+      <c r="A847" s="33"/>
       <c r="B847" s="9"/>
       <c r="C847" s="9"/>
       <c r="D847" s="9"/>
@@ -16193,7 +16240,7 @@
       <c r="L847" s="9"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="A848" s="32"/>
+      <c r="A848" s="33"/>
       <c r="B848" s="9"/>
       <c r="C848" s="9"/>
       <c r="D848" s="9"/>
@@ -16207,7 +16254,7 @@
       <c r="L848" s="9"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="A849" s="32"/>
+      <c r="A849" s="33"/>
       <c r="B849" s="9"/>
       <c r="C849" s="9"/>
       <c r="D849" s="9"/>
@@ -16221,7 +16268,7 @@
       <c r="L849" s="9"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="A850" s="32"/>
+      <c r="A850" s="33"/>
       <c r="B850" s="9"/>
       <c r="C850" s="9"/>
       <c r="D850" s="9"/>
@@ -16235,7 +16282,7 @@
       <c r="L850" s="9"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="A851" s="32"/>
+      <c r="A851" s="33"/>
       <c r="B851" s="9"/>
       <c r="C851" s="9"/>
       <c r="D851" s="9"/>
@@ -16249,7 +16296,7 @@
       <c r="L851" s="9"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="A852" s="32"/>
+      <c r="A852" s="33"/>
       <c r="B852" s="9"/>
       <c r="C852" s="9"/>
       <c r="D852" s="9"/>
@@ -16263,7 +16310,7 @@
       <c r="L852" s="9"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="A853" s="32"/>
+      <c r="A853" s="33"/>
       <c r="B853" s="9"/>
       <c r="C853" s="9"/>
       <c r="D853" s="9"/>
@@ -16277,7 +16324,7 @@
       <c r="L853" s="9"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="A854" s="32"/>
+      <c r="A854" s="33"/>
       <c r="B854" s="9"/>
       <c r="C854" s="9"/>
       <c r="D854" s="9"/>
@@ -16291,7 +16338,7 @@
       <c r="L854" s="9"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="32"/>
+      <c r="A855" s="33"/>
       <c r="B855" s="9"/>
       <c r="C855" s="9"/>
       <c r="D855" s="9"/>
@@ -16305,7 +16352,7 @@
       <c r="L855" s="9"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="A856" s="32"/>
+      <c r="A856" s="33"/>
       <c r="B856" s="9"/>
       <c r="C856" s="9"/>
       <c r="D856" s="9"/>
@@ -16319,7 +16366,7 @@
       <c r="L856" s="9"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="A857" s="32"/>
+      <c r="A857" s="33"/>
       <c r="B857" s="9"/>
       <c r="C857" s="9"/>
       <c r="D857" s="9"/>
@@ -16333,7 +16380,7 @@
       <c r="L857" s="9"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="A858" s="32"/>
+      <c r="A858" s="33"/>
       <c r="B858" s="9"/>
       <c r="C858" s="9"/>
       <c r="D858" s="9"/>
@@ -16347,7 +16394,7 @@
       <c r="L858" s="9"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="A859" s="32"/>
+      <c r="A859" s="33"/>
       <c r="B859" s="9"/>
       <c r="C859" s="9"/>
       <c r="D859" s="9"/>
@@ -16361,7 +16408,7 @@
       <c r="L859" s="9"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="A860" s="32"/>
+      <c r="A860" s="33"/>
       <c r="B860" s="9"/>
       <c r="C860" s="9"/>
       <c r="D860" s="9"/>
@@ -16375,7 +16422,7 @@
       <c r="L860" s="9"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="A861" s="32"/>
+      <c r="A861" s="33"/>
       <c r="B861" s="9"/>
       <c r="C861" s="9"/>
       <c r="D861" s="9"/>
@@ -16389,7 +16436,7 @@
       <c r="L861" s="9"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="32"/>
+      <c r="A862" s="33"/>
       <c r="B862" s="9"/>
       <c r="C862" s="9"/>
       <c r="D862" s="9"/>
@@ -16403,7 +16450,7 @@
       <c r="L862" s="9"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="A863" s="32"/>
+      <c r="A863" s="33"/>
       <c r="B863" s="9"/>
       <c r="C863" s="9"/>
       <c r="D863" s="9"/>
@@ -16417,7 +16464,7 @@
       <c r="L863" s="9"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="A864" s="32"/>
+      <c r="A864" s="33"/>
       <c r="B864" s="9"/>
       <c r="C864" s="9"/>
       <c r="D864" s="9"/>
@@ -16431,7 +16478,7 @@
       <c r="L864" s="9"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="A865" s="32"/>
+      <c r="A865" s="33"/>
       <c r="B865" s="9"/>
       <c r="C865" s="9"/>
       <c r="D865" s="9"/>
@@ -16445,7 +16492,7 @@
       <c r="L865" s="9"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="A866" s="32"/>
+      <c r="A866" s="33"/>
       <c r="B866" s="9"/>
       <c r="C866" s="9"/>
       <c r="D866" s="9"/>
@@ -16459,7 +16506,7 @@
       <c r="L866" s="9"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="A867" s="32"/>
+      <c r="A867" s="33"/>
       <c r="B867" s="9"/>
       <c r="C867" s="9"/>
       <c r="D867" s="9"/>
@@ -16473,7 +16520,7 @@
       <c r="L867" s="9"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="A868" s="32"/>
+      <c r="A868" s="33"/>
       <c r="B868" s="9"/>
       <c r="C868" s="9"/>
       <c r="D868" s="9"/>
@@ -16487,7 +16534,7 @@
       <c r="L868" s="9"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="32"/>
+      <c r="A869" s="33"/>
       <c r="B869" s="9"/>
       <c r="C869" s="9"/>
       <c r="D869" s="9"/>
@@ -16501,7 +16548,7 @@
       <c r="L869" s="9"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="A870" s="32"/>
+      <c r="A870" s="33"/>
       <c r="B870" s="9"/>
       <c r="C870" s="9"/>
       <c r="D870" s="9"/>
@@ -16515,7 +16562,7 @@
       <c r="L870" s="9"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="A871" s="32"/>
+      <c r="A871" s="33"/>
       <c r="B871" s="9"/>
       <c r="C871" s="9"/>
       <c r="D871" s="9"/>
@@ -16529,7 +16576,7 @@
       <c r="L871" s="9"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="A872" s="32"/>
+      <c r="A872" s="33"/>
       <c r="B872" s="9"/>
       <c r="C872" s="9"/>
       <c r="D872" s="9"/>
@@ -16543,7 +16590,7 @@
       <c r="L872" s="9"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="A873" s="32"/>
+      <c r="A873" s="33"/>
       <c r="B873" s="9"/>
       <c r="C873" s="9"/>
       <c r="D873" s="9"/>
@@ -16557,7 +16604,7 @@
       <c r="L873" s="9"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="A874" s="32"/>
+      <c r="A874" s="33"/>
       <c r="B874" s="9"/>
       <c r="C874" s="9"/>
       <c r="D874" s="9"/>
@@ -16571,7 +16618,7 @@
       <c r="L874" s="9"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="A875" s="32"/>
+      <c r="A875" s="33"/>
       <c r="B875" s="9"/>
       <c r="C875" s="9"/>
       <c r="D875" s="9"/>
@@ -16585,7 +16632,7 @@
       <c r="L875" s="9"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="A876" s="32"/>
+      <c r="A876" s="33"/>
       <c r="B876" s="9"/>
       <c r="C876" s="9"/>
       <c r="D876" s="9"/>
@@ -16599,7 +16646,7 @@
       <c r="L876" s="9"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="A877" s="32"/>
+      <c r="A877" s="33"/>
       <c r="B877" s="9"/>
       <c r="C877" s="9"/>
       <c r="D877" s="9"/>
@@ -16613,7 +16660,7 @@
       <c r="L877" s="9"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="A878" s="32"/>
+      <c r="A878" s="33"/>
       <c r="B878" s="9"/>
       <c r="C878" s="9"/>
       <c r="D878" s="9"/>
@@ -16627,7 +16674,7 @@
       <c r="L878" s="9"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="A879" s="32"/>
+      <c r="A879" s="33"/>
       <c r="B879" s="9"/>
       <c r="C879" s="9"/>
       <c r="D879" s="9"/>
@@ -16641,7 +16688,7 @@
       <c r="L879" s="9"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="A880" s="32"/>
+      <c r="A880" s="33"/>
       <c r="B880" s="9"/>
       <c r="C880" s="9"/>
       <c r="D880" s="9"/>
@@ -16655,7 +16702,7 @@
       <c r="L880" s="9"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="A881" s="32"/>
+      <c r="A881" s="33"/>
       <c r="B881" s="9"/>
       <c r="C881" s="9"/>
       <c r="D881" s="9"/>
@@ -16669,7 +16716,7 @@
       <c r="L881" s="9"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="A882" s="32"/>
+      <c r="A882" s="33"/>
       <c r="B882" s="9"/>
       <c r="C882" s="9"/>
       <c r="D882" s="9"/>
@@ -16683,7 +16730,7 @@
       <c r="L882" s="9"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="A883" s="32"/>
+      <c r="A883" s="33"/>
       <c r="B883" s="9"/>
       <c r="C883" s="9"/>
       <c r="D883" s="9"/>
@@ -16697,7 +16744,7 @@
       <c r="L883" s="9"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="A884" s="32"/>
+      <c r="A884" s="33"/>
       <c r="B884" s="9"/>
       <c r="C884" s="9"/>
       <c r="D884" s="9"/>
@@ -16711,7 +16758,7 @@
       <c r="L884" s="9"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="A885" s="32"/>
+      <c r="A885" s="33"/>
       <c r="B885" s="9"/>
       <c r="C885" s="9"/>
       <c r="D885" s="9"/>
@@ -16725,7 +16772,7 @@
       <c r="L885" s="9"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="A886" s="32"/>
+      <c r="A886" s="33"/>
       <c r="B886" s="9"/>
       <c r="C886" s="9"/>
       <c r="D886" s="9"/>
@@ -16739,7 +16786,7 @@
       <c r="L886" s="9"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="A887" s="32"/>
+      <c r="A887" s="33"/>
       <c r="B887" s="9"/>
       <c r="C887" s="9"/>
       <c r="D887" s="9"/>
@@ -16753,7 +16800,7 @@
       <c r="L887" s="9"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="A888" s="32"/>
+      <c r="A888" s="33"/>
       <c r="B888" s="9"/>
       <c r="C888" s="9"/>
       <c r="D888" s="9"/>
@@ -16767,7 +16814,7 @@
       <c r="L888" s="9"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="A889" s="32"/>
+      <c r="A889" s="33"/>
       <c r="B889" s="9"/>
       <c r="C889" s="9"/>
       <c r="D889" s="9"/>
@@ -16781,7 +16828,7 @@
       <c r="L889" s="9"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="A890" s="32"/>
+      <c r="A890" s="33"/>
       <c r="B890" s="9"/>
       <c r="C890" s="9"/>
       <c r="D890" s="9"/>
@@ -16795,7 +16842,7 @@
       <c r="L890" s="9"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="A891" s="32"/>
+      <c r="A891" s="33"/>
       <c r="B891" s="9"/>
       <c r="C891" s="9"/>
       <c r="D891" s="9"/>
@@ -16809,7 +16856,7 @@
       <c r="L891" s="9"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="A892" s="32"/>
+      <c r="A892" s="33"/>
       <c r="B892" s="9"/>
       <c r="C892" s="9"/>
       <c r="D892" s="9"/>
@@ -16823,7 +16870,7 @@
       <c r="L892" s="9"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="A893" s="32"/>
+      <c r="A893" s="33"/>
       <c r="B893" s="9"/>
       <c r="C893" s="9"/>
       <c r="D893" s="9"/>
@@ -16837,7 +16884,7 @@
       <c r="L893" s="9"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="A894" s="32"/>
+      <c r="A894" s="33"/>
       <c r="B894" s="9"/>
       <c r="C894" s="9"/>
       <c r="D894" s="9"/>
@@ -16851,7 +16898,7 @@
       <c r="L894" s="9"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="A895" s="32"/>
+      <c r="A895" s="33"/>
       <c r="B895" s="9"/>
       <c r="C895" s="9"/>
       <c r="D895" s="9"/>
@@ -16865,7 +16912,7 @@
       <c r="L895" s="9"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="A896" s="32"/>
+      <c r="A896" s="33"/>
       <c r="B896" s="9"/>
       <c r="C896" s="9"/>
       <c r="D896" s="9"/>
@@ -16879,7 +16926,7 @@
       <c r="L896" s="9"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="A897" s="32"/>
+      <c r="A897" s="33"/>
       <c r="B897" s="9"/>
       <c r="C897" s="9"/>
       <c r="D897" s="9"/>
@@ -16893,7 +16940,7 @@
       <c r="L897" s="9"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="A898" s="32"/>
+      <c r="A898" s="33"/>
       <c r="B898" s="9"/>
       <c r="C898" s="9"/>
       <c r="D898" s="9"/>
@@ -16907,7 +16954,7 @@
       <c r="L898" s="9"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="A899" s="32"/>
+      <c r="A899" s="33"/>
       <c r="B899" s="9"/>
       <c r="C899" s="9"/>
       <c r="D899" s="9"/>
@@ -16921,7 +16968,7 @@
       <c r="L899" s="9"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="A900" s="32"/>
+      <c r="A900" s="33"/>
       <c r="B900" s="9"/>
       <c r="C900" s="9"/>
       <c r="D900" s="9"/>
@@ -16935,7 +16982,7 @@
       <c r="L900" s="9"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="A901" s="32"/>
+      <c r="A901" s="33"/>
       <c r="B901" s="9"/>
       <c r="C901" s="9"/>
       <c r="D901" s="9"/>
@@ -16949,7 +16996,7 @@
       <c r="L901" s="9"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="A902" s="32"/>
+      <c r="A902" s="33"/>
       <c r="B902" s="9"/>
       <c r="C902" s="9"/>
       <c r="D902" s="9"/>
@@ -16963,7 +17010,7 @@
       <c r="L902" s="9"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="A903" s="32"/>
+      <c r="A903" s="33"/>
       <c r="B903" s="9"/>
       <c r="C903" s="9"/>
       <c r="D903" s="9"/>
@@ -16977,7 +17024,7 @@
       <c r="L903" s="9"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="A904" s="32"/>
+      <c r="A904" s="33"/>
       <c r="B904" s="9"/>
       <c r="C904" s="9"/>
       <c r="D904" s="9"/>
@@ -16991,7 +17038,7 @@
       <c r="L904" s="9"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="A905" s="32"/>
+      <c r="A905" s="33"/>
       <c r="B905" s="9"/>
       <c r="C905" s="9"/>
       <c r="D905" s="9"/>
@@ -17005,7 +17052,7 @@
       <c r="L905" s="9"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="A906" s="32"/>
+      <c r="A906" s="33"/>
       <c r="B906" s="9"/>
       <c r="C906" s="9"/>
       <c r="D906" s="9"/>
@@ -17019,7 +17066,7 @@
       <c r="L906" s="9"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="A907" s="32"/>
+      <c r="A907" s="33"/>
       <c r="B907" s="9"/>
       <c r="C907" s="9"/>
       <c r="D907" s="9"/>
@@ -17033,7 +17080,7 @@
       <c r="L907" s="9"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="A908" s="32"/>
+      <c r="A908" s="33"/>
       <c r="B908" s="9"/>
       <c r="C908" s="9"/>
       <c r="D908" s="9"/>
@@ -17047,7 +17094,7 @@
       <c r="L908" s="9"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="A909" s="32"/>
+      <c r="A909" s="33"/>
       <c r="B909" s="9"/>
       <c r="C909" s="9"/>
       <c r="D909" s="9"/>
@@ -17061,7 +17108,7 @@
       <c r="L909" s="9"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="A910" s="32"/>
+      <c r="A910" s="33"/>
       <c r="B910" s="9"/>
       <c r="C910" s="9"/>
       <c r="D910" s="9"/>
@@ -17075,7 +17122,7 @@
       <c r="L910" s="9"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="A911" s="32"/>
+      <c r="A911" s="33"/>
       <c r="B911" s="9"/>
       <c r="C911" s="9"/>
       <c r="D911" s="9"/>
@@ -17089,7 +17136,7 @@
       <c r="L911" s="9"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="A912" s="32"/>
+      <c r="A912" s="33"/>
       <c r="B912" s="9"/>
       <c r="C912" s="9"/>
       <c r="D912" s="9"/>
@@ -17103,7 +17150,7 @@
       <c r="L912" s="9"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="A913" s="32"/>
+      <c r="A913" s="33"/>
       <c r="B913" s="9"/>
       <c r="C913" s="9"/>
       <c r="D913" s="9"/>
@@ -17117,7 +17164,7 @@
       <c r="L913" s="9"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="A914" s="32"/>
+      <c r="A914" s="33"/>
       <c r="B914" s="9"/>
       <c r="C914" s="9"/>
       <c r="D914" s="9"/>
@@ -17131,7 +17178,7 @@
       <c r="L914" s="9"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="A915" s="32"/>
+      <c r="A915" s="33"/>
       <c r="B915" s="9"/>
       <c r="C915" s="9"/>
       <c r="D915" s="9"/>
@@ -17145,7 +17192,7 @@
       <c r="L915" s="9"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="A916" s="32"/>
+      <c r="A916" s="33"/>
       <c r="B916" s="9"/>
       <c r="C916" s="9"/>
       <c r="D916" s="9"/>
@@ -17159,7 +17206,7 @@
       <c r="L916" s="9"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="A917" s="32"/>
+      <c r="A917" s="33"/>
       <c r="B917" s="9"/>
       <c r="C917" s="9"/>
       <c r="D917" s="9"/>
@@ -17173,7 +17220,7 @@
       <c r="L917" s="9"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="A918" s="32"/>
+      <c r="A918" s="33"/>
       <c r="B918" s="9"/>
       <c r="C918" s="9"/>
       <c r="D918" s="9"/>
@@ -17187,7 +17234,7 @@
       <c r="L918" s="9"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="A919" s="32"/>
+      <c r="A919" s="33"/>
       <c r="B919" s="9"/>
       <c r="C919" s="9"/>
       <c r="D919" s="9"/>
@@ -17201,7 +17248,7 @@
       <c r="L919" s="9"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="A920" s="32"/>
+      <c r="A920" s="33"/>
       <c r="B920" s="9"/>
       <c r="C920" s="9"/>
       <c r="D920" s="9"/>
@@ -17215,7 +17262,7 @@
       <c r="L920" s="9"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="A921" s="32"/>
+      <c r="A921" s="33"/>
       <c r="B921" s="9"/>
       <c r="C921" s="9"/>
       <c r="D921" s="9"/>
@@ -17229,7 +17276,7 @@
       <c r="L921" s="9"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="A922" s="32"/>
+      <c r="A922" s="33"/>
       <c r="B922" s="9"/>
       <c r="C922" s="9"/>
       <c r="D922" s="9"/>
@@ -17243,7 +17290,7 @@
       <c r="L922" s="9"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="A923" s="32"/>
+      <c r="A923" s="33"/>
       <c r="B923" s="9"/>
       <c r="C923" s="9"/>
       <c r="D923" s="9"/>
@@ -17257,7 +17304,7 @@
       <c r="L923" s="9"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="A924" s="32"/>
+      <c r="A924" s="33"/>
       <c r="B924" s="9"/>
       <c r="C924" s="9"/>
       <c r="D924" s="9"/>
@@ -17271,7 +17318,7 @@
       <c r="L924" s="9"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="A925" s="32"/>
+      <c r="A925" s="33"/>
       <c r="B925" s="9"/>
       <c r="C925" s="9"/>
       <c r="D925" s="9"/>
@@ -17285,7 +17332,7 @@
       <c r="L925" s="9"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="A926" s="32"/>
+      <c r="A926" s="33"/>
       <c r="B926" s="9"/>
       <c r="C926" s="9"/>
       <c r="D926" s="9"/>
@@ -17299,7 +17346,7 @@
       <c r="L926" s="9"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="A927" s="32"/>
+      <c r="A927" s="33"/>
       <c r="B927" s="9"/>
       <c r="C927" s="9"/>
       <c r="D927" s="9"/>
@@ -17313,7 +17360,7 @@
       <c r="L927" s="9"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="A928" s="32"/>
+      <c r="A928" s="33"/>
       <c r="B928" s="9"/>
       <c r="C928" s="9"/>
       <c r="D928" s="9"/>
@@ -17327,7 +17374,7 @@
       <c r="L928" s="9"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="A929" s="32"/>
+      <c r="A929" s="33"/>
       <c r="B929" s="9"/>
       <c r="C929" s="9"/>
       <c r="D929" s="9"/>
@@ -17341,7 +17388,7 @@
       <c r="L929" s="9"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="A930" s="32"/>
+      <c r="A930" s="33"/>
       <c r="B930" s="9"/>
       <c r="C930" s="9"/>
       <c r="D930" s="9"/>
@@ -17355,7 +17402,7 @@
       <c r="L930" s="9"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="A931" s="32"/>
+      <c r="A931" s="33"/>
       <c r="B931" s="9"/>
       <c r="C931" s="9"/>
       <c r="D931" s="9"/>
@@ -17369,7 +17416,7 @@
       <c r="L931" s="9"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="32"/>
+      <c r="A932" s="33"/>
       <c r="B932" s="9"/>
       <c r="C932" s="9"/>
       <c r="D932" s="9"/>
@@ -17383,7 +17430,7 @@
       <c r="L932" s="9"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="A933" s="32"/>
+      <c r="A933" s="33"/>
       <c r="B933" s="9"/>
       <c r="C933" s="9"/>
       <c r="D933" s="9"/>
@@ -17397,7 +17444,7 @@
       <c r="L933" s="9"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="A934" s="32"/>
+      <c r="A934" s="33"/>
       <c r="B934" s="9"/>
       <c r="C934" s="9"/>
       <c r="D934" s="9"/>
@@ -17411,7 +17458,7 @@
       <c r="L934" s="9"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="A935" s="32"/>
+      <c r="A935" s="33"/>
       <c r="B935" s="9"/>
       <c r="C935" s="9"/>
       <c r="D935" s="9"/>
@@ -17425,7 +17472,7 @@
       <c r="L935" s="9"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="A936" s="32"/>
+      <c r="A936" s="33"/>
       <c r="B936" s="9"/>
       <c r="C936" s="9"/>
       <c r="D936" s="9"/>
@@ -17439,7 +17486,7 @@
       <c r="L936" s="9"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="A937" s="32"/>
+      <c r="A937" s="33"/>
       <c r="B937" s="9"/>
       <c r="C937" s="9"/>
       <c r="D937" s="9"/>
@@ -17453,7 +17500,7 @@
       <c r="L937" s="9"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="A938" s="32"/>
+      <c r="A938" s="33"/>
       <c r="B938" s="9"/>
       <c r="C938" s="9"/>
       <c r="D938" s="9"/>
@@ -17467,7 +17514,7 @@
       <c r="L938" s="9"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="A939" s="32"/>
+      <c r="A939" s="33"/>
       <c r="B939" s="9"/>
       <c r="C939" s="9"/>
       <c r="D939" s="9"/>
@@ -17481,7 +17528,7 @@
       <c r="L939" s="9"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="A940" s="32"/>
+      <c r="A940" s="33"/>
       <c r="B940" s="9"/>
       <c r="C940" s="9"/>
       <c r="D940" s="9"/>
@@ -17495,7 +17542,7 @@
       <c r="L940" s="9"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="A941" s="32"/>
+      <c r="A941" s="33"/>
       <c r="B941" s="9"/>
       <c r="C941" s="9"/>
       <c r="D941" s="9"/>
@@ -17509,7 +17556,7 @@
       <c r="L941" s="9"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="A942" s="32"/>
+      <c r="A942" s="33"/>
       <c r="B942" s="9"/>
       <c r="C942" s="9"/>
       <c r="D942" s="9"/>
@@ -17523,7 +17570,7 @@
       <c r="L942" s="9"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="A943" s="32"/>
+      <c r="A943" s="33"/>
       <c r="B943" s="9"/>
       <c r="C943" s="9"/>
       <c r="D943" s="9"/>
@@ -17537,7 +17584,7 @@
       <c r="L943" s="9"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="A944" s="32"/>
+      <c r="A944" s="33"/>
       <c r="B944" s="9"/>
       <c r="C944" s="9"/>
       <c r="D944" s="9"/>
@@ -17551,7 +17598,7 @@
       <c r="L944" s="9"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="A945" s="32"/>
+      <c r="A945" s="33"/>
       <c r="B945" s="9"/>
       <c r="C945" s="9"/>
       <c r="D945" s="9"/>
@@ -17565,7 +17612,7 @@
       <c r="L945" s="9"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="A946" s="32"/>
+      <c r="A946" s="33"/>
       <c r="B946" s="9"/>
       <c r="C946" s="9"/>
       <c r="D946" s="9"/>
@@ -17579,7 +17626,7 @@
       <c r="L946" s="9"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="A947" s="32"/>
+      <c r="A947" s="33"/>
       <c r="B947" s="9"/>
       <c r="C947" s="9"/>
       <c r="D947" s="9"/>
@@ -17593,7 +17640,7 @@
       <c r="L947" s="9"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="A948" s="32"/>
+      <c r="A948" s="33"/>
       <c r="B948" s="9"/>
       <c r="C948" s="9"/>
       <c r="D948" s="9"/>
@@ -17607,7 +17654,7 @@
       <c r="L948" s="9"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="A949" s="32"/>
+      <c r="A949" s="33"/>
       <c r="B949" s="9"/>
       <c r="C949" s="9"/>
       <c r="D949" s="9"/>
@@ -17621,7 +17668,7 @@
       <c r="L949" s="9"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="A950" s="32"/>
+      <c r="A950" s="33"/>
       <c r="B950" s="9"/>
       <c r="C950" s="9"/>
       <c r="D950" s="9"/>
@@ -17635,7 +17682,7 @@
       <c r="L950" s="9"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="A951" s="32"/>
+      <c r="A951" s="33"/>
       <c r="B951" s="9"/>
       <c r="C951" s="9"/>
       <c r="D951" s="9"/>
@@ -17649,7 +17696,7 @@
       <c r="L951" s="9"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="A952" s="32"/>
+      <c r="A952" s="33"/>
       <c r="B952" s="9"/>
       <c r="C952" s="9"/>
       <c r="D952" s="9"/>
@@ -17663,7 +17710,7 @@
       <c r="L952" s="9"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="A953" s="32"/>
+      <c r="A953" s="33"/>
       <c r="B953" s="9"/>
       <c r="C953" s="9"/>
       <c r="D953" s="9"/>
@@ -17677,7 +17724,7 @@
       <c r="L953" s="9"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="32"/>
+      <c r="A954" s="33"/>
       <c r="B954" s="9"/>
       <c r="C954" s="9"/>
       <c r="D954" s="9"/>
@@ -17691,7 +17738,7 @@
       <c r="L954" s="9"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="32"/>
+      <c r="A955" s="33"/>
       <c r="B955" s="9"/>
       <c r="C955" s="9"/>
       <c r="D955" s="9"/>
@@ -17705,7 +17752,7 @@
       <c r="L955" s="9"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="32"/>
+      <c r="A956" s="33"/>
       <c r="B956" s="9"/>
       <c r="C956" s="9"/>
       <c r="D956" s="9"/>
@@ -17719,7 +17766,7 @@
       <c r="L956" s="9"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="32"/>
+      <c r="A957" s="33"/>
       <c r="B957" s="9"/>
       <c r="C957" s="9"/>
       <c r="D957" s="9"/>
@@ -17733,7 +17780,7 @@
       <c r="L957" s="9"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="32"/>
+      <c r="A958" s="33"/>
       <c r="B958" s="9"/>
       <c r="C958" s="9"/>
       <c r="D958" s="9"/>
@@ -17747,7 +17794,7 @@
       <c r="L958" s="9"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="32"/>
+      <c r="A959" s="33"/>
       <c r="B959" s="9"/>
       <c r="C959" s="9"/>
       <c r="D959" s="9"/>
@@ -17761,7 +17808,7 @@
       <c r="L959" s="9"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="32"/>
+      <c r="A960" s="33"/>
       <c r="B960" s="9"/>
       <c r="C960" s="9"/>
       <c r="D960" s="9"/>
@@ -17775,7 +17822,7 @@
       <c r="L960" s="9"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="32"/>
+      <c r="A961" s="33"/>
       <c r="B961" s="9"/>
       <c r="C961" s="9"/>
       <c r="D961" s="9"/>
@@ -17789,7 +17836,7 @@
       <c r="L961" s="9"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="32"/>
+      <c r="A962" s="33"/>
       <c r="B962" s="9"/>
       <c r="C962" s="9"/>
       <c r="D962" s="9"/>
@@ -17803,7 +17850,7 @@
       <c r="L962" s="9"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="32"/>
+      <c r="A963" s="33"/>
       <c r="B963" s="9"/>
       <c r="C963" s="9"/>
       <c r="D963" s="9"/>
@@ -17817,7 +17864,7 @@
       <c r="L963" s="9"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="32"/>
+      <c r="A964" s="33"/>
       <c r="B964" s="9"/>
       <c r="C964" s="9"/>
       <c r="D964" s="9"/>
@@ -17831,7 +17878,7 @@
       <c r="L964" s="9"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="A965" s="32"/>
+      <c r="A965" s="33"/>
       <c r="B965" s="9"/>
       <c r="C965" s="9"/>
       <c r="D965" s="9"/>
@@ -17845,7 +17892,7 @@
       <c r="L965" s="9"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="A966" s="32"/>
+      <c r="A966" s="33"/>
       <c r="B966" s="9"/>
       <c r="C966" s="9"/>
       <c r="D966" s="9"/>
@@ -17859,7 +17906,7 @@
       <c r="L966" s="9"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="32"/>
+      <c r="A967" s="33"/>
       <c r="B967" s="9"/>
       <c r="C967" s="9"/>
       <c r="D967" s="9"/>
@@ -17873,7 +17920,7 @@
       <c r="L967" s="9"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="A968" s="32"/>
+      <c r="A968" s="33"/>
       <c r="B968" s="9"/>
       <c r="C968" s="9"/>
       <c r="D968" s="9"/>
@@ -17887,7 +17934,7 @@
       <c r="L968" s="9"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="A969" s="32"/>
+      <c r="A969" s="33"/>
       <c r="B969" s="9"/>
       <c r="C969" s="9"/>
       <c r="D969" s="9"/>
@@ -17901,7 +17948,7 @@
       <c r="L969" s="9"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="A970" s="32"/>
+      <c r="A970" s="33"/>
       <c r="B970" s="9"/>
       <c r="C970" s="9"/>
       <c r="D970" s="9"/>
@@ -17915,7 +17962,7 @@
       <c r="L970" s="9"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="A971" s="32"/>
+      <c r="A971" s="33"/>
       <c r="B971" s="9"/>
       <c r="C971" s="9"/>
       <c r="D971" s="9"/>
@@ -17929,7 +17976,7 @@
       <c r="L971" s="9"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="32"/>
+      <c r="A972" s="33"/>
       <c r="B972" s="9"/>
       <c r="C972" s="9"/>
       <c r="D972" s="9"/>
@@ -17943,7 +17990,7 @@
       <c r="L972" s="9"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="32"/>
+      <c r="A973" s="33"/>
       <c r="B973" s="9"/>
       <c r="C973" s="9"/>
       <c r="D973" s="9"/>
@@ -17957,7 +18004,7 @@
       <c r="L973" s="9"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="32"/>
+      <c r="A974" s="33"/>
       <c r="B974" s="9"/>
       <c r="C974" s="9"/>
       <c r="D974" s="9"/>
@@ -17971,7 +18018,7 @@
       <c r="L974" s="9"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="32"/>
+      <c r="A975" s="33"/>
       <c r="B975" s="9"/>
       <c r="C975" s="9"/>
       <c r="D975" s="9"/>
@@ -17985,7 +18032,7 @@
       <c r="L975" s="9"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="32"/>
+      <c r="A976" s="33"/>
       <c r="B976" s="9"/>
       <c r="C976" s="9"/>
       <c r="D976" s="9"/>
@@ -17999,7 +18046,7 @@
       <c r="L976" s="9"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="32"/>
+      <c r="A977" s="33"/>
       <c r="B977" s="9"/>
       <c r="C977" s="9"/>
       <c r="D977" s="9"/>
@@ -18013,7 +18060,7 @@
       <c r="L977" s="9"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="32"/>
+      <c r="A978" s="33"/>
       <c r="B978" s="9"/>
       <c r="C978" s="9"/>
       <c r="D978" s="9"/>
@@ -18027,7 +18074,7 @@
       <c r="L978" s="9"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="32"/>
+      <c r="A979" s="33"/>
       <c r="B979" s="9"/>
       <c r="C979" s="9"/>
       <c r="D979" s="9"/>
@@ -18041,7 +18088,7 @@
       <c r="L979" s="9"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="32"/>
+      <c r="A980" s="33"/>
       <c r="B980" s="9"/>
       <c r="C980" s="9"/>
       <c r="D980" s="9"/>
@@ -18055,7 +18102,7 @@
       <c r="L980" s="9"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="32"/>
+      <c r="A981" s="33"/>
       <c r="B981" s="9"/>
       <c r="C981" s="9"/>
       <c r="D981" s="9"/>
@@ -18069,7 +18116,7 @@
       <c r="L981" s="9"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="32"/>
+      <c r="A982" s="33"/>
       <c r="B982" s="9"/>
       <c r="C982" s="9"/>
       <c r="D982" s="9"/>
@@ -18083,7 +18130,7 @@
       <c r="L982" s="9"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="32"/>
+      <c r="A983" s="33"/>
       <c r="B983" s="9"/>
       <c r="C983" s="9"/>
       <c r="D983" s="9"/>
@@ -18097,7 +18144,7 @@
       <c r="L983" s="9"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="32"/>
+      <c r="A984" s="33"/>
       <c r="B984" s="9"/>
       <c r="C984" s="9"/>
       <c r="D984" s="9"/>
@@ -18111,7 +18158,7 @@
       <c r="L984" s="9"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="32"/>
+      <c r="A985" s="33"/>
       <c r="B985" s="9"/>
       <c r="C985" s="9"/>
       <c r="D985" s="9"/>
@@ -18125,7 +18172,7 @@
       <c r="L985" s="9"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="32"/>
+      <c r="A986" s="33"/>
       <c r="B986" s="9"/>
       <c r="C986" s="9"/>
       <c r="D986" s="9"/>
@@ -18139,7 +18186,7 @@
       <c r="L986" s="9"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="32"/>
+      <c r="A987" s="33"/>
       <c r="B987" s="9"/>
       <c r="C987" s="9"/>
       <c r="D987" s="9"/>
@@ -18153,7 +18200,7 @@
       <c r="L987" s="9"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="32"/>
+      <c r="A988" s="33"/>
       <c r="B988" s="9"/>
       <c r="C988" s="9"/>
       <c r="D988" s="9"/>
@@ -18167,7 +18214,7 @@
       <c r="L988" s="9"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="32"/>
+      <c r="A989" s="33"/>
       <c r="B989" s="9"/>
       <c r="C989" s="9"/>
       <c r="D989" s="9"/>
@@ -18181,7 +18228,7 @@
       <c r="L989" s="9"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="32"/>
+      <c r="A990" s="33"/>
       <c r="B990" s="9"/>
       <c r="C990" s="9"/>
       <c r="D990" s="9"/>
@@ -18195,7 +18242,7 @@
       <c r="L990" s="9"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="32"/>
+      <c r="A991" s="33"/>
       <c r="B991" s="9"/>
       <c r="C991" s="9"/>
       <c r="D991" s="9"/>
@@ -18209,7 +18256,7 @@
       <c r="L991" s="9"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="32"/>
+      <c r="A992" s="33"/>
       <c r="B992" s="9"/>
       <c r="C992" s="9"/>
       <c r="D992" s="9"/>
@@ -18223,7 +18270,7 @@
       <c r="L992" s="9"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="32"/>
+      <c r="A993" s="33"/>
       <c r="B993" s="9"/>
       <c r="C993" s="9"/>
       <c r="D993" s="9"/>
@@ -18237,7 +18284,7 @@
       <c r="L993" s="9"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="32"/>
+      <c r="A994" s="33"/>
       <c r="B994" s="9"/>
       <c r="C994" s="9"/>
       <c r="D994" s="9"/>
@@ -18251,7 +18298,7 @@
       <c r="L994" s="9"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="32"/>
+      <c r="A995" s="33"/>
       <c r="B995" s="9"/>
       <c r="C995" s="9"/>
       <c r="D995" s="9"/>
@@ -18265,7 +18312,7 @@
       <c r="L995" s="9"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="32"/>
+      <c r="A996" s="33"/>
       <c r="B996" s="9"/>
       <c r="C996" s="9"/>
       <c r="D996" s="9"/>
@@ -18279,7 +18326,7 @@
       <c r="L996" s="9"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="32"/>
+      <c r="A997" s="33"/>
       <c r="B997" s="9"/>
       <c r="C997" s="9"/>
       <c r="D997" s="9"/>
@@ -18293,7 +18340,7 @@
       <c r="L997" s="9"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="32"/>
+      <c r="A998" s="33"/>
       <c r="B998" s="9"/>
       <c r="C998" s="9"/>
       <c r="D998" s="9"/>
@@ -18307,7 +18354,7 @@
       <c r="L998" s="9"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="32"/>
+      <c r="A999" s="33"/>
       <c r="B999" s="9"/>
       <c r="C999" s="9"/>
       <c r="D999" s="9"/>
@@ -18321,7 +18368,7 @@
       <c r="L999" s="9"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="32"/>
+      <c r="A1000" s="33"/>
       <c r="B1000" s="9"/>
       <c r="C1000" s="9"/>
       <c r="D1000" s="9"/>
@@ -18335,7 +18382,7 @@
       <c r="L1000" s="9"/>
     </row>
     <row r="1001" ht="15.75" customHeight="1">
-      <c r="A1001" s="32"/>
+      <c r="A1001" s="33"/>
       <c r="B1001" s="9"/>
       <c r="C1001" s="9"/>
       <c r="D1001" s="9"/>
@@ -18349,7 +18396,7 @@
       <c r="L1001" s="9"/>
     </row>
     <row r="1002" ht="15.75" customHeight="1">
-      <c r="A1002" s="32"/>
+      <c r="A1002" s="33"/>
       <c r="B1002" s="9"/>
       <c r="C1002" s="9"/>
       <c r="D1002" s="9"/>
@@ -18363,7 +18410,7 @@
       <c r="L1002" s="9"/>
     </row>
     <row r="1003" ht="15.75" customHeight="1">
-      <c r="A1003" s="32"/>
+      <c r="A1003" s="33"/>
       <c r="B1003" s="9"/>
       <c r="C1003" s="9"/>
       <c r="D1003" s="9"/>
@@ -18377,7 +18424,7 @@
       <c r="L1003" s="9"/>
     </row>
     <row r="1004" ht="15.75" customHeight="1">
-      <c r="A1004" s="32"/>
+      <c r="A1004" s="33"/>
       <c r="B1004" s="9"/>
       <c r="C1004" s="9"/>
       <c r="D1004" s="9"/>
@@ -18391,7 +18438,7 @@
       <c r="L1004" s="9"/>
     </row>
     <row r="1005" ht="15.75" customHeight="1">
-      <c r="A1005" s="32"/>
+      <c r="A1005" s="33"/>
       <c r="B1005" s="9"/>
       <c r="C1005" s="9"/>
       <c r="D1005" s="9"/>
@@ -18405,7 +18452,7 @@
       <c r="L1005" s="9"/>
     </row>
     <row r="1006" ht="15.75" customHeight="1">
-      <c r="A1006" s="32"/>
+      <c r="A1006" s="33"/>
       <c r="B1006" s="9"/>
       <c r="C1006" s="9"/>
       <c r="D1006" s="9"/>
@@ -18419,7 +18466,7 @@
       <c r="L1006" s="9"/>
     </row>
     <row r="1007" ht="15.75" customHeight="1">
-      <c r="A1007" s="32"/>
+      <c r="A1007" s="33"/>
       <c r="B1007" s="9"/>
       <c r="C1007" s="9"/>
       <c r="D1007" s="9"/>
@@ -18433,7 +18480,7 @@
       <c r="L1007" s="9"/>
     </row>
     <row r="1008" ht="15.75" customHeight="1">
-      <c r="A1008" s="32"/>
+      <c r="A1008" s="33"/>
       <c r="B1008" s="9"/>
       <c r="C1008" s="9"/>
       <c r="D1008" s="9"/>
@@ -18447,7 +18494,7 @@
       <c r="L1008" s="9"/>
     </row>
     <row r="1009" ht="15.75" customHeight="1">
-      <c r="A1009" s="32"/>
+      <c r="A1009" s="33"/>
       <c r="B1009" s="9"/>
       <c r="C1009" s="9"/>
       <c r="D1009" s="9"/>
@@ -18461,9 +18508,9 @@
       <c r="L1009" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$M$121">
-    <sortState ref="A1:M121">
-      <sortCondition ref="A1:A121"/>
+  <autoFilter ref="$A$1:$M$122">
+    <sortState ref="A1:M122">
+      <sortCondition ref="A1:A122"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
@@ -18585,14 +18632,14 @@
     <hyperlink r:id="rId116" ref="I112"/>
     <hyperlink r:id="rId117" ref="I113"/>
     <hyperlink r:id="rId118" ref="I114"/>
-    <hyperlink r:id="rId119" ref="L114"/>
-    <hyperlink r:id="rId120" ref="I115"/>
-    <hyperlink r:id="rId121" ref="I116"/>
-    <hyperlink r:id="rId122" ref="I117"/>
-    <hyperlink r:id="rId123" ref="I118"/>
-    <hyperlink r:id="rId124" ref="I119"/>
-    <hyperlink r:id="rId125" ref="I120"/>
-    <hyperlink r:id="rId126" ref="I121"/>
+    <hyperlink r:id="rId119" ref="I115"/>
+    <hyperlink r:id="rId120" ref="I116"/>
+    <hyperlink r:id="rId121" ref="I117"/>
+    <hyperlink r:id="rId122" ref="I118"/>
+    <hyperlink r:id="rId123" ref="I119"/>
+    <hyperlink r:id="rId124" ref="I120"/>
+    <hyperlink r:id="rId125" ref="I121"/>
+    <hyperlink r:id="rId126" ref="I122"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -1236,7 +1236,7 @@
     <t>Rob Schneider</t>
   </si>
   <si>
-    <t>Pierce the Veil</t>
+    <t>Health</t>
   </si>
   <si>
     <t>Co-Headline tour with Pierce the Veil</t>
@@ -5770,7 +5770,7 @@
       <c r="B114" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C114" s="11" t="s">
+      <c r="C114" s="13" t="s">
         <v>407</v>
       </c>
       <c r="D114" s="11" t="s">

--- a/Concert History.xlsx
+++ b/Concert History.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Attended Show List" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Attended Show List'!$A$1:$M$122</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Attended Show List'!$A$1:$M$123</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="435">
   <si>
     <t>Date</t>
   </si>
@@ -1198,6 +1198,15 @@
   </si>
   <si>
     <t>Skeletour World Tour</t>
+  </si>
+  <si>
+    <t>The Offspring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPERCHARGED Worldwide in '25 </t>
+  </si>
+  <si>
+    <t>Jimmy Eat World, New Found Glory</t>
   </si>
   <si>
     <t>Foreigner</t>
@@ -1413,7 +1422,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1490,6 +1499,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
@@ -5586,156 +5598,156 @@
       <c r="L108" s="9"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="10">
-        <v>45867.0</v>
-      </c>
-      <c r="B109" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C109" s="11" t="s">
+      <c r="A109" s="6">
+        <v>45854.0</v>
+      </c>
+      <c r="B109" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C109" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="D109" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E109" s="19" t="s">
+      <c r="D109" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E109" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="F109" s="11" t="s">
-        <v>130</v>
+      <c r="F109" s="13" t="s">
+        <v>262</v>
       </c>
       <c r="G109" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="H109" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="H109" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I109" s="20" t="s">
+      <c r="I109" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="J109" s="21" t="s">
+      <c r="J109" s="22" t="s">
         <v>396</v>
       </c>
-      <c r="K109" s="9"/>
+      <c r="K109" s="7" t="s">
+        <v>397</v>
+      </c>
       <c r="L109" s="9"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="10">
-        <v>45890.0</v>
+        <v>45867.0</v>
       </c>
       <c r="B110" s="18" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E110" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>364</v>
+        <v>130</v>
       </c>
       <c r="G110" s="13" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="H110" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I110" s="24" t="s">
+      <c r="I110" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J110" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="K110" s="21" t="s">
         <v>399</v>
       </c>
+      <c r="K110" s="9"/>
       <c r="L110" s="9"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="6">
+      <c r="A111" s="10">
+        <v>45890.0</v>
+      </c>
+      <c r="B111" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E111" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F111" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="G111" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="H111" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I111" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J111" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="K111" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="L111" s="9"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="6">
         <v>45897.0</v>
       </c>
-      <c r="B111" s="26" t="s">
+      <c r="B112" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C112" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D111" s="11" t="s">
+      <c r="D112" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="E111" s="19" t="s">
+      <c r="E112" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="F111" s="11" t="s">
+      <c r="F112" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="G111" s="13" t="s">
+      <c r="G112" s="13" t="s">
         <v>233</v>
-      </c>
-      <c r="H111" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="I111" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="J111" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="K111" s="21" t="s">
-        <v>401</v>
-      </c>
-      <c r="L111" s="9"/>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="10">
-        <v>45905.0</v>
-      </c>
-      <c r="B112" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C112" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D112" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E112" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F112" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="G112" s="13" t="s">
-        <v>276</v>
       </c>
       <c r="H112" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="I112" s="24" t="s">
+      <c r="I112" s="32" t="s">
         <v>27</v>
       </c>
       <c r="J112" s="21" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K112" s="21" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L112" s="9"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="10">
-        <v>45911.0</v>
+        <v>45905.0</v>
       </c>
       <c r="B113" s="18" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>404</v>
+        <v>102</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>75</v>
@@ -5747,28 +5759,28 @@
         <v>364</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>69</v>
+        <v>276</v>
       </c>
       <c r="H113" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I113" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I113" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J113" s="21" t="s">
         <v>405</v>
       </c>
-      <c r="K113" s="22" t="s">
+      <c r="K113" s="21" t="s">
         <v>406</v>
       </c>
       <c r="L113" s="9"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="10">
-        <v>45955.0</v>
+        <v>45911.0</v>
       </c>
       <c r="B114" s="18" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C114" s="13" t="s">
         <v>407</v>
@@ -5780,36 +5792,34 @@
         <v>76</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>262</v>
+        <v>364</v>
       </c>
       <c r="G114" s="13" t="s">
-        <v>233</v>
+        <v>69</v>
       </c>
       <c r="H114" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I114" s="24" t="s">
+      <c r="I114" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J114" s="22" t="s">
+      <c r="J114" s="21" t="s">
         <v>408</v>
       </c>
       <c r="K114" s="22" t="s">
         <v>409</v>
       </c>
-      <c r="L114" s="32" t="s">
-        <v>410</v>
-      </c>
+      <c r="L114" s="9"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="10">
-        <v>45965.0</v>
+        <v>45955.0</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C115" s="11" t="s">
-        <v>71</v>
+        <v>62</v>
+      </c>
+      <c r="C115" s="13" t="s">
+        <v>410</v>
       </c>
       <c r="D115" s="11" t="s">
         <v>75</v>
@@ -5818,7 +5828,7 @@
         <v>76</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>150</v>
+        <v>262</v>
       </c>
       <c r="G115" s="13" t="s">
         <v>233</v>
@@ -5826,38 +5836,40 @@
       <c r="H115" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I115" s="20" t="s">
+      <c r="I115" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="J115" s="21" t="s">
+      <c r="J115" s="22" t="s">
         <v>411</v>
       </c>
       <c r="K115" s="22" t="s">
         <v>412</v>
       </c>
-      <c r="L115" s="9"/>
+      <c r="L115" s="33" t="s">
+        <v>413</v>
+      </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="10">
-        <v>46063.0</v>
+        <v>45965.0</v>
       </c>
       <c r="B116" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="E116" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>271</v>
+        <v>150</v>
       </c>
       <c r="G116" s="13" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="H116" s="11" t="s">
         <v>18</v>
@@ -5866,31 +5878,31 @@
         <v>27</v>
       </c>
       <c r="J116" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="K116" s="9" t="s">
-        <v>403</v>
+        <v>414</v>
+      </c>
+      <c r="K116" s="22" t="s">
+        <v>415</v>
       </c>
       <c r="L116" s="9"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="10">
-        <v>46088.0</v>
+        <v>46063.0</v>
       </c>
       <c r="B117" s="18" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>413</v>
+        <v>102</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>344</v>
+        <v>140</v>
       </c>
       <c r="E117" s="19" t="s">
-        <v>183</v>
+        <v>76</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>414</v>
+        <v>271</v>
       </c>
       <c r="G117" s="13" t="s">
         <v>164</v>
@@ -5898,210 +5910,232 @@
       <c r="H117" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I117" s="24" t="s">
+      <c r="I117" s="20" t="s">
         <v>27</v>
       </c>
       <c r="J117" s="21" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="K117" s="9" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="L117" s="9"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="10">
-        <v>46097.0</v>
+        <v>46088.0</v>
       </c>
       <c r="B118" s="18" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C118" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="E118" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="F118" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="D118" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E118" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F118" s="11" t="s">
-        <v>364</v>
-      </c>
       <c r="G118" s="13" t="s">
-        <v>233</v>
+        <v>164</v>
       </c>
       <c r="H118" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I118" s="20" t="s">
+      <c r="I118" s="24" t="s">
         <v>27</v>
       </c>
       <c r="J118" s="21" t="s">
         <v>418</v>
       </c>
-      <c r="K118" s="21" t="s">
+      <c r="K118" s="9" t="s">
         <v>419</v>
       </c>
       <c r="L118" s="9"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="6">
+      <c r="A119" s="10">
+        <v>46097.0</v>
+      </c>
+      <c r="B119" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C119" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E119" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F119" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="G119" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="H119" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J119" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="K119" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="L119" s="9"/>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="6">
         <v>46107.0</v>
       </c>
-      <c r="B119" s="7" t="s">
+      <c r="B120" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C119" s="7" t="s">
+      <c r="C120" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D119" s="7" t="s">
+      <c r="D120" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E119" s="8" t="s">
+      <c r="E120" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F119" s="7" t="s">
+      <c r="F120" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G119" s="7" t="s">
+      <c r="G120" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="H119" s="7" t="s">
+      <c r="H120" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I119" s="17" t="s">
+      <c r="I120" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J119" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="K119" s="9"/>
-      <c r="L119" s="9"/>
-    </row>
-    <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="10">
-        <v>46113.0</v>
-      </c>
-      <c r="B120" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C120" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D120" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E120" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F120" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="G120" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="H120" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="I120" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="J120" s="21" t="s">
-        <v>421</v>
-      </c>
-      <c r="K120" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="L120" s="7" t="s">
+      <c r="J120" s="7" t="s">
         <v>423</v>
       </c>
+      <c r="K120" s="9"/>
+      <c r="L120" s="9"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="10">
+        <v>46113.0</v>
+      </c>
+      <c r="B121" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E121" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F121" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G121" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="H121" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I121" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J121" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="K121" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="L121" s="7" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="10">
         <v>46129.0</v>
       </c>
-      <c r="B121" s="9" t="s">
+      <c r="B122" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C121" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="D121" s="9" t="s">
+      <c r="C122" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="D122" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E121" s="16" t="s">
+      <c r="E122" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F121" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="G121" s="7" t="s">
+      <c r="F122" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="G122" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="H121" s="9" t="s">
+      <c r="H122" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="I121" s="14" t="s">
+      <c r="I122" s="14" t="s">
         <v>27</v>
-      </c>
-      <c r="J121" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="K121" s="9"/>
-      <c r="L121" s="9"/>
-    </row>
-    <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="6">
-        <v>46156.0</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F122" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="H122" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I122" s="17" t="s">
-        <v>428</v>
       </c>
       <c r="J122" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="K122" s="7" t="s">
+      <c r="K122" s="9"/>
+      <c r="L122" s="9"/>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="6">
+        <v>46156.0</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F123" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="L122" s="7" t="s">
+      <c r="G123" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I123" s="17" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="10"/>
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="16"/>
-      <c r="F123" s="9"/>
-      <c r="G123" s="9"/>
-      <c r="H123" s="9"/>
-      <c r="I123" s="9"/>
-      <c r="J123" s="9"/>
-      <c r="K123" s="9"/>
-      <c r="L123" s="9"/>
+      <c r="J123" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="K123" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="L123" s="7" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
@@ -8596,7 +8630,7 @@
       <c r="L301" s="9"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="33"/>
+      <c r="A302" s="10"/>
       <c r="B302" s="9"/>
       <c r="C302" s="9"/>
       <c r="D302" s="9"/>
@@ -8610,7 +8644,7 @@
       <c r="L302" s="9"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="33"/>
+      <c r="A303" s="34"/>
       <c r="B303" s="9"/>
       <c r="C303" s="9"/>
       <c r="D303" s="9"/>
@@ -8624,7 +8658,7 @@
       <c r="L303" s="9"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="33"/>
+      <c r="A304" s="34"/>
       <c r="B304" s="9"/>
       <c r="C304" s="9"/>
       <c r="D304" s="9"/>
@@ -8638,7 +8672,7 @@
       <c r="L304" s="9"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="33"/>
+      <c r="A305" s="34"/>
       <c r="B305" s="9"/>
       <c r="C305" s="9"/>
       <c r="D305" s="9"/>
@@ -8652,7 +8686,7 @@
       <c r="L305" s="9"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="33"/>
+      <c r="A306" s="34"/>
       <c r="B306" s="9"/>
       <c r="C306" s="9"/>
       <c r="D306" s="9"/>
@@ -8666,7 +8700,7 @@
       <c r="L306" s="9"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="33"/>
+      <c r="A307" s="34"/>
       <c r="B307" s="9"/>
       <c r="C307" s="9"/>
       <c r="D307" s="9"/>
@@ -8680,7 +8714,7 @@
       <c r="L307" s="9"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="33"/>
+      <c r="A308" s="34"/>
       <c r="B308" s="9"/>
       <c r="C308" s="9"/>
       <c r="D308" s="9"/>
@@ -8694,7 +8728,7 @@
       <c r="L308" s="9"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="33"/>
+      <c r="A309" s="34"/>
       <c r="B309" s="9"/>
       <c r="C309" s="9"/>
       <c r="D309" s="9"/>
@@ -8708,7 +8742,7 @@
       <c r="L309" s="9"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="33"/>
+      <c r="A310" s="34"/>
       <c r="B310" s="9"/>
       <c r="C310" s="9"/>
       <c r="D310" s="9"/>
@@ -8722,7 +8756,7 @@
       <c r="L310" s="9"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="33"/>
+      <c r="A311" s="34"/>
       <c r="B311" s="9"/>
       <c r="C311" s="9"/>
       <c r="D311" s="9"/>
@@ -8736,7 +8770,7 @@
       <c r="L311" s="9"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="33"/>
+      <c r="A312" s="34"/>
       <c r="B312" s="9"/>
       <c r="C312" s="9"/>
       <c r="D312" s="9"/>
@@ -8750,7 +8784,7 @@
       <c r="L312" s="9"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="33"/>
+      <c r="A313" s="34"/>
       <c r="B313" s="9"/>
       <c r="C313" s="9"/>
       <c r="D313" s="9"/>
@@ -8764,7 +8798,7 @@
       <c r="L313" s="9"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="33"/>
+      <c r="A314" s="34"/>
       <c r="B314" s="9"/>
       <c r="C314" s="9"/>
       <c r="D314" s="9"/>
@@ -8778,7 +8812,7 @@
       <c r="L314" s="9"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="33"/>
+      <c r="A315" s="34"/>
       <c r="B315" s="9"/>
       <c r="C315" s="9"/>
       <c r="D315" s="9"/>
@@ -8792,7 +8826,7 @@
       <c r="L315" s="9"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="33"/>
+      <c r="A316" s="34"/>
       <c r="B316" s="9"/>
       <c r="C316" s="9"/>
       <c r="D316" s="9"/>
@@ -8806,7 +8840,7 @@
       <c r="L316" s="9"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="33"/>
+      <c r="A317" s="34"/>
       <c r="B317" s="9"/>
       <c r="C317" s="9"/>
       <c r="D317" s="9"/>
@@ -8820,7 +8854,7 @@
       <c r="L317" s="9"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="A318" s="33"/>
+      <c r="A318" s="34"/>
       <c r="B318" s="9"/>
       <c r="C318" s="9"/>
       <c r="D318" s="9"/>
@@ -8834,7 +8868,7 @@
       <c r="L318" s="9"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="A319" s="33"/>
+      <c r="A319" s="34"/>
       <c r="B319" s="9"/>
       <c r="C319" s="9"/>
       <c r="D319" s="9"/>
@@ -8848,7 +8882,7 @@
       <c r="L319" s="9"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="33"/>
+      <c r="A320" s="34"/>
       <c r="B320" s="9"/>
       <c r="C320" s="9"/>
       <c r="D320" s="9"/>
@@ -8862,7 +8896,7 @@
       <c r="L320" s="9"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="A321" s="33"/>
+      <c r="A321" s="34"/>
       <c r="B321" s="9"/>
       <c r="C321" s="9"/>
       <c r="D321" s="9"/>
@@ -8876,7 +8910,7 @@
       <c r="L321" s="9"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="33"/>
+      <c r="A322" s="34"/>
       <c r="B322" s="9"/>
       <c r="C322" s="9"/>
       <c r="D322" s="9"/>
@@ -8890,7 +8924,7 @@
       <c r="L322" s="9"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="33"/>
+      <c r="A323" s="34"/>
       <c r="B323" s="9"/>
       <c r="C323" s="9"/>
       <c r="D323" s="9"/>
@@ -8904,7 +8938,7 @@
       <c r="L323" s="9"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="33"/>
+      <c r="A324" s="34"/>
       <c r="B324" s="9"/>
       <c r="C324" s="9"/>
       <c r="D324" s="9"/>
@@ -8918,7 +8952,7 @@
       <c r="L324" s="9"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="A325" s="33"/>
+      <c r="A325" s="34"/>
       <c r="B325" s="9"/>
       <c r="C325" s="9"/>
       <c r="D325" s="9"/>
@@ -8932,7 +8966,7 @@
       <c r="L325" s="9"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="33"/>
+      <c r="A326" s="34"/>
       <c r="B326" s="9"/>
       <c r="C326" s="9"/>
       <c r="D326" s="9"/>
@@ -8946,7 +8980,7 @@
       <c r="L326" s="9"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="A327" s="33"/>
+      <c r="A327" s="34"/>
       <c r="B327" s="9"/>
       <c r="C327" s="9"/>
       <c r="D327" s="9"/>
@@ -8960,7 +8994,7 @@
       <c r="L327" s="9"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="A328" s="33"/>
+      <c r="A328" s="34"/>
       <c r="B328" s="9"/>
       <c r="C328" s="9"/>
       <c r="D328" s="9"/>
@@ -8974,7 +9008,7 @@
       <c r="L328" s="9"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="33"/>
+      <c r="A329" s="34"/>
       <c r="B329" s="9"/>
       <c r="C329" s="9"/>
       <c r="D329" s="9"/>
@@ -8988,7 +9022,7 @@
       <c r="L329" s="9"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="33"/>
+      <c r="A330" s="34"/>
       <c r="B330" s="9"/>
       <c r="C330" s="9"/>
       <c r="D330" s="9"/>
@@ -9002,7 +9036,7 @@
       <c r="L330" s="9"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="A331" s="33"/>
+      <c r="A331" s="34"/>
       <c r="B331" s="9"/>
       <c r="C331" s="9"/>
       <c r="D331" s="9"/>
@@ -9016,7 +9050,7 @@
       <c r="L331" s="9"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="33"/>
+      <c r="A332" s="34"/>
       <c r="B332" s="9"/>
       <c r="C332" s="9"/>
       <c r="D332" s="9"/>
@@ -9030,7 +9064,7 @@
       <c r="L332" s="9"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="33"/>
+      <c r="A333" s="34"/>
       <c r="B333" s="9"/>
       <c r="C333" s="9"/>
       <c r="D333" s="9"/>
@@ -9044,7 +9078,7 @@
       <c r="L333" s="9"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="A334" s="33"/>
+      <c r="A334" s="34"/>
       <c r="B334" s="9"/>
       <c r="C334" s="9"/>
       <c r="D334" s="9"/>
@@ -9058,7 +9092,7 @@
       <c r="L334" s="9"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="33"/>
+      <c r="A335" s="34"/>
       <c r="B335" s="9"/>
       <c r="C335" s="9"/>
       <c r="D335" s="9"/>
@@ -9072,7 +9106,7 @@
       <c r="L335" s="9"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="33"/>
+      <c r="A336" s="34"/>
       <c r="B336" s="9"/>
       <c r="C336" s="9"/>
       <c r="D336" s="9"/>
@@ -9086,7 +9120,7 @@
       <c r="L336" s="9"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="33"/>
+      <c r="A337" s="34"/>
       <c r="B337" s="9"/>
       <c r="C337" s="9"/>
       <c r="D337" s="9"/>
@@ -9100,7 +9134,7 @@
       <c r="L337" s="9"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="33"/>
+      <c r="A338" s="34"/>
       <c r="B338" s="9"/>
       <c r="C338" s="9"/>
       <c r="D338" s="9"/>
@@ -9114,7 +9148,7 @@
       <c r="L338" s="9"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="33"/>
+      <c r="A339" s="34"/>
       <c r="B339" s="9"/>
       <c r="C339" s="9"/>
       <c r="D339" s="9"/>
@@ -9128,7 +9162,7 @@
       <c r="L339" s="9"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="33"/>
+      <c r="A340" s="34"/>
       <c r="B340" s="9"/>
       <c r="C340" s="9"/>
       <c r="D340" s="9"/>
@@ -9142,7 +9176,7 @@
       <c r="L340" s="9"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="A341" s="33"/>
+      <c r="A341" s="34"/>
       <c r="B341" s="9"/>
       <c r="C341" s="9"/>
       <c r="D341" s="9"/>
@@ -9156,7 +9190,7 @@
       <c r="L341" s="9"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="A342" s="33"/>
+      <c r="A342" s="34"/>
       <c r="B342" s="9"/>
       <c r="C342" s="9"/>
       <c r="D342" s="9"/>
@@ -9170,7 +9204,7 @@
       <c r="L342" s="9"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="33"/>
+      <c r="A343" s="34"/>
       <c r="B343" s="9"/>
       <c r="C343" s="9"/>
       <c r="D343" s="9"/>
@@ -9184,7 +9218,7 @@
       <c r="L343" s="9"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="A344" s="33"/>
+      <c r="A344" s="34"/>
       <c r="B344" s="9"/>
       <c r="C344" s="9"/>
       <c r="D344" s="9"/>
@@ -9198,7 +9232,7 @@
       <c r="L344" s="9"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="A345" s="33"/>
+      <c r="A345" s="34"/>
       <c r="B345" s="9"/>
       <c r="C345" s="9"/>
       <c r="D345" s="9"/>
@@ -9212,7 +9246,7 @@
       <c r="L345" s="9"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="A346" s="33"/>
+      <c r="A346" s="34"/>
       <c r="B346" s="9"/>
       <c r="C346" s="9"/>
       <c r="D346" s="9"/>
@@ -9226,7 +9260,7 @@
       <c r="L346" s="9"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="A347" s="33"/>
+      <c r="A347" s="34"/>
       <c r="B347" s="9"/>
       <c r="C347" s="9"/>
       <c r="D347" s="9"/>
@@ -9240,7 +9274,7 @@
       <c r="L347" s="9"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="A348" s="33"/>
+      <c r="A348" s="34"/>
       <c r="B348" s="9"/>
       <c r="C348" s="9"/>
       <c r="D348" s="9"/>
@@ -9254,7 +9288,7 @@
       <c r="L348" s="9"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="A349" s="33"/>
+      <c r="A349" s="34"/>
       <c r="B349" s="9"/>
       <c r="C349" s="9"/>
       <c r="D349" s="9"/>
@@ -9268,7 +9302,7 @@
       <c r="L349" s="9"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="33"/>
+      <c r="A350" s="34"/>
       <c r="B350" s="9"/>
       <c r="C350" s="9"/>
       <c r="D350" s="9"/>
@@ -9282,7 +9316,7 @@
       <c r="L350" s="9"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="33"/>
+      <c r="A351" s="34"/>
       <c r="B351" s="9"/>
       <c r="C351" s="9"/>
       <c r="D351" s="9"/>
@@ -9296,7 +9330,7 @@
       <c r="L351" s="9"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="33"/>
+      <c r="A352" s="34"/>
       <c r="B352" s="9"/>
       <c r="C352" s="9"/>
       <c r="D352" s="9"/>
@@ -9310,7 +9344,7 @@
       <c r="L352" s="9"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="33"/>
+      <c r="A353" s="34"/>
       <c r="B353" s="9"/>
       <c r="C353" s="9"/>
       <c r="D353" s="9"/>
@@ -9324,7 +9358,7 @@
       <c r="L353" s="9"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="33"/>
+      <c r="A354" s="34"/>
       <c r="B354" s="9"/>
       <c r="C354" s="9"/>
       <c r="D354" s="9"/>
@@ -9338,7 +9372,7 @@
       <c r="L354" s="9"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="33"/>
+      <c r="A355" s="34"/>
       <c r="B355" s="9"/>
       <c r="C355" s="9"/>
       <c r="D355" s="9"/>
@@ -9352,7 +9386,7 @@
       <c r="L355" s="9"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="33"/>
+      <c r="A356" s="34"/>
       <c r="B356" s="9"/>
       <c r="C356" s="9"/>
       <c r="D356" s="9"/>
@@ -9366,7 +9400,7 @@
       <c r="L356" s="9"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="33"/>
+      <c r="A357" s="34"/>
       <c r="B357" s="9"/>
       <c r="C357" s="9"/>
       <c r="D357" s="9"/>
@@ -9380,7 +9414,7 @@
       <c r="L357" s="9"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="33"/>
+      <c r="A358" s="34"/>
       <c r="B358" s="9"/>
       <c r="C358" s="9"/>
       <c r="D358" s="9"/>
@@ -9394,7 +9428,7 @@
       <c r="L358" s="9"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="33"/>
+      <c r="A359" s="34"/>
       <c r="B359" s="9"/>
       <c r="C359" s="9"/>
       <c r="D359" s="9"/>
@@ -9408,7 +9442,7 @@
       <c r="L359" s="9"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="33"/>
+      <c r="A360" s="34"/>
       <c r="B360" s="9"/>
       <c r="C360" s="9"/>
       <c r="D360" s="9"/>
@@ -9422,7 +9456,7 @@
       <c r="L360" s="9"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="33"/>
+      <c r="A361" s="34"/>
       <c r="B361" s="9"/>
       <c r="C361" s="9"/>
       <c r="D361" s="9"/>
@@ -9436,7 +9470,7 @@
       <c r="L361" s="9"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="33"/>
+      <c r="A362" s="34"/>
       <c r="B362" s="9"/>
       <c r="C362" s="9"/>
       <c r="D362" s="9"/>
@@ -9450,7 +9484,7 @@
       <c r="L362" s="9"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="33"/>
+      <c r="A363" s="34"/>
       <c r="B363" s="9"/>
       <c r="C363" s="9"/>
       <c r="D363" s="9"/>
@@ -9464,7 +9498,7 @@
       <c r="L363" s="9"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="33"/>
+      <c r="A364" s="34"/>
       <c r="B364" s="9"/>
       <c r="C364" s="9"/>
       <c r="D364" s="9"/>
@@ -9478,7 +9512,7 @@
       <c r="L364" s="9"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="33"/>
+      <c r="A365" s="34"/>
       <c r="B365" s="9"/>
       <c r="C365" s="9"/>
       <c r="D365" s="9"/>
@@ -9492,7 +9526,7 @@
       <c r="L365" s="9"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="33"/>
+      <c r="A366" s="34"/>
       <c r="B366" s="9"/>
       <c r="C366" s="9"/>
       <c r="D366" s="9"/>
@@ -9506,7 +9540,7 @@
       <c r="L366" s="9"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="33"/>
+      <c r="A367" s="34"/>
       <c r="B367" s="9"/>
       <c r="C367" s="9"/>
       <c r="D367" s="9"/>
@@ -9520,7 +9554,7 @@
       <c r="L367" s="9"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="33"/>
+      <c r="A368" s="34"/>
       <c r="B368" s="9"/>
       <c r="C368" s="9"/>
       <c r="D368" s="9"/>
@@ -9534,7 +9568,7 @@
       <c r="L368" s="9"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="33"/>
+      <c r="A369" s="34"/>
       <c r="B369" s="9"/>
       <c r="C369" s="9"/>
       <c r="D369" s="9"/>
@@ -9548,7 +9582,7 @@
       <c r="L369" s="9"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="33"/>
+      <c r="A370" s="34"/>
       <c r="B370" s="9"/>
       <c r="C370" s="9"/>
       <c r="D370" s="9"/>
@@ -9562,7 +9596,7 @@
       <c r="L370" s="9"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="33"/>
+      <c r="A371" s="34"/>
       <c r="B371" s="9"/>
       <c r="C371" s="9"/>
       <c r="D371" s="9"/>
@@ -9576,7 +9610,7 @@
       <c r="L371" s="9"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="33"/>
+      <c r="A372" s="34"/>
       <c r="B372" s="9"/>
       <c r="C372" s="9"/>
       <c r="D372" s="9"/>
@@ -9590,7 +9624,7 @@
       <c r="L372" s="9"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="33"/>
+      <c r="A373" s="34"/>
       <c r="B373" s="9"/>
       <c r="C373" s="9"/>
       <c r="D373" s="9"/>
@@ -9604,7 +9638,7 @@
       <c r="L373" s="9"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="33"/>
+      <c r="A374" s="34"/>
       <c r="B374" s="9"/>
       <c r="C374" s="9"/>
       <c r="D374" s="9"/>
@@ -9618,7 +9652,7 @@
       <c r="L374" s="9"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="33"/>
+      <c r="A375" s="34"/>
       <c r="B375" s="9"/>
       <c r="C375" s="9"/>
       <c r="D375" s="9"/>
@@ -9632,7 +9666,7 @@
       <c r="L375" s="9"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="33"/>
+      <c r="A376" s="34"/>
       <c r="B376" s="9"/>
       <c r="C376" s="9"/>
       <c r="D376" s="9"/>
@@ -9646,7 +9680,7 @@
       <c r="L376" s="9"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="33"/>
+      <c r="A377" s="34"/>
       <c r="B377" s="9"/>
       <c r="C377" s="9"/>
       <c r="D377" s="9"/>
@@ -9660,7 +9694,7 @@
       <c r="L377" s="9"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="33"/>
+      <c r="A378" s="34"/>
       <c r="B378" s="9"/>
       <c r="C378" s="9"/>
       <c r="D378" s="9"/>
@@ -9674,7 +9708,7 @@
       <c r="L378" s="9"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="A379" s="33"/>
+      <c r="A379" s="34"/>
       <c r="B379" s="9"/>
       <c r="C379" s="9"/>
       <c r="D379" s="9"/>
@@ -9688,7 +9722,7 @@
       <c r="L379" s="9"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="33"/>
+      <c r="A380" s="34"/>
       <c r="B380" s="9"/>
       <c r="C380" s="9"/>
       <c r="D380" s="9"/>
@@ -9702,7 +9736,7 @@
       <c r="L380" s="9"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="A381" s="33"/>
+      <c r="A381" s="34"/>
       <c r="B381" s="9"/>
       <c r="C381" s="9"/>
       <c r="D381" s="9"/>
@@ -9716,7 +9750,7 @@
       <c r="L381" s="9"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="33"/>
+      <c r="A382" s="34"/>
       <c r="B382" s="9"/>
       <c r="C382" s="9"/>
       <c r="D382" s="9"/>
@@ -9730,7 +9764,7 @@
       <c r="L382" s="9"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="33"/>
+      <c r="A383" s="34"/>
       <c r="B383" s="9"/>
       <c r="C383" s="9"/>
       <c r="D383" s="9"/>
@@ -9744,7 +9778,7 @@
       <c r="L383" s="9"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="A384" s="33"/>
+      <c r="A384" s="34"/>
       <c r="B384" s="9"/>
       <c r="C384" s="9"/>
       <c r="D384" s="9"/>
@@ -9758,7 +9792,7 @@
       <c r="L384" s="9"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="33"/>
+      <c r="A385" s="34"/>
       <c r="B385" s="9"/>
       <c r="C385" s="9"/>
       <c r="D385" s="9"/>
@@ -9772,7 +9806,7 @@
       <c r="L385" s="9"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="33"/>
+      <c r="A386" s="34"/>
       <c r="B386" s="9"/>
       <c r="C386" s="9"/>
       <c r="D386" s="9"/>
@@ -9786,7 +9820,7 @@
       <c r="L386" s="9"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="A387" s="33"/>
+      <c r="A387" s="34"/>
       <c r="B387" s="9"/>
       <c r="C387" s="9"/>
       <c r="D387" s="9"/>
@@ -9800,7 +9834,7 @@
       <c r="L387" s="9"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="A388" s="33"/>
+      <c r="A388" s="34"/>
       <c r="B388" s="9"/>
       <c r="C388" s="9"/>
       <c r="D388" s="9"/>
@@ -9814,7 +9848,7 @@
       <c r="L388" s="9"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="A389" s="33"/>
+      <c r="A389" s="34"/>
       <c r="B389" s="9"/>
       <c r="C389" s="9"/>
       <c r="D389" s="9"/>
@@ -9828,7 +9862,7 @@
       <c r="L389" s="9"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="33"/>
+      <c r="A390" s="34"/>
       <c r="B390" s="9"/>
       <c r="C390" s="9"/>
       <c r="D390" s="9"/>
@@ -9842,7 +9876,7 @@
       <c r="L390" s="9"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="33"/>
+      <c r="A391" s="34"/>
       <c r="B391" s="9"/>
       <c r="C391" s="9"/>
       <c r="D391" s="9"/>
@@ -9856,7 +9890,7 @@
       <c r="L391" s="9"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="A392" s="33"/>
+      <c r="A392" s="34"/>
       <c r="B392" s="9"/>
       <c r="C392" s="9"/>
       <c r="D392" s="9"/>
@@ -9870,7 +9904,7 @@
       <c r="L392" s="9"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="33"/>
+      <c r="A393" s="34"/>
       <c r="B393" s="9"/>
       <c r="C393" s="9"/>
       <c r="D393" s="9"/>
@@ -9884,7 +9918,7 @@
       <c r="L393" s="9"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="A394" s="33"/>
+      <c r="A394" s="34"/>
       <c r="B394" s="9"/>
       <c r="C394" s="9"/>
       <c r="D394" s="9"/>
@@ -9898,7 +9932,7 @@
       <c r="L394" s="9"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="33"/>
+      <c r="A395" s="34"/>
       <c r="B395" s="9"/>
       <c r="C395" s="9"/>
       <c r="D395" s="9"/>
@@ -9912,7 +9946,7 @@
       <c r="L395" s="9"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="33"/>
+      <c r="A396" s="34"/>
       <c r="B396" s="9"/>
       <c r="C396" s="9"/>
       <c r="D396" s="9"/>
@@ -9926,7 +9960,7 @@
       <c r="L396" s="9"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="A397" s="33"/>
+      <c r="A397" s="34"/>
       <c r="B397" s="9"/>
       <c r="C397" s="9"/>
       <c r="D397" s="9"/>
@@ -9940,7 +9974,7 @@
       <c r="L397" s="9"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="A398" s="33"/>
+      <c r="A398" s="34"/>
       <c r="B398" s="9"/>
       <c r="C398" s="9"/>
       <c r="D398" s="9"/>
@@ -9954,7 +9988,7 @@
       <c r="L398" s="9"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="33"/>
+      <c r="A399" s="34"/>
       <c r="B399" s="9"/>
       <c r="C399" s="9"/>
       <c r="D399" s="9"/>
@@ -9968,7 +10002,7 @@
       <c r="L399" s="9"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="A400" s="33"/>
+      <c r="A400" s="34"/>
       <c r="B400" s="9"/>
       <c r="C400" s="9"/>
       <c r="D400" s="9"/>
@@ -9982,7 +10016,7 @@
       <c r="L400" s="9"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="33"/>
+      <c r="A401" s="34"/>
       <c r="B401" s="9"/>
       <c r="C401" s="9"/>
       <c r="D401" s="9"/>
@@ -9996,7 +10030,7 @@
       <c r="L401" s="9"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="33"/>
+      <c r="A402" s="34"/>
       <c r="B402" s="9"/>
       <c r="C402" s="9"/>
       <c r="D402" s="9"/>
@@ -10010,7 +10044,7 @@
       <c r="L402" s="9"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="A403" s="33"/>
+      <c r="A403" s="34"/>
       <c r="B403" s="9"/>
       <c r="C403" s="9"/>
       <c r="D403" s="9"/>
@@ -10024,7 +10058,7 @@
       <c r="L403" s="9"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="A404" s="33"/>
+      <c r="A404" s="34"/>
       <c r="B404" s="9"/>
       <c r="C404" s="9"/>
       <c r="D404" s="9"/>
@@ -10038,7 +10072,7 @@
       <c r="L404" s="9"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="A405" s="33"/>
+      <c r="A405" s="34"/>
       <c r="B405" s="9"/>
       <c r="C405" s="9"/>
       <c r="D405" s="9"/>
@@ -10052,7 +10086,7 @@
       <c r="L405" s="9"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="A406" s="33"/>
+      <c r="A406" s="34"/>
       <c r="B406" s="9"/>
       <c r="C406" s="9"/>
       <c r="D406" s="9"/>
@@ -10066,7 +10100,7 @@
       <c r="L406" s="9"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="A407" s="33"/>
+      <c r="A407" s="34"/>
       <c r="B407" s="9"/>
       <c r="C407" s="9"/>
       <c r="D407" s="9"/>
@@ -10080,7 +10114,7 @@
       <c r="L407" s="9"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="A408" s="33"/>
+      <c r="A408" s="34"/>
       <c r="B408" s="9"/>
       <c r="C408" s="9"/>
       <c r="D408" s="9"/>
@@ -10094,7 +10128,7 @@
       <c r="L408" s="9"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="A409" s="33"/>
+      <c r="A409" s="34"/>
       <c r="B409" s="9"/>
       <c r="C409" s="9"/>
       <c r="D409" s="9"/>
@@ -10108,7 +10142,7 @@
       <c r="L409" s="9"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="A410" s="33"/>
+      <c r="A410" s="34"/>
       <c r="B410" s="9"/>
       <c r="C410" s="9"/>
       <c r="D410" s="9"/>
@@ -10122,7 +10156,7 @@
       <c r="L410" s="9"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="A411" s="33"/>
+      <c r="A411" s="34"/>
       <c r="B411" s="9"/>
       <c r="C411" s="9"/>
       <c r="D411" s="9"/>
@@ -10136,7 +10170,7 @@
       <c r="L411" s="9"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="A412" s="33"/>
+      <c r="A412" s="34"/>
       <c r="B412" s="9"/>
       <c r="C412" s="9"/>
       <c r="D412" s="9"/>
@@ -10150,7 +10184,7 @@
       <c r="L412" s="9"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="33"/>
+      <c r="A413" s="34"/>
       <c r="B413" s="9"/>
       <c r="C413" s="9"/>
       <c r="D413" s="9"/>
@@ -10164,7 +10198,7 @@
       <c r="L413" s="9"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="A414" s="33"/>
+      <c r="A414" s="34"/>
       <c r="B414" s="9"/>
       <c r="C414" s="9"/>
       <c r="D414" s="9"/>
@@ -10178,7 +10212,7 @@
       <c r="L414" s="9"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="A415" s="33"/>
+      <c r="A415" s="34"/>
       <c r="B415" s="9"/>
       <c r="C415" s="9"/>
       <c r="D415" s="9"/>
@@ -10192,7 +10226,7 @@
       <c r="L415" s="9"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="33"/>
+      <c r="A416" s="34"/>
       <c r="B416" s="9"/>
       <c r="C416" s="9"/>
       <c r="D416" s="9"/>
@@ -10206,7 +10240,7 @@
       <c r="L416" s="9"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="A417" s="33"/>
+      <c r="A417" s="34"/>
       <c r="B417" s="9"/>
       <c r="C417" s="9"/>
       <c r="D417" s="9"/>
@@ -10220,7 +10254,7 @@
       <c r="L417" s="9"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="A418" s="33"/>
+      <c r="A418" s="34"/>
       <c r="B418" s="9"/>
       <c r="C418" s="9"/>
       <c r="D418" s="9"/>
@@ -10234,7 +10268,7 @@
       <c r="L418" s="9"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="A419" s="33"/>
+      <c r="A419" s="34"/>
       <c r="B419" s="9"/>
       <c r="C419" s="9"/>
       <c r="D419" s="9"/>
@@ -10248,7 +10282,7 @@
       <c r="L419" s="9"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="A420" s="33"/>
+      <c r="A420" s="34"/>
       <c r="B420" s="9"/>
       <c r="C420" s="9"/>
       <c r="D420" s="9"/>
@@ -10262,7 +10296,7 @@
       <c r="L420" s="9"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="A421" s="33"/>
+      <c r="A421" s="34"/>
       <c r="B421" s="9"/>
       <c r="C421" s="9"/>
       <c r="D421" s="9"/>
@@ -10276,7 +10310,7 @@
       <c r="L421" s="9"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="33"/>
+      <c r="A422" s="34"/>
       <c r="B422" s="9"/>
       <c r="C422" s="9"/>
       <c r="D422" s="9"/>
@@ -10290,7 +10324,7 @@
       <c r="L422" s="9"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="A423" s="33"/>
+      <c r="A423" s="34"/>
       <c r="B423" s="9"/>
       <c r="C423" s="9"/>
       <c r="D423" s="9"/>
@@ -10304,7 +10338,7 @@
       <c r="L423" s="9"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="A424" s="33"/>
+      <c r="A424" s="34"/>
       <c r="B424" s="9"/>
       <c r="C424" s="9"/>
       <c r="D424" s="9"/>
@@ -10318,7 +10352,7 @@
       <c r="L424" s="9"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="33"/>
+      <c r="A425" s="34"/>
       <c r="B425" s="9"/>
       <c r="C425" s="9"/>
       <c r="D425" s="9"/>
@@ -10332,7 +10366,7 @@
       <c r="L425" s="9"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="33"/>
+      <c r="A426" s="34"/>
       <c r="B426" s="9"/>
       <c r="C426" s="9"/>
       <c r="D426" s="9"/>
@@ -10346,7 +10380,7 @@
       <c r="L426" s="9"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="33"/>
+      <c r="A427" s="34"/>
       <c r="B427" s="9"/>
       <c r="C427" s="9"/>
       <c r="D427" s="9"/>
@@ -10360,7 +10394,7 @@
       <c r="L427" s="9"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="33"/>
+      <c r="A428" s="34"/>
       <c r="B428" s="9"/>
       <c r="C428" s="9"/>
       <c r="D428" s="9"/>
@@ -10374,7 +10408,7 @@
       <c r="L428" s="9"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="A429" s="33"/>
+      <c r="A429" s="34"/>
       <c r="B429" s="9"/>
       <c r="C429" s="9"/>
       <c r="D429" s="9"/>
@@ -10388,7 +10422,7 @@
       <c r="L429" s="9"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="33"/>
+      <c r="A430" s="34"/>
       <c r="B430" s="9"/>
       <c r="C430" s="9"/>
       <c r="D430" s="9"/>
@@ -10402,7 +10436,7 @@
       <c r="L430" s="9"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="33"/>
+      <c r="A431" s="34"/>
       <c r="B431" s="9"/>
       <c r="C431" s="9"/>
       <c r="D431" s="9"/>
@@ -10416,7 +10450,7 @@
       <c r="L431" s="9"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="33"/>
+      <c r="A432" s="34"/>
       <c r="B432" s="9"/>
       <c r="C432" s="9"/>
       <c r="D432" s="9"/>
@@ -10430,7 +10464,7 @@
       <c r="L432" s="9"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="33"/>
+      <c r="A433" s="34"/>
       <c r="B433" s="9"/>
       <c r="C433" s="9"/>
       <c r="D433" s="9"/>
@@ -10444,7 +10478,7 @@
       <c r="L433" s="9"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="33"/>
+      <c r="A434" s="34"/>
       <c r="B434" s="9"/>
       <c r="C434" s="9"/>
       <c r="D434" s="9"/>
@@ -10458,7 +10492,7 @@
       <c r="L434" s="9"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="33"/>
+      <c r="A435" s="34"/>
       <c r="B435" s="9"/>
       <c r="C435" s="9"/>
       <c r="D435" s="9"/>
@@ -10472,7 +10506,7 @@
       <c r="L435" s="9"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="33"/>
+      <c r="A436" s="34"/>
       <c r="B436" s="9"/>
       <c r="C436" s="9"/>
       <c r="D436" s="9"/>
@@ -10486,7 +10520,7 @@
       <c r="L436" s="9"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="33"/>
+      <c r="A437" s="34"/>
       <c r="B437" s="9"/>
       <c r="C437" s="9"/>
       <c r="D437" s="9"/>
@@ -10500,7 +10534,7 @@
       <c r="L437" s="9"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="33"/>
+      <c r="A438" s="34"/>
       <c r="B438" s="9"/>
       <c r="C438" s="9"/>
       <c r="D438" s="9"/>
@@ -10514,7 +10548,7 @@
       <c r="L438" s="9"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="33"/>
+      <c r="A439" s="34"/>
       <c r="B439" s="9"/>
       <c r="C439" s="9"/>
       <c r="D439" s="9"/>
@@ -10528,7 +10562,7 @@
       <c r="L439" s="9"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="33"/>
+      <c r="A440" s="34"/>
       <c r="B440" s="9"/>
       <c r="C440" s="9"/>
       <c r="D440" s="9"/>
@@ -10542,7 +10576,7 @@
       <c r="L440" s="9"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="33"/>
+      <c r="A441" s="34"/>
       <c r="B441" s="9"/>
       <c r="C441" s="9"/>
       <c r="D441" s="9"/>
@@ -10556,7 +10590,7 @@
       <c r="L441" s="9"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="33"/>
+      <c r="A442" s="34"/>
       <c r="B442" s="9"/>
       <c r="C442" s="9"/>
       <c r="D442" s="9"/>
@@ -10570,7 +10604,7 @@
       <c r="L442" s="9"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="33"/>
+      <c r="A443" s="34"/>
       <c r="B443" s="9"/>
       <c r="C443" s="9"/>
       <c r="D443" s="9"/>
@@ -10584,7 +10618,7 @@
       <c r="L443" s="9"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="33"/>
+      <c r="A444" s="34"/>
       <c r="B444" s="9"/>
       <c r="C444" s="9"/>
       <c r="D444" s="9"/>
@@ -10598,7 +10632,7 @@
       <c r="L444" s="9"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="33"/>
+      <c r="A445" s="34"/>
       <c r="B445" s="9"/>
       <c r="C445" s="9"/>
       <c r="D445" s="9"/>
@@ -10612,7 +10646,7 @@
       <c r="L445" s="9"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="33"/>
+      <c r="A446" s="34"/>
       <c r="B446" s="9"/>
       <c r="C446" s="9"/>
       <c r="D446" s="9"/>
@@ -10626,7 +10660,7 @@
       <c r="L446" s="9"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="A447" s="33"/>
+      <c r="A447" s="34"/>
       <c r="B447" s="9"/>
       <c r="C447" s="9"/>
       <c r="D447" s="9"/>
@@ -10640,7 +10674,7 @@
       <c r="L447" s="9"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="A448" s="33"/>
+      <c r="A448" s="34"/>
       <c r="B448" s="9"/>
       <c r="C448" s="9"/>
       <c r="D448" s="9"/>
@@ -10654,7 +10688,7 @@
       <c r="L448" s="9"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="A449" s="33"/>
+      <c r="A449" s="34"/>
       <c r="B449" s="9"/>
       <c r="C449" s="9"/>
       <c r="D449" s="9"/>
@@ -10668,7 +10702,7 @@
       <c r="L449" s="9"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="A450" s="33"/>
+      <c r="A450" s="34"/>
       <c r="B450" s="9"/>
       <c r="C450" s="9"/>
       <c r="D450" s="9"/>
@@ -10682,7 +10716,7 @@
       <c r="L450" s="9"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="33"/>
+      <c r="A451" s="34"/>
       <c r="B451" s="9"/>
       <c r="C451" s="9"/>
       <c r="D451" s="9"/>
@@ -10696,7 +10730,7 @@
       <c r="L451" s="9"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="A452" s="33"/>
+      <c r="A452" s="34"/>
       <c r="B452" s="9"/>
       <c r="C452" s="9"/>
       <c r="D452" s="9"/>
@@ -10710,7 +10744,7 @@
       <c r="L452" s="9"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="33"/>
+      <c r="A453" s="34"/>
       <c r="B453" s="9"/>
       <c r="C453" s="9"/>
       <c r="D453" s="9"/>
@@ -10724,7 +10758,7 @@
       <c r="L453" s="9"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="A454" s="33"/>
+      <c r="A454" s="34"/>
       <c r="B454" s="9"/>
       <c r="C454" s="9"/>
       <c r="D454" s="9"/>
@@ -10738,7 +10772,7 @@
       <c r="L454" s="9"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="A455" s="33"/>
+      <c r="A455" s="34"/>
       <c r="B455" s="9"/>
       <c r="C455" s="9"/>
       <c r="D455" s="9"/>
@@ -10752,7 +10786,7 @@
       <c r="L455" s="9"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="33"/>
+      <c r="A456" s="34"/>
       <c r="B456" s="9"/>
       <c r="C456" s="9"/>
       <c r="D456" s="9"/>
@@ -10766,7 +10800,7 @@
       <c r="L456" s="9"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="A457" s="33"/>
+      <c r="A457" s="34"/>
       <c r="B457" s="9"/>
       <c r="C457" s="9"/>
       <c r="D457" s="9"/>
@@ -10780,7 +10814,7 @@
       <c r="L457" s="9"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="A458" s="33"/>
+      <c r="A458" s="34"/>
       <c r="B458" s="9"/>
       <c r="C458" s="9"/>
       <c r="D458" s="9"/>
@@ -10794,7 +10828,7 @@
       <c r="L458" s="9"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="A459" s="33"/>
+      <c r="A459" s="34"/>
       <c r="B459" s="9"/>
       <c r="C459" s="9"/>
       <c r="D459" s="9"/>
@@ -10808,7 +10842,7 @@
       <c r="L459" s="9"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="A460" s="33"/>
+      <c r="A460" s="34"/>
       <c r="B460" s="9"/>
       <c r="C460" s="9"/>
       <c r="D460" s="9"/>
@@ -10822,7 +10856,7 @@
       <c r="L460" s="9"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="33"/>
+      <c r="A461" s="34"/>
       <c r="B461" s="9"/>
       <c r="C461" s="9"/>
       <c r="D461" s="9"/>
@@ -10836,7 +10870,7 @@
       <c r="L461" s="9"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="33"/>
+      <c r="A462" s="34"/>
       <c r="B462" s="9"/>
       <c r="C462" s="9"/>
       <c r="D462" s="9"/>
@@ -10850,7 +10884,7 @@
       <c r="L462" s="9"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="A463" s="33"/>
+      <c r="A463" s="34"/>
       <c r="B463" s="9"/>
       <c r="C463" s="9"/>
       <c r="D463" s="9"/>
@@ -10864,7 +10898,7 @@
       <c r="L463" s="9"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="33"/>
+      <c r="A464" s="34"/>
       <c r="B464" s="9"/>
       <c r="C464" s="9"/>
       <c r="D464" s="9"/>
@@ -10878,7 +10912,7 @@
       <c r="L464" s="9"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="33"/>
+      <c r="A465" s="34"/>
       <c r="B465" s="9"/>
       <c r="C465" s="9"/>
       <c r="D465" s="9"/>
@@ -10892,7 +10926,7 @@
       <c r="L465" s="9"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="33"/>
+      <c r="A466" s="34"/>
       <c r="B466" s="9"/>
       <c r="C466" s="9"/>
       <c r="D466" s="9"/>
@@ -10906,7 +10940,7 @@
       <c r="L466" s="9"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="A467" s="33"/>
+      <c r="A467" s="34"/>
       <c r="B467" s="9"/>
       <c r="C467" s="9"/>
       <c r="D467" s="9"/>
@@ -10920,7 +10954,7 @@
       <c r="L467" s="9"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="33"/>
+      <c r="A468" s="34"/>
       <c r="B468" s="9"/>
       <c r="C468" s="9"/>
       <c r="D468" s="9"/>
@@ -10934,7 +10968,7 @@
       <c r="L468" s="9"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="33"/>
+      <c r="A469" s="34"/>
       <c r="B469" s="9"/>
       <c r="C469" s="9"/>
       <c r="D469" s="9"/>
@@ -10948,7 +10982,7 @@
       <c r="L469" s="9"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="33"/>
+      <c r="A470" s="34"/>
       <c r="B470" s="9"/>
       <c r="C470" s="9"/>
       <c r="D470" s="9"/>
@@ -10962,7 +10996,7 @@
       <c r="L470" s="9"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="33"/>
+      <c r="A471" s="34"/>
       <c r="B471" s="9"/>
       <c r="C471" s="9"/>
       <c r="D471" s="9"/>
@@ -10976,7 +11010,7 @@
       <c r="L471" s="9"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="A472" s="33"/>
+      <c r="A472" s="34"/>
       <c r="B472" s="9"/>
       <c r="C472" s="9"/>
       <c r="D472" s="9"/>
@@ -10990,7 +11024,7 @@
       <c r="L472" s="9"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="33"/>
+      <c r="A473" s="34"/>
       <c r="B473" s="9"/>
       <c r="C473" s="9"/>
       <c r="D473" s="9"/>
@@ -11004,7 +11038,7 @@
       <c r="L473" s="9"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="A474" s="33"/>
+      <c r="A474" s="34"/>
       <c r="B474" s="9"/>
       <c r="C474" s="9"/>
       <c r="D474" s="9"/>
@@ -11018,7 +11052,7 @@
       <c r="L474" s="9"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="33"/>
+      <c r="A475" s="34"/>
       <c r="B475" s="9"/>
       <c r="C475" s="9"/>
       <c r="D475" s="9"/>
@@ -11032,7 +11066,7 @@
       <c r="L475" s="9"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="33"/>
+      <c r="A476" s="34"/>
       <c r="B476" s="9"/>
       <c r="C476" s="9"/>
       <c r="D476" s="9"/>
@@ -11046,7 +11080,7 @@
       <c r="L476" s="9"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="33"/>
+      <c r="A477" s="34"/>
       <c r="B477" s="9"/>
       <c r="C477" s="9"/>
       <c r="D477" s="9"/>
@@ -11060,7 +11094,7 @@
       <c r="L477" s="9"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="33"/>
+      <c r="A478" s="34"/>
       <c r="B478" s="9"/>
       <c r="C478" s="9"/>
       <c r="D478" s="9"/>
@@ -11074,7 +11108,7 @@
       <c r="L478" s="9"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="A479" s="33"/>
+      <c r="A479" s="34"/>
       <c r="B479" s="9"/>
       <c r="C479" s="9"/>
       <c r="D479" s="9"/>
@@ -11088,7 +11122,7 @@
       <c r="L479" s="9"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="A480" s="33"/>
+      <c r="A480" s="34"/>
       <c r="B480" s="9"/>
       <c r="C480" s="9"/>
       <c r="D480" s="9"/>
@@ -11102,7 +11136,7 @@
       <c r="L480" s="9"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="A481" s="33"/>
+      <c r="A481" s="34"/>
       <c r="B481" s="9"/>
       <c r="C481" s="9"/>
       <c r="D481" s="9"/>
@@ -11116,7 +11150,7 @@
       <c r="L481" s="9"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="A482" s="33"/>
+      <c r="A482" s="34"/>
       <c r="B482" s="9"/>
       <c r="C482" s="9"/>
       <c r="D482" s="9"/>
@@ -11130,7 +11164,7 @@
       <c r="L482" s="9"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="A483" s="33"/>
+      <c r="A483" s="34"/>
       <c r="B483" s="9"/>
       <c r="C483" s="9"/>
       <c r="D483" s="9"/>
@@ -11144,7 +11178,7 @@
       <c r="L483" s="9"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="A484" s="33"/>
+      <c r="A484" s="34"/>
       <c r="B484" s="9"/>
       <c r="C484" s="9"/>
       <c r="D484" s="9"/>
@@ -11158,7 +11192,7 @@
       <c r="L484" s="9"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="A485" s="33"/>
+      <c r="A485" s="34"/>
       <c r="B485" s="9"/>
       <c r="C485" s="9"/>
       <c r="D485" s="9"/>
@@ -11172,7 +11206,7 @@
       <c r="L485" s="9"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="A486" s="33"/>
+      <c r="A486" s="34"/>
       <c r="B486" s="9"/>
       <c r="C486" s="9"/>
       <c r="D486" s="9"/>
@@ -11186,7 +11220,7 @@
       <c r="L486" s="9"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="A487" s="33"/>
+      <c r="A487" s="34"/>
       <c r="B487" s="9"/>
       <c r="C487" s="9"/>
       <c r="D487" s="9"/>
@@ -11200,7 +11234,7 @@
       <c r="L487" s="9"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="A488" s="33"/>
+      <c r="A488" s="34"/>
       <c r="B488" s="9"/>
       <c r="C488" s="9"/>
       <c r="D488" s="9"/>
@@ -11214,7 +11248,7 @@
       <c r="L488" s="9"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="A489" s="33"/>
+      <c r="A489" s="34"/>
       <c r="B489" s="9"/>
       <c r="C489" s="9"/>
       <c r="D489" s="9"/>
@@ -11228,7 +11262,7 @@
       <c r="L489" s="9"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="A490" s="33"/>
+      <c r="A490" s="34"/>
       <c r="B490" s="9"/>
       <c r="C490" s="9"/>
       <c r="D490" s="9"/>
@@ -11242,7 +11276,7 @@
       <c r="L490" s="9"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="A491" s="33"/>
+      <c r="A491" s="34"/>
       <c r="B491" s="9"/>
       <c r="C491" s="9"/>
       <c r="D491" s="9"/>
@@ -11256,7 +11290,7 @@
       <c r="L491" s="9"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="A492" s="33"/>
+      <c r="A492" s="34"/>
       <c r="B492" s="9"/>
       <c r="C492" s="9"/>
       <c r="D492" s="9"/>
@@ -11270,7 +11304,7 @@
       <c r="L492" s="9"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="A493" s="33"/>
+      <c r="A493" s="34"/>
       <c r="B493" s="9"/>
       <c r="C493" s="9"/>
       <c r="D493" s="9"/>
@@ -11284,7 +11318,7 @@
       <c r="L493" s="9"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="A494" s="33"/>
+      <c r="A494" s="34"/>
       <c r="B494" s="9"/>
       <c r="C494" s="9"/>
       <c r="D494" s="9"/>
@@ -11298,7 +11332,7 @@
       <c r="L494" s="9"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="A495" s="33"/>
+      <c r="A495" s="34"/>
       <c r="B495" s="9"/>
       <c r="C495" s="9"/>
       <c r="D495" s="9"/>
@@ -11312,7 +11346,7 @@
       <c r="L495" s="9"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="A496" s="33"/>
+      <c r="A496" s="34"/>
       <c r="B496" s="9"/>
       <c r="C496" s="9"/>
       <c r="D496" s="9"/>
@@ -11326,7 +11360,7 @@
       <c r="L496" s="9"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="A497" s="33"/>
+      <c r="A497" s="34"/>
       <c r="B497" s="9"/>
       <c r="C497" s="9"/>
       <c r="D497" s="9"/>
@@ -11340,7 +11374,7 @@
       <c r="L497" s="9"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="A498" s="33"/>
+      <c r="A498" s="34"/>
       <c r="B498" s="9"/>
       <c r="C498" s="9"/>
       <c r="D498" s="9"/>
@@ -11354,7 +11388,7 @@
       <c r="L498" s="9"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="A499" s="33"/>
+      <c r="A499" s="34"/>
       <c r="B499" s="9"/>
       <c r="C499" s="9"/>
       <c r="D499" s="9"/>
@@ -11368,7 +11402,7 @@
       <c r="L499" s="9"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="A500" s="33"/>
+      <c r="A500" s="34"/>
       <c r="B500" s="9"/>
       <c r="C500" s="9"/>
       <c r="D500" s="9"/>
@@ -11382,7 +11416,7 @@
       <c r="L500" s="9"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="A501" s="33"/>
+      <c r="A501" s="34"/>
       <c r="B501" s="9"/>
       <c r="C501" s="9"/>
       <c r="D501" s="9"/>
@@ -11396,7 +11430,7 @@
       <c r="L501" s="9"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="A502" s="33"/>
+      <c r="A502" s="34"/>
       <c r="B502" s="9"/>
       <c r="C502" s="9"/>
       <c r="D502" s="9"/>
@@ -11410,7 +11444,7 @@
       <c r="L502" s="9"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="A503" s="33"/>
+      <c r="A503" s="34"/>
       <c r="B503" s="9"/>
       <c r="C503" s="9"/>
       <c r="D503" s="9"/>
@@ -11424,7 +11458,7 @@
       <c r="L503" s="9"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="A504" s="33"/>
+      <c r="A504" s="34"/>
       <c r="B504" s="9"/>
       <c r="C504" s="9"/>
       <c r="D504" s="9"/>
@@ -11438,7 +11472,7 @@
       <c r="L504" s="9"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="A505" s="33"/>
+      <c r="A505" s="34"/>
       <c r="B505" s="9"/>
       <c r="C505" s="9"/>
       <c r="D505" s="9"/>
@@ -11452,7 +11486,7 @@
       <c r="L505" s="9"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="A506" s="33"/>
+      <c r="A506" s="34"/>
       <c r="B506" s="9"/>
       <c r="C506" s="9"/>
       <c r="D506" s="9"/>
@@ -11466,7 +11500,7 @@
       <c r="L506" s="9"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="A507" s="33"/>
+      <c r="A507" s="34"/>
       <c r="B507" s="9"/>
       <c r="C507" s="9"/>
       <c r="D507" s="9"/>
@@ -11480,7 +11514,7 @@
       <c r="L507" s="9"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="A508" s="33"/>
+      <c r="A508" s="34"/>
       <c r="B508" s="9"/>
       <c r="C508" s="9"/>
       <c r="D508" s="9"/>
@@ -11494,7 +11528,7 @@
       <c r="L508" s="9"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="A509" s="33"/>
+      <c r="A509" s="34"/>
       <c r="B509" s="9"/>
       <c r="C509" s="9"/>
       <c r="D509" s="9"/>
@@ -11508,7 +11542,7 @@
       <c r="L509" s="9"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="A510" s="33"/>
+      <c r="A510" s="34"/>
       <c r="B510" s="9"/>
       <c r="C510" s="9"/>
       <c r="D510" s="9"/>
@@ -11522,7 +11556,7 @@
       <c r="L510" s="9"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="A511" s="33"/>
+      <c r="A511" s="34"/>
       <c r="B511" s="9"/>
       <c r="C511" s="9"/>
       <c r="D511" s="9"/>
@@ -11536,7 +11570,7 @@
       <c r="L511" s="9"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="A512" s="33"/>
+      <c r="A512" s="34"/>
       <c r="B512" s="9"/>
       <c r="C512" s="9"/>
       <c r="D512" s="9"/>
@@ -11550,7 +11584,7 @@
       <c r="L512" s="9"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="A513" s="33"/>
+      <c r="A513" s="34"/>
       <c r="B513" s="9"/>
       <c r="C513" s="9"/>
       <c r="D513" s="9"/>
@@ -11564,7 +11598,7 @@
       <c r="L513" s="9"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="A514" s="33"/>
+      <c r="A514" s="34"/>
       <c r="B514" s="9"/>
       <c r="C514" s="9"/>
       <c r="D514" s="9"/>
@@ -11578,7 +11612,7 @@
       <c r="L514" s="9"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="A515" s="33"/>
+      <c r="A515" s="34"/>
       <c r="B515" s="9"/>
       <c r="C515" s="9"/>
       <c r="D515" s="9"/>
@@ -11592,7 +11626,7 @@
       <c r="L515" s="9"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="A516" s="33"/>
+      <c r="A516" s="34"/>
       <c r="B516" s="9"/>
       <c r="C516" s="9"/>
       <c r="D516" s="9"/>
@@ -11606,7 +11640,7 @@
       <c r="L516" s="9"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="A517" s="33"/>
+      <c r="A517" s="34"/>
       <c r="B517" s="9"/>
       <c r="C517" s="9"/>
       <c r="D517" s="9"/>
@@ -11620,7 +11654,7 @@
       <c r="L517" s="9"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="A518" s="33"/>
+      <c r="A518" s="34"/>
       <c r="B518" s="9"/>
       <c r="C518" s="9"/>
       <c r="D518" s="9"/>
@@ -11634,7 +11668,7 @@
       <c r="L518" s="9"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="A519" s="33"/>
+      <c r="A519" s="34"/>
       <c r="B519" s="9"/>
       <c r="C519" s="9"/>
       <c r="D519" s="9"/>
@@ -11648,7 +11682,7 @@
       <c r="L519" s="9"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="A520" s="33"/>
+      <c r="A520" s="34"/>
       <c r="B520" s="9"/>
       <c r="C520" s="9"/>
       <c r="D520" s="9"/>
@@ -11662,7 +11696,7 @@
       <c r="L520" s="9"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="A521" s="33"/>
+      <c r="A521" s="34"/>
       <c r="B521" s="9"/>
       <c r="C521" s="9"/>
       <c r="D521" s="9"/>
@@ -11676,7 +11710,7 @@
       <c r="L521" s="9"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="A522" s="33"/>
+      <c r="A522" s="34"/>
       <c r="B522" s="9"/>
       <c r="C522" s="9"/>
       <c r="D522" s="9"/>
@@ -11690,7 +11724,7 @@
       <c r="L522" s="9"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="A523" s="33"/>
+      <c r="A523" s="34"/>
       <c r="B523" s="9"/>
       <c r="C523" s="9"/>
       <c r="D523" s="9"/>
@@ -11704,7 +11738,7 @@
       <c r="L523" s="9"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="A524" s="33"/>
+      <c r="A524" s="34"/>
       <c r="B524" s="9"/>
       <c r="C524" s="9"/>
       <c r="D524" s="9"/>
@@ -11718,7 +11752,7 @@
       <c r="L524" s="9"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="A525" s="33"/>
+      <c r="A525" s="34"/>
       <c r="B525" s="9"/>
       <c r="C525" s="9"/>
       <c r="D525" s="9"/>
@@ -11732,7 +11766,7 @@
       <c r="L525" s="9"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="A526" s="33"/>
+      <c r="A526" s="34"/>
       <c r="B526" s="9"/>
       <c r="C526" s="9"/>
       <c r="D526" s="9"/>
@@ -11746,7 +11780,7 @@
       <c r="L526" s="9"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="A527" s="33"/>
+      <c r="A527" s="34"/>
       <c r="B527" s="9"/>
       <c r="C527" s="9"/>
       <c r="D527" s="9"/>
@@ -11760,7 +11794,7 @@
       <c r="L527" s="9"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="A528" s="33"/>
+      <c r="A528" s="34"/>
       <c r="B528" s="9"/>
       <c r="C528" s="9"/>
       <c r="D528" s="9"/>
@@ -11774,7 +11808,7 @@
       <c r="L528" s="9"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="A529" s="33"/>
+      <c r="A529" s="34"/>
       <c r="B529" s="9"/>
       <c r="C529" s="9"/>
       <c r="D529" s="9"/>
@@ -11788,7 +11822,7 @@
       <c r="L529" s="9"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="A530" s="33"/>
+      <c r="A530" s="34"/>
       <c r="B530" s="9"/>
       <c r="C530" s="9"/>
       <c r="D530" s="9"/>
@@ -11802,7 +11836,7 @@
       <c r="L530" s="9"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="A531" s="33"/>
+      <c r="A531" s="34"/>
       <c r="B531" s="9"/>
       <c r="C531" s="9"/>
       <c r="D531" s="9"/>
@@ -11816,7 +11850,7 @@
       <c r="L531" s="9"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="A532" s="33"/>
+      <c r="A532" s="34"/>
       <c r="B532" s="9"/>
       <c r="C532" s="9"/>
       <c r="D532" s="9"/>
@@ -11830,7 +11864,7 @@
       <c r="L532" s="9"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="A533" s="33"/>
+      <c r="A533" s="34"/>
       <c r="B533" s="9"/>
       <c r="C533" s="9"/>
       <c r="D533" s="9"/>
@@ -11844,7 +11878,7 @@
       <c r="L533" s="9"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="A534" s="33"/>
+      <c r="A534" s="34"/>
       <c r="B534" s="9"/>
       <c r="C534" s="9"/>
       <c r="D534" s="9"/>
@@ -11858,7 +11892,7 @@
       <c r="L534" s="9"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="A535" s="33"/>
+      <c r="A535" s="34"/>
       <c r="B535" s="9"/>
       <c r="C535" s="9"/>
       <c r="D535" s="9"/>
@@ -11872,7 +11906,7 @@
       <c r="L535" s="9"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="A536" s="33"/>
+      <c r="A536" s="34"/>
       <c r="B536" s="9"/>
       <c r="C536" s="9"/>
       <c r="D536" s="9"/>
@@ -11886,7 +11920,7 @@
       <c r="L536" s="9"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="A537" s="33"/>
+      <c r="A537" s="34"/>
       <c r="B537" s="9"/>
       <c r="C537" s="9"/>
       <c r="D537" s="9"/>
@@ -11900,7 +11934,7 @@
       <c r="L537" s="9"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="A538" s="33"/>
+      <c r="A538" s="34"/>
       <c r="B538" s="9"/>
       <c r="C538" s="9"/>
       <c r="D538" s="9"/>
@@ -11914,7 +11948,7 @@
       <c r="L538" s="9"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="A539" s="33"/>
+      <c r="A539" s="34"/>
       <c r="B539" s="9"/>
       <c r="C539" s="9"/>
       <c r="D539" s="9"/>
@@ -11928,7 +11962,7 @@
       <c r="L539" s="9"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="A540" s="33"/>
+      <c r="A540" s="34"/>
       <c r="B540" s="9"/>
       <c r="C540" s="9"/>
       <c r="D540" s="9"/>
@@ -11942,7 +11976,7 @@
       <c r="L540" s="9"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="A541" s="33"/>
+      <c r="A541" s="34"/>
       <c r="B541" s="9"/>
       <c r="C541" s="9"/>
       <c r="D541" s="9"/>
@@ -11956,7 +11990,7 @@
       <c r="L541" s="9"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="A542" s="33"/>
+      <c r="A542" s="34"/>
       <c r="B542" s="9"/>
       <c r="C542" s="9"/>
       <c r="D542" s="9"/>
@@ -11970,7 +12004,7 @@
       <c r="L542" s="9"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="A543" s="33"/>
+      <c r="A543" s="34"/>
       <c r="B543" s="9"/>
       <c r="C543" s="9"/>
       <c r="D543" s="9"/>
@@ -11984,7 +12018,7 @@
       <c r="L543" s="9"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="A544" s="33"/>
+      <c r="A544" s="34"/>
       <c r="B544" s="9"/>
       <c r="C544" s="9"/>
       <c r="D544" s="9"/>
@@ -11998,7 +12032,7 @@
       <c r="L544" s="9"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="A545" s="33"/>
+      <c r="A545" s="34"/>
       <c r="B545" s="9"/>
       <c r="C545" s="9"/>
       <c r="D545" s="9"/>
@@ -12012,7 +12046,7 @@
       <c r="L545" s="9"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="A546" s="33"/>
+      <c r="A546" s="34"/>
       <c r="B546" s="9"/>
       <c r="C546" s="9"/>
       <c r="D546" s="9"/>
@@ -12026,7 +12060,7 @@
       <c r="L546" s="9"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="A547" s="33"/>
+      <c r="A547" s="34"/>
       <c r="B547" s="9"/>
       <c r="C547" s="9"/>
       <c r="D547" s="9"/>
@@ -12040,7 +12074,7 @@
       <c r="L547" s="9"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="A548" s="33"/>
+      <c r="A548" s="34"/>
       <c r="B548" s="9"/>
       <c r="C548" s="9"/>
       <c r="D548" s="9"/>
@@ -12054,7 +12088,7 @@
       <c r="L548" s="9"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="A549" s="33"/>
+      <c r="A549" s="34"/>
       <c r="B549" s="9"/>
       <c r="C549" s="9"/>
       <c r="D549" s="9"/>
@@ -12068,7 +12102,7 @@
       <c r="L549" s="9"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="A550" s="33"/>
+      <c r="A550" s="34"/>
       <c r="B550" s="9"/>
       <c r="C550" s="9"/>
       <c r="D550" s="9"/>
@@ -12082,7 +12116,7 @@
       <c r="L550" s="9"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="A551" s="33"/>
+      <c r="A551" s="34"/>
       <c r="B551" s="9"/>
       <c r="C551" s="9"/>
       <c r="D551" s="9"/>
@@ -12096,7 +12130,7 @@
       <c r="L551" s="9"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="A552" s="33"/>
+      <c r="A552" s="34"/>
       <c r="B552" s="9"/>
       <c r="C552" s="9"/>
       <c r="D552" s="9"/>
@@ -12110,7 +12144,7 @@
       <c r="L552" s="9"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="A553" s="33"/>
+      <c r="A553" s="34"/>
       <c r="B553" s="9"/>
       <c r="C553" s="9"/>
       <c r="D553" s="9"/>
@@ -12124,7 +12158,7 @@
       <c r="L553" s="9"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="A554" s="33"/>
+      <c r="A554" s="34"/>
       <c r="B554" s="9"/>
       <c r="C554" s="9"/>
       <c r="D554" s="9"/>
@@ -12138,7 +12172,7 @@
       <c r="L554" s="9"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="A555" s="33"/>
+      <c r="A555" s="34"/>
       <c r="B555" s="9"/>
       <c r="C555" s="9"/>
       <c r="D555" s="9"/>
@@ -12152,7 +12186,7 @@
       <c r="L555" s="9"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="A556" s="33"/>
+      <c r="A556" s="34"/>
       <c r="B556" s="9"/>
       <c r="C556" s="9"/>
       <c r="D556" s="9"/>
@@ -12166,7 +12200,7 @@
       <c r="L556" s="9"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="A557" s="33"/>
+      <c r="A557" s="34"/>
       <c r="B557" s="9"/>
       <c r="C557" s="9"/>
       <c r="D557" s="9"/>
@@ -12180,7 +12214,7 @@
       <c r="L557" s="9"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="A558" s="33"/>
+      <c r="A558" s="34"/>
       <c r="B558" s="9"/>
       <c r="C558" s="9"/>
       <c r="D558" s="9"/>
@@ -12194,7 +12228,7 @@
       <c r="L558" s="9"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="A559" s="33"/>
+      <c r="A559" s="34"/>
       <c r="B559" s="9"/>
       <c r="C559" s="9"/>
       <c r="D559" s="9"/>
@@ -12208,7 +12242,7 @@
       <c r="L559" s="9"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="A560" s="33"/>
+      <c r="A560" s="34"/>
       <c r="B560" s="9"/>
       <c r="C560" s="9"/>
       <c r="D560" s="9"/>
@@ -12222,7 +12256,7 @@
       <c r="L560" s="9"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="A561" s="33"/>
+      <c r="A561" s="34"/>
       <c r="B561" s="9"/>
       <c r="C561" s="9"/>
       <c r="D561" s="9"/>
@@ -12236,7 +12270,7 @@
       <c r="L561" s="9"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="A562" s="33"/>
+      <c r="A562" s="34"/>
       <c r="B562" s="9"/>
       <c r="C562" s="9"/>
       <c r="D562" s="9"/>
@@ -12250,7 +12284,7 @@
       <c r="L562" s="9"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="A563" s="33"/>
+      <c r="A563" s="34"/>
       <c r="B563" s="9"/>
       <c r="C563" s="9"/>
       <c r="D563" s="9"/>
@@ -12264,7 +12298,7 @@
       <c r="L563" s="9"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="A564" s="33"/>
+      <c r="A564" s="34"/>
       <c r="B564" s="9"/>
       <c r="C564" s="9"/>
       <c r="D564" s="9"/>
@@ -12278,7 +12312,7 @@
       <c r="L564" s="9"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="A565" s="33"/>
+      <c r="A565" s="34"/>
       <c r="B565" s="9"/>
       <c r="C565" s="9"/>
       <c r="D565" s="9"/>
@@ -12292,7 +12326,7 @@
       <c r="L565" s="9"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="A566" s="33"/>
+      <c r="A566" s="34"/>
       <c r="B566" s="9"/>
       <c r="C566" s="9"/>
       <c r="D566" s="9"/>
@@ -12306,7 +12340,7 @@
       <c r="L566" s="9"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="A567" s="33"/>
+      <c r="A567" s="34"/>
       <c r="B567" s="9"/>
       <c r="C567" s="9"/>
       <c r="D567" s="9"/>
@@ -12320,7 +12354,7 @@
       <c r="L567" s="9"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="A568" s="33"/>
+      <c r="A568" s="34"/>
       <c r="B568" s="9"/>
       <c r="C568" s="9"/>
       <c r="D568" s="9"/>
@@ -12334,7 +12368,7 @@
       <c r="L568" s="9"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="A569" s="33"/>
+      <c r="A569" s="34"/>
       <c r="B569" s="9"/>
       <c r="C569" s="9"/>
       <c r="D569" s="9"/>
@@ -12348,7 +12382,7 @@
       <c r="L569" s="9"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="A570" s="33"/>
+      <c r="A570" s="34"/>
       <c r="B570" s="9"/>
       <c r="C570" s="9"/>
       <c r="D570" s="9"/>
@@ -12362,7 +12396,7 @@
       <c r="L570" s="9"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="A571" s="33"/>
+      <c r="A571" s="34"/>
       <c r="B571" s="9"/>
       <c r="C571" s="9"/>
       <c r="D571" s="9"/>
@@ -12376,7 +12410,7 @@
       <c r="L571" s="9"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="A572" s="33"/>
+      <c r="A572" s="34"/>
       <c r="B572" s="9"/>
       <c r="C572" s="9"/>
       <c r="D572" s="9"/>
@@ -12390,7 +12424,7 @@
       <c r="L572" s="9"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="A573" s="33"/>
+      <c r="A573" s="34"/>
       <c r="B573" s="9"/>
       <c r="C573" s="9"/>
       <c r="D573" s="9"/>
@@ -12404,7 +12438,7 @@
       <c r="L573" s="9"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="A574" s="33"/>
+      <c r="A574" s="34"/>
       <c r="B574" s="9"/>
       <c r="C574" s="9"/>
       <c r="D574" s="9"/>
@@ -12418,7 +12452,7 @@
       <c r="L574" s="9"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="A575" s="33"/>
+      <c r="A575" s="34"/>
       <c r="B575" s="9"/>
       <c r="C575" s="9"/>
       <c r="D575" s="9"/>
@@ -12432,7 +12466,7 @@
       <c r="L575" s="9"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="A576" s="33"/>
+      <c r="A576" s="34"/>
       <c r="B576" s="9"/>
       <c r="C576" s="9"/>
       <c r="D576" s="9"/>
@@ -12446,7 +12480,7 @@
       <c r="L576" s="9"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="A577" s="33"/>
+      <c r="A577" s="34"/>
       <c r="B577" s="9"/>
       <c r="C577" s="9"/>
       <c r="D577" s="9"/>
@@ -12460,7 +12494,7 @@
       <c r="L577" s="9"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="A578" s="33"/>
+      <c r="A578" s="34"/>
       <c r="B578" s="9"/>
       <c r="C578" s="9"/>
       <c r="D578" s="9"/>
@@ -12474,7 +12508,7 @@
       <c r="L578" s="9"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="A579" s="33"/>
+      <c r="A579" s="34"/>
       <c r="B579" s="9"/>
       <c r="C579" s="9"/>
       <c r="D579" s="9"/>
@@ -12488,7 +12522,7 @@
       <c r="L579" s="9"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="A580" s="33"/>
+      <c r="A580" s="34"/>
       <c r="B580" s="9"/>
       <c r="C580" s="9"/>
       <c r="D580" s="9"/>
@@ -12502,7 +12536,7 @@
       <c r="L580" s="9"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="A581" s="33"/>
+      <c r="A581" s="34"/>
       <c r="B581" s="9"/>
       <c r="C581" s="9"/>
       <c r="D581" s="9"/>
@@ -12516,7 +12550,7 @@
       <c r="L581" s="9"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="A582" s="33"/>
+      <c r="A582" s="34"/>
       <c r="B582" s="9"/>
       <c r="C582" s="9"/>
       <c r="D582" s="9"/>
@@ -12530,7 +12564,7 @@
       <c r="L582" s="9"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="A583" s="33"/>
+      <c r="A583" s="34"/>
       <c r="B583" s="9"/>
       <c r="C583" s="9"/>
       <c r="D583" s="9"/>
@@ -12544,7 +12578,7 @@
       <c r="L583" s="9"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="A584" s="33"/>
+      <c r="A584" s="34"/>
       <c r="B584" s="9"/>
       <c r="C584" s="9"/>
       <c r="D584" s="9"/>
@@ -12558,7 +12592,7 @@
       <c r="L584" s="9"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="A585" s="33"/>
+      <c r="A585" s="34"/>
       <c r="B585" s="9"/>
       <c r="C585" s="9"/>
       <c r="D585" s="9"/>
@@ -12572,7 +12606,7 @@
       <c r="L585" s="9"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="A586" s="33"/>
+      <c r="A586" s="34"/>
       <c r="B586" s="9"/>
       <c r="C586" s="9"/>
       <c r="D586" s="9"/>
@@ -12586,7 +12620,7 @@
       <c r="L586" s="9"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="A587" s="33"/>
+      <c r="A587" s="34"/>
       <c r="B587" s="9"/>
       <c r="C587" s="9"/>
       <c r="D587" s="9"/>
@@ -12600,7 +12634,7 @@
       <c r="L587" s="9"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="A588" s="33"/>
+      <c r="A588" s="34"/>
       <c r="B588" s="9"/>
       <c r="C588" s="9"/>
       <c r="D588" s="9"/>
@@ -12614,7 +12648,7 @@
       <c r="L588" s="9"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="A589" s="33"/>
+      <c r="A589" s="34"/>
       <c r="B589" s="9"/>
       <c r="C589" s="9"/>
       <c r="D589" s="9"/>
@@ -12628,7 +12662,7 @@
       <c r="L589" s="9"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="A590" s="33"/>
+      <c r="A590" s="34"/>
       <c r="B590" s="9"/>
       <c r="C590" s="9"/>
       <c r="D590" s="9"/>
@@ -12642,7 +12676,7 @@
       <c r="L590" s="9"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="A591" s="33"/>
+      <c r="A591" s="34"/>
       <c r="B591" s="9"/>
       <c r="C591" s="9"/>
       <c r="D591" s="9"/>
@@ -12656,7 +12690,7 @@
       <c r="L591" s="9"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="A592" s="33"/>
+      <c r="A592" s="34"/>
       <c r="B592" s="9"/>
       <c r="C592" s="9"/>
       <c r="D592" s="9"/>
@@ -12670,7 +12704,7 @@
       <c r="L592" s="9"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="A593" s="33"/>
+      <c r="A593" s="34"/>
       <c r="B593" s="9"/>
       <c r="C593" s="9"/>
       <c r="D593" s="9"/>
@@ -12684,7 +12718,7 @@
       <c r="L593" s="9"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="A594" s="33"/>
+      <c r="A594" s="34"/>
       <c r="B594" s="9"/>
       <c r="C594" s="9"/>
       <c r="D594" s="9"/>
@@ -12698,7 +12732,7 @@
       <c r="L594" s="9"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="A595" s="33"/>
+      <c r="A595" s="34"/>
       <c r="B595" s="9"/>
       <c r="C595" s="9"/>
       <c r="D595" s="9"/>
@@ -12712,7 +12746,7 @@
       <c r="L595" s="9"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="A596" s="33"/>
+      <c r="A596" s="34"/>
       <c r="B596" s="9"/>
       <c r="C596" s="9"/>
       <c r="D596" s="9"/>
@@ -12726,7 +12760,7 @@
       <c r="L596" s="9"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="A597" s="33"/>
+      <c r="A597" s="34"/>
       <c r="B597" s="9"/>
       <c r="C597" s="9"/>
       <c r="D597" s="9"/>
@@ -12740,7 +12774,7 @@
       <c r="L597" s="9"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="A598" s="33"/>
+      <c r="A598" s="34"/>
       <c r="B598" s="9"/>
       <c r="C598" s="9"/>
       <c r="D598" s="9"/>
@@ -12754,7 +12788,7 @@
       <c r="L598" s="9"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="A599" s="33"/>
+      <c r="A599" s="34"/>
       <c r="B599" s="9"/>
       <c r="C599" s="9"/>
       <c r="D599" s="9"/>
@@ -12768,7 +12802,7 @@
       <c r="L599" s="9"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="A600" s="33"/>
+      <c r="A600" s="34"/>
       <c r="B600" s="9"/>
       <c r="C600" s="9"/>
       <c r="D600" s="9"/>
@@ -12782,7 +12816,7 @@
       <c r="L600" s="9"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="A601" s="33"/>
+      <c r="A601" s="34"/>
       <c r="B601" s="9"/>
       <c r="C601" s="9"/>
       <c r="D601" s="9"/>
@@ -12796,7 +12830,7 @@
       <c r="L601" s="9"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="A602" s="33"/>
+      <c r="A602" s="34"/>
       <c r="B602" s="9"/>
       <c r="C602" s="9"/>
       <c r="D602" s="9"/>
@@ -12810,7 +12844,7 @@
       <c r="L602" s="9"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="A603" s="33"/>
+      <c r="A603" s="34"/>
       <c r="B603" s="9"/>
       <c r="C603" s="9"/>
       <c r="D603" s="9"/>
@@ -12824,7 +12858,7 @@
       <c r="L603" s="9"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="A604" s="33"/>
+      <c r="A604" s="34"/>
       <c r="B604" s="9"/>
       <c r="C604" s="9"/>
       <c r="D604" s="9"/>
@@ -12838,7 +12872,7 @@
       <c r="L604" s="9"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="A605" s="33"/>
+      <c r="A605" s="34"/>
       <c r="B605" s="9"/>
       <c r="C605" s="9"/>
       <c r="D605" s="9"/>
@@ -12852,7 +12886,7 @@
       <c r="L605" s="9"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="A606" s="33"/>
+      <c r="A606" s="34"/>
       <c r="B606" s="9"/>
       <c r="C606" s="9"/>
       <c r="D606" s="9"/>
@@ -12866,7 +12900,7 @@
       <c r="L606" s="9"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="A607" s="33"/>
+      <c r="A607" s="34"/>
       <c r="B607" s="9"/>
       <c r="C607" s="9"/>
       <c r="D607" s="9"/>
@@ -12880,7 +12914,7 @@
       <c r="L607" s="9"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="A608" s="33"/>
+      <c r="A608" s="34"/>
       <c r="B608" s="9"/>
       <c r="C608" s="9"/>
       <c r="D608" s="9"/>
@@ -12894,7 +12928,7 @@
       <c r="L608" s="9"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="A609" s="33"/>
+      <c r="A609" s="34"/>
       <c r="B609" s="9"/>
       <c r="C609" s="9"/>
       <c r="D609" s="9"/>
@@ -12908,7 +12942,7 @@
       <c r="L609" s="9"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="A610" s="33"/>
+      <c r="A610" s="34"/>
       <c r="B610" s="9"/>
       <c r="C610" s="9"/>
       <c r="D610" s="9"/>
@@ -12922,7 +12956,7 @@
       <c r="L610" s="9"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="A611" s="33"/>
+      <c r="A611" s="34"/>
       <c r="B611" s="9"/>
       <c r="C611" s="9"/>
       <c r="D611" s="9"/>
@@ -12936,7 +12970,7 @@
       <c r="L611" s="9"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="A612" s="33"/>
+      <c r="A612" s="34"/>
       <c r="B612" s="9"/>
       <c r="C612" s="9"/>
       <c r="D612" s="9"/>
@@ -12950,7 +12984,7 @@
       <c r="L612" s="9"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="A613" s="33"/>
+      <c r="A613" s="34"/>
       <c r="B613" s="9"/>
       <c r="C613" s="9"/>
       <c r="D613" s="9"/>
@@ -12964,7 +12998,7 @@
       <c r="L613" s="9"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="A614" s="33"/>
+      <c r="A614" s="34"/>
       <c r="B614" s="9"/>
       <c r="C614" s="9"/>
       <c r="D614" s="9"/>
@@ -12978,7 +13012,7 @@
       <c r="L614" s="9"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="A615" s="33"/>
+      <c r="A615" s="34"/>
       <c r="B615" s="9"/>
       <c r="C615" s="9"/>
       <c r="D615" s="9"/>
@@ -12992,7 +13026,7 @@
       <c r="L615" s="9"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="A616" s="33"/>
+      <c r="A616" s="34"/>
       <c r="B616" s="9"/>
       <c r="C616" s="9"/>
       <c r="D616" s="9"/>
@@ -13006,7 +13040,7 @@
       <c r="L616" s="9"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="A617" s="33"/>
+      <c r="A617" s="34"/>
       <c r="B617" s="9"/>
       <c r="C617" s="9"/>
       <c r="D617" s="9"/>
@@ -13020,7 +13054,7 @@
       <c r="L617" s="9"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="A618" s="33"/>
+      <c r="A618" s="34"/>
       <c r="B618" s="9"/>
       <c r="C618" s="9"/>
       <c r="D618" s="9"/>
@@ -13034,7 +13068,7 @@
       <c r="L618" s="9"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="A619" s="33"/>
+      <c r="A619" s="34"/>
       <c r="B619" s="9"/>
       <c r="C619" s="9"/>
       <c r="D619" s="9"/>
@@ -13048,7 +13082,7 @@
       <c r="L619" s="9"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="A620" s="33"/>
+      <c r="A620" s="34"/>
       <c r="B620" s="9"/>
       <c r="C620" s="9"/>
       <c r="D620" s="9"/>
@@ -13062,7 +13096,7 @@
       <c r="L620" s="9"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="A621" s="33"/>
+      <c r="A621" s="34"/>
       <c r="B621" s="9"/>
       <c r="C621" s="9"/>
       <c r="D621" s="9"/>
@@ -13076,7 +13110,7 @@
       <c r="L621" s="9"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="A622" s="33"/>
+      <c r="A622" s="34"/>
       <c r="B622" s="9"/>
       <c r="C622" s="9"/>
       <c r="D622" s="9"/>
@@ -13090,7 +13124,7 @@
       <c r="L622" s="9"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="A623" s="33"/>
+      <c r="A623" s="34"/>
       <c r="B623" s="9"/>
       <c r="C623" s="9"/>
       <c r="D623" s="9"/>
@@ -13104,7 +13138,7 @@
       <c r="L623" s="9"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="A624" s="33"/>
+      <c r="A624" s="34"/>
       <c r="B624" s="9"/>
       <c r="C624" s="9"/>
       <c r="D624" s="9"/>
@@ -13118,7 +13152,7 @@
       <c r="L624" s="9"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="A625" s="33"/>
+      <c r="A625" s="34"/>
       <c r="B625" s="9"/>
       <c r="C625" s="9"/>
       <c r="D625" s="9"/>
@@ -13132,7 +13166,7 @@
       <c r="L625" s="9"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="A626" s="33"/>
+      <c r="A626" s="34"/>
       <c r="B626" s="9"/>
       <c r="C626" s="9"/>
       <c r="D626" s="9"/>
@@ -13146,7 +13180,7 @@
       <c r="L626" s="9"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="A627" s="33"/>
+      <c r="A627" s="34"/>
       <c r="B627" s="9"/>
       <c r="C627" s="9"/>
       <c r="D627" s="9"/>
@@ -13160,7 +13194,7 @@
       <c r="L627" s="9"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="A628" s="33"/>
+      <c r="A628" s="34"/>
       <c r="B628" s="9"/>
       <c r="C628" s="9"/>
       <c r="D628" s="9"/>
@@ -13174,7 +13208,7 @@
       <c r="L628" s="9"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="A629" s="33"/>
+      <c r="A629" s="34"/>
       <c r="B629" s="9"/>
       <c r="C629" s="9"/>
       <c r="D629" s="9"/>
@@ -13188,7 +13222,7 @@
       <c r="L629" s="9"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="A630" s="33"/>
+      <c r="A630" s="34"/>
       <c r="B630" s="9"/>
       <c r="C630" s="9"/>
       <c r="D630" s="9"/>
@@ -13202,7 +13236,7 @@
       <c r="L630" s="9"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="A631" s="33"/>
+      <c r="A631" s="34"/>
       <c r="B631" s="9"/>
       <c r="C631" s="9"/>
       <c r="D631" s="9"/>
@@ -13216,7 +13250,7 @@
       <c r="L631" s="9"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="A632" s="33"/>
+      <c r="A632" s="34"/>
       <c r="B632" s="9"/>
       <c r="C632" s="9"/>
       <c r="D632" s="9"/>
@@ -13230,7 +13264,7 @@
       <c r="L632" s="9"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="A633" s="33"/>
+      <c r="A633" s="34"/>
       <c r="B633" s="9"/>
       <c r="C633" s="9"/>
       <c r="D633" s="9"/>
@@ -13244,7 +13278,7 @@
       <c r="L633" s="9"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="A634" s="33"/>
+      <c r="A634" s="34"/>
       <c r="B634" s="9"/>
       <c r="C634" s="9"/>
       <c r="D634" s="9"/>
@@ -13258,7 +13292,7 @@
       <c r="L634" s="9"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="A635" s="33"/>
+      <c r="A635" s="34"/>
       <c r="B635" s="9"/>
       <c r="C635" s="9"/>
       <c r="D635" s="9"/>
@@ -13272,7 +13306,7 @@
       <c r="L635" s="9"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="A636" s="33"/>
+      <c r="A636" s="34"/>
       <c r="B636" s="9"/>
       <c r="C636" s="9"/>
       <c r="D636" s="9"/>
@@ -13286,7 +13320,7 @@
       <c r="L636" s="9"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="A637" s="33"/>
+      <c r="A637" s="34"/>
       <c r="B637" s="9"/>
       <c r="C637" s="9"/>
       <c r="D637" s="9"/>
@@ -13300,7 +13334,7 @@
       <c r="L637" s="9"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="A638" s="33"/>
+      <c r="A638" s="34"/>
       <c r="B638" s="9"/>
       <c r="C638" s="9"/>
       <c r="D638" s="9"/>
@@ -13314,7 +13348,7 @@
       <c r="L638" s="9"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="A639" s="33"/>
+      <c r="A639" s="34"/>
       <c r="B639" s="9"/>
       <c r="C639" s="9"/>
       <c r="D639" s="9"/>
@@ -13328,7 +13362,7 @@
       <c r="L639" s="9"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="A640" s="33"/>
+      <c r="A640" s="34"/>
       <c r="B640" s="9"/>
       <c r="C640" s="9"/>
       <c r="D640" s="9"/>
@@ -13342,7 +13376,7 @@
       <c r="L640" s="9"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="A641" s="33"/>
+      <c r="A641" s="34"/>
       <c r="B641" s="9"/>
       <c r="C641" s="9"/>
       <c r="D641" s="9"/>
@@ -13356,7 +13390,7 @@
       <c r="L641" s="9"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="A642" s="33"/>
+      <c r="A642" s="34"/>
       <c r="B642" s="9"/>
       <c r="C642" s="9"/>
       <c r="D642" s="9"/>
@@ -13370,7 +13404,7 @@
       <c r="L642" s="9"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="A643" s="33"/>
+      <c r="A643" s="34"/>
       <c r="B643" s="9"/>
       <c r="C643" s="9"/>
       <c r="D643" s="9"/>
@@ -13384,7 +13418,7 @@
       <c r="L643" s="9"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="A644" s="33"/>
+      <c r="A644" s="34"/>
       <c r="B644" s="9"/>
       <c r="C644" s="9"/>
       <c r="D644" s="9"/>
@@ -13398,7 +13432,7 @@
       <c r="L644" s="9"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="A645" s="33"/>
+      <c r="A645" s="34"/>
       <c r="B645" s="9"/>
       <c r="C645" s="9"/>
       <c r="D645" s="9"/>
@@ -13412,7 +13446,7 @@
       <c r="L645" s="9"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="A646" s="33"/>
+      <c r="A646" s="34"/>
       <c r="B646" s="9"/>
       <c r="C646" s="9"/>
       <c r="D646" s="9"/>
@@ -13426,7 +13460,7 @@
       <c r="L646" s="9"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="A647" s="33"/>
+      <c r="A647" s="34"/>
       <c r="B647" s="9"/>
       <c r="C647" s="9"/>
       <c r="D647" s="9"/>
@@ -13440,7 +13474,7 @@
       <c r="L647" s="9"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="A648" s="33"/>
+      <c r="A648" s="34"/>
       <c r="B648" s="9"/>
       <c r="C648" s="9"/>
       <c r="D648" s="9"/>
@@ -13454,7 +13488,7 @@
       <c r="L648" s="9"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="A649" s="33"/>
+      <c r="A649" s="34"/>
       <c r="B649" s="9"/>
       <c r="C649" s="9"/>
       <c r="D649" s="9"/>
@@ -13468,7 +13502,7 @@
       <c r="L649" s="9"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="A650" s="33"/>
+      <c r="A650" s="34"/>
       <c r="B650" s="9"/>
       <c r="C650" s="9"/>
       <c r="D650" s="9"/>
@@ -13482,7 +13516,7 @@
       <c r="L650" s="9"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="A651" s="33"/>
+      <c r="A651" s="34"/>
       <c r="B651" s="9"/>
       <c r="C651" s="9"/>
       <c r="D651" s="9"/>
@@ -13496,7 +13530,7 @@
       <c r="L651" s="9"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="A652" s="33"/>
+      <c r="A652" s="34"/>
       <c r="B652" s="9"/>
       <c r="C652" s="9"/>
       <c r="D652" s="9"/>
@@ -13510,7 +13544,7 @@
       <c r="L652" s="9"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="A653" s="33"/>
+      <c r="A653" s="34"/>
       <c r="B653" s="9"/>
       <c r="C653" s="9"/>
       <c r="D653" s="9"/>
@@ -13524,7 +13558,7 @@
       <c r="L653" s="9"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="A654" s="33"/>
+      <c r="A654" s="34"/>
       <c r="B654" s="9"/>
       <c r="C654" s="9"/>
       <c r="D654" s="9"/>
@@ -13538,7 +13572,7 @@
       <c r="L654" s="9"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="A655" s="33"/>
+      <c r="A655" s="34"/>
       <c r="B655" s="9"/>
       <c r="C655" s="9"/>
       <c r="D655" s="9"/>
@@ -13552,7 +13586,7 @@
       <c r="L655" s="9"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="A656" s="33"/>
+      <c r="A656" s="34"/>
       <c r="B656" s="9"/>
       <c r="C656" s="9"/>
       <c r="D656" s="9"/>
@@ -13566,7 +13600,7 @@
       <c r="L656" s="9"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="A657" s="33"/>
+      <c r="A657" s="34"/>
       <c r="B657" s="9"/>
       <c r="C657" s="9"/>
       <c r="D657" s="9"/>
@@ -13580,7 +13614,7 @@
       <c r="L657" s="9"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="A658" s="33"/>
+      <c r="A658" s="34"/>
       <c r="B658" s="9"/>
       <c r="C658" s="9"/>
       <c r="D658" s="9"/>
@@ -13594,7 +13628,7 @@
       <c r="L658" s="9"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="A659" s="33"/>
+      <c r="A659" s="34"/>
       <c r="B659" s="9"/>
       <c r="C659" s="9"/>
       <c r="D659" s="9"/>
@@ -13608,7 +13642,7 @@
       <c r="L659" s="9"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="A660" s="33"/>
+      <c r="A660" s="34"/>
       <c r="B660" s="9"/>
       <c r="C660" s="9"/>
       <c r="D660" s="9"/>
@@ -13622,7 +13656,7 @@
       <c r="L660" s="9"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="A661" s="33"/>
+      <c r="A661" s="34"/>
       <c r="B661" s="9"/>
       <c r="C661" s="9"/>
       <c r="D661" s="9"/>
@@ -13636,7 +13670,7 @@
       <c r="L661" s="9"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="A662" s="33"/>
+      <c r="A662" s="34"/>
       <c r="B662" s="9"/>
       <c r="C662" s="9"/>
       <c r="D662" s="9"/>
@@ -13650,7 +13684,7 @@
       <c r="L662" s="9"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="A663" s="33"/>
+      <c r="A663" s="34"/>
       <c r="B663" s="9"/>
       <c r="C663" s="9"/>
       <c r="D663" s="9"/>
@@ -13664,7 +13698,7 @@
       <c r="L663" s="9"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="A664" s="33"/>
+      <c r="A664" s="34"/>
       <c r="B664" s="9"/>
       <c r="C664" s="9"/>
       <c r="D664" s="9"/>
@@ -13678,7 +13712,7 @@
       <c r="L664" s="9"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="A665" s="33"/>
+      <c r="A665" s="34"/>
       <c r="B665" s="9"/>
       <c r="C665" s="9"/>
       <c r="D665" s="9"/>
@@ -13692,7 +13726,7 @@
       <c r="L665" s="9"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="A666" s="33"/>
+      <c r="A666" s="34"/>
       <c r="B666" s="9"/>
       <c r="C666" s="9"/>
       <c r="D666" s="9"/>
@@ -13706,7 +13740,7 @@
       <c r="L666" s="9"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="A667" s="33"/>
+      <c r="A667" s="34"/>
       <c r="B667" s="9"/>
       <c r="C667" s="9"/>
       <c r="D667" s="9"/>
@@ -13720,7 +13754,7 @@
       <c r="L667" s="9"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="A668" s="33"/>
+      <c r="A668" s="34"/>
       <c r="B668" s="9"/>
       <c r="C668" s="9"/>
       <c r="D668" s="9"/>
@@ -13734,7 +13768,7 @@
       <c r="L668" s="9"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="A669" s="33"/>
+      <c r="A669" s="34"/>
       <c r="B669" s="9"/>
       <c r="C669" s="9"/>
       <c r="D669" s="9"/>
@@ -13748,7 +13782,7 @@
       <c r="L669" s="9"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="A670" s="33"/>
+      <c r="A670" s="34"/>
       <c r="B670" s="9"/>
       <c r="C670" s="9"/>
       <c r="D670" s="9"/>
@@ -13762,7 +13796,7 @@
       <c r="L670" s="9"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="A671" s="33"/>
+      <c r="A671" s="34"/>
       <c r="B671" s="9"/>
       <c r="C671" s="9"/>
       <c r="D671" s="9"/>
@@ -13776,7 +13810,7 @@
       <c r="L671" s="9"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="A672" s="33"/>
+      <c r="A672" s="34"/>
       <c r="B672" s="9"/>
       <c r="C672" s="9"/>
       <c r="D672" s="9"/>
@@ -13790,7 +13824,7 @@
       <c r="L672" s="9"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="A673" s="33"/>
+      <c r="A673" s="34"/>
       <c r="B673" s="9"/>
       <c r="C673" s="9"/>
       <c r="D673" s="9"/>
@@ -13804,7 +13838,7 @@
       <c r="L673" s="9"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="A674" s="33"/>
+      <c r="A674" s="34"/>
       <c r="B674" s="9"/>
       <c r="C674" s="9"/>
       <c r="D674" s="9"/>
@@ -13818,7 +13852,7 @@
       <c r="L674" s="9"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="A675" s="33"/>
+      <c r="A675" s="34"/>
       <c r="B675" s="9"/>
       <c r="C675" s="9"/>
       <c r="D675" s="9"/>
@@ -13832,7 +13866,7 @@
       <c r="L675" s="9"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="A676" s="33"/>
+      <c r="A676" s="34"/>
       <c r="B676" s="9"/>
       <c r="C676" s="9"/>
       <c r="D676" s="9"/>
@@ -13846,7 +13880,7 @@
       <c r="L676" s="9"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="A677" s="33"/>
+      <c r="A677" s="34"/>
       <c r="B677" s="9"/>
       <c r="C677" s="9"/>
       <c r="D677" s="9"/>
@@ -13860,7 +13894,7 @@
       <c r="L677" s="9"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="A678" s="33"/>
+      <c r="A678" s="34"/>
       <c r="B678" s="9"/>
       <c r="C678" s="9"/>
       <c r="D678" s="9"/>
@@ -13874,7 +13908,7 @@
       <c r="L678" s="9"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="A679" s="33"/>
+      <c r="A679" s="34"/>
       <c r="B679" s="9"/>
       <c r="C679" s="9"/>
       <c r="D679" s="9"/>
@@ -13888,7 +13922,7 @@
       <c r="L679" s="9"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="A680" s="33"/>
+      <c r="A680" s="34"/>
       <c r="B680" s="9"/>
       <c r="C680" s="9"/>
       <c r="D680" s="9"/>
@@ -13902,7 +13936,7 @@
       <c r="L680" s="9"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="A681" s="33"/>
+      <c r="A681" s="34"/>
       <c r="B681" s="9"/>
       <c r="C681" s="9"/>
       <c r="D681" s="9"/>
@@ -13916,7 +13950,7 @@
       <c r="L681" s="9"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="A682" s="33"/>
+      <c r="A682" s="34"/>
       <c r="B682" s="9"/>
       <c r="C682" s="9"/>
       <c r="D682" s="9"/>
@@ -13930,7 +13964,7 @@
       <c r="L682" s="9"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="A683" s="33"/>
+      <c r="A683" s="34"/>
       <c r="B683" s="9"/>
       <c r="C683" s="9"/>
       <c r="D683" s="9"/>
@@ -13944,7 +13978,7 @@
       <c r="L683" s="9"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="A684" s="33"/>
+      <c r="A684" s="34"/>
       <c r="B684" s="9"/>
       <c r="C684" s="9"/>
       <c r="D684" s="9"/>
@@ -13958,7 +13992,7 @@
       <c r="L684" s="9"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="A685" s="33"/>
+      <c r="A685" s="34"/>
       <c r="B685" s="9"/>
       <c r="C685" s="9"/>
       <c r="D685" s="9"/>
@@ -13972,7 +14006,7 @@
       <c r="L685" s="9"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="A686" s="33"/>
+      <c r="A686" s="34"/>
       <c r="B686" s="9"/>
       <c r="C686" s="9"/>
       <c r="D686" s="9"/>
@@ -13986,7 +14020,7 @@
       <c r="L686" s="9"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="A687" s="33"/>
+      <c r="A687" s="34"/>
       <c r="B687" s="9"/>
       <c r="C687" s="9"/>
       <c r="D687" s="9"/>
@@ -14000,7 +14034,7 @@
       <c r="L687" s="9"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="A688" s="33"/>
+      <c r="A688" s="34"/>
       <c r="B688" s="9"/>
       <c r="C688" s="9"/>
       <c r="D688" s="9"/>
@@ -14014,7 +14048,7 @@
       <c r="L688" s="9"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="A689" s="33"/>
+      <c r="A689" s="34"/>
       <c r="B689" s="9"/>
       <c r="C689" s="9"/>
       <c r="D689" s="9"/>
@@ -14028,7 +14062,7 @@
       <c r="L689" s="9"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="A690" s="33"/>
+      <c r="A690" s="34"/>
       <c r="B690" s="9"/>
       <c r="C690" s="9"/>
       <c r="D690" s="9"/>
@@ -14042,7 +14076,7 @@
       <c r="L690" s="9"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="A691" s="33"/>
+      <c r="A691" s="34"/>
       <c r="B691" s="9"/>
       <c r="C691" s="9"/>
       <c r="D691" s="9"/>
@@ -14056,7 +14090,7 @@
       <c r="L691" s="9"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="A692" s="33"/>
+      <c r="A692" s="34"/>
       <c r="B692" s="9"/>
       <c r="C692" s="9"/>
       <c r="D692" s="9"/>
@@ -14070,7 +14104,7 @@
       <c r="L692" s="9"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="A693" s="33"/>
+      <c r="A693" s="34"/>
       <c r="B693" s="9"/>
       <c r="C693" s="9"/>
       <c r="D693" s="9"/>
@@ -14084,7 +14118,7 @@
       <c r="L693" s="9"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="A694" s="33"/>
+      <c r="A694" s="34"/>
       <c r="B694" s="9"/>
       <c r="C694" s="9"/>
       <c r="D694" s="9"/>
@@ -14098,7 +14132,7 @@
       <c r="L694" s="9"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="A695" s="33"/>
+      <c r="A695" s="34"/>
       <c r="B695" s="9"/>
       <c r="C695" s="9"/>
       <c r="D695" s="9"/>
@@ -14112,7 +14146,7 @@
       <c r="L695" s="9"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="A696" s="33"/>
+      <c r="A696" s="34"/>
       <c r="B696" s="9"/>
       <c r="C696" s="9"/>
       <c r="D696" s="9"/>
@@ -14126,7 +14160,7 @@
       <c r="L696" s="9"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="A697" s="33"/>
+      <c r="A697" s="34"/>
       <c r="B697" s="9"/>
       <c r="C697" s="9"/>
       <c r="D697" s="9"/>
@@ -14140,7 +14174,7 @@
       <c r="L697" s="9"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="A698" s="33"/>
+      <c r="A698" s="34"/>
       <c r="B698" s="9"/>
       <c r="C698" s="9"/>
       <c r="D698" s="9"/>
@@ -14154,7 +14188,7 @@
       <c r="L698" s="9"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="A699" s="33"/>
+      <c r="A699" s="34"/>
       <c r="B699" s="9"/>
       <c r="C699" s="9"/>
       <c r="D699" s="9"/>
@@ -14168,7 +14202,7 @@
       <c r="L699" s="9"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="A700" s="33"/>
+      <c r="A700" s="34"/>
       <c r="B700" s="9"/>
       <c r="C700" s="9"/>
       <c r="D700" s="9"/>
@@ -14182,7 +14216,7 @@
       <c r="L700" s="9"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="A701" s="33"/>
+      <c r="A701" s="34"/>
       <c r="B701" s="9"/>
       <c r="C701" s="9"/>
       <c r="D701" s="9"/>
@@ -14196,7 +14230,7 @@
       <c r="L701" s="9"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="A702" s="33"/>
+      <c r="A702" s="34"/>
       <c r="B702" s="9"/>
       <c r="C702" s="9"/>
       <c r="D702" s="9"/>
@@ -14210,7 +14244,7 @@
       <c r="L702" s="9"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="A703" s="33"/>
+      <c r="A703" s="34"/>
       <c r="B703" s="9"/>
       <c r="C703" s="9"/>
       <c r="D703" s="9"/>
@@ -14224,7 +14258,7 @@
       <c r="L703" s="9"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="A704" s="33"/>
+      <c r="A704" s="34"/>
       <c r="B704" s="9"/>
       <c r="C704" s="9"/>
       <c r="D704" s="9"/>
@@ -14238,7 +14272,7 @@
       <c r="L704" s="9"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="A705" s="33"/>
+      <c r="A705" s="34"/>
       <c r="B705" s="9"/>
       <c r="C705" s="9"/>
       <c r="D705" s="9"/>
@@ -14252,7 +14286,7 @@
       <c r="L705" s="9"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="A706" s="33"/>
+      <c r="A706" s="34"/>
       <c r="B706" s="9"/>
       <c r="C706" s="9"/>
       <c r="D706" s="9"/>
@@ -14266,7 +14300,7 @@
       <c r="L706" s="9"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="A707" s="33"/>
+      <c r="A707" s="34"/>
       <c r="B707" s="9"/>
       <c r="C707" s="9"/>
       <c r="D707" s="9"/>
@@ -14280,7 +14314,7 @@
       <c r="L707" s="9"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="A708" s="33"/>
+      <c r="A708" s="34"/>
       <c r="B708" s="9"/>
       <c r="C708" s="9"/>
       <c r="D708" s="9"/>
@@ -14294,7 +14328,7 @@
       <c r="L708" s="9"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="A709" s="33"/>
+      <c r="A709" s="34"/>
       <c r="B709" s="9"/>
       <c r="C709" s="9"/>
       <c r="D709" s="9"/>
@@ -14308,7 +14342,7 @@
       <c r="L709" s="9"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="A710" s="33"/>
+      <c r="A710" s="34"/>
       <c r="B710" s="9"/>
       <c r="C710" s="9"/>
       <c r="D710" s="9"/>
@@ -14322,7 +14356,7 @@
       <c r="L710" s="9"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="A711" s="33"/>
+      <c r="A711" s="34"/>
       <c r="B711" s="9"/>
       <c r="C711" s="9"/>
       <c r="D711" s="9"/>
@@ -14336,7 +14370,7 @@
       <c r="L711" s="9"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="A712" s="33"/>
+      <c r="A712" s="34"/>
       <c r="B712" s="9"/>
       <c r="C712" s="9"/>
       <c r="D712" s="9"/>
@@ -14350,7 +14384,7 @@
       <c r="L712" s="9"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="A713" s="33"/>
+      <c r="A713" s="34"/>
       <c r="B713" s="9"/>
       <c r="C713" s="9"/>
       <c r="D713" s="9"/>
@@ -14364,7 +14398,7 @@
       <c r="L713" s="9"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="A714" s="33"/>
+      <c r="A714" s="34"/>
       <c r="B714" s="9"/>
       <c r="C714" s="9"/>
       <c r="D714" s="9"/>
@@ -14378,7 +14412,7 @@
       <c r="L714" s="9"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="A715" s="33"/>
+      <c r="A715" s="34"/>
       <c r="B715" s="9"/>
       <c r="C715" s="9"/>
       <c r="D715" s="9"/>
@@ -14392,7 +14426,7 @@
       <c r="L715" s="9"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="A716" s="33"/>
+      <c r="A716" s="34"/>
       <c r="B716" s="9"/>
       <c r="C716" s="9"/>
       <c r="D716" s="9"/>
@@ -14406,7 +14440,7 @@
       <c r="L716" s="9"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="A717" s="33"/>
+      <c r="A717" s="34"/>
       <c r="B717" s="9"/>
       <c r="C717" s="9"/>
       <c r="D717" s="9"/>
@@ -14420,7 +14454,7 @@
       <c r="L717" s="9"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="A718" s="33"/>
+      <c r="A718" s="34"/>
       <c r="B718" s="9"/>
       <c r="C718" s="9"/>
       <c r="D718" s="9"/>
@@ -14434,7 +14468,7 @@
       <c r="L718" s="9"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="A719" s="33"/>
+      <c r="A719" s="34"/>
       <c r="B719" s="9"/>
       <c r="C719" s="9"/>
       <c r="D719" s="9"/>
@@ -14448,7 +14482,7 @@
       <c r="L719" s="9"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="A720" s="33"/>
+      <c r="A720" s="34"/>
       <c r="B720" s="9"/>
       <c r="C720" s="9"/>
       <c r="D720" s="9"/>
@@ -14462,7 +14496,7 @@
       <c r="L720" s="9"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="A721" s="33"/>
+      <c r="A721" s="34"/>
       <c r="B721" s="9"/>
       <c r="C721" s="9"/>
       <c r="D721" s="9"/>
@@ -14476,7 +14510,7 @@
       <c r="L721" s="9"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="A722" s="33"/>
+      <c r="A722" s="34"/>
       <c r="B722" s="9"/>
       <c r="C722" s="9"/>
       <c r="D722" s="9"/>
@@ -14490,7 +14524,7 @@
       <c r="L722" s="9"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="A723" s="33"/>
+      <c r="A723" s="34"/>
       <c r="B723" s="9"/>
       <c r="C723" s="9"/>
       <c r="D723" s="9"/>
@@ -14504,7 +14538,7 @@
       <c r="L723" s="9"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="A724" s="33"/>
+      <c r="A724" s="34"/>
       <c r="B724" s="9"/>
       <c r="C724" s="9"/>
       <c r="D724" s="9"/>
@@ -14518,7 +14552,7 @@
       <c r="L724" s="9"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="A725" s="33"/>
+      <c r="A725" s="34"/>
       <c r="B725" s="9"/>
       <c r="C725" s="9"/>
       <c r="D725" s="9"/>
@@ -14532,7 +14566,7 @@
       <c r="L725" s="9"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="A726" s="33"/>
+      <c r="A726" s="34"/>
       <c r="B726" s="9"/>
       <c r="C726" s="9"/>
       <c r="D726" s="9"/>
@@ -14546,7 +14580,7 @@
       <c r="L726" s="9"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="A727" s="33"/>
+      <c r="A727" s="34"/>
       <c r="B727" s="9"/>
       <c r="C727" s="9"/>
       <c r="D727" s="9"/>
@@ -14560,7 +14594,7 @@
       <c r="L727" s="9"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="A728" s="33"/>
+      <c r="A728" s="34"/>
       <c r="B728" s="9"/>
       <c r="C728" s="9"/>
       <c r="D728" s="9"/>
@@ -14574,7 +14608,7 @@
       <c r="L728" s="9"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="A729" s="33"/>
+      <c r="A729" s="34"/>
       <c r="B729" s="9"/>
       <c r="C729" s="9"/>
       <c r="D729" s="9"/>
@@ -14588,7 +14622,7 @@
       <c r="L729" s="9"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="A730" s="33"/>
+      <c r="A730" s="34"/>
       <c r="B730" s="9"/>
       <c r="C730" s="9"/>
       <c r="D730" s="9"/>
@@ -14602,7 +14636,7 @@
       <c r="L730" s="9"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="A731" s="33"/>
+      <c r="A731" s="34"/>
       <c r="B731" s="9"/>
       <c r="C731" s="9"/>
       <c r="D731" s="9"/>
@@ -14616,7 +14650,7 @@
       <c r="L731" s="9"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="A732" s="33"/>
+      <c r="A732" s="34"/>
       <c r="B732" s="9"/>
       <c r="C732" s="9"/>
       <c r="D732" s="9"/>
@@ -14630,7 +14664,7 @@
       <c r="L732" s="9"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="A733" s="33"/>
+      <c r="A733" s="34"/>
       <c r="B733" s="9"/>
       <c r="C733" s="9"/>
       <c r="D733" s="9"/>
@@ -14644,7 +14678,7 @@
       <c r="L733" s="9"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="A734" s="33"/>
+      <c r="A734" s="34"/>
       <c r="B734" s="9"/>
       <c r="C734" s="9"/>
       <c r="D734" s="9"/>
@@ -14658,7 +14692,7 @@
       <c r="L734" s="9"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="A735" s="33"/>
+      <c r="A735" s="34"/>
       <c r="B735" s="9"/>
       <c r="C735" s="9"/>
       <c r="D735" s="9"/>
@@ -14672,7 +14706,7 @@
       <c r="L735" s="9"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="A736" s="33"/>
+      <c r="A736" s="34"/>
       <c r="B736" s="9"/>
       <c r="C736" s="9"/>
       <c r="D736" s="9"/>
@@ -14686,7 +14720,7 @@
       <c r="L736" s="9"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="A737" s="33"/>
+      <c r="A737" s="34"/>
       <c r="B737" s="9"/>
       <c r="C737" s="9"/>
       <c r="D737" s="9"/>
@@ -14700,7 +14734,7 @@
       <c r="L737" s="9"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="A738" s="33"/>
+      <c r="A738" s="34"/>
       <c r="B738" s="9"/>
       <c r="C738" s="9"/>
       <c r="D738" s="9"/>
@@ -14714,7 +14748,7 @@
       <c r="L738" s="9"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="A739" s="33"/>
+      <c r="A739" s="34"/>
       <c r="B739" s="9"/>
       <c r="C739" s="9"/>
       <c r="D739" s="9"/>
@@ -14728,7 +14762,7 @@
       <c r="L739" s="9"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="A740" s="33"/>
+      <c r="A740" s="34"/>
       <c r="B740" s="9"/>
       <c r="C740" s="9"/>
       <c r="D740" s="9"/>
@@ -14742,7 +14776,7 @@
       <c r="L740" s="9"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="A741" s="33"/>
+      <c r="A741" s="34"/>
       <c r="B741" s="9"/>
       <c r="C741" s="9"/>
       <c r="D741" s="9"/>
@@ -14756,7 +14790,7 @@
       <c r="L741" s="9"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="A742" s="33"/>
+      <c r="A742" s="34"/>
       <c r="B742" s="9"/>
       <c r="C742" s="9"/>
       <c r="D742" s="9"/>
@@ -14770,7 +14804,7 @@
       <c r="L742" s="9"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="A743" s="33"/>
+      <c r="A743" s="34"/>
       <c r="B743" s="9"/>
       <c r="C743" s="9"/>
       <c r="D743" s="9"/>
@@ -14784,7 +14818,7 @@
       <c r="L743" s="9"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="A744" s="33"/>
+      <c r="A744" s="34"/>
       <c r="B744" s="9"/>
       <c r="C744" s="9"/>
       <c r="D744" s="9"/>
@@ -14798,7 +14832,7 @@
       <c r="L744" s="9"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="A745" s="33"/>
+      <c r="A745" s="34"/>
       <c r="B745" s="9"/>
       <c r="C745" s="9"/>
       <c r="D745" s="9"/>
@@ -14812,7 +14846,7 @@
       <c r="L745" s="9"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="A746" s="33"/>
+      <c r="A746" s="34"/>
       <c r="B746" s="9"/>
       <c r="C746" s="9"/>
       <c r="D746" s="9"/>
@@ -14826,7 +14860,7 @@
       <c r="L746" s="9"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="A747" s="33"/>
+      <c r="A747" s="34"/>
       <c r="B747" s="9"/>
       <c r="C747" s="9"/>
       <c r="D747" s="9"/>
@@ -14840,7 +14874,7 @@
       <c r="L747" s="9"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="A748" s="33"/>
+      <c r="A748" s="34"/>
       <c r="B748" s="9"/>
       <c r="C748" s="9"/>
       <c r="D748" s="9"/>
@@ -14854,7 +14888,7 @@
       <c r="L748" s="9"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="A749" s="33"/>
+      <c r="A749" s="34"/>
       <c r="B749" s="9"/>
       <c r="C749" s="9"/>
       <c r="D749" s="9"/>
@@ -14868,7 +14902,7 @@
       <c r="L749" s="9"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="A750" s="33"/>
+      <c r="A750" s="34"/>
       <c r="B750" s="9"/>
       <c r="C750" s="9"/>
       <c r="D750" s="9"/>
@@ -14882,7 +14916,7 @@
       <c r="L750" s="9"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="A751" s="33"/>
+      <c r="A751" s="34"/>
       <c r="B751" s="9"/>
       <c r="C751" s="9"/>
       <c r="D751" s="9"/>
@@ -14896,7 +14930,7 @@
       <c r="L751" s="9"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="A752" s="33"/>
+      <c r="A752" s="34"/>
       <c r="B752" s="9"/>
       <c r="C752" s="9"/>
       <c r="D752" s="9"/>
@@ -14910,7 +14944,7 @@
       <c r="L752" s="9"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="A753" s="33"/>
+      <c r="A753" s="34"/>
       <c r="B753" s="9"/>
       <c r="C753" s="9"/>
       <c r="D753" s="9"/>
@@ -14924,7 +14958,7 @@
       <c r="L753" s="9"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="A754" s="33"/>
+      <c r="A754" s="34"/>
       <c r="B754" s="9"/>
       <c r="C754" s="9"/>
       <c r="D754" s="9"/>
@@ -14938,7 +14972,7 @@
       <c r="L754" s="9"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="A755" s="33"/>
+      <c r="A755" s="34"/>
       <c r="B755" s="9"/>
       <c r="C755" s="9"/>
       <c r="D755" s="9"/>
@@ -14952,7 +14986,7 @@
       <c r="L755" s="9"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="A756" s="33"/>
+      <c r="A756" s="34"/>
       <c r="B756" s="9"/>
       <c r="C756" s="9"/>
       <c r="D756" s="9"/>
@@ -14966,7 +15000,7 @@
       <c r="L756" s="9"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="A757" s="33"/>
+      <c r="A757" s="34"/>
       <c r="B757" s="9"/>
       <c r="C757" s="9"/>
       <c r="D757" s="9"/>
@@ -14980,7 +15014,7 @@
       <c r="L757" s="9"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="A758" s="33"/>
+      <c r="A758" s="34"/>
       <c r="B758" s="9"/>
       <c r="C758" s="9"/>
       <c r="D758" s="9"/>
@@ -14994,7 +15028,7 @@
       <c r="L758" s="9"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="A759" s="33"/>
+      <c r="A759" s="34"/>
       <c r="B759" s="9"/>
       <c r="C759" s="9"/>
       <c r="D759" s="9"/>
@@ -15008,7 +15042,7 @@
       <c r="L759" s="9"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="A760" s="33"/>
+      <c r="A760" s="34"/>
       <c r="B760" s="9"/>
       <c r="C760" s="9"/>
       <c r="D760" s="9"/>
@@ -15022,7 +15056,7 @@
       <c r="L760" s="9"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="A761" s="33"/>
+      <c r="A761" s="34"/>
       <c r="B761" s="9"/>
       <c r="C761" s="9"/>
       <c r="D761" s="9"/>
@@ -15036,7 +15070,7 @@
       <c r="L761" s="9"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="A762" s="33"/>
+      <c r="A762" s="34"/>
       <c r="B762" s="9"/>
       <c r="C762" s="9"/>
       <c r="D762" s="9"/>
@@ -15050,7 +15084,7 @@
       <c r="L762" s="9"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="A763" s="33"/>
+      <c r="A763" s="34"/>
       <c r="B763" s="9"/>
       <c r="C763" s="9"/>
       <c r="D763" s="9"/>
@@ -15064,7 +15098,7 @@
       <c r="L763" s="9"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="A764" s="33"/>
+      <c r="A764" s="34"/>
       <c r="B764" s="9"/>
       <c r="C764" s="9"/>
       <c r="D764" s="9"/>
@@ -15078,7 +15112,7 @@
       <c r="L764" s="9"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="A765" s="33"/>
+      <c r="A765" s="34"/>
       <c r="B765" s="9"/>
       <c r="C765" s="9"/>
       <c r="D765" s="9"/>
@@ -15092,7 +15126,7 @@
       <c r="L765" s="9"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="A766" s="33"/>
+      <c r="A766" s="34"/>
       <c r="B766" s="9"/>
       <c r="C766" s="9"/>
       <c r="D766" s="9"/>
@@ -15106,7 +15140,7 @@
       <c r="L766" s="9"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="A767" s="33"/>
+      <c r="A767" s="34"/>
       <c r="B767" s="9"/>
       <c r="C767" s="9"/>
       <c r="D767" s="9"/>
@@ -15120,7 +15154,7 @@
       <c r="L767" s="9"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="A768" s="33"/>
+      <c r="A768" s="34"/>
       <c r="B768" s="9"/>
       <c r="C768" s="9"/>
       <c r="D768" s="9"/>
@@ -15134,7 +15168,7 @@
       <c r="L768" s="9"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="A769" s="33"/>
+      <c r="A769" s="34"/>
       <c r="B769" s="9"/>
       <c r="C769" s="9"/>
       <c r="D769" s="9"/>
@@ -15148,7 +15182,7 @@
       <c r="L769" s="9"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="A770" s="33"/>
+      <c r="A770" s="34"/>
       <c r="B770" s="9"/>
       <c r="C770" s="9"/>
       <c r="D770" s="9"/>
@@ -15162,7 +15196,7 @@
       <c r="L770" s="9"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="A771" s="33"/>
+      <c r="A771" s="34"/>
       <c r="B771" s="9"/>
       <c r="C771" s="9"/>
       <c r="D771" s="9"/>
@@ -15176,7 +15210,7 @@
       <c r="L771" s="9"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="A772" s="33"/>
+      <c r="A772" s="34"/>
       <c r="B772" s="9"/>
       <c r="C772" s="9"/>
       <c r="D772" s="9"/>
@@ -15190,7 +15224,7 @@
       <c r="L772" s="9"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="A773" s="33"/>
+      <c r="A773" s="34"/>
       <c r="B773" s="9"/>
       <c r="C773" s="9"/>
       <c r="D773" s="9"/>
@@ -15204,7 +15238,7 @@
       <c r="L773" s="9"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="A774" s="33"/>
+      <c r="A774" s="34"/>
       <c r="B774" s="9"/>
       <c r="C774" s="9"/>
       <c r="D774" s="9"/>
@@ -15218,7 +15252,7 @@
       <c r="L774" s="9"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="A775" s="33"/>
+      <c r="A775" s="34"/>
       <c r="B775" s="9"/>
       <c r="C775" s="9"/>
       <c r="D775" s="9"/>
@@ -15232,7 +15266,7 @@
       <c r="L775" s="9"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="A776" s="33"/>
+      <c r="A776" s="34"/>
       <c r="B776" s="9"/>
       <c r="C776" s="9"/>
       <c r="D776" s="9"/>
@@ -15246,7 +15280,7 @@
       <c r="L776" s="9"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="A777" s="33"/>
+      <c r="A777" s="34"/>
       <c r="B777" s="9"/>
       <c r="C777" s="9"/>
       <c r="D777" s="9"/>
@@ -15260,7 +15294,7 @@
       <c r="L777" s="9"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="A778" s="33"/>
+      <c r="A778" s="34"/>
       <c r="B778" s="9"/>
       <c r="C778" s="9"/>
       <c r="D778" s="9"/>
@@ -15274,7 +15308,7 @@
       <c r="L778" s="9"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="A779" s="33"/>
+      <c r="A779" s="34"/>
       <c r="B779" s="9"/>
       <c r="C779" s="9"/>
       <c r="D779" s="9"/>
@@ -15288,7 +15322,7 @@
       <c r="L779" s="9"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="A780" s="33"/>
+      <c r="A780" s="34"/>
       <c r="B780" s="9"/>
       <c r="C780" s="9"/>
       <c r="D780" s="9"/>
@@ -15302,7 +15336,7 @@
       <c r="L780" s="9"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="A781" s="33"/>
+      <c r="A781" s="34"/>
       <c r="B781" s="9"/>
       <c r="C781" s="9"/>
       <c r="D781" s="9"/>
@@ -15316,7 +15350,7 @@
       <c r="L781" s="9"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="A782" s="33"/>
+      <c r="A782" s="34"/>
       <c r="B782" s="9"/>
       <c r="C782" s="9"/>
       <c r="D782" s="9"/>
@@ -15330,7 +15364,7 @@
       <c r="L782" s="9"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="A783" s="33"/>
+      <c r="A783" s="34"/>
       <c r="B783" s="9"/>
       <c r="C783" s="9"/>
       <c r="D783" s="9"/>
@@ -15344,7 +15378,7 @@
       <c r="L783" s="9"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="A784" s="33"/>
+      <c r="A784" s="34"/>
       <c r="B784" s="9"/>
       <c r="C784" s="9"/>
       <c r="D784" s="9"/>
@@ -15358,7 +15392,7 @@
       <c r="L784" s="9"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="A785" s="33"/>
+      <c r="A785" s="34"/>
       <c r="B785" s="9"/>
       <c r="C785" s="9"/>
       <c r="D785" s="9"/>
@@ -15372,7 +15406,7 @@
       <c r="L785" s="9"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="A786" s="33"/>
+      <c r="A786" s="34"/>
       <c r="B786" s="9"/>
       <c r="C786" s="9"/>
       <c r="D786" s="9"/>
@@ -15386,7 +15420,7 @@
       <c r="L786" s="9"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="A787" s="33"/>
+      <c r="A787" s="34"/>
       <c r="B787" s="9"/>
       <c r="C787" s="9"/>
       <c r="D787" s="9"/>
@@ -15400,7 +15434,7 @@
       <c r="L787" s="9"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="A788" s="33"/>
+      <c r="A788" s="34"/>
       <c r="B788" s="9"/>
       <c r="C788" s="9"/>
       <c r="D788" s="9"/>
@@ -15414,7 +15448,7 @@
       <c r="L788" s="9"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="A789" s="33"/>
+      <c r="A789" s="34"/>
       <c r="B789" s="9"/>
       <c r="C789" s="9"/>
       <c r="D789" s="9"/>
@@ -15428,7 +15462,7 @@
       <c r="L789" s="9"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="A790" s="33"/>
+      <c r="A790" s="34"/>
       <c r="B790" s="9"/>
       <c r="C790" s="9"/>
       <c r="D790" s="9"/>
@@ -15442,7 +15476,7 @@
       <c r="L790" s="9"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="A791" s="33"/>
+      <c r="A791" s="34"/>
       <c r="B791" s="9"/>
       <c r="C791" s="9"/>
       <c r="D791" s="9"/>
@@ -15456,7 +15490,7 @@
       <c r="L791" s="9"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="A792" s="33"/>
+      <c r="A792" s="34"/>
       <c r="B792" s="9"/>
       <c r="C792" s="9"/>
       <c r="D792" s="9"/>
@@ -15470,7 +15504,7 @@
       <c r="L792" s="9"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="A793" s="33"/>
+      <c r="A793" s="34"/>
       <c r="B793" s="9"/>
       <c r="C793" s="9"/>
       <c r="D793" s="9"/>
@@ -15484,7 +15518,7 @@
       <c r="L793" s="9"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="A794" s="33"/>
+      <c r="A794" s="34"/>
       <c r="B794" s="9"/>
       <c r="C794" s="9"/>
       <c r="D794" s="9"/>
@@ -15498,7 +15532,7 @@
       <c r="L794" s="9"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="A795" s="33"/>
+      <c r="A795" s="34"/>
       <c r="B795" s="9"/>
       <c r="C795" s="9"/>
       <c r="D795" s="9"/>
@@ -15512,7 +15546,7 @@
       <c r="L795" s="9"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="A796" s="33"/>
+      <c r="A796" s="34"/>
       <c r="B796" s="9"/>
       <c r="C796" s="9"/>
       <c r="D796" s="9"/>
@@ -15526,7 +15560,7 @@
       <c r="L796" s="9"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="A797" s="33"/>
+      <c r="A797" s="34"/>
       <c r="B797" s="9"/>
       <c r="C797" s="9"/>
       <c r="D797" s="9"/>
@@ -15540,7 +15574,7 @@
       <c r="L797" s="9"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="A798" s="33"/>
+      <c r="A798" s="34"/>
       <c r="B798" s="9"/>
       <c r="C798" s="9"/>
       <c r="D798" s="9"/>
@@ -15554,7 +15588,7 @@
       <c r="L798" s="9"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="A799" s="33"/>
+      <c r="A799" s="34"/>
       <c r="B799" s="9"/>
       <c r="C799" s="9"/>
       <c r="D799" s="9"/>
@@ -15568,7 +15602,7 @@
       <c r="L799" s="9"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="A800" s="33"/>
+      <c r="A800" s="34"/>
       <c r="B800" s="9"/>
       <c r="C800" s="9"/>
       <c r="D800" s="9"/>
@@ -15582,7 +15616,7 @@
       <c r="L800" s="9"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="A801" s="33"/>
+      <c r="A801" s="34"/>
       <c r="B801" s="9"/>
       <c r="C801" s="9"/>
       <c r="D801" s="9"/>
@@ -15596,7 +15630,7 @@
       <c r="L801" s="9"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="33"/>
+      <c r="A802" s="34"/>
       <c r="B802" s="9"/>
       <c r="C802" s="9"/>
       <c r="D802" s="9"/>
@@ -15610,7 +15644,7 @@
       <c r="L802" s="9"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="A803" s="33"/>
+      <c r="A803" s="34"/>
       <c r="B803" s="9"/>
       <c r="C803" s="9"/>
       <c r="D803" s="9"/>
@@ -15624,7 +15658,7 @@
       <c r="L803" s="9"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="A804" s="33"/>
+      <c r="A804" s="34"/>
       <c r="B804" s="9"/>
       <c r="C804" s="9"/>
       <c r="D804" s="9"/>
@@ -15638,7 +15672,7 @@
       <c r="L804" s="9"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="A805" s="33"/>
+      <c r="A805" s="34"/>
       <c r="B805" s="9"/>
       <c r="C805" s="9"/>
       <c r="D805" s="9"/>
@@ -15652,7 +15686,7 @@
       <c r="L805" s="9"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="A806" s="33"/>
+      <c r="A806" s="34"/>
       <c r="B806" s="9"/>
       <c r="C806" s="9"/>
       <c r="D806" s="9"/>
@@ -15666,7 +15700,7 @@
       <c r="L806" s="9"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="A807" s="33"/>
+      <c r="A807" s="34"/>
       <c r="B807" s="9"/>
       <c r="C807" s="9"/>
       <c r="D807" s="9"/>
@@ -15680,7 +15714,7 @@
       <c r="L807" s="9"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="A808" s="33"/>
+      <c r="A808" s="34"/>
       <c r="B808" s="9"/>
       <c r="C808" s="9"/>
       <c r="D808" s="9"/>
@@ -15694,7 +15728,7 @@
       <c r="L808" s="9"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="A809" s="33"/>
+      <c r="A809" s="34"/>
       <c r="B809" s="9"/>
       <c r="C809" s="9"/>
       <c r="D809" s="9"/>
@@ -15708,7 +15742,7 @@
       <c r="L809" s="9"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="A810" s="33"/>
+      <c r="A810" s="34"/>
       <c r="B810" s="9"/>
       <c r="C810" s="9"/>
       <c r="D810" s="9"/>
@@ -15722,7 +15756,7 @@
       <c r="L810" s="9"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="A811" s="33"/>
+      <c r="A811" s="34"/>
       <c r="B811" s="9"/>
       <c r="C811" s="9"/>
       <c r="D811" s="9"/>
@@ -15736,7 +15770,7 @@
       <c r="L811" s="9"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="A812" s="33"/>
+      <c r="A812" s="34"/>
       <c r="B812" s="9"/>
       <c r="C812" s="9"/>
       <c r="D812" s="9"/>
@@ -15750,7 +15784,7 @@
       <c r="L812" s="9"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="A813" s="33"/>
+      <c r="A813" s="34"/>
       <c r="B813" s="9"/>
       <c r="C813" s="9"/>
       <c r="D813" s="9"/>
@@ -15764,7 +15798,7 @@
       <c r="L813" s="9"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="A814" s="33"/>
+      <c r="A814" s="34"/>
       <c r="B814" s="9"/>
       <c r="C814" s="9"/>
       <c r="D814" s="9"/>
@@ -15778,7 +15812,7 @@
       <c r="L814" s="9"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="A815" s="33"/>
+      <c r="A815" s="34"/>
       <c r="B815" s="9"/>
       <c r="C815" s="9"/>
       <c r="D815" s="9"/>
@@ -15792,7 +15826,7 @@
       <c r="L815" s="9"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="A816" s="33"/>
+      <c r="A816" s="34"/>
       <c r="B816" s="9"/>
       <c r="C816" s="9"/>
       <c r="D816" s="9"/>
@@ -15806,7 +15840,7 @@
       <c r="L816" s="9"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="A817" s="33"/>
+      <c r="A817" s="34"/>
       <c r="B817" s="9"/>
       <c r="C817" s="9"/>
       <c r="D817" s="9"/>
@@ -15820,7 +15854,7 @@
       <c r="L817" s="9"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="A818" s="33"/>
+      <c r="A818" s="34"/>
       <c r="B818" s="9"/>
       <c r="C818" s="9"/>
       <c r="D818" s="9"/>
@@ -15834,7 +15868,7 @@
       <c r="L818" s="9"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="A819" s="33"/>
+      <c r="A819" s="34"/>
       <c r="B819" s="9"/>
       <c r="C819" s="9"/>
       <c r="D819" s="9"/>
@@ -15848,7 +15882,7 @@
       <c r="L819" s="9"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="A820" s="33"/>
+      <c r="A820" s="34"/>
       <c r="B820" s="9"/>
       <c r="C820" s="9"/>
       <c r="D820" s="9"/>
@@ -15862,7 +15896,7 @@
       <c r="L820" s="9"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="A821" s="33"/>
+      <c r="A821" s="34"/>
       <c r="B821" s="9"/>
       <c r="C821" s="9"/>
       <c r="D821" s="9"/>
@@ -15876,7 +15910,7 @@
       <c r="L821" s="9"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="A822" s="33"/>
+      <c r="A822" s="34"/>
       <c r="B822" s="9"/>
       <c r="C822" s="9"/>
       <c r="D822" s="9"/>
@@ -15890,7 +15924,7 @@
       <c r="L822" s="9"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="A823" s="33"/>
+      <c r="A823" s="34"/>
       <c r="B823" s="9"/>
       <c r="C823" s="9"/>
       <c r="D823" s="9"/>
@@ -15904,7 +15938,7 @@
       <c r="L823" s="9"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="A824" s="33"/>
+      <c r="A824" s="34"/>
       <c r="B824" s="9"/>
       <c r="C824" s="9"/>
       <c r="D824" s="9"/>
@@ -15918,7 +15952,7 @@
       <c r="L824" s="9"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="A825" s="33"/>
+      <c r="A825" s="34"/>
       <c r="B825" s="9"/>
       <c r="C825" s="9"/>
       <c r="D825" s="9"/>
@@ -15932,7 +15966,7 @@
       <c r="L825" s="9"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="A826" s="33"/>
+      <c r="A826" s="34"/>
       <c r="B826" s="9"/>
       <c r="C826" s="9"/>
       <c r="D826" s="9"/>
@@ -15946,7 +15980,7 @@
       <c r="L826" s="9"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="A827" s="33"/>
+      <c r="A827" s="34"/>
       <c r="B827" s="9"/>
       <c r="C827" s="9"/>
       <c r="D827" s="9"/>
@@ -15960,7 +15994,7 @@
       <c r="L827" s="9"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="A828" s="33"/>
+      <c r="A828" s="34"/>
       <c r="B828" s="9"/>
       <c r="C828" s="9"/>
       <c r="D828" s="9"/>
@@ -15974,7 +16008,7 @@
       <c r="L828" s="9"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="A829" s="33"/>
+      <c r="A829" s="34"/>
       <c r="B829" s="9"/>
       <c r="C829" s="9"/>
       <c r="D829" s="9"/>
@@ -15988,7 +16022,7 @@
       <c r="L829" s="9"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="A830" s="33"/>
+      <c r="A830" s="34"/>
       <c r="B830" s="9"/>
       <c r="C830" s="9"/>
       <c r="D830" s="9"/>
@@ -16002,7 +16036,7 @@
       <c r="L830" s="9"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="A831" s="33"/>
+      <c r="A831" s="34"/>
       <c r="B831" s="9"/>
       <c r="C831" s="9"/>
       <c r="D831" s="9"/>
@@ -16016,7 +16050,7 @@
       <c r="L831" s="9"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="A832" s="33"/>
+      <c r="A832" s="34"/>
       <c r="B832" s="9"/>
       <c r="C832" s="9"/>
       <c r="D832" s="9"/>
@@ -16030,7 +16064,7 @@
       <c r="L832" s="9"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="A833" s="33"/>
+      <c r="A833" s="34"/>
       <c r="B833" s="9"/>
       <c r="C833" s="9"/>
       <c r="D833" s="9"/>
@@ -16044,7 +16078,7 @@
       <c r="L833" s="9"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="A834" s="33"/>
+      <c r="A834" s="34"/>
       <c r="B834" s="9"/>
       <c r="C834" s="9"/>
       <c r="D834" s="9"/>
@@ -16058,7 +16092,7 @@
       <c r="L834" s="9"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="A835" s="33"/>
+      <c r="A835" s="34"/>
       <c r="B835" s="9"/>
       <c r="C835" s="9"/>
       <c r="D835" s="9"/>
@@ -16072,7 +16106,7 @@
       <c r="L835" s="9"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="A836" s="33"/>
+      <c r="A836" s="34"/>
       <c r="B836" s="9"/>
       <c r="C836" s="9"/>
       <c r="D836" s="9"/>
@@ -16086,7 +16120,7 @@
       <c r="L836" s="9"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="A837" s="33"/>
+      <c r="A837" s="34"/>
       <c r="B837" s="9"/>
       <c r="C837" s="9"/>
       <c r="D837" s="9"/>
@@ -16100,7 +16134,7 @@
       <c r="L837" s="9"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="A838" s="33"/>
+      <c r="A838" s="34"/>
       <c r="B838" s="9"/>
       <c r="C838" s="9"/>
       <c r="D838" s="9"/>
@@ -16114,7 +16148,7 @@
       <c r="L838" s="9"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="A839" s="33"/>
+      <c r="A839" s="34"/>
       <c r="B839" s="9"/>
       <c r="C839" s="9"/>
       <c r="D839" s="9"/>
@@ -16128,7 +16162,7 @@
       <c r="L839" s="9"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="A840" s="33"/>
+      <c r="A840" s="34"/>
       <c r="B840" s="9"/>
       <c r="C840" s="9"/>
       <c r="D840" s="9"/>
@@ -16142,7 +16176,7 @@
       <c r="L840" s="9"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="A841" s="33"/>
+      <c r="A841" s="34"/>
       <c r="B841" s="9"/>
       <c r="C841" s="9"/>
       <c r="D841" s="9"/>
@@ -16156,7 +16190,7 @@
       <c r="L841" s="9"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="A842" s="33"/>
+      <c r="A842" s="34"/>
       <c r="B842" s="9"/>
       <c r="C842" s="9"/>
       <c r="D842" s="9"/>
@@ -16170,7 +16204,7 @@
       <c r="L842" s="9"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="A843" s="33"/>
+      <c r="A843" s="34"/>
       <c r="B843" s="9"/>
       <c r="C843" s="9"/>
       <c r="D843" s="9"/>
@@ -16184,7 +16218,7 @@
       <c r="L843" s="9"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="A844" s="33"/>
+      <c r="A844" s="34"/>
       <c r="B844" s="9"/>
       <c r="C844" s="9"/>
       <c r="D844" s="9"/>
@@ -16198,7 +16232,7 @@
       <c r="L844" s="9"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="A845" s="33"/>
+      <c r="A845" s="34"/>
       <c r="B845" s="9"/>
       <c r="C845" s="9"/>
       <c r="D845" s="9"/>
@@ -16212,7 +16246,7 @@
       <c r="L845" s="9"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="A846" s="33"/>
+      <c r="A846" s="34"/>
       <c r="B846" s="9"/>
       <c r="C846" s="9"/>
       <c r="D846" s="9"/>
@@ -16226,7 +16260,7 @@
       <c r="L846" s="9"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="A847" s="33"/>
+      <c r="A847" s="34"/>
       <c r="B847" s="9"/>
       <c r="C847" s="9"/>
       <c r="D847" s="9"/>
@@ -16240,7 +16274,7 @@
       <c r="L847" s="9"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="A848" s="33"/>
+      <c r="A848" s="34"/>
       <c r="B848" s="9"/>
       <c r="C848" s="9"/>
       <c r="D848" s="9"/>
@@ -16254,7 +16288,7 @@
       <c r="L848" s="9"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="A849" s="33"/>
+      <c r="A849" s="34"/>
       <c r="B849" s="9"/>
       <c r="C849" s="9"/>
       <c r="D849" s="9"/>
@@ -16268,7 +16302,7 @@
       <c r="L849" s="9"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="A850" s="33"/>
+      <c r="A850" s="34"/>
       <c r="B850" s="9"/>
       <c r="C850" s="9"/>
       <c r="D850" s="9"/>
@@ -16282,7 +16316,7 @@
       <c r="L850" s="9"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="A851" s="33"/>
+      <c r="A851" s="34"/>
       <c r="B851" s="9"/>
       <c r="C851" s="9"/>
       <c r="D851" s="9"/>
@@ -16296,7 +16330,7 @@
       <c r="L851" s="9"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="A852" s="33"/>
+      <c r="A852" s="34"/>
       <c r="B852" s="9"/>
       <c r="C852" s="9"/>
       <c r="D852" s="9"/>
@@ -16310,7 +16344,7 @@
       <c r="L852" s="9"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="A853" s="33"/>
+      <c r="A853" s="34"/>
       <c r="B853" s="9"/>
       <c r="C853" s="9"/>
       <c r="D853" s="9"/>
@@ -16324,7 +16358,7 @@
       <c r="L853" s="9"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="A854" s="33"/>
+      <c r="A854" s="34"/>
       <c r="B854" s="9"/>
       <c r="C854" s="9"/>
       <c r="D854" s="9"/>
@@ -16338,7 +16372,7 @@
       <c r="L854" s="9"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="33"/>
+      <c r="A855" s="34"/>
       <c r="B855" s="9"/>
       <c r="C855" s="9"/>
       <c r="D855" s="9"/>
@@ -16352,7 +16386,7 @@
       <c r="L855" s="9"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="A856" s="33"/>
+      <c r="A856" s="34"/>
       <c r="B856" s="9"/>
       <c r="C856" s="9"/>
       <c r="D856" s="9"/>
@@ -16366,7 +16400,7 @@
       <c r="L856" s="9"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="A857" s="33"/>
+      <c r="A857" s="34"/>
       <c r="B857" s="9"/>
       <c r="C857" s="9"/>
       <c r="D857" s="9"/>
@@ -16380,7 +16414,7 @@
       <c r="L857" s="9"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="A858" s="33"/>
+      <c r="A858" s="34"/>
       <c r="B858" s="9"/>
       <c r="C858" s="9"/>
       <c r="D858" s="9"/>
@@ -16394,7 +16428,7 @@
       <c r="L858" s="9"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="A859" s="33"/>
+      <c r="A859" s="34"/>
       <c r="B859" s="9"/>
       <c r="C859" s="9"/>
       <c r="D859" s="9"/>
@@ -16408,7 +16442,7 @@
       <c r="L859" s="9"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="A860" s="33"/>
+      <c r="A860" s="34"/>
       <c r="B860" s="9"/>
       <c r="C860" s="9"/>
       <c r="D860" s="9"/>
@@ -16422,7 +16456,7 @@
       <c r="L860" s="9"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="A861" s="33"/>
+      <c r="A861" s="34"/>
       <c r="B861" s="9"/>
       <c r="C861" s="9"/>
       <c r="D861" s="9"/>
@@ -16436,7 +16470,7 @@
       <c r="L861" s="9"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="33"/>
+      <c r="A862" s="34"/>
       <c r="B862" s="9"/>
       <c r="C862" s="9"/>
       <c r="D862" s="9"/>
@@ -16450,7 +16484,7 @@
       <c r="L862" s="9"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="A863" s="33"/>
+      <c r="A863" s="34"/>
       <c r="B863" s="9"/>
       <c r="C863" s="9"/>
       <c r="D863" s="9"/>
@@ -16464,7 +16498,7 @@
       <c r="L863" s="9"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="A864" s="33"/>
+      <c r="A864" s="34"/>
       <c r="B864" s="9"/>
       <c r="C864" s="9"/>
       <c r="D864" s="9"/>
@@ -16478,7 +16512,7 @@
       <c r="L864" s="9"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="A865" s="33"/>
+      <c r="A865" s="34"/>
       <c r="B865" s="9"/>
       <c r="C865" s="9"/>
       <c r="D865" s="9"/>
@@ -16492,7 +16526,7 @@
       <c r="L865" s="9"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="A866" s="33"/>
+      <c r="A866" s="34"/>
       <c r="B866" s="9"/>
       <c r="C866" s="9"/>
       <c r="D866" s="9"/>
@@ -16506,7 +16540,7 @@
       <c r="L866" s="9"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="A867" s="33"/>
+      <c r="A867" s="34"/>
       <c r="B867" s="9"/>
       <c r="C867" s="9"/>
       <c r="D867" s="9"/>
@@ -16520,7 +16554,7 @@
       <c r="L867" s="9"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="A868" s="33"/>
+      <c r="A868" s="34"/>
       <c r="B868" s="9"/>
       <c r="C868" s="9"/>
       <c r="D868" s="9"/>
@@ -16534,7 +16568,7 @@
       <c r="L868" s="9"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="33"/>
+      <c r="A869" s="34"/>
       <c r="B869" s="9"/>
       <c r="C869" s="9"/>
       <c r="D869" s="9"/>
@@ -16548,7 +16582,7 @@
       <c r="L869" s="9"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="A870" s="33"/>
+      <c r="A870" s="34"/>
       <c r="B870" s="9"/>
       <c r="C870" s="9"/>
       <c r="D870" s="9"/>
@@ -16562,7 +16596,7 @@
       <c r="L870" s="9"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="A871" s="33"/>
+      <c r="A871" s="34"/>
       <c r="B871" s="9"/>
       <c r="C871" s="9"/>
       <c r="D871" s="9"/>
@@ -16576,7 +16610,7 @@
       <c r="L871" s="9"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="A872" s="33"/>
+      <c r="A872" s="34"/>
       <c r="B872" s="9"/>
       <c r="C872" s="9"/>
       <c r="D872" s="9"/>
@@ -16590,7 +16624,7 @@
       <c r="L872" s="9"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="A873" s="33"/>
+      <c r="A873" s="34"/>
       <c r="B873" s="9"/>
       <c r="C873" s="9"/>
       <c r="D873" s="9"/>
@@ -16604,7 +16638,7 @@
       <c r="L873" s="9"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="A874" s="33"/>
+      <c r="A874" s="34"/>
       <c r="B874" s="9"/>
       <c r="C874" s="9"/>
       <c r="D874" s="9"/>
@@ -16618,7 +16652,7 @@
       <c r="L874" s="9"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="A875" s="33"/>
+      <c r="A875" s="34"/>
       <c r="B875" s="9"/>
       <c r="C875" s="9"/>
       <c r="D875" s="9"/>
@@ -16632,7 +16666,7 @@
       <c r="L875" s="9"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="A876" s="33"/>
+      <c r="A876" s="34"/>
       <c r="B876" s="9"/>
       <c r="C876" s="9"/>
       <c r="D876" s="9"/>
@@ -16646,7 +16680,7 @@
       <c r="L876" s="9"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="A877" s="33"/>
+      <c r="A877" s="34"/>
       <c r="B877" s="9"/>
       <c r="C877" s="9"/>
       <c r="D877" s="9"/>
@@ -16660,7 +16694,7 @@
       <c r="L877" s="9"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="A878" s="33"/>
+      <c r="A878" s="34"/>
       <c r="B878" s="9"/>
       <c r="C878" s="9"/>
       <c r="D878" s="9"/>
@@ -16674,7 +16708,7 @@
       <c r="L878" s="9"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="A879" s="33"/>
+      <c r="A879" s="34"/>
       <c r="B879" s="9"/>
       <c r="C879" s="9"/>
       <c r="D879" s="9"/>
@@ -16688,7 +16722,7 @@
       <c r="L879" s="9"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="A880" s="33"/>
+      <c r="A880" s="34"/>
       <c r="B880" s="9"/>
       <c r="C880" s="9"/>
       <c r="D880" s="9"/>
@@ -16702,7 +16736,7 @@
       <c r="L880" s="9"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="A881" s="33"/>
+      <c r="A881" s="34"/>
       <c r="B881" s="9"/>
       <c r="C881" s="9"/>
       <c r="D881" s="9"/>
@@ -16716,7 +16750,7 @@
       <c r="L881" s="9"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="A882" s="33"/>
+      <c r="A882" s="34"/>
       <c r="B882" s="9"/>
       <c r="C882" s="9"/>
       <c r="D882" s="9"/>
@@ -16730,7 +16764,7 @@
       <c r="L882" s="9"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="A883" s="33"/>
+      <c r="A883" s="34"/>
       <c r="B883" s="9"/>
       <c r="C883" s="9"/>
       <c r="D883" s="9"/>
@@ -16744,7 +16778,7 @@
       <c r="L883" s="9"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="A884" s="33"/>
+      <c r="A884" s="34"/>
       <c r="B884" s="9"/>
       <c r="C884" s="9"/>
       <c r="D884" s="9"/>
@@ -16758,7 +16792,7 @@
       <c r="L884" s="9"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="A885" s="33"/>
+      <c r="A885" s="34"/>
       <c r="B885" s="9"/>
       <c r="C885" s="9"/>
       <c r="D885" s="9"/>
@@ -16772,7 +16806,7 @@
       <c r="L885" s="9"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="A886" s="33"/>
+      <c r="A886" s="34"/>
       <c r="B886" s="9"/>
       <c r="C886" s="9"/>
       <c r="D886" s="9"/>
@@ -16786,7 +16820,7 @@
       <c r="L886" s="9"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="A887" s="33"/>
+      <c r="A887" s="34"/>
       <c r="B887" s="9"/>
       <c r="C887" s="9"/>
       <c r="D887" s="9"/>
@@ -16800,7 +16834,7 @@
       <c r="L887" s="9"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="A888" s="33"/>
+      <c r="A888" s="34"/>
       <c r="B888" s="9"/>
       <c r="C888" s="9"/>
       <c r="D888" s="9"/>
@@ -16814,7 +16848,7 @@
       <c r="L888" s="9"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="A889" s="33"/>
+      <c r="A889" s="34"/>
       <c r="B889" s="9"/>
       <c r="C889" s="9"/>
       <c r="D889" s="9"/>
@@ -16828,7 +16862,7 @@
       <c r="L889" s="9"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="A890" s="33"/>
+      <c r="A890" s="34"/>
       <c r="B890" s="9"/>
       <c r="C890" s="9"/>
       <c r="D890" s="9"/>
@@ -16842,7 +16876,7 @@
       <c r="L890" s="9"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="A891" s="33"/>
+      <c r="A891" s="34"/>
       <c r="B891" s="9"/>
       <c r="C891" s="9"/>
       <c r="D891" s="9"/>
@@ -16856,7 +16890,7 @@
       <c r="L891" s="9"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="A892" s="33"/>
+      <c r="A892" s="34"/>
       <c r="B892" s="9"/>
       <c r="C892" s="9"/>
       <c r="D892" s="9"/>
@@ -16870,7 +16904,7 @@
       <c r="L892" s="9"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="A893" s="33"/>
+      <c r="A893" s="34"/>
       <c r="B893" s="9"/>
       <c r="C893" s="9"/>
       <c r="D893" s="9"/>
@@ -16884,7 +16918,7 @@
       <c r="L893" s="9"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="A894" s="33"/>
+      <c r="A894" s="34"/>
       <c r="B894" s="9"/>
       <c r="C894" s="9"/>
       <c r="D894" s="9"/>
@@ -16898,7 +16932,7 @@
       <c r="L894" s="9"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="A895" s="33"/>
+      <c r="A895" s="34"/>
       <c r="B895" s="9"/>
       <c r="C895" s="9"/>
       <c r="D895" s="9"/>
@@ -16912,7 +16946,7 @@
       <c r="L895" s="9"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="A896" s="33"/>
+      <c r="A896" s="34"/>
       <c r="B896" s="9"/>
       <c r="C896" s="9"/>
       <c r="D896" s="9"/>
@@ -16926,7 +16960,7 @@
       <c r="L896" s="9"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="A897" s="33"/>
+      <c r="A897" s="34"/>
       <c r="B897" s="9"/>
       <c r="C897" s="9"/>
       <c r="D897" s="9"/>
@@ -16940,7 +16974,7 @@
       <c r="L897" s="9"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="A898" s="33"/>
+      <c r="A898" s="34"/>
       <c r="B898" s="9"/>
       <c r="C898" s="9"/>
       <c r="D898" s="9"/>
@@ -16954,7 +16988,7 @@
       <c r="L898" s="9"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="A899" s="33"/>
+      <c r="A899" s="34"/>
       <c r="B899" s="9"/>
       <c r="C899" s="9"/>
       <c r="D899" s="9"/>
@@ -16968,7 +17002,7 @@
       <c r="L899" s="9"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="A900" s="33"/>
+      <c r="A900" s="34"/>
       <c r="B900" s="9"/>
       <c r="C900" s="9"/>
       <c r="D900" s="9"/>
@@ -16982,7 +17016,7 @@
       <c r="L900" s="9"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="A901" s="33"/>
+      <c r="A901" s="34"/>
       <c r="B901" s="9"/>
       <c r="C901" s="9"/>
       <c r="D901" s="9"/>
@@ -16996,7 +17030,7 @@
       <c r="L901" s="9"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="A902" s="33"/>
+      <c r="A902" s="34"/>
       <c r="B902" s="9"/>
       <c r="C902" s="9"/>
       <c r="D902" s="9"/>
@@ -17010,7 +17044,7 @@
       <c r="L902" s="9"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="A903" s="33"/>
+      <c r="A903" s="34"/>
       <c r="B903" s="9"/>
       <c r="C903" s="9"/>
       <c r="D903" s="9"/>
@@ -17024,7 +17058,7 @@
       <c r="L903" s="9"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="A904" s="33"/>
+      <c r="A904" s="34"/>
       <c r="B904" s="9"/>
       <c r="C904" s="9"/>
       <c r="D904" s="9"/>
@@ -17038,7 +17072,7 @@
       <c r="L904" s="9"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="A905" s="33"/>
+      <c r="A905" s="34"/>
       <c r="B905" s="9"/>
       <c r="C905" s="9"/>
       <c r="D905" s="9"/>
@@ -17052,7 +17086,7 @@
       <c r="L905" s="9"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="A906" s="33"/>
+      <c r="A906" s="34"/>
       <c r="B906" s="9"/>
       <c r="C906" s="9"/>
       <c r="D906" s="9"/>
@@ -17066,7 +17100,7 @@
       <c r="L906" s="9"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="A907" s="33"/>
+      <c r="A907" s="34"/>
       <c r="B907" s="9"/>
       <c r="C907" s="9"/>
       <c r="D907" s="9"/>
@@ -17080,7 +17114,7 @@
       <c r="L907" s="9"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="A908" s="33"/>
+      <c r="A908" s="34"/>
       <c r="B908" s="9"/>
       <c r="C908" s="9"/>
       <c r="D908" s="9"/>
@@ -17094,7 +17128,7 @@
       <c r="L908" s="9"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="A909" s="33"/>
+      <c r="A909" s="34"/>
       <c r="B909" s="9"/>
       <c r="C909" s="9"/>
       <c r="D909" s="9"/>
@@ -17108,7 +17142,7 @@
       <c r="L909" s="9"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="A910" s="33"/>
+      <c r="A910" s="34"/>
       <c r="B910" s="9"/>
       <c r="C910" s="9"/>
       <c r="D910" s="9"/>
@@ -17122,7 +17156,7 @@
       <c r="L910" s="9"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="A911" s="33"/>
+      <c r="A911" s="34"/>
       <c r="B911" s="9"/>
       <c r="C911" s="9"/>
       <c r="D911" s="9"/>
@@ -17136,7 +17170,7 @@
       <c r="L911" s="9"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="A912" s="33"/>
+      <c r="A912" s="34"/>
       <c r="B912" s="9"/>
       <c r="C912" s="9"/>
       <c r="D912" s="9"/>
@@ -17150,7 +17184,7 @@
       <c r="L912" s="9"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="A913" s="33"/>
+      <c r="A913" s="34"/>
       <c r="B913" s="9"/>
       <c r="C913" s="9"/>
       <c r="D913" s="9"/>
@@ -17164,7 +17198,7 @@
       <c r="L913" s="9"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="A914" s="33"/>
+      <c r="A914" s="34"/>
       <c r="B914" s="9"/>
       <c r="C914" s="9"/>
       <c r="D914" s="9"/>
@@ -17178,7 +17212,7 @@
       <c r="L914" s="9"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="A915" s="33"/>
+      <c r="A915" s="34"/>
       <c r="B915" s="9"/>
       <c r="C915" s="9"/>
       <c r="D915" s="9"/>
@@ -17192,7 +17226,7 @@
       <c r="L915" s="9"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="A916" s="33"/>
+      <c r="A916" s="34"/>
       <c r="B916" s="9"/>
       <c r="C916" s="9"/>
       <c r="D916" s="9"/>
@@ -17206,7 +17240,7 @@
       <c r="L916" s="9"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="A917" s="33"/>
+      <c r="A917" s="34"/>
       <c r="B917" s="9"/>
       <c r="C917" s="9"/>
       <c r="D917" s="9"/>
@@ -17220,7 +17254,7 @@
       <c r="L917" s="9"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="A918" s="33"/>
+      <c r="A918" s="34"/>
       <c r="B918" s="9"/>
       <c r="C918" s="9"/>
       <c r="D918" s="9"/>
@@ -17234,7 +17268,7 @@
       <c r="L918" s="9"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="A919" s="33"/>
+      <c r="A919" s="34"/>
       <c r="B919" s="9"/>
       <c r="C919" s="9"/>
       <c r="D919" s="9"/>
@@ -17248,7 +17282,7 @@
       <c r="L919" s="9"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="A920" s="33"/>
+      <c r="A920" s="34"/>
       <c r="B920" s="9"/>
       <c r="C920" s="9"/>
       <c r="D920" s="9"/>
@@ -17262,7 +17296,7 @@
       <c r="L920" s="9"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="A921" s="33"/>
+      <c r="A921" s="34"/>
       <c r="B921" s="9"/>
       <c r="C921" s="9"/>
       <c r="D921" s="9"/>
@@ -17276,7 +17310,7 @@
       <c r="L921" s="9"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="A922" s="33"/>
+      <c r="A922" s="34"/>
       <c r="B922" s="9"/>
       <c r="C922" s="9"/>
       <c r="D922" s="9"/>
@@ -17290,7 +17324,7 @@
       <c r="L922" s="9"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="A923" s="33"/>
+      <c r="A923" s="34"/>
       <c r="B923" s="9"/>
       <c r="C923" s="9"/>
       <c r="D923" s="9"/>
@@ -17304,7 +17338,7 @@
       <c r="L923" s="9"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="A924" s="33"/>
+      <c r="A924" s="34"/>
       <c r="B924" s="9"/>
       <c r="C924" s="9"/>
       <c r="D924" s="9"/>
@@ -17318,7 +17352,7 @@
       <c r="L924" s="9"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="A925" s="33"/>
+      <c r="A925" s="34"/>
       <c r="B925" s="9"/>
       <c r="C925" s="9"/>
       <c r="D925" s="9"/>
@@ -17332,7 +17366,7 @@
       <c r="L925" s="9"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="A926" s="33"/>
+      <c r="A926" s="34"/>
       <c r="B926" s="9"/>
       <c r="C926" s="9"/>
       <c r="D926" s="9"/>
@@ -17346,7 +17380,7 @@
       <c r="L926" s="9"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="A927" s="33"/>
+      <c r="A927" s="34"/>
       <c r="B927" s="9"/>
       <c r="C927" s="9"/>
       <c r="D927" s="9"/>
@@ -17360,7 +17394,7 @@
       <c r="L927" s="9"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="A928" s="33"/>
+      <c r="A928" s="34"/>
       <c r="B928" s="9"/>
       <c r="C928" s="9"/>
       <c r="D928" s="9"/>
@@ -17374,7 +17408,7 @@
       <c r="L928" s="9"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="A929" s="33"/>
+      <c r="A929" s="34"/>
       <c r="B929" s="9"/>
       <c r="C929" s="9"/>
       <c r="D929" s="9"/>
@@ -17388,7 +17422,7 @@
       <c r="L929" s="9"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="A930" s="33"/>
+      <c r="A930" s="34"/>
       <c r="B930" s="9"/>
       <c r="C930" s="9"/>
       <c r="D930" s="9"/>
@@ -17402,7 +17436,7 @@
       <c r="L930" s="9"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="A931" s="33"/>
+      <c r="A931" s="34"/>
       <c r="B931" s="9"/>
       <c r="C931" s="9"/>
       <c r="D931" s="9"/>
@@ -17416,7 +17450,7 @@
       <c r="L931" s="9"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="33"/>
+      <c r="A932" s="34"/>
       <c r="B932" s="9"/>
       <c r="C932" s="9"/>
       <c r="D932" s="9"/>
@@ -17430,7 +17464,7 @@
       <c r="L932" s="9"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="A933" s="33"/>
+      <c r="A933" s="34"/>
       <c r="B933" s="9"/>
       <c r="C933" s="9"/>
       <c r="D933" s="9"/>
@@ -17444,7 +17478,7 @@
       <c r="L933" s="9"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="A934" s="33"/>
+      <c r="A934" s="34"/>
       <c r="B934" s="9"/>
       <c r="C934" s="9"/>
       <c r="D934" s="9"/>
@@ -17458,7 +17492,7 @@
       <c r="L934" s="9"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="A935" s="33"/>
+      <c r="A935" s="34"/>
       <c r="B935" s="9"/>
       <c r="C935" s="9"/>
       <c r="D935" s="9"/>
@@ -17472,7 +17506,7 @@
       <c r="L935" s="9"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="A936" s="33"/>
+      <c r="A936" s="34"/>
       <c r="B936" s="9"/>
       <c r="C936" s="9"/>
       <c r="D936" s="9"/>
@@ -17486,7 +17520,7 @@
       <c r="L936" s="9"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="A937" s="33"/>
+      <c r="A937" s="34"/>
       <c r="B937" s="9"/>
       <c r="C937" s="9"/>
       <c r="D937" s="9"/>
@@ -17500,7 +17534,7 @@
       <c r="L937" s="9"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="A938" s="33"/>
+      <c r="A938" s="34"/>
       <c r="B938" s="9"/>
       <c r="C938" s="9"/>
       <c r="D938" s="9"/>
@@ -17514,7 +17548,7 @@
       <c r="L938" s="9"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="A939" s="33"/>
+      <c r="A939" s="34"/>
       <c r="B939" s="9"/>
       <c r="C939" s="9"/>
       <c r="D939" s="9"/>
@@ -17528,7 +17562,7 @@
       <c r="L939" s="9"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="A940" s="33"/>
+      <c r="A940" s="34"/>
       <c r="B940" s="9"/>
       <c r="C940" s="9"/>
       <c r="D940" s="9"/>
@@ -17542,7 +17576,7 @@
       <c r="L940" s="9"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="A941" s="33"/>
+      <c r="A941" s="34"/>
       <c r="B941" s="9"/>
       <c r="C941" s="9"/>
       <c r="D941" s="9"/>
@@ -17556,7 +17590,7 @@
       <c r="L941" s="9"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="A942" s="33"/>
+      <c r="A942" s="34"/>
       <c r="B942" s="9"/>
       <c r="C942" s="9"/>
       <c r="D942" s="9"/>
@@ -17570,7 +17604,7 @@
       <c r="L942" s="9"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="A943" s="33"/>
+      <c r="A943" s="34"/>
       <c r="B943" s="9"/>
       <c r="C943" s="9"/>
       <c r="D943" s="9"/>
@@ -17584,7 +17618,7 @@
       <c r="L943" s="9"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="A944" s="33"/>
+      <c r="A944" s="34"/>
       <c r="B944" s="9"/>
       <c r="C944" s="9"/>
       <c r="D944" s="9"/>
@@ -17598,7 +17632,7 @@
       <c r="L944" s="9"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="A945" s="33"/>
+      <c r="A945" s="34"/>
       <c r="B945" s="9"/>
       <c r="C945" s="9"/>
       <c r="D945" s="9"/>
@@ -17612,7 +17646,7 @@
       <c r="L945" s="9"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="A946" s="33"/>
+      <c r="A946" s="34"/>
       <c r="B946" s="9"/>
       <c r="C946" s="9"/>
       <c r="D946" s="9"/>
@@ -17626,7 +17660,7 @@
       <c r="L946" s="9"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="A947" s="33"/>
+      <c r="A947" s="34"/>
       <c r="B947" s="9"/>
       <c r="C947" s="9"/>
       <c r="D947" s="9"/>
@@ -17640,7 +17674,7 @@
       <c r="L947" s="9"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="A948" s="33"/>
+      <c r="A948" s="34"/>
       <c r="B948" s="9"/>
       <c r="C948" s="9"/>
       <c r="D948" s="9"/>
@@ -17654,7 +17688,7 @@
       <c r="L948" s="9"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="A949" s="33"/>
+      <c r="A949" s="34"/>
       <c r="B949" s="9"/>
       <c r="C949" s="9"/>
       <c r="D949" s="9"/>
@@ -17668,7 +17702,7 @@
       <c r="L949" s="9"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="A950" s="33"/>
+      <c r="A950" s="34"/>
       <c r="B950" s="9"/>
       <c r="C950" s="9"/>
       <c r="D950" s="9"/>
@@ -17682,7 +17716,7 @@
       <c r="L950" s="9"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="A951" s="33"/>
+      <c r="A951" s="34"/>
       <c r="B951" s="9"/>
       <c r="C951" s="9"/>
       <c r="D951" s="9"/>
@@ -17696,7 +17730,7 @@
       <c r="L951" s="9"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="A952" s="33"/>
+      <c r="A952" s="34"/>
       <c r="B952" s="9"/>
       <c r="C952" s="9"/>
       <c r="D952" s="9"/>
@@ -17710,7 +17744,7 @@
       <c r="L952" s="9"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="A953" s="33"/>
+      <c r="A953" s="34"/>
       <c r="B953" s="9"/>
       <c r="C953" s="9"/>
       <c r="D953" s="9"/>
@@ -17724,7 +17758,7 @@
       <c r="L953" s="9"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="33"/>
+      <c r="A954" s="34"/>
       <c r="B954" s="9"/>
       <c r="C954" s="9"/>
       <c r="D954" s="9"/>
@@ -17738,7 +17772,7 @@
       <c r="L954" s="9"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="33"/>
+      <c r="A955" s="34"/>
       <c r="B955" s="9"/>
       <c r="C955" s="9"/>
       <c r="D955" s="9"/>
@@ -17752,7 +17786,7 @@
       <c r="L955" s="9"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="33"/>
+      <c r="A956" s="34"/>
       <c r="B956" s="9"/>
       <c r="C956" s="9"/>
       <c r="D956" s="9"/>
@@ -17766,7 +17800,7 @@
       <c r="L956" s="9"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="33"/>
+      <c r="A957" s="34"/>
       <c r="B957" s="9"/>
       <c r="C957" s="9"/>
       <c r="D957" s="9"/>
@@ -17780,7 +17814,7 @@
       <c r="L957" s="9"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="33"/>
+      <c r="A958" s="34"/>
       <c r="B958" s="9"/>
       <c r="C958" s="9"/>
       <c r="D958" s="9"/>
@@ -17794,7 +17828,7 @@
       <c r="L958" s="9"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="33"/>
+      <c r="A959" s="34"/>
       <c r="B959" s="9"/>
       <c r="C959" s="9"/>
       <c r="D959" s="9"/>
@@ -17808,7 +17842,7 @@
       <c r="L959" s="9"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="33"/>
+      <c r="A960" s="34"/>
       <c r="B960" s="9"/>
       <c r="C960" s="9"/>
       <c r="D960" s="9"/>
@@ -17822,7 +17856,7 @@
       <c r="L960" s="9"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="33"/>
+      <c r="A961" s="34"/>
       <c r="B961" s="9"/>
       <c r="C961" s="9"/>
       <c r="D961" s="9"/>
@@ -17836,7 +17870,7 @@
       <c r="L961" s="9"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="33"/>
+      <c r="A962" s="34"/>
       <c r="B962" s="9"/>
       <c r="C962" s="9"/>
       <c r="D962" s="9"/>
@@ -17850,7 +17884,7 @@
       <c r="L962" s="9"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="33"/>
+      <c r="A963" s="34"/>
       <c r="B963" s="9"/>
       <c r="C963" s="9"/>
       <c r="D963" s="9"/>
@@ -17864,7 +17898,7 @@
       <c r="L963" s="9"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="33"/>
+      <c r="A964" s="34"/>
       <c r="B964" s="9"/>
       <c r="C964" s="9"/>
       <c r="D964" s="9"/>
@@ -17878,7 +17912,7 @@
       <c r="L964" s="9"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="A965" s="33"/>
+      <c r="A965" s="34"/>
       <c r="B965" s="9"/>
       <c r="C965" s="9"/>
       <c r="D965" s="9"/>
@@ -17892,7 +17926,7 @@
       <c r="L965" s="9"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="A966" s="33"/>
+      <c r="A966" s="34"/>
       <c r="B966" s="9"/>
       <c r="C966" s="9"/>
       <c r="D966" s="9"/>
@@ -17906,7 +17940,7 @@
       <c r="L966" s="9"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="33"/>
+      <c r="A967" s="34"/>
       <c r="B967" s="9"/>
       <c r="C967" s="9"/>
       <c r="D967" s="9"/>
@@ -17920,7 +17954,7 @@
       <c r="L967" s="9"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="A968" s="33"/>
+      <c r="A968" s="34"/>
       <c r="B968" s="9"/>
       <c r="C968" s="9"/>
       <c r="D968" s="9"/>
@@ -17934,7 +17968,7 @@
       <c r="L968" s="9"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="A969" s="33"/>
+      <c r="A969" s="34"/>
       <c r="B969" s="9"/>
       <c r="C969" s="9"/>
       <c r="D969" s="9"/>
@@ -17948,7 +17982,7 @@
       <c r="L969" s="9"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="A970" s="33"/>
+      <c r="A970" s="34"/>
       <c r="B970" s="9"/>
       <c r="C970" s="9"/>
       <c r="D970" s="9"/>
@@ -17962,7 +17996,7 @@
       <c r="L970" s="9"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="A971" s="33"/>
+      <c r="A971" s="34"/>
       <c r="B971" s="9"/>
       <c r="C971" s="9"/>
       <c r="D971" s="9"/>
@@ -17976,7 +18010,7 @@
       <c r="L971" s="9"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="33"/>
+      <c r="A972" s="34"/>
       <c r="B972" s="9"/>
       <c r="C972" s="9"/>
       <c r="D972" s="9"/>
@@ -17990,7 +18024,7 @@
       <c r="L972" s="9"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="33"/>
+      <c r="A973" s="34"/>
       <c r="B973" s="9"/>
       <c r="C973" s="9"/>
       <c r="D973" s="9"/>
@@ -18004,7 +18038,7 @@
       <c r="L973" s="9"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="33"/>
+      <c r="A974" s="34"/>
       <c r="B974" s="9"/>
       <c r="C974" s="9"/>
       <c r="D974" s="9"/>
@@ -18018,7 +18052,7 @@
       <c r="L974" s="9"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="33"/>
+      <c r="A975" s="34"/>
       <c r="B975" s="9"/>
       <c r="C975" s="9"/>
       <c r="D975" s="9"/>
@@ -18032,7 +18066,7 @@
       <c r="L975" s="9"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="33"/>
+      <c r="A976" s="34"/>
       <c r="B976" s="9"/>
       <c r="C976" s="9"/>
       <c r="D976" s="9"/>
@@ -18046,7 +18080,7 @@
       <c r="L976" s="9"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="33"/>
+      <c r="A977" s="34"/>
       <c r="B977" s="9"/>
       <c r="C977" s="9"/>
       <c r="D977" s="9"/>
@@ -18060,7 +18094,7 @@
       <c r="L977" s="9"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="33"/>
+      <c r="A978" s="34"/>
       <c r="B978" s="9"/>
       <c r="C978" s="9"/>
       <c r="D978" s="9"/>
@@ -18074,7 +18108,7 @@
       <c r="L978" s="9"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="33"/>
+      <c r="A979" s="34"/>
       <c r="B979" s="9"/>
       <c r="C979" s="9"/>
       <c r="D979" s="9"/>
@@ -18088,7 +18122,7 @@
       <c r="L979" s="9"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="33"/>
+      <c r="A980" s="34"/>
       <c r="B980" s="9"/>
       <c r="C980" s="9"/>
       <c r="D980" s="9"/>
@@ -18102,7 +18136,7 @@
       <c r="L980" s="9"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="33"/>
+      <c r="A981" s="34"/>
       <c r="B981" s="9"/>
       <c r="C981" s="9"/>
       <c r="D981" s="9"/>
@@ -18116,7 +18150,7 @@
       <c r="L981" s="9"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="33"/>
+      <c r="A982" s="34"/>
       <c r="B982" s="9"/>
       <c r="C982" s="9"/>
       <c r="D982" s="9"/>
@@ -18130,7 +18164,7 @@
       <c r="L982" s="9"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="33"/>
+      <c r="A983" s="34"/>
       <c r="B983" s="9"/>
       <c r="C983" s="9"/>
       <c r="D983" s="9"/>
@@ -18144,7 +18178,7 @@
       <c r="L983" s="9"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="33"/>
+      <c r="A984" s="34"/>
       <c r="B984" s="9"/>
       <c r="C984" s="9"/>
       <c r="D984" s="9"/>
@@ -18158,7 +18192,7 @@
       <c r="L984" s="9"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="33"/>
+      <c r="A985" s="34"/>
       <c r="B985" s="9"/>
       <c r="C985" s="9"/>
       <c r="D985" s="9"/>
@@ -18172,7 +18206,7 @@
       <c r="L985" s="9"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="33"/>
+      <c r="A986" s="34"/>
       <c r="B986" s="9"/>
       <c r="C986" s="9"/>
       <c r="D986" s="9"/>
@@ -18186,7 +18220,7 @@
       <c r="L986" s="9"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="33"/>
+      <c r="A987" s="34"/>
       <c r="B987" s="9"/>
       <c r="C987" s="9"/>
       <c r="D987" s="9"/>
@@ -18200,7 +18234,7 @@
       <c r="L987" s="9"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="33"/>
+      <c r="A988" s="34"/>
       <c r="B988" s="9"/>
       <c r="C988" s="9"/>
       <c r="D988" s="9"/>
@@ -18214,7 +18248,7 @@
       <c r="L988" s="9"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="33"/>
+      <c r="A989" s="34"/>
       <c r="B989" s="9"/>
       <c r="C989" s="9"/>
       <c r="D989" s="9"/>
@@ -18228,7 +18262,7 @@
       <c r="L989" s="9"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="33"/>
+      <c r="A990" s="34"/>
       <c r="B990" s="9"/>
       <c r="C990" s="9"/>
       <c r="D990" s="9"/>
@@ -18242,7 +18276,7 @@
       <c r="L990" s="9"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="33"/>
+      <c r="A991" s="34"/>
       <c r="B991" s="9"/>
       <c r="C991" s="9"/>
       <c r="D991" s="9"/>
@@ -18256,7 +18290,7 @@
       <c r="L991" s="9"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="33"/>
+      <c r="A992" s="34"/>
       <c r="B992" s="9"/>
       <c r="C992" s="9"/>
       <c r="D992" s="9"/>
@@ -18270,7 +18304,7 @@
       <c r="L992" s="9"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="33"/>
+      <c r="A993" s="34"/>
       <c r="B993" s="9"/>
       <c r="C993" s="9"/>
       <c r="D993" s="9"/>
@@ -18284,7 +18318,7 @@
       <c r="L993" s="9"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="33"/>
+      <c r="A994" s="34"/>
       <c r="B994" s="9"/>
       <c r="C994" s="9"/>
       <c r="D994" s="9"/>
@@ -18298,7 +18332,7 @@
       <c r="L994" s="9"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="33"/>
+      <c r="A995" s="34"/>
       <c r="B995" s="9"/>
       <c r="C995" s="9"/>
       <c r="D995" s="9"/>
@@ -18312,7 +18346,7 @@
       <c r="L995" s="9"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="33"/>
+      <c r="A996" s="34"/>
       <c r="B996" s="9"/>
       <c r="C996" s="9"/>
       <c r="D996" s="9"/>
@@ -18326,7 +18360,7 @@
       <c r="L996" s="9"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="33"/>
+      <c r="A997" s="34"/>
       <c r="B997" s="9"/>
       <c r="C997" s="9"/>
       <c r="D997" s="9"/>
@@ -18340,7 +18374,7 @@
       <c r="L997" s="9"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="33"/>
+      <c r="A998" s="34"/>
       <c r="B998" s="9"/>
       <c r="C998" s="9"/>
       <c r="D998" s="9"/>
@@ -18354,7 +18388,7 @@
       <c r="L998" s="9"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="33"/>
+      <c r="A999" s="34"/>
       <c r="B999" s="9"/>
       <c r="C999" s="9"/>
       <c r="D999" s="9"/>
@@ -18368,7 +18402,7 @@
       <c r="L999" s="9"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="33"/>
+      <c r="A1000" s="34"/>
       <c r="B1000" s="9"/>
       <c r="C1000" s="9"/>
       <c r="D1000" s="9"/>
@@ -18382,7 +18416,7 @@
       <c r="L1000" s="9"/>
     </row>
     <row r="1001" ht="15.75" customHeight="1">
-      <c r="A1001" s="33"/>
+      <c r="A1001" s="34"/>
       <c r="B1001" s="9"/>
       <c r="C1001" s="9"/>
       <c r="D1001" s="9"/>
@@ -18396,7 +18430,7 @@
       <c r="L1001" s="9"/>
     </row>
     <row r="1002" ht="15.75" customHeight="1">
-      <c r="A1002" s="33"/>
+      <c r="A1002" s="34"/>
       <c r="B1002" s="9"/>
       <c r="C1002" s="9"/>
       <c r="D1002" s="9"/>
@@ -18410,7 +18444,7 @@
       <c r="L1002" s="9"/>
     </row>
     <row r="1003" ht="15.75" customHeight="1">
-      <c r="A1003" s="33"/>
+      <c r="A1003" s="34"/>
       <c r="B1003" s="9"/>
       <c r="C1003" s="9"/>
       <c r="D1003" s="9"/>
@@ -18424,7 +18458,7 @@
       <c r="L1003" s="9"/>
     </row>
     <row r="1004" ht="15.75" customHeight="1">
-      <c r="A1004" s="33"/>
+      <c r="A1004" s="34"/>
       <c r="B1004" s="9"/>
       <c r="C1004" s="9"/>
       <c r="D1004" s="9"/>
@@ -18438,7 +18472,7 @@
       <c r="L1004" s="9"/>
     </row>
     <row r="1005" ht="15.75" customHeight="1">
-      <c r="A1005" s="33"/>
+      <c r="A1005" s="34"/>
       <c r="B1005" s="9"/>
       <c r="C1005" s="9"/>
       <c r="D1005" s="9"/>
@@ -18452,7 +18486,7 @@
       <c r="L1005" s="9"/>
     </row>
     <row r="1006" ht="15.75" customHeight="1">
-      <c r="A1006" s="33"/>
+      <c r="A1006" s="34"/>
       <c r="B1006" s="9"/>
       <c r="C1006" s="9"/>
       <c r="D1006" s="9"/>
@@ -18466,7 +18500,7 @@
       <c r="L1006" s="9"/>
     </row>
     <row r="1007" ht="15.75" customHeight="1">
-      <c r="A1007" s="33"/>
+      <c r="A1007" s="34"/>
       <c r="B1007" s="9"/>
       <c r="C1007" s="9"/>
       <c r="D1007" s="9"/>
@@ -18480,7 +18514,7 @@
       <c r="L1007" s="9"/>
     </row>
     <row r="1008" ht="15.75" customHeight="1">
-      <c r="A1008" s="33"/>
+      <c r="A1008" s="34"/>
       <c r="B1008" s="9"/>
       <c r="C1008" s="9"/>
       <c r="D1008" s="9"/>
@@ -18494,7 +18528,7 @@
       <c r="L1008" s="9"/>
     </row>
     <row r="1009" ht="15.75" customHeight="1">
-      <c r="A1009" s="33"/>
+      <c r="A1009" s="34"/>
       <c r="B1009" s="9"/>
       <c r="C1009" s="9"/>
       <c r="D1009" s="9"/>
@@ -18507,10 +18541,24 @@
       <c r="K1009" s="9"/>
       <c r="L1009" s="9"/>
     </row>
+    <row r="1010" ht="15.75" customHeight="1">
+      <c r="A1010" s="34"/>
+      <c r="B1010" s="9"/>
+      <c r="C1010" s="9"/>
+      <c r="D1010" s="9"/>
+      <c r="E1010" s="16"/>
+      <c r="F1010" s="9"/>
+      <c r="G1010" s="9"/>
+      <c r="H1010" s="9"/>
+      <c r="I1010" s="9"/>
+      <c r="J1010" s="9"/>
+      <c r="K1010" s="9"/>
+      <c r="L1010" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$M$122">
-    <sortState ref="A1:M122">
-      <sortCondition ref="A1:A122"/>
+  <autoFilter ref="$A$1:$M$123">
+    <sortState ref="A1:M123">
+      <sortCondition ref="A1:A123"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
@@ -18640,10 +18688,11 @@
     <hyperlink r:id="rId124" ref="I120"/>
     <hyperlink r:id="rId125" ref="I121"/>
     <hyperlink r:id="rId126" ref="I122"/>
+    <hyperlink r:id="rId127" ref="I123"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId127"/>
+  <drawing r:id="rId128"/>
 </worksheet>
 </file>